--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -19,9 +19,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">대학원!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">더위사냥!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">버번!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">빅딜!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">더위사냥!$A$1:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">버번!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">빅딜!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">뿌용뿌용!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">인형나라!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">칠사모!$A$1:$J$31</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2224" uniqueCount="751">
   <si>
     <t>guild_name</t>
   </si>
@@ -309,6 +309,24 @@
     <t>2</t>
   </si>
   <si>
+    <t>괴챠반</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B4%B4%EC%B1%A0%EB%B0%98</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>3779조 9660억 4199만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>명동이</t>
   </si>
   <si>
@@ -318,27 +336,9 @@
     <t>비숍</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>3245조 684억 6500만</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>괴챠반</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B4%B4%EC%B1%A0%EB%B0%98</t>
-  </si>
-  <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>3204조 8824억 2626만</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
@@ -378,25 +378,25 @@
     <t>6</t>
   </si>
   <si>
+    <t>윤꼬밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EA%BC%AC%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>2156조 1091억 1210만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>디매트로돈</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EB%A7%A4%ED%8A%B8%EB%A1%9C%EB%8F%88</t>
   </si>
   <si>
-    <t>2146조 5713억 9703만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>윤꼬밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EA%BC%AC%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>1830조 1454억 192만</t>
+    <t>2148조 7069억 2080만</t>
   </si>
   <si>
     <t>8</t>
@@ -426,7 +426,7 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>1405조 9567억 7448만</t>
+    <t>1495조 9351억 651만</t>
   </si>
   <si>
     <t>10</t>
@@ -453,7 +453,7 @@
     <t>https://mgf.gg/contents/character.php?n=Pakachu9999</t>
   </si>
   <si>
-    <t>1111조 2237억 7409만</t>
+    <t>1142조 2566억 8130만</t>
   </si>
   <si>
     <t>12</t>
@@ -480,31 +480,31 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EA%B8%80%EB%A6%AC%EC%89%AC</t>
   </si>
   <si>
-    <t>981조 8306억 6598만</t>
+    <t>1022조 5383억 5173만</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
+    <t>똥땅이횽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EB%95%85%EC%9D%B4%ED%9A%BD</t>
+  </si>
+  <si>
+    <t>776조 7613억 8822만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>혁바</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EB%B0%94</t>
   </si>
   <si>
-    <t>773조 9543억 1435만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>똥땅이횽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EB%95%85%EC%9D%B4%ED%9A%BD</t>
-  </si>
-  <si>
-    <t>727조 1015억 2662만</t>
+    <t>775조 4786억 1213만</t>
   </si>
   <si>
     <t>16</t>
@@ -516,7 +516,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%94%EC%A7%80</t>
   </si>
   <si>
-    <t>720조 6461억 5197만</t>
+    <t>753조 791억 3550만</t>
   </si>
   <si>
     <t>17</t>
@@ -540,7 +540,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%96%EC%9D%B4</t>
   </si>
   <si>
-    <t>646조 56억 5787만</t>
+    <t>681조 4944억 9400만</t>
   </si>
   <si>
     <t>19</t>
@@ -552,31 +552,31 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9C%A8%EB%A8%B8%ED%91%B8</t>
   </si>
   <si>
-    <t>642조 2231억 9071만</t>
+    <t>666조 9853억 6246만</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
+    <t>오우솃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%9A%B0%EC%86%83</t>
+  </si>
+  <si>
+    <t>623조 4349억 2383만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>혜미니현미니</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EB%AF%B8%EB%8B%88%ED%98%84%EB%AF%B8%EB%8B%88</t>
   </si>
   <si>
-    <t>574조 9893억 7196만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>오우솃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%9A%B0%EC%86%83</t>
-  </si>
-  <si>
-    <t>567조 398억 7136만</t>
+    <t>588조 1465억 3109만</t>
   </si>
   <si>
     <t>22</t>
@@ -603,7 +603,7 @@
     <t>캡틴</t>
   </si>
   <si>
-    <t>425조 2685억 1641만</t>
+    <t>477조 4769억 4575만</t>
   </si>
   <si>
     <t>24</t>
@@ -615,12 +615,24 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%BF%BC%EC%B9%B4</t>
   </si>
   <si>
-    <t>385조 6741억 4044만</t>
+    <t>390조 3037억 2972만</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
+    <t>정섭이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%84%AD%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>384조 5653억 9771만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
     <t>니누고</t>
   </si>
   <si>
@@ -633,18 +645,6 @@
     <t>377조 4506억 6398만</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>정섭이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%84%AD%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>363조 2721억 3766만</t>
-  </si>
-  <si>
     <t>27</t>
   </si>
   <si>
@@ -660,16 +660,28 @@
     <t>28</t>
   </si>
   <si>
+    <t>여덟시</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8D%9F%EC%8B%9C</t>
+  </si>
+  <si>
+    <t>313조 7265억 4684만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
     <t>돼짱</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%BC%EC%A7%B1</t>
   </si>
   <si>
-    <t>306조 3982억 4727만</t>
-  </si>
-  <si>
-    <t>29</t>
+    <t>307조 5404억 2549만</t>
+  </si>
+  <si>
+    <t>30</t>
   </si>
   <si>
     <t>젤로젤리</t>
@@ -681,25 +693,13 @@
     <t>304조 3439억 3321만</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>여덟시</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8D%9F%EC%8B%9C</t>
-  </si>
-  <si>
-    <t>282조 2270억 1691만</t>
-  </si>
-  <si>
     <t>김치싸대기</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
   </si>
   <si>
-    <t>7906조 7238억 2174만</t>
+    <t>8232조 3835억 8286만</t>
   </si>
   <si>
     <t>굴러가는일상</t>
@@ -708,7 +708,28 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
   </si>
   <si>
-    <t>5275조 6486억 443만</t>
+    <t>5286조 3617억 27만</t>
+  </si>
+  <si>
+    <t>두향</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%ED%96%A5</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>3428조 96억 9692만</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>3164조 1968억 5216만</t>
   </si>
   <si>
     <t>몽호</t>
@@ -720,28 +741,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>3109조 3775억 1324만</t>
-  </si>
-  <si>
-    <t>두향</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%ED%96%A5</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>3106조 3758억 3080만</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>2878조 5956억 6653만</t>
+    <t>3155조 7739억 8662만</t>
   </si>
   <si>
     <t>엘라임</t>
@@ -750,7 +750,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
   </si>
   <si>
-    <t>2490조 7844억 7914만</t>
+    <t>2712조 6401억 5428만</t>
   </si>
   <si>
     <t>흑두부</t>
@@ -759,7 +759,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>2095조 8298억 2089만</t>
+    <t>2262조 57억 2121만</t>
   </si>
   <si>
     <t>서포터즈</t>
@@ -768,7 +768,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>1816조 5376억 7272만</t>
+    <t>1975조 9326억 3392만</t>
   </si>
   <si>
     <t>KR#TAKIN9CP37</t>
@@ -777,7 +777,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>1537조 2505억 2514만</t>
+    <t>1650조 4569억 6002만</t>
   </si>
   <si>
     <t>퍼퓸</t>
@@ -786,7 +786,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
   </si>
   <si>
-    <t>1353조 6552억 288만</t>
+    <t>1367조 1278억 9128만</t>
   </si>
   <si>
     <t>야가다</t>
@@ -816,28 +816,28 @@
     <t>972조 2153억 1957만</t>
   </si>
   <si>
+    <t>불보독지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
+  </si>
+  <si>
+    <t>934조 1730억 4089만</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
   </si>
   <si>
     <t>918조 9796억 5248만</t>
   </si>
   <si>
-    <t>불보독지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
-  </si>
-  <si>
-    <t>893조 7791억 2578만</t>
-  </si>
-  <si>
     <t>우후</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>863조 8591억 6792만</t>
+    <t>886조 8406억 7534만</t>
   </si>
   <si>
     <t>호우기</t>
@@ -846,7 +846,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>725조 3107억 9252만</t>
+    <t>823조 2725억 3337만</t>
   </si>
   <si>
     <t>정태준</t>
@@ -855,16 +855,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
   </si>
   <si>
-    <t>703조 4068억 5130만</t>
-  </si>
-  <si>
-    <t>막차탄토끼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%89%EC%B0%A8%ED%83%84%ED%86%A0%EB%81%BC</t>
-  </si>
-  <si>
-    <t>642조 4043억 3477만</t>
+    <t>747조 6479억 4857만</t>
   </si>
   <si>
     <t>좀치는형님</t>
@@ -873,7 +864,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
   </si>
   <si>
-    <t>576조 9303억 7005만</t>
+    <t>619조 9042억 7800만</t>
   </si>
   <si>
     <t>팡대지</t>
@@ -891,7 +882,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>396조 506억 4801만</t>
+    <t>418조 2231억 6534만</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -900,7 +891,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
   </si>
   <si>
-    <t>371조 9523억 1021만</t>
+    <t>372조 5745억 3012만</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -909,7 +900,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>343조 8712억 3221만</t>
+    <t>352조 5575억 4369만</t>
   </si>
   <si>
     <t>박준우2</t>
@@ -918,7 +909,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
   </si>
   <si>
-    <t>301조 7207억 2277만</t>
+    <t>312조 7168억 9611만</t>
   </si>
   <si>
     <t>솔인</t>
@@ -930,7 +921,25 @@
     <t>108</t>
   </si>
   <si>
-    <t>260조 9371억 8629만</t>
+    <t>298조 2305억 9860만</t>
+  </si>
+  <si>
+    <t>꼬북빵야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
+  </si>
+  <si>
+    <t>206조 9922억 631만</t>
+  </si>
+  <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>203조 4743억 4374만</t>
   </si>
   <si>
     <t>꾸르꾸르</t>
@@ -948,31 +957,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>193조 4998억 774만</t>
-  </si>
-  <si>
-    <t>여눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
-  </si>
-  <si>
-    <t>186조 7994억 7947만</t>
-  </si>
-  <si>
-    <t>꼬북빵야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
-  </si>
-  <si>
-    <t>178조 7593억 2042만</t>
+    <t>194조 2882억 2735만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EC%9A%A9%EB%BF%8C%EC%9A%A9%EB%BF%A1%EB%BF%A1</t>
   </si>
   <si>
-    <t>1경 4656조 4100억 3368만</t>
+    <t>1경 5261조 982억 3155만</t>
   </si>
   <si>
     <t>뿌용뿌용뽕뽕</t>
@@ -984,7 +975,16 @@
     <t>다크나이트</t>
   </si>
   <si>
-    <t>4920조 7946억 8400만</t>
+    <t>5489조 6741억 8929만</t>
+  </si>
+  <si>
+    <t>공항동노갈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%95%AD%EB%8F%99%EB%85%B8%EA%B0%88</t>
+  </si>
+  <si>
+    <t>2846조 2751억 9524만</t>
   </si>
   <si>
     <t>양대리</t>
@@ -993,7 +993,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%8C%80%EB%A6%AC</t>
   </si>
   <si>
-    <t>1961조 7126억 1627만</t>
+    <t>2072조 9196억 1204만</t>
   </si>
   <si>
     <t>뿌용뿌용까꿍</t>
@@ -1011,7 +1011,7 @@
     <t>https://mgf.gg/contents/character.php?n=Kopite</t>
   </si>
   <si>
-    <t>1375조 4471억 6530만</t>
+    <t>1526조 8722억 8363만</t>
   </si>
   <si>
     <t>남태평</t>
@@ -1020,7 +1020,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%ED%83%9C%ED%8F%89</t>
   </si>
   <si>
-    <t>1089조 438억 1488만</t>
+    <t>1216조 7749억 4936만</t>
+  </si>
+  <si>
+    <t>돌아온짜누</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%95%84%EC%98%A8%EC%A7%9C%EB%88%84</t>
+  </si>
+  <si>
+    <t>1129조 3268억 1943만</t>
   </si>
   <si>
     <t>토망쳐</t>
@@ -1032,13 +1041,13 @@
     <t>1061조 2908억 4962만</t>
   </si>
   <si>
-    <t>돌아온짜누</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%95%84%EC%98%A8%EC%A7%9C%EB%88%84</t>
-  </si>
-  <si>
-    <t>984조 6697억 1400만</t>
+    <t>노곽철</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EA%B3%BD%EC%B2%A0</t>
+  </si>
+  <si>
+    <t>980조 3105억 4537만</t>
   </si>
   <si>
     <t>팔마</t>
@@ -1050,22 +1059,13 @@
     <t>930조 3534억 1206만</t>
   </si>
   <si>
-    <t>노곽철</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EA%B3%BD%EC%B2%A0</t>
-  </si>
-  <si>
-    <t>898조 5211억 7413만</t>
-  </si>
-  <si>
     <t>뿌용뿌용뿅뿅</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EC%9A%A9%EB%BF%8C%EC%9A%A9%EB%BF%85%EB%BF%85</t>
   </si>
   <si>
-    <t>828조 8467억 2191만</t>
+    <t>844조 9185억 4201만</t>
   </si>
   <si>
     <t>이성일</t>
@@ -1077,13 +1077,22 @@
     <t>826조 5468억 7528만</t>
   </si>
   <si>
-    <t>매력꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A0%A5%EA%BD%83</t>
-  </si>
-  <si>
-    <t>732조 3095억 5718만</t>
+    <t>Ai사냥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Ai%EC%82%AC%EB%83%A5</t>
+  </si>
+  <si>
+    <t>814조 6812억 7583만</t>
+  </si>
+  <si>
+    <t>수빈똥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%B9%88%EB%98%A5</t>
+  </si>
+  <si>
+    <t>755조 7292억 5489만</t>
   </si>
   <si>
     <t>꿀벌재미니</t>
@@ -1092,16 +1101,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EB%B2%8C%EC%9E%AC%EB%AF%B8%EB%8B%88</t>
   </si>
   <si>
-    <t>705조 1728억 8826만</t>
-  </si>
-  <si>
-    <t>수빈똥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%B9%88%EB%98%A5</t>
-  </si>
-  <si>
-    <t>694조 9732억 7302만</t>
+    <t>730조 507억 6773만</t>
   </si>
   <si>
     <t>쿠키칩</t>
@@ -1119,16 +1119,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%ED%9B%84%ED%9B%88</t>
   </si>
   <si>
-    <t>667조 4422억 7014만</t>
-  </si>
-  <si>
-    <t>Ai사냥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Ai%EC%82%AC%EB%83%A5</t>
-  </si>
-  <si>
-    <t>666조 3874억 4278만</t>
+    <t>683조 4299억 121만</t>
   </si>
   <si>
     <t>트투</t>
@@ -1137,7 +1128,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8A%B8%ED%88%AC</t>
   </si>
   <si>
-    <t>592조 8785억 7182만</t>
+    <t>606조 7961억 2592만</t>
   </si>
   <si>
     <t>비속어금지중</t>
@@ -1146,7 +1137,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%86%8D%EC%96%B4%EA%B8%88%EC%A7%80%EC%A4%91</t>
   </si>
   <si>
-    <t>582조 6575억 9891만</t>
+    <t>588조 5530억 5868만</t>
   </si>
   <si>
     <t>탑뎅</t>
@@ -1164,7 +1155,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EC%B2%9C%EB%8F%99%EC%A3%BC%EC%A0%91%EA%BE%BC</t>
   </si>
   <si>
-    <t>503조 4309억 4240만</t>
+    <t>524조 8371억 3177만</t>
+  </si>
+  <si>
+    <t>밤바밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%A4%EB%B0%94%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>518조 4058억 8333만</t>
   </si>
   <si>
     <t>정맨정맨</t>
@@ -1173,16 +1173,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%A7%A8%EC%A0%95%EB%A7%A8</t>
   </si>
   <si>
-    <t>458조 9452억 2420만</t>
-  </si>
-  <si>
-    <t>밤바밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%A4%EB%B0%94%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>437조 4567억 4034만</t>
+    <t>477조 7642억 1340만</t>
   </si>
   <si>
     <t>본딩</t>
@@ -1194,22 +1185,22 @@
     <t>437조 1898억 8917만</t>
   </si>
   <si>
+    <t>그이뜌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EC%9D%B4%EB%9C%8C</t>
+  </si>
+  <si>
+    <t>378조 1528억 9711만</t>
+  </si>
+  <si>
     <t>대항해시대</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%ED%95%AD%ED%95%B4%EC%8B%9C%EB%8C%80</t>
   </si>
   <si>
-    <t>346조 5037억 5530만</t>
-  </si>
-  <si>
-    <t>그이뜌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EC%9D%B4%EB%9C%8C</t>
-  </si>
-  <si>
-    <t>335조 6179억 4517만</t>
+    <t>347조 4924억 7745만</t>
   </si>
   <si>
     <t>MELLOO</t>
@@ -1218,7 +1209,7 @@
     <t>https://mgf.gg/contents/character.php?n=MELLOO</t>
   </si>
   <si>
-    <t>312조 6907억 4896만</t>
+    <t>332조 3896억 394만</t>
   </si>
   <si>
     <t>이게제맛</t>
@@ -1227,7 +1218,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B2%8C%EC%A0%9C%EB%A7%9B</t>
   </si>
   <si>
-    <t>278조 6776억 3921만</t>
+    <t>299조 3596억 4195만</t>
   </si>
   <si>
     <t>냥냥쨉쨉</t>
@@ -1239,7 +1230,7 @@
     <t>106</t>
   </si>
   <si>
-    <t>162조 864억 8435만</t>
+    <t>166조 5292억 2023만</t>
   </si>
   <si>
     <t>응냥</t>
@@ -1248,7 +1239,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%91%EB%83%A5</t>
   </si>
   <si>
-    <t>6183조 5370억 2668만</t>
+    <t>6677조 1957억 9205만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EA%B5%AC%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
@@ -1266,7 +1257,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>4404조 9622억 7673만</t>
+    <t>4590조 3097억 9297만</t>
   </si>
   <si>
     <t>우리집욕조</t>
@@ -1275,7 +1266,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%A6%AC%EC%A7%91%EC%9A%95%EC%A1%B0</t>
   </si>
   <si>
-    <t>2422조 609억 7951만</t>
+    <t>2600조 7893억 3897만</t>
   </si>
   <si>
     <t>뚝불장군님</t>
@@ -1284,7 +1275,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9D%EB%B6%88%EC%9E%A5%EA%B5%B0%EB%8B%98</t>
   </si>
   <si>
-    <t>2289조 8792억 6349만</t>
+    <t>2322조 6365억 3822만</t>
   </si>
   <si>
     <t>빠떼루미야옹</t>
@@ -1293,7 +1284,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%96%BC%EB%A3%A8%EB%AF%B8%EC%95%BC%EC%98%B9</t>
   </si>
   <si>
-    <t>2061조 6577억 3234만</t>
+    <t>2116조 7299억 2177만</t>
   </si>
   <si>
     <t>채윰이</t>
@@ -1302,7 +1293,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EC%9C%B0%EC%9D%B4</t>
   </si>
   <si>
-    <t>1437조 9510억 9288만</t>
+    <t>1588조 116억 8582만</t>
+  </si>
+  <si>
+    <t>환직</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EC%A7%81</t>
+  </si>
+  <si>
+    <t>1153조 8750억 9307만</t>
   </si>
   <si>
     <t>라다크</t>
@@ -1311,16 +1311,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%8B%A4%ED%81%AC</t>
   </si>
   <si>
-    <t>1108조 4737억 5902만</t>
-  </si>
-  <si>
-    <t>환직</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EC%A7%81</t>
-  </si>
-  <si>
-    <t>1081조 6342억 1462만</t>
+    <t>1129조 8748억 1239만</t>
   </si>
   <si>
     <t>초퍄</t>
@@ -1332,13 +1323,31 @@
     <t>881조 7169억 1004만</t>
   </si>
   <si>
+    <t>조선제일히로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%84%A0%EC%A0%9C%EC%9D%BC%ED%9E%88%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>864조 3400억 4240만</t>
+  </si>
+  <si>
     <t>공주라귱</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EC%A3%BC%EB%9D%BC%EA%B7%B1</t>
   </si>
   <si>
-    <t>822조 1037억 3526만</t>
+    <t>858조 6302억 2926만</t>
+  </si>
+  <si>
+    <t>장빡이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B9%A1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>728조 8378억 8526만</t>
   </si>
   <si>
     <t>E2E승</t>
@@ -1350,15 +1359,6 @@
     <t>720조 7294억 848만</t>
   </si>
   <si>
-    <t>조선제일히로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%84%A0%EC%A0%9C%EC%9D%BC%ED%9E%88%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>716조 5060억 1948만</t>
-  </si>
-  <si>
     <t>은월출시기원</t>
   </si>
   <si>
@@ -1368,15 +1368,6 @@
     <t>712조 1557억 1686만</t>
   </si>
   <si>
-    <t>장빡이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B9%A1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>666조 3618억 1246만</t>
-  </si>
-  <si>
     <t>아첩</t>
   </si>
   <si>
@@ -1386,13 +1377,22 @@
     <t>643조 454억 8144만</t>
   </si>
   <si>
+    <t>호박머리베컴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%B0%95%EB%A8%B8%EB%A6%AC%EB%B2%A0%EC%BB%B4</t>
+  </si>
+  <si>
+    <t>626조 4514억 3867만</t>
+  </si>
+  <si>
     <t>Lr로키</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=Lr%EB%A1%9C%ED%82%A4</t>
   </si>
   <si>
-    <t>602조 1426억 4985만</t>
+    <t>611조 7930억 2431만</t>
   </si>
   <si>
     <t>자루니</t>
@@ -1401,16 +1401,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EB%A3%A8%EB%8B%88</t>
   </si>
   <si>
-    <t>584조 2016억 1094만</t>
-  </si>
-  <si>
-    <t>호박머리베컴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%B0%95%EB%A8%B8%EB%A6%AC%EB%B2%A0%EC%BB%B4</t>
-  </si>
-  <si>
-    <t>568조 9644억 7620만</t>
+    <t>610조 5298억 4168만</t>
   </si>
   <si>
     <t>새파</t>
@@ -1419,7 +1410,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%88%ED%8C%8C</t>
   </si>
   <si>
-    <t>531조 2490억 1128만</t>
+    <t>550조 706억 6074만</t>
+  </si>
+  <si>
+    <t>힘떡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%98%EB%96%A1</t>
+  </si>
+  <si>
+    <t>482조 4236억 8290만</t>
   </si>
   <si>
     <t>뚱법</t>
@@ -1431,22 +1431,13 @@
     <t>480조 9199억 406만</t>
   </si>
   <si>
-    <t>힘떡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%98%EB%96%A1</t>
-  </si>
-  <si>
-    <t>478조 8037억 3406만</t>
-  </si>
-  <si>
     <t>모범택시기사</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%B2%94%ED%83%9D%EC%8B%9C%EA%B8%B0%EC%82%AC</t>
   </si>
   <si>
-    <t>441조 6746억 7292만</t>
+    <t>456조 6296억 7326만</t>
   </si>
   <si>
     <t>3대900상남자</t>
@@ -1455,7 +1446,7 @@
     <t>https://mgf.gg/contents/character.php?n=3%EB%8C%80900%EC%83%81%EB%82%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>391조 3962억 7812만</t>
+    <t>415조 2194억 2643만</t>
   </si>
   <si>
     <t>바임쥬베룩</t>
@@ -1464,7 +1455,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EC%9E%84%EC%A5%AC%EB%B2%A0%EB%A3%A9</t>
   </si>
   <si>
-    <t>368조 3415억 4100만</t>
+    <t>387조 5361억 8706만</t>
   </si>
   <si>
     <t>예짜까</t>
@@ -1473,7 +1464,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%A7%9C%EA%B9%8C</t>
   </si>
   <si>
-    <t>322조 1857억 6803만</t>
+    <t>339조 3769억 1972만</t>
   </si>
   <si>
     <t>KR#PTWFLYUM5X</t>
@@ -1482,7 +1473,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23PTWFLYUM5X</t>
   </si>
   <si>
-    <t>320조 4116억 8135만</t>
+    <t>322조 4088억 4588만</t>
   </si>
   <si>
     <t>청약환불</t>
@@ -1491,7 +1482,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%AD%EC%95%BD%ED%99%98%EB%B6%88</t>
   </si>
   <si>
-    <t>268조 8525억 9042만</t>
+    <t>291조 1198억 3446만</t>
   </si>
   <si>
     <t>귀막구</t>
@@ -1500,7 +1491,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EB%A7%89%EA%B5%AC</t>
   </si>
   <si>
-    <t>265조 4962억 673만</t>
+    <t>265조 5769억 2417만</t>
   </si>
   <si>
     <t>Trusthim</t>
@@ -1509,7 +1500,7 @@
     <t>https://mgf.gg/contents/character.php?n=Trusthim</t>
   </si>
   <si>
-    <t>240조 6261억 8248만</t>
+    <t>253조 1810억 7997만</t>
   </si>
   <si>
     <t>강댜</t>
@@ -1518,7 +1509,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%8C%9C</t>
   </si>
   <si>
-    <t>1경 2053조 2673억 2672만</t>
+    <t>1경 2379조 21억 4484만</t>
   </si>
   <si>
     <t>빵녕</t>
@@ -1527,13 +1518,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EB%85%95</t>
   </si>
   <si>
-    <t>8279조 3402억 8855만</t>
+    <t>8537조 7372억 5501만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B6%A9%EB%91%98%EA%B8%B0</t>
   </si>
   <si>
-    <t>6970조 2416억 2624만</t>
+    <t>7229조 4623억 1746만</t>
   </si>
   <si>
     <t>실프</t>
@@ -1542,7 +1533,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%ED%94%84</t>
   </si>
   <si>
-    <t>937조 2813억 6495만</t>
+    <t>1036조 7000억 1875만</t>
   </si>
   <si>
     <t>냠늄</t>
@@ -1560,7 +1551,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8E%98%EB%A0%88%EB%A1%9C%EB%A1%9C%EC%89%90</t>
   </si>
   <si>
-    <t>849조 6565억 9289만</t>
+    <t>852조 3661억 8471만</t>
   </si>
   <si>
     <t>보호소</t>
@@ -1569,7 +1560,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%ED%98%B8%EC%86%8C</t>
   </si>
   <si>
-    <t>695조 3248억 8155만</t>
+    <t>741조 7423억 6528만</t>
   </si>
   <si>
     <t>쮸르</t>
@@ -1578,7 +1569,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AE%B8%EB%A5%B4</t>
   </si>
   <si>
-    <t>619조 271억 9728만</t>
+    <t>672조 3152억 8174만</t>
   </si>
   <si>
     <t>더대충</t>
@@ -1587,7 +1578,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%94%EB%8C%80%EC%B6%A9</t>
   </si>
   <si>
-    <t>558조 7199억 7828만</t>
+    <t>582조 2858억 8141만</t>
   </si>
   <si>
     <t>끼꼬</t>
@@ -1608,6 +1599,15 @@
     <t>466조 1671억 8772만</t>
   </si>
   <si>
+    <t>더적당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%94%EC%A0%81%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>461조 9287억 2943만</t>
+  </si>
+  <si>
     <t>갈매기</t>
   </si>
   <si>
@@ -1617,22 +1617,13 @@
     <t>444조 4405억 6370만</t>
   </si>
   <si>
-    <t>더적당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%94%EC%A0%81%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>423조 7738억 711만</t>
-  </si>
-  <si>
     <t>꿀꿀이의모험</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%BF%80%EC%9D%B4%EC%9D%98%EB%AA%A8%ED%97%98</t>
   </si>
   <si>
-    <t>373조 2872억 8492만</t>
+    <t>380조 3942억 952만</t>
   </si>
   <si>
     <t>사랑해제명</t>
@@ -1641,7 +1632,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%95%B4%EC%A0%9C%EB%AA%85</t>
   </si>
   <si>
-    <t>346조 3718억 376만</t>
+    <t>376조 9315억 3362만</t>
+  </si>
+  <si>
+    <t>퍄딤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8D%84%EB%94%A4</t>
+  </si>
+  <si>
+    <t>324조 9226억 8199만</t>
   </si>
   <si>
     <t>냥찐</t>
@@ -1650,16 +1650,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%EC%B0%90</t>
   </si>
   <si>
-    <t>320조 3351억 4136만</t>
-  </si>
-  <si>
-    <t>퍄딤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8D%84%EB%94%A4</t>
-  </si>
-  <si>
-    <t>306조 4771억 7028만</t>
+    <t>321조 9126억 2800만</t>
   </si>
   <si>
     <t>시루</t>
@@ -1668,7 +1659,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%A3%A8</t>
   </si>
   <si>
-    <t>293조 3470억 1718만</t>
+    <t>310조 3097억 1002만</t>
   </si>
   <si>
     <t>환불스토리</t>
@@ -1677,7 +1668,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%8A%A4%ED%86%A0%EB%A6%AC</t>
   </si>
   <si>
-    <t>249조 9226억 6572만</t>
+    <t>284조 9892억 6059만</t>
   </si>
   <si>
     <t>소동</t>
@@ -1686,7 +1677,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%8F%99</t>
   </si>
   <si>
-    <t>167조 9998억 1724만</t>
+    <t>170조 56억 4930만</t>
+  </si>
+  <si>
+    <t>초코파베</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%ED%8C%8C%EB%B2%A0</t>
+  </si>
+  <si>
+    <t>165조 482억 2314만</t>
   </si>
   <si>
     <t>취란</t>
@@ -1695,16 +1695,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B7%A8%EB%9E%80</t>
   </si>
   <si>
-    <t>159조 793억 1829만</t>
-  </si>
-  <si>
-    <t>초코파베</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%ED%8C%8C%EB%B2%A0</t>
-  </si>
-  <si>
-    <t>158조 5618억 3086만</t>
+    <t>161조 3890억 3007만</t>
   </si>
   <si>
     <t>달디달고나</t>
@@ -1716,7 +1707,7 @@
     <t>107</t>
   </si>
   <si>
-    <t>153조 4285억 5591만</t>
+    <t>156조 7512억 7471만</t>
   </si>
   <si>
     <t>키류</t>
@@ -1734,7 +1725,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EA%B5%A5%EA%B5%A5</t>
   </si>
   <si>
-    <t>146조 5830억 2792만</t>
+    <t>146조 8774억 6343만</t>
   </si>
   <si>
     <t>해졍</t>
@@ -1743,19 +1734,19 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%A1%8D</t>
   </si>
   <si>
-    <t>97조 8844억 8155만</t>
-  </si>
-  <si>
-    <t>민아파더</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%95%84%ED%8C%8C%EB%8D%94</t>
+    <t>99조 3957억 784만</t>
+  </si>
+  <si>
+    <t>홍뎐잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EB%8E%90%EC%9E%89</t>
   </si>
   <si>
     <t>105</t>
   </si>
   <si>
-    <t>85조 9946억 9695만</t>
+    <t>97조 9081억 3497만</t>
   </si>
   <si>
     <t>꾸륭</t>
@@ -1770,15 +1761,6 @@
     <t>79조 542억 1853만</t>
   </si>
   <si>
-    <t>홍뎐잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EB%8E%90%EC%9E%89</t>
-  </si>
-  <si>
-    <t>78조 7475억 3536만</t>
-  </si>
-  <si>
     <t>허숖</t>
   </si>
   <si>
@@ -1788,7 +1770,7 @@
     <t>102</t>
   </si>
   <si>
-    <t>8조 6183억 5846만</t>
+    <t>8조 9789억 6926만</t>
   </si>
   <si>
     <t>날짜별</t>
@@ -1806,7 +1788,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%EC%8A%A4%ED%84%B0%ED%83%9C%ED%98%B8</t>
   </si>
   <si>
-    <t>1경 574조 3919억 9981만</t>
+    <t>1경 1368조 3472억 6753만</t>
   </si>
   <si>
     <t>시간별</t>
@@ -1815,7 +1797,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B0%84%EB%B3%84</t>
   </si>
   <si>
-    <t>8108조 8046억 8647만</t>
+    <t>9738조 3179억 8182만</t>
   </si>
   <si>
     <t>힝솜</t>
@@ -1824,13 +1806,13 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%9D%EC%86%9C</t>
   </si>
   <si>
-    <t>1666조 5787억 9407만</t>
+    <t>1676조 1242억 1113만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%A0%EC%82%AC%EB%AA%A8</t>
   </si>
   <si>
-    <t>1387조 4030억 6049만</t>
+    <t>1447조 6868억 9727만</t>
   </si>
   <si>
     <t>딩믕</t>
@@ -1839,7 +1821,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%A9%EB%AF%95</t>
   </si>
   <si>
-    <t>863조 1364억 6911만</t>
+    <t>865조 8064억 3438만</t>
   </si>
   <si>
     <t>챤믕</t>
@@ -1857,7 +1839,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EB%82%A8%EC%B9%9C%EC%A9%94%EB%8D%94%EB%9D%BC</t>
   </si>
   <si>
-    <t>434조 5495억 4357만</t>
+    <t>489조 6118억 2198만</t>
   </si>
   <si>
     <t>헌믕</t>
@@ -1866,7 +1848,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%97%8C%EB%AF%95</t>
   </si>
   <si>
-    <t>307조 845억 549만</t>
+    <t>420조 1662억 8553만</t>
   </si>
   <si>
     <t>윤성33</t>
@@ -1875,7 +1857,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EC%84%B133</t>
   </si>
   <si>
-    <t>235조 3192억 4913만</t>
+    <t>258조 6142억 3522만</t>
   </si>
   <si>
     <t>비숍의미래</t>
@@ -1884,7 +1866,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EC%9D%98%EB%AF%B8%EB%9E%98</t>
   </si>
   <si>
-    <t>223조 7259억 3067만</t>
+    <t>233조 1980억 5873만</t>
   </si>
   <si>
     <t>오배건만</t>
@@ -1893,7 +1875,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%B0%B0%EA%B1%B4%EB%A7%8C</t>
   </si>
   <si>
-    <t>199조 5200억 188만</t>
+    <t>206조 8650억 5485만</t>
   </si>
   <si>
     <t>썬믕</t>
@@ -1902,7 +1884,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EB%AF%95</t>
   </si>
   <si>
-    <t>151조 4718억 3261만</t>
+    <t>193조 9640억 2570만</t>
+  </si>
+  <si>
+    <t>비믕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%AF%95</t>
+  </si>
+  <si>
+    <t>136조 785억 2906만</t>
   </si>
   <si>
     <t>꽃믕</t>
@@ -1920,16 +1911,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%AC%98</t>
   </si>
   <si>
-    <t>98조 5636억 5257만</t>
-  </si>
-  <si>
-    <t>비믕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%AF%95</t>
-  </si>
-  <si>
-    <t>84조 3396억 5161만</t>
+    <t>107조 4011억 1890만</t>
+  </si>
+  <si>
+    <t>풀뱅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%92%80%EB%B1%85</t>
+  </si>
+  <si>
+    <t>86조 4644억 4331만</t>
   </si>
   <si>
     <t>몽치장군</t>
@@ -1941,13 +1932,13 @@
     <t>80조 8800억 1482만</t>
   </si>
   <si>
-    <t>풀뱅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%92%80%EB%B1%85</t>
-  </si>
-  <si>
-    <t>76조 6806억 5001만</t>
+    <t>사믕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%AF%95</t>
+  </si>
+  <si>
+    <t>74조 6560억 5919만</t>
   </si>
   <si>
     <t>득찬이</t>
@@ -1965,16 +1956,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A7%B1%EB%82%98%EB%84%A4</t>
   </si>
   <si>
-    <t>53조 6625억 3964만</t>
-  </si>
-  <si>
-    <t>사믕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%AF%95</t>
-  </si>
-  <si>
-    <t>50조 5601억 1463만</t>
+    <t>59조 468억 7529만</t>
   </si>
   <si>
     <t>또믕</t>
@@ -1983,7 +1965,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%AF%95</t>
   </si>
   <si>
-    <t>47조 9977억 9994만</t>
+    <t>57조 4796억 2124만</t>
   </si>
   <si>
     <t>iamai</t>
@@ -1992,7 +1974,28 @@
     <t>https://mgf.gg/contents/character.php?n=iamai</t>
   </si>
   <si>
-    <t>47조 5509억 4365만</t>
+    <t>51조 4130억 3037만</t>
+  </si>
+  <si>
+    <t>칠믕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B9%A0%EB%AF%95</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>46조 7313억 6666만</t>
+  </si>
+  <si>
+    <t>망해또띠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%ED%95%B4%EB%98%90%EB%9D%A0</t>
+  </si>
+  <si>
+    <t>42조 5193억 8584만</t>
   </si>
   <si>
     <t>뚜에이</t>
@@ -2001,16 +2004,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EC%97%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>32조 5128억 2284만</t>
-  </si>
-  <si>
-    <t>망해또띠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%ED%95%B4%EB%98%90%EB%9D%A0</t>
-  </si>
-  <si>
-    <t>31조 7217억 2621만</t>
+    <t>41조 9104억 9358만</t>
   </si>
   <si>
     <t>츄믕</t>
@@ -2019,19 +2013,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B8%84%EB%AF%95</t>
   </si>
   <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>30조 2709억 2125만</t>
-  </si>
-  <si>
-    <t>칠믕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B9%A0%EB%AF%95</t>
-  </si>
-  <si>
-    <t>29조 6707억 9224만</t>
+    <t>31조 8091억 4445만</t>
   </si>
   <si>
     <t>주캄</t>
@@ -2040,7 +2022,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%BA%84</t>
   </si>
   <si>
-    <t>17조 4043억 7939만</t>
+    <t>20조 6876억 6074만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EB%AF%95</t>
@@ -2055,241 +2037,232 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%81%EC%86%9C</t>
   </si>
   <si>
+    <t>9조 9552억 1088만</t>
+  </si>
+  <si>
+    <t>교주만두</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%90%EC%A3%BC%EB%A7%8C%EB%91%90</t>
+  </si>
+  <si>
+    <t>3경 6011조 9366억 9688만</t>
+  </si>
+  <si>
+    <t>할바이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%B0%94%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>166조 5767억 3940만</t>
+  </si>
+  <si>
+    <t>섹밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B9%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>152조 1727억 5092만</t>
+  </si>
+  <si>
+    <t>대구남성</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EA%B5%AC%EB%82%A8%EC%84%B1</t>
+  </si>
+  <si>
+    <t>44조 3150억 1610만</t>
+  </si>
+  <si>
+    <t>KR#0P7W5X70V4</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%230P7W5X70V4</t>
+  </si>
+  <si>
+    <t>41조 5854억 8868만</t>
+  </si>
+  <si>
+    <t>코잉코잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%9E%89%EC%BD%94%EC%9E%89</t>
+  </si>
+  <si>
+    <t>25조 8623억 2646만</t>
+  </si>
+  <si>
+    <t>낭랑28세</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%9E%9128%EC%84%B8</t>
+  </si>
+  <si>
+    <t>23조 8905억 6160만</t>
+  </si>
+  <si>
+    <t>토벤숍이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%B2%A4%EC%88%8D%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>22조 8212억 9298만</t>
+  </si>
+  <si>
+    <t>돈성</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%84%B1</t>
+  </si>
+  <si>
+    <t>21조 6662억 2588만</t>
+  </si>
+  <si>
+    <t>뭐하는게임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AD%90%ED%95%98%EB%8A%94%EA%B2%8C%EC%9E%84</t>
+  </si>
+  <si>
+    <t>21조 5418억 4559만</t>
+  </si>
+  <si>
+    <t>씅놈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%94%85%EB%86%88</t>
+  </si>
+  <si>
+    <t>20조 7502억 4689만</t>
+  </si>
+  <si>
+    <t>빵신궁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EC%8B%A0%EA%B6%81</t>
+  </si>
+  <si>
+    <t>20조 2279억 1258만</t>
+  </si>
+  <si>
+    <t>우루차</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%A3%A8%EC%B0%A8</t>
+  </si>
+  <si>
+    <t>16조 6631억 1648만</t>
+  </si>
+  <si>
+    <t>마키맛키마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%82%A4%EB%A7%9B%ED%82%A4%EB%A7%88</t>
+  </si>
+  <si>
+    <t>16조 4912억 4548만</t>
+  </si>
+  <si>
+    <t>킬혁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%AC%ED%98%81</t>
+  </si>
+  <si>
+    <t>16조 4486억 443만</t>
+  </si>
+  <si>
+    <t>썬콜우체국</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9A%B0%EC%B2%B4%EA%B5%AD</t>
+  </si>
+  <si>
+    <t>15조 572억 3019만</t>
+  </si>
+  <si>
+    <t>고통받는갈비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%ED%86%B5%EB%B0%9B%EB%8A%94%EA%B0%88%EB%B9%84</t>
+  </si>
+  <si>
+    <t>14조 6124억 1564만</t>
+  </si>
+  <si>
+    <t>배렛나루왁서</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%EB%A0%9B%EB%82%98%EB%A3%A8%EC%99%81%EC%84%9C</t>
+  </si>
+  <si>
+    <t>14조 3217억 9742만</t>
+  </si>
+  <si>
+    <t>밀초크코</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%EC%B4%88%ED%81%AC%EC%BD%94</t>
+  </si>
+  <si>
+    <t>13조 9894억 3978만</t>
+  </si>
+  <si>
+    <t>오스띤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%8A%A4%EB%9D%A4</t>
+  </si>
+  <si>
+    <t>13조 2804억 8772만</t>
+  </si>
+  <si>
+    <t>땡요나퐁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%95%A1%EC%9A%94%EB%82%98%ED%90%81</t>
+  </si>
+  <si>
+    <t>11조 8161억 3024만</t>
+  </si>
+  <si>
+    <t>썬콜법사ss</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%ACss</t>
+  </si>
+  <si>
+    <t>11조 2554억 5294만</t>
+  </si>
+  <si>
+    <t>문보겨엉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B3%B4%EA%B2%A8%EC%97%89</t>
+  </si>
+  <si>
+    <t>10조 8206억 4738만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%ED%82%A4%EB%B9%84%ED%82%A4</t>
+  </si>
+  <si>
+    <t>5조 2933억 6128만</t>
+  </si>
+  <si>
+    <t>포디케이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%94%94%EC%BC%80%EC%9D%B4</t>
+  </si>
+  <si>
     <t>101</t>
   </si>
   <si>
-    <t>9조 1648억 8953만</t>
-  </si>
-  <si>
-    <t>교주만두</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%90%EC%A3%BC%EB%A7%8C%EB%91%90</t>
-  </si>
-  <si>
-    <t>3경 6011조 9366억 9688만</t>
-  </si>
-  <si>
-    <t>할바이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%B0%94%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>166조 5767억 3940만</t>
-  </si>
-  <si>
-    <t>섹밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B9%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>146조 3448억 6731만</t>
-  </si>
-  <si>
-    <t>홉삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%89%EC%82%90</t>
-  </si>
-  <si>
-    <t>116조 7225억 1359만</t>
-  </si>
-  <si>
-    <t>KR#0P7W5X70V4</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=KR%230P7W5X70V4</t>
-  </si>
-  <si>
-    <t>41조 5854억 8868만</t>
-  </si>
-  <si>
-    <t>대구남성</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EA%B5%AC%EB%82%A8%EC%84%B1</t>
-  </si>
-  <si>
-    <t>40조 8150억 8258만</t>
-  </si>
-  <si>
-    <t>코잉코잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%9E%89%EC%BD%94%EC%9E%89</t>
-  </si>
-  <si>
-    <t>23조 7158억 1776만</t>
-  </si>
-  <si>
-    <t>토벤숍이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%B2%A4%EC%88%8D%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>22조 1401억 8507만</t>
-  </si>
-  <si>
-    <t>씅놈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%94%85%EB%86%88</t>
-  </si>
-  <si>
-    <t>20조 7502억 4689만</t>
-  </si>
-  <si>
-    <t>뭐하는게임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AD%90%ED%95%98%EB%8A%94%EA%B2%8C%EC%9E%84</t>
-  </si>
-  <si>
-    <t>20조 275억 9670만</t>
-  </si>
-  <si>
-    <t>낭랑28세</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%9E%9128%EC%84%B8</t>
-  </si>
-  <si>
-    <t>19조 6782억 9344만</t>
-  </si>
-  <si>
-    <t>돈성</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%84%B1</t>
-  </si>
-  <si>
-    <t>19조 3277억 7934만</t>
-  </si>
-  <si>
-    <t>빵신궁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EC%8B%A0%EA%B6%81</t>
-  </si>
-  <si>
-    <t>19조 2350억 3089만</t>
-  </si>
-  <si>
-    <t>우루차</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%A3%A8%EC%B0%A8</t>
-  </si>
-  <si>
-    <t>16조 6631억 1648만</t>
-  </si>
-  <si>
-    <t>킬혁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%AC%ED%98%81</t>
-  </si>
-  <si>
-    <t>15조 7207억 4485만</t>
-  </si>
-  <si>
-    <t>썬콜우체국</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9A%B0%EC%B2%B4%EA%B5%AD</t>
-  </si>
-  <si>
-    <t>15조 477억 1961만</t>
-  </si>
-  <si>
-    <t>배렛나루왁서</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%EB%A0%9B%EB%82%98%EB%A3%A8%EC%99%81%EC%84%9C</t>
-  </si>
-  <si>
-    <t>14조 3217억 9742만</t>
-  </si>
-  <si>
-    <t>밀초크코</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%EC%B4%88%ED%81%AC%EC%BD%94</t>
-  </si>
-  <si>
-    <t>13조 7612억 2807만</t>
-  </si>
-  <si>
-    <t>고통받는갈비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%ED%86%B5%EB%B0%9B%EB%8A%94%EA%B0%88%EB%B9%84</t>
-  </si>
-  <si>
-    <t>13조 5167억 9618만</t>
-  </si>
-  <si>
-    <t>마키맛키마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%82%A4%EB%A7%9B%ED%82%A4%EB%A7%88</t>
-  </si>
-  <si>
-    <t>12조 1066억 8222만</t>
-  </si>
-  <si>
-    <t>썬콜법사ss</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%ACss</t>
-  </si>
-  <si>
-    <t>11조 1192억 31만</t>
-  </si>
-  <si>
-    <t>땡요나퐁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%95%A1%EC%9A%94%EB%82%98%ED%90%81</t>
-  </si>
-  <si>
-    <t>10조 8756억 7417만</t>
-  </si>
-  <si>
-    <t>문보겨엉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B3%B4%EA%B2%A8%EC%97%89</t>
-  </si>
-  <si>
-    <t>10조 8206억 4738만</t>
-  </si>
-  <si>
-    <t>오스띤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%8A%A4%EB%9D%A4</t>
-  </si>
-  <si>
-    <t>10조 4018억 8403만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%ED%82%A4%EB%B9%84%ED%82%A4</t>
-  </si>
-  <si>
-    <t>4조 9006억 7864만</t>
-  </si>
-  <si>
-    <t>포디케이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%94%94%EC%BC%80%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>4조 6028억 5852만</t>
+    <t>4조 7936억 3362만</t>
   </si>
   <si>
     <t>경기도인</t>
@@ -2298,7 +2271,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EA%B8%B0%EB%8F%84%EC%9D%B8</t>
   </si>
   <si>
-    <t>4조 4355억 9549만</t>
+    <t>4조 6102억 3838만</t>
   </si>
   <si>
     <t>즈나니</t>
@@ -2310,7 +2283,7 @@
     <t>99</t>
   </si>
   <si>
-    <t>1조 5873억 5487만</t>
+    <t>2조 570억 3535만</t>
   </si>
 </sst>
 </file>
@@ -3259,10 +3232,10 @@
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>117</v>
@@ -3291,10 +3264,10 @@
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>121</v>
@@ -3419,7 +3392,7 @@
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>106</v>
@@ -3483,7 +3456,7 @@
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>106</v>
@@ -3515,7 +3488,7 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>106</v>
@@ -3547,7 +3520,7 @@
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>106</v>
@@ -3611,7 +3584,7 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>106</v>
@@ -3710,7 +3683,7 @@
         <v>94</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>177</v>
@@ -3742,7 +3715,7 @@
         <v>100</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>181</v>
@@ -3771,7 +3744,7 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>144</v>
@@ -3806,7 +3779,7 @@
         <v>189</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>190</v>
@@ -3835,7 +3808,7 @@
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>144</v>
@@ -3867,13 +3840,13 @@
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3884,25 +3857,25 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>203</v>
@@ -3931,7 +3904,7 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>144</v>
@@ -3963,10 +3936,10 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>211</v>
@@ -3995,7 +3968,7 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>144</v>
@@ -4027,10 +4000,10 @@
         <v>87</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>198</v>
+        <v>144</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>219</v>
@@ -4079,7 +4052,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4175,7 +4148,7 @@
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>95</v>
@@ -4207,10 +4180,10 @@
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>94</v>
+        <v>228</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>228</v>
+        <v>112</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>229</v>
@@ -4239,13 +4212,13 @@
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>233</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -4259,22 +4232,22 @@
         <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>236</v>
@@ -4335,7 +4308,7 @@
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>106</v>
@@ -4431,7 +4404,7 @@
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>95</v>
@@ -4527,7 +4500,7 @@
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>106</v>
@@ -4547,25 +4520,25 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>33</v>
+        <v>261</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>33</v>
+        <v>261</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -4579,19 +4552,19 @@
         <v>154</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>263</v>
+        <v>33</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>263</v>
+        <v>33</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>264</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>87</v>
+        <v>129</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>144</v>
@@ -4687,7 +4660,7 @@
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>106</v>
@@ -4719,7 +4692,7 @@
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>144</v>
@@ -4751,7 +4724,7 @@
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>144</v>
@@ -4783,10 +4756,10 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>283</v>
@@ -4815,10 +4788,10 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>286</v>
@@ -4847,10 +4820,10 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>289</v>
@@ -4879,10 +4852,10 @@
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>292</v>
@@ -4911,13 +4884,13 @@
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>94</v>
+        <v>228</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>198</v>
+        <v>295</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -4928,25 +4901,25 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>232</v>
+        <v>100</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>299</v>
@@ -4975,10 +4948,10 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>302</v>
@@ -5007,10 +4980,10 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>305</v>
@@ -5039,10 +5012,10 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>308</v>
@@ -5051,40 +5024,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -5115,7 +5056,6 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5132,7 +5072,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5182,7 +5122,7 @@
         <v>41</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>129</v>
@@ -5191,10 +5131,10 @@
         <v>189</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5208,25 +5148,25 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5240,25 +5180,25 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5272,25 +5212,25 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5304,25 +5244,25 @@
         <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>95</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5336,25 +5276,25 @@
         <v>114</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5368,25 +5308,25 @@
         <v>118</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>106</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5400,25 +5340,25 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>106</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5432,25 +5372,25 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5464,13 +5404,13 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
@@ -5482,7 +5422,7 @@
         <v>95</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5496,25 +5436,25 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5528,25 +5468,25 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5560,25 +5500,25 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>198</v>
+        <v>144</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5592,25 +5532,25 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5624,25 +5564,25 @@
         <v>154</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5656,25 +5596,25 @@
         <v>158</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>144</v>
+        <v>95</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5688,25 +5628,25 @@
         <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5720,25 +5660,25 @@
         <v>166</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5752,25 +5692,25 @@
         <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>106</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5784,25 +5724,25 @@
         <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5816,25 +5756,25 @@
         <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5848,13 +5788,13 @@
         <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
@@ -5863,10 +5803,10 @@
         <v>189</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5880,13 +5820,13 @@
         <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
@@ -5895,10 +5835,10 @@
         <v>100</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>298</v>
+        <v>202</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5912,13 +5852,13 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
@@ -5927,10 +5867,10 @@
         <v>94</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>198</v>
+        <v>295</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5944,25 +5884,25 @@
         <v>195</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>198</v>
+        <v>144</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5973,28 +5913,28 @@
         <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>198</v>
+        <v>295</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6008,25 +5948,25 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>298</v>
+        <v>202</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6040,13 +5980,13 @@
         <v>208</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
@@ -6058,7 +5998,7 @@
         <v>144</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6072,13 +6012,13 @@
         <v>212</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
@@ -6087,10 +6027,10 @@
         <v>88</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6104,13 +6044,13 @@
         <v>216</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>87</v>
@@ -6119,10 +6059,10 @@
         <v>111</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6220,13 +6160,13 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
@@ -6238,7 +6178,7 @@
         <v>89</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6258,7 +6198,7 @@
         <v>49</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>129</v>
@@ -6267,10 +6207,10 @@
         <v>111</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6284,25 +6224,25 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6316,13 +6256,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
@@ -6334,7 +6274,7 @@
         <v>112</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6348,25 +6288,25 @@
         <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>112</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6380,25 +6320,25 @@
         <v>114</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>112</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6412,25 +6352,25 @@
         <v>118</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>95</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6444,25 +6384,25 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>135</v>
+        <v>407</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>95</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6476,25 +6416,25 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>410</v>
+        <v>135</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>95</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6508,25 +6448,25 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>95</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6540,25 +6480,25 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6572,25 +6512,25 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6604,13 +6544,13 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
@@ -6622,7 +6562,7 @@
         <v>144</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6636,25 +6576,25 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6668,13 +6608,13 @@
         <v>154</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
@@ -6686,7 +6626,7 @@
         <v>144</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6700,25 +6640,25 @@
         <v>158</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6732,25 +6672,25 @@
         <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6764,25 +6704,25 @@
         <v>166</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6796,25 +6736,25 @@
         <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6828,13 +6768,13 @@
         <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
@@ -6846,7 +6786,7 @@
         <v>144</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6860,25 +6800,25 @@
         <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6892,25 +6832,25 @@
         <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6924,13 +6864,13 @@
         <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
@@ -6942,7 +6882,7 @@
         <v>144</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6956,13 +6896,13 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
@@ -6974,7 +6914,7 @@
         <v>144</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6988,13 +6928,13 @@
         <v>195</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
@@ -7003,10 +6943,10 @@
         <v>135</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>298</v>
+        <v>202</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7017,28 +6957,28 @@
         <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7052,13 +6992,13 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
@@ -7067,10 +7007,10 @@
         <v>111</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7084,25 +7024,25 @@
         <v>208</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7116,13 +7056,13 @@
         <v>212</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
@@ -7131,10 +7071,10 @@
         <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -7148,25 +7088,25 @@
         <v>216</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -7212,7 +7152,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -7221,7 +7161,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7265,25 +7205,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -7297,25 +7237,25 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>89</v>
+        <v>235</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -7335,7 +7275,7 @@
         <v>57</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>129</v>
@@ -7344,10 +7284,10 @@
         <v>189</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -7361,25 +7301,25 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>95</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -7393,13 +7333,13 @@
         <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
@@ -7411,7 +7351,7 @@
         <v>144</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -7425,13 +7365,13 @@
         <v>114</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
@@ -7443,7 +7383,7 @@
         <v>106</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -7457,25 +7397,25 @@
         <v>118</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -7489,25 +7429,25 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>106</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -7521,25 +7461,25 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -7553,13 +7493,13 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
@@ -7568,10 +7508,10 @@
         <v>88</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -7585,25 +7525,25 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -7617,25 +7557,25 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>94</v>
+        <v>189</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -7649,25 +7589,25 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>189</v>
+        <v>100</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -7681,25 +7621,25 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -7713,25 +7653,25 @@
         <v>154</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -7745,25 +7685,25 @@
         <v>158</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>144</v>
+        <v>295</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -7777,25 +7717,25 @@
         <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>298</v>
+        <v>144</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -7809,25 +7749,25 @@
         <v>166</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -7841,13 +7781,13 @@
         <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
@@ -7856,10 +7796,10 @@
         <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -7873,25 +7813,25 @@
         <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -7905,25 +7845,25 @@
         <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -7937,25 +7877,25 @@
         <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -7969,25 +7909,25 @@
         <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>561</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -8001,25 +7941,25 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -8033,25 +7973,25 @@
         <v>195</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -8062,28 +8002,28 @@
         <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -8097,25 +8037,25 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>571</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>574</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -8129,13 +8069,13 @@
         <v>208</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
@@ -8144,10 +8084,10 @@
         <v>88</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -8161,64 +8101,32 @@
         <v>212</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>581</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -8249,7 +8157,6 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8310,25 +8217,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>112</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -8342,13 +8249,13 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
@@ -8357,10 +8264,10 @@
         <v>135</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -8374,25 +8281,25 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -8406,25 +8313,25 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -8444,19 +8351,19 @@
         <v>58</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -8470,25 +8377,25 @@
         <v>114</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -8502,25 +8409,25 @@
         <v>118</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -8534,25 +8441,25 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -8566,25 +8473,25 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -8598,25 +8505,25 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -8630,25 +8537,25 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -8662,25 +8569,25 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>401</v>
+        <v>557</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -8694,13 +8601,13 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
@@ -8709,10 +8616,10 @@
         <v>111</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>573</v>
+        <v>398</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -8726,25 +8633,25 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -8758,25 +8665,25 @@
         <v>154</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -8790,25 +8697,25 @@
         <v>158</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -8822,25 +8729,25 @@
         <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -8854,25 +8761,25 @@
         <v>166</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -8886,25 +8793,25 @@
         <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>316</v>
+        <v>135</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -8918,25 +8825,25 @@
         <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>100</v>
+        <v>313</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -8950,25 +8857,25 @@
         <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -8982,25 +8889,25 @@
         <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -9014,25 +8921,25 @@
         <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -9046,25 +8953,25 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>577</v>
+        <v>650</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -9078,25 +8985,25 @@
         <v>195</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -9107,28 +9014,28 @@
         <v>58</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>662</v>
+        <v>570</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -9142,25 +9049,25 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>584</v>
+        <v>650</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -9174,13 +9081,13 @@
         <v>208</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
@@ -9189,10 +9096,10 @@
         <v>135</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>584</v>
+        <v>650</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -9212,19 +9119,19 @@
         <v>66</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>129</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -9238,13 +9145,13 @@
         <v>216</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>87</v>
@@ -9253,10 +9160,10 @@
         <v>135</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>674</v>
+        <v>578</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>34</v>
@@ -9302,7 +9209,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -9354,25 +9261,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -9386,25 +9293,25 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -9418,13 +9325,13 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
@@ -9433,10 +9340,10 @@
         <v>88</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -9450,25 +9357,25 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -9482,25 +9389,25 @@
         <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -9514,25 +9421,25 @@
         <v>114</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>407</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -9546,25 +9453,25 @@
         <v>118</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>662</v>
+        <v>574</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -9578,13 +9485,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
@@ -9593,10 +9500,10 @@
         <v>189</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -9610,25 +9517,25 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>130</v>
+        <v>313</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>662</v>
+        <v>574</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -9642,13 +9549,13 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
@@ -9657,10 +9564,10 @@
         <v>130</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -9674,25 +9581,25 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>410</v>
+        <v>130</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -9706,25 +9613,25 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>316</v>
+        <v>407</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>577</v>
+        <v>650</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9738,25 +9645,25 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>410</v>
+        <v>100</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9770,25 +9677,25 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>662</v>
+        <v>574</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9802,13 +9709,13 @@
         <v>154</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
@@ -9817,10 +9724,10 @@
         <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9834,13 +9741,13 @@
         <v>158</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
@@ -9849,10 +9756,10 @@
         <v>111</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9866,25 +9773,25 @@
         <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9898,25 +9805,25 @@
         <v>166</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9930,25 +9837,25 @@
         <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9962,25 +9869,25 @@
         <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>577</v>
+        <v>650</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9994,25 +9901,25 @@
         <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>111</v>
+        <v>228</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -10026,25 +9933,25 @@
         <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -10058,25 +9965,25 @@
         <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -10090,25 +9997,25 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>745</v>
+        <v>75</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>745</v>
+        <v>75</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>87</v>
+        <v>129</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>88</v>
+        <v>313</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>662</v>
+        <v>578</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -10122,25 +10029,25 @@
         <v>195</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>75</v>
+        <v>740</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>75</v>
+        <v>740</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>316</v>
+        <v>94</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>584</v>
+        <v>742</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -10151,28 +10058,28 @@
         <v>67</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>100</v>
+        <v>189</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>674</v>
+        <v>742</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -10186,13 +10093,13 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
@@ -10201,49 +10108,17 @@
         <v>189</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>674</v>
+        <v>749</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J28"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -10272,7 +10147,6 @@
     <hyperlink ref="E26" r:id="rId25"/>
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
-    <sheet name="인형나라" sheetId="2" r:id="rId2"/>
-    <sheet name="빅딜" sheetId="3" r:id="rId3"/>
-    <sheet name="뿌용뿌용" sheetId="4" r:id="rId4"/>
+    <sheet name="뿌용뿌용" sheetId="2" r:id="rId2"/>
+    <sheet name="인형나라" sheetId="3" r:id="rId3"/>
+    <sheet name="빅딜" sheetId="4" r:id="rId4"/>
     <sheet name="대학원" sheetId="5" r:id="rId5"/>
     <sheet name="버번" sheetId="6" r:id="rId6"/>
     <sheet name="칠사모" sheetId="7" r:id="rId7"/>
@@ -21,9 +21,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">대학원!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">더위사냥!$A$1:$J$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">버번!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">빅딜!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">뿌용뿌용!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">인형나라!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">빅딜!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">뿌용뿌용!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">인형나라!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">칠사모!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -72,30 +72,54 @@
     <t>data_date</t>
   </si>
   <si>
+    <t>뿌용뿌용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%BF%8C%EC%9A%A9%EB%BF%8C%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>Scania</t>
+  </si>
+  <si>
+    <t>Scania 10</t>
+  </si>
+  <si>
+    <t>434</t>
+  </si>
+  <si>
+    <t>8위</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>3경 9895조 3461억 1982만</t>
+  </si>
+  <si>
+    <t>투력 2조이상 3일미접속자 강퇴조치</t>
+  </si>
+  <si>
+    <t>뿌용뿌용뿡뿡</t>
+  </si>
+  <si>
+    <t>2026.09.12</t>
+  </si>
+  <si>
     <t>인형나라</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B8%ED%98%95%EB%82%98%EB%9D%BC</t>
   </si>
   <si>
-    <t>Scania</t>
-  </si>
-  <si>
     <t>Scania 25</t>
   </si>
   <si>
     <t>424</t>
   </si>
   <si>
-    <t>8위</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
     <t>4경 1501조 7441억 8574만</t>
   </si>
   <si>
@@ -105,9 +129,6 @@
     <t>최영교</t>
   </si>
   <si>
-    <t>2026.09.12</t>
-  </si>
-  <si>
     <t>빅딜</t>
   </si>
   <si>
@@ -138,27 +159,6 @@
     <t>2026.09.13</t>
   </si>
   <si>
-    <t>뿌용뿌용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%BF%8C%EC%9A%A9%EB%BF%8C%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>Scania 10</t>
-  </si>
-  <si>
-    <t>434</t>
-  </si>
-  <si>
-    <t>3경 9895조 3461억 1982만</t>
-  </si>
-  <si>
-    <t>투력 2조이상 3일미접속자 강퇴조치</t>
-  </si>
-  <si>
-    <t>뿌용뿌용뿡뿡</t>
-  </si>
-  <si>
     <t>대학원</t>
   </si>
   <si>
@@ -288,96 +288,465 @@
     <t>1</t>
   </si>
   <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EC%9A%A9%EB%BF%8C%EC%9A%A9%EB%BF%A1%EB%BF%A1</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>1경 5261조 982억 3155만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>뿌용뿌용뽕뽕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EC%9A%A9%EB%BF%8C%EC%9A%A9%EB%BD%95%EB%BD%95</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>5489조 6741억 8929만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>공항동노갈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%95%AD%EB%8F%99%EB%85%B8%EA%B0%88</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>2846조 2751억 9524만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>양대리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%8C%80%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>2072조 9196억 1204만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>뿌용뿌용까꿍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EC%9A%A9%EB%BF%8C%EC%9A%A9%EA%B9%8C%EA%BF%8D</t>
+  </si>
+  <si>
+    <t>1630조 2167억 5284만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Kopite</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Kopite</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>1526조 8722억 8363만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>남태평</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%ED%83%9C%ED%8F%89</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>1216조 7749억 4936만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>돌아온짜누</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%95%84%EC%98%A8%EC%A7%9C%EB%88%84</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>1129조 3268억 1943만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>토망쳐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A7%9D%EC%B3%90</t>
+  </si>
+  <si>
+    <t>1061조 2908억 4962만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>노곽철</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EA%B3%BD%EC%B2%A0</t>
+  </si>
+  <si>
+    <t>980조 3105억 4537만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>팔마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%94%EB%A7%88</t>
+  </si>
+  <si>
+    <t>930조 3534억 1206만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>뿌용뿌용뿅뿅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EC%9A%A9%EB%BF%8C%EC%9A%A9%EB%BF%85%EB%BF%85</t>
+  </si>
+  <si>
+    <t>844조 9185억 4201만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>이성일</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%84%B1%EC%9D%BC</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>826조 5468억 7528만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Ai사냥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Ai%EC%82%AC%EB%83%A5</t>
+  </si>
+  <si>
+    <t>814조 6812억 7583만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>수빈똥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%B9%88%EB%98%A5</t>
+  </si>
+  <si>
+    <t>755조 7292억 5489만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>꿀벌재미니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EB%B2%8C%EC%9E%AC%EB%AF%B8%EB%8B%88</t>
+  </si>
+  <si>
+    <t>730조 507억 6773만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>쿠키칩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%ED%82%A4%EC%B9%A9</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>692조 6606억 1774만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>경후훈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%ED%9B%84%ED%9B%88</t>
+  </si>
+  <si>
+    <t>683조 4299억 121만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>트투</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8A%B8%ED%88%AC</t>
+  </si>
+  <si>
+    <t>606조 7961억 2592만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>비속어금지중</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%86%8D%EC%96%B4%EA%B8%88%EC%A7%80%EC%A4%91</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>588조 5530억 5868만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>탑뎅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%91%EB%8E%85</t>
+  </si>
+  <si>
+    <t>540조 124억 5753만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>봉천동주접꾼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EC%B2%9C%EB%8F%99%EC%A3%BC%EC%A0%91%EA%BE%BC</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>524조 8371억 3177만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>밤바밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%A4%EB%B0%94%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>518조 4058억 8333만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>정맨정맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%A7%A8%EC%A0%95%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>477조 7642억 1340만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>본딩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B8%EB%94%A9</t>
+  </si>
+  <si>
+    <t>437조 1898억 8917만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>그이뜌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EC%9D%B4%EB%9C%8C</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>378조 1528억 9711만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>대항해시대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%ED%95%AD%ED%95%B4%EC%8B%9C%EB%8C%80</t>
+  </si>
+  <si>
+    <t>347조 4924억 7745만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>MELLOO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=MELLOO</t>
+  </si>
+  <si>
+    <t>332조 3896억 394만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>이게제맛</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B2%8C%EC%A0%9C%EB%A7%9B</t>
+  </si>
+  <si>
+    <t>299조 3596억 4195만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>냥냥쨉쨉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%EB%83%A5%EC%A8%89%EC%A8%89</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>166조 5292억 2023만</t>
+  </si>
+  <si>
     <t>글쟈</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%80%EC%9F%88</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>1경 447조 5129억 7199만</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>괴챠반</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B4%B4%EC%B1%A0%EB%B0%98</t>
   </si>
   <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>3779조 9660억 4199만</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>명동이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EB%8F%99%EC%9D%B4</t>
   </si>
   <si>
-    <t>비숍</t>
-  </si>
-  <si>
     <t>3245조 684억 6500만</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>유놈</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%86%88</t>
   </si>
   <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>2621조 4061억 2859만</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>꿀꿀맛</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%BF%80%EB%A7%9B</t>
   </si>
   <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
     <t>113</t>
   </si>
   <si>
     <t>2386조 8932억 4753만</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>윤꼬밍</t>
   </si>
   <si>
@@ -387,9 +756,6 @@
     <t>2156조 1091억 1210만</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>디매트로돈</t>
   </si>
   <si>
@@ -399,9 +765,6 @@
     <t>2148조 7069억 2080만</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>사오토메란마</t>
   </si>
   <si>
@@ -414,39 +777,21 @@
     <t>1707조 4498억 8759만</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%98%81%EA%B5%90</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
     <t>1495조 9351억 651만</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>김훈한</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%9B%88%ED%95%9C</t>
   </si>
   <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
     <t>1152조 7813억 2778만</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>Pakachu9999</t>
   </si>
   <si>
@@ -456,24 +801,15 @@
     <t>1142조 2566억 8130만</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>구엉이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EC%97%89%EC%9D%B4</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>1052조 5398억 161만</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>잉글리쉬</t>
   </si>
   <si>
@@ -483,9 +819,6 @@
     <t>1022조 5383억 5173만</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>똥땅이횽</t>
   </si>
   <si>
@@ -495,9 +828,6 @@
     <t>776조 7613억 8822만</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>혁바</t>
   </si>
   <si>
@@ -507,9 +837,6 @@
     <t>775조 4786억 1213만</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>범지</t>
   </si>
   <si>
@@ -519,9 +846,6 @@
     <t>753조 791억 3550만</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>디메트로돈</t>
   </si>
   <si>
@@ -531,9 +855,6 @@
     <t>704조 9735억 7649만</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>솖이</t>
   </si>
   <si>
@@ -543,9 +864,6 @@
     <t>681조 4944억 9400만</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
     <t>뜨머푸</t>
   </si>
   <si>
@@ -555,9 +873,6 @@
     <t>666조 9853억 6246만</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>오우솃</t>
   </si>
   <si>
@@ -567,9 +882,6 @@
     <t>623조 4349억 2383만</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>혜미니현미니</t>
   </si>
   <si>
@@ -579,9 +891,6 @@
     <t>588조 1465억 3109만</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>옆구리두방</t>
   </si>
   <si>
@@ -591,24 +900,15 @@
     <t>511조 7625억 5353만</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
     <t>쀏뀱쪍</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%80%8F%EB%80%B1%EC%AA%8D</t>
   </si>
   <si>
-    <t>캡틴</t>
-  </si>
-  <si>
     <t>477조 4769억 4575만</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
     <t>양쿼카</t>
   </si>
   <si>
@@ -618,9 +918,6 @@
     <t>390조 3037억 2972만</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
     <t>정섭이</t>
   </si>
   <si>
@@ -630,24 +927,15 @@
     <t>384조 5653억 9771만</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
     <t>니누고</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%88%84%EA%B3%A0</t>
   </si>
   <si>
-    <t>109</t>
-  </si>
-  <si>
     <t>377조 4506억 6398만</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
     <t>연속기</t>
   </si>
   <si>
@@ -657,9 +945,6 @@
     <t>330조 108억 9811만</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
     <t>여덟시</t>
   </si>
   <si>
@@ -669,9 +954,6 @@
     <t>313조 7265억 4684만</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
     <t>돼짱</t>
   </si>
   <si>
@@ -681,9 +963,6 @@
     <t>307조 5404억 2549만</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>젤로젤리</t>
   </si>
   <si>
@@ -738,9 +1017,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
   </si>
   <si>
-    <t>115</t>
-  </si>
-  <si>
     <t>3155조 7739억 8662만</t>
   </si>
   <si>
@@ -918,9 +1194,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
   </si>
   <si>
-    <t>108</t>
-  </si>
-  <si>
     <t>298조 2305억 9860만</t>
   </si>
   <si>
@@ -960,279 +1233,6 @@
     <t>194조 2882억 2735만</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EC%9A%A9%EB%BF%8C%EC%9A%A9%EB%BF%A1%EB%BF%A1</t>
-  </si>
-  <si>
-    <t>1경 5261조 982억 3155만</t>
-  </si>
-  <si>
-    <t>뿌용뿌용뽕뽕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EC%9A%A9%EB%BF%8C%EC%9A%A9%EB%BD%95%EB%BD%95</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>5489조 6741억 8929만</t>
-  </si>
-  <si>
-    <t>공항동노갈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%95%AD%EB%8F%99%EB%85%B8%EA%B0%88</t>
-  </si>
-  <si>
-    <t>2846조 2751억 9524만</t>
-  </si>
-  <si>
-    <t>양대리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%8C%80%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>2072조 9196억 1204만</t>
-  </si>
-  <si>
-    <t>뿌용뿌용까꿍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EC%9A%A9%EB%BF%8C%EC%9A%A9%EA%B9%8C%EA%BF%8D</t>
-  </si>
-  <si>
-    <t>1630조 2167억 5284만</t>
-  </si>
-  <si>
-    <t>Kopite</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Kopite</t>
-  </si>
-  <si>
-    <t>1526조 8722억 8363만</t>
-  </si>
-  <si>
-    <t>남태평</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%ED%83%9C%ED%8F%89</t>
-  </si>
-  <si>
-    <t>1216조 7749억 4936만</t>
-  </si>
-  <si>
-    <t>돌아온짜누</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%95%84%EC%98%A8%EC%A7%9C%EB%88%84</t>
-  </si>
-  <si>
-    <t>1129조 3268억 1943만</t>
-  </si>
-  <si>
-    <t>토망쳐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A7%9D%EC%B3%90</t>
-  </si>
-  <si>
-    <t>1061조 2908억 4962만</t>
-  </si>
-  <si>
-    <t>노곽철</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EA%B3%BD%EC%B2%A0</t>
-  </si>
-  <si>
-    <t>980조 3105억 4537만</t>
-  </si>
-  <si>
-    <t>팔마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%94%EB%A7%88</t>
-  </si>
-  <si>
-    <t>930조 3534억 1206만</t>
-  </si>
-  <si>
-    <t>뿌용뿌용뿅뿅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EC%9A%A9%EB%BF%8C%EC%9A%A9%EB%BF%85%EB%BF%85</t>
-  </si>
-  <si>
-    <t>844조 9185억 4201만</t>
-  </si>
-  <si>
-    <t>이성일</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%84%B1%EC%9D%BC</t>
-  </si>
-  <si>
-    <t>826조 5468억 7528만</t>
-  </si>
-  <si>
-    <t>Ai사냥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Ai%EC%82%AC%EB%83%A5</t>
-  </si>
-  <si>
-    <t>814조 6812억 7583만</t>
-  </si>
-  <si>
-    <t>수빈똥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%B9%88%EB%98%A5</t>
-  </si>
-  <si>
-    <t>755조 7292억 5489만</t>
-  </si>
-  <si>
-    <t>꿀벌재미니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EB%B2%8C%EC%9E%AC%EB%AF%B8%EB%8B%88</t>
-  </si>
-  <si>
-    <t>730조 507억 6773만</t>
-  </si>
-  <si>
-    <t>쿠키칩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%ED%82%A4%EC%B9%A9</t>
-  </si>
-  <si>
-    <t>692조 6606억 1774만</t>
-  </si>
-  <si>
-    <t>경후훈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%ED%9B%84%ED%9B%88</t>
-  </si>
-  <si>
-    <t>683조 4299억 121만</t>
-  </si>
-  <si>
-    <t>트투</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8A%B8%ED%88%AC</t>
-  </si>
-  <si>
-    <t>606조 7961억 2592만</t>
-  </si>
-  <si>
-    <t>비속어금지중</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%86%8D%EC%96%B4%EA%B8%88%EC%A7%80%EC%A4%91</t>
-  </si>
-  <si>
-    <t>588조 5530억 5868만</t>
-  </si>
-  <si>
-    <t>탑뎅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%91%EB%8E%85</t>
-  </si>
-  <si>
-    <t>540조 124억 5753만</t>
-  </si>
-  <si>
-    <t>봉천동주접꾼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EC%B2%9C%EB%8F%99%EC%A3%BC%EC%A0%91%EA%BE%BC</t>
-  </si>
-  <si>
-    <t>524조 8371억 3177만</t>
-  </si>
-  <si>
-    <t>밤바밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%A4%EB%B0%94%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>518조 4058억 8333만</t>
-  </si>
-  <si>
-    <t>정맨정맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%A7%A8%EC%A0%95%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>477조 7642억 1340만</t>
-  </si>
-  <si>
-    <t>본딩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B8%EB%94%A9</t>
-  </si>
-  <si>
-    <t>437조 1898억 8917만</t>
-  </si>
-  <si>
-    <t>그이뜌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EC%9D%B4%EB%9C%8C</t>
-  </si>
-  <si>
-    <t>378조 1528억 9711만</t>
-  </si>
-  <si>
-    <t>대항해시대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%ED%95%AD%ED%95%B4%EC%8B%9C%EB%8C%80</t>
-  </si>
-  <si>
-    <t>347조 4924억 7745만</t>
-  </si>
-  <si>
-    <t>MELLOO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=MELLOO</t>
-  </si>
-  <si>
-    <t>332조 3896억 394만</t>
-  </si>
-  <si>
-    <t>이게제맛</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B2%8C%EC%A0%9C%EB%A7%9B</t>
-  </si>
-  <si>
-    <t>299조 3596억 4195만</t>
-  </si>
-  <si>
-    <t>냥냥쨉쨉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%EB%83%A5%EC%A8%89%EC%A8%89</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>166조 5292억 2023만</t>
-  </si>
-  <si>
     <t>응냥</t>
   </si>
   <si>
@@ -2073,7 +2073,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EA%B5%AC%EB%82%A8%EC%84%B1</t>
   </si>
   <si>
-    <t>44조 3150억 1610만</t>
+    <t>45조 3365억 505만</t>
   </si>
   <si>
     <t>KR#0P7W5X70V4</t>
@@ -2085,6 +2085,15 @@
     <t>41조 5854억 8868만</t>
   </si>
   <si>
+    <t>토벤숍이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%B2%A4%EC%88%8D%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>26조 7528억 929만</t>
+  </si>
+  <si>
     <t>코잉코잉</t>
   </si>
   <si>
@@ -2100,16 +2109,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%9E%9128%EC%84%B8</t>
   </si>
   <si>
-    <t>23조 8905억 6160만</t>
-  </si>
-  <si>
-    <t>토벤숍이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%B2%A4%EC%88%8D%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>22조 8212억 9298만</t>
+    <t>25조 2673억 4067만</t>
   </si>
   <si>
     <t>돈성</t>
@@ -2118,7 +2118,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%84%B1</t>
   </si>
   <si>
-    <t>21조 6662억 2588만</t>
+    <t>23조 8541억 6331만</t>
   </si>
   <si>
     <t>뭐하는게임</t>
@@ -2127,7 +2127,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AD%90%ED%95%98%EB%8A%94%EA%B2%8C%EC%9E%84</t>
   </si>
   <si>
-    <t>21조 5418억 4559만</t>
+    <t>23조 5853억 4333만</t>
   </si>
   <si>
     <t>씅놈</t>
@@ -2136,7 +2136,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%94%85%EB%86%88</t>
   </si>
   <si>
-    <t>20조 7502억 4689만</t>
+    <t>21조 3712억 5539만</t>
   </si>
   <si>
     <t>빵신궁</t>
@@ -2145,7 +2145,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EC%8B%A0%EA%B6%81</t>
   </si>
   <si>
-    <t>20조 2279억 1258만</t>
+    <t>20조 2419억 1039만</t>
+  </si>
+  <si>
+    <t>고통받는갈비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%ED%86%B5%EB%B0%9B%EB%8A%94%EA%B0%88%EB%B9%84</t>
+  </si>
+  <si>
+    <t>17조 6645억 8393만</t>
   </si>
   <si>
     <t>우루차</t>
@@ -2154,7 +2163,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%A3%A8%EC%B0%A8</t>
   </si>
   <si>
-    <t>16조 6631억 1648만</t>
+    <t>17조 4285억 3882만</t>
+  </si>
+  <si>
+    <t>킬혁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%AC%ED%98%81</t>
+  </si>
+  <si>
+    <t>17조 3707억 784만</t>
   </si>
   <si>
     <t>마키맛키마</t>
@@ -2163,16 +2181,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%82%A4%EB%A7%9B%ED%82%A4%EB%A7%88</t>
   </si>
   <si>
-    <t>16조 4912억 4548만</t>
-  </si>
-  <si>
-    <t>킬혁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%AC%ED%98%81</t>
-  </si>
-  <si>
-    <t>16조 4486억 443만</t>
+    <t>17조 373억 733만</t>
   </si>
   <si>
     <t>썬콜우체국</t>
@@ -2181,16 +2190,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9A%B0%EC%B2%B4%EA%B5%AD</t>
   </si>
   <si>
-    <t>15조 572억 3019만</t>
-  </si>
-  <si>
-    <t>고통받는갈비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%ED%86%B5%EB%B0%9B%EB%8A%94%EA%B0%88%EB%B9%84</t>
-  </si>
-  <si>
-    <t>14조 6124억 1564만</t>
+    <t>15조 3863억 9808만</t>
   </si>
   <si>
     <t>배렛나루왁서</t>
@@ -2199,7 +2199,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%EB%A0%9B%EB%82%98%EB%A3%A8%EC%99%81%EC%84%9C</t>
   </si>
   <si>
-    <t>14조 3217억 9742만</t>
+    <t>14조 8540억 9005만</t>
   </si>
   <si>
     <t>밀초크코</t>
@@ -2208,7 +2208,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%EC%B4%88%ED%81%AC%EC%BD%94</t>
   </si>
   <si>
-    <t>13조 9894억 3978만</t>
+    <t>14조 325억 727만</t>
   </si>
   <si>
     <t>오스띤</t>
@@ -2226,7 +2226,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%95%A1%EC%9A%94%EB%82%98%ED%90%81</t>
   </si>
   <si>
-    <t>11조 8161억 3024만</t>
+    <t>11조 8263억 4058만</t>
   </si>
   <si>
     <t>썬콜법사ss</t>
@@ -2235,7 +2235,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%ACss</t>
   </si>
   <si>
-    <t>11조 2554억 5294만</t>
+    <t>11조 3529억 6307만</t>
   </si>
   <si>
     <t>문보겨엉</t>
@@ -2262,7 +2262,7 @@
     <t>101</t>
   </si>
   <si>
-    <t>4조 7936억 3362만</t>
+    <t>4조 8308억 2590만</t>
   </si>
   <si>
     <t>경기도인</t>
@@ -2283,7 +2283,7 @@
     <t>99</t>
   </si>
   <si>
-    <t>2조 570억 3535만</t>
+    <t>2조 4344억 6314만</t>
   </si>
 </sst>
 </file>
@@ -2764,66 +2764,66 @@
         <v>28</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="M3" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2905,7 +2905,7 @@
         <v>57</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2946,7 +2946,7 @@
         <v>66</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -3012,7 +3012,7 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
@@ -3060,25 +3060,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3089,19 +3089,19 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>94</v>
@@ -3133,16 +3133,16 @@
         <v>99</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3153,28 +3153,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3185,28 +3185,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3217,25 +3217,25 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>117</v>
@@ -3261,16 +3261,16 @@
         <v>120</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3281,28 +3281,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3313,25 +3313,25 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>23</v>
+        <v>129</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>23</v>
+        <v>129</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>131</v>
@@ -3357,16 +3357,16 @@
         <v>134</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3377,28 +3377,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3409,28 +3409,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3441,28 +3441,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3473,28 +3473,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3505,28 +3505,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3537,28 +3537,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3569,25 +3569,25 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>165</v>
@@ -3613,13 +3613,13 @@
         <v>168</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>169</v>
@@ -3645,13 +3645,13 @@
         <v>172</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>173</v>
@@ -3677,16 +3677,16 @@
         <v>176</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>106</v>
+        <v>177</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3697,28 +3697,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3729,28 +3729,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="H23" s="2" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3761,28 +3761,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>189</v>
+        <v>100</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>106</v>
+        <v>177</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3793,28 +3793,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3825,28 +3825,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3857,28 +3857,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>100</v>
+        <v>203</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3889,28 +3889,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3921,28 +3921,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>202</v>
+        <v>147</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3953,28 +3953,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3985,28 +3985,28 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>100</v>
+        <v>203</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>144</v>
+        <v>220</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -4052,1023 +4052,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J30"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
@@ -5110,31 +4099,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>41</v>
+        <v>222</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>41</v>
+        <v>222</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>309</v>
+        <v>223</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>189</v>
+        <v>121</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>235</v>
+        <v>95</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>310</v>
+        <v>224</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5142,31 +4131,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>311</v>
+        <v>225</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>311</v>
+        <v>225</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>312</v>
+        <v>226</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>313</v>
+        <v>126</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>314</v>
+        <v>227</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5174,31 +4163,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>315</v>
+        <v>228</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>315</v>
+        <v>228</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>316</v>
+        <v>229</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>317</v>
+        <v>230</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5206,31 +4195,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>318</v>
+        <v>231</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>318</v>
+        <v>231</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>319</v>
+        <v>232</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>320</v>
+        <v>233</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5238,31 +4227,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>321</v>
+        <v>234</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>321</v>
+        <v>234</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>322</v>
+        <v>235</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>100</v>
+        <v>203</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>95</v>
+        <v>236</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>323</v>
+        <v>237</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5270,31 +4259,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>324</v>
+        <v>238</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>324</v>
+        <v>238</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>325</v>
+        <v>239</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>326</v>
+        <v>240</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5302,31 +4291,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>327</v>
+        <v>241</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>327</v>
+        <v>241</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>328</v>
+        <v>242</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>329</v>
+        <v>243</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5334,31 +4323,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>330</v>
+        <v>244</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>330</v>
+        <v>244</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>331</v>
+        <v>245</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>246</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>332</v>
+        <v>247</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5366,31 +4355,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>333</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>333</v>
+        <v>31</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>334</v>
+        <v>248</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>335</v>
+        <v>249</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5398,31 +4387,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>336</v>
+        <v>250</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>336</v>
+        <v>250</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>337</v>
+        <v>251</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>338</v>
+        <v>252</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5430,31 +4419,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>339</v>
+        <v>253</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>339</v>
+        <v>253</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>340</v>
+        <v>254</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>341</v>
+        <v>255</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5462,31 +4451,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>342</v>
+        <v>256</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>342</v>
+        <v>256</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>343</v>
+        <v>257</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>344</v>
+        <v>258</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5494,31 +4483,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>345</v>
+        <v>259</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>345</v>
+        <v>259</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>346</v>
+        <v>260</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>347</v>
+        <v>261</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5526,31 +4515,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>348</v>
+        <v>262</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>348</v>
+        <v>262</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>349</v>
+        <v>263</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>350</v>
+        <v>264</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5558,31 +4547,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>351</v>
+        <v>265</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>351</v>
+        <v>265</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>352</v>
+        <v>266</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>313</v>
+        <v>116</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>353</v>
+        <v>267</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5590,31 +4579,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>354</v>
+        <v>268</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>354</v>
+        <v>268</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>355</v>
+        <v>269</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>356</v>
+        <v>270</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5622,31 +4611,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>357</v>
+        <v>271</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>357</v>
+        <v>271</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>358</v>
+        <v>272</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>359</v>
+        <v>273</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5654,31 +4643,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>166</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>360</v>
+        <v>274</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>360</v>
+        <v>274</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>361</v>
+        <v>275</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>88</v>
+        <v>203</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>362</v>
+        <v>276</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5686,31 +4675,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>363</v>
+        <v>277</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>363</v>
+        <v>277</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>364</v>
+        <v>278</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>365</v>
+        <v>279</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5718,31 +4707,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>366</v>
+        <v>280</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>366</v>
+        <v>280</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>367</v>
+        <v>281</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>202</v>
+        <v>107</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>368</v>
+        <v>282</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5750,31 +4739,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>369</v>
+        <v>283</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>369</v>
+        <v>283</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>370</v>
+        <v>284</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>202</v>
+        <v>147</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>371</v>
+        <v>285</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5782,31 +4771,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>372</v>
+        <v>286</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>372</v>
+        <v>286</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>373</v>
+        <v>287</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>189</v>
+        <v>100</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>295</v>
+        <v>147</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>374</v>
+        <v>288</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5814,31 +4803,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>375</v>
+        <v>289</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>375</v>
+        <v>289</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>376</v>
+        <v>290</v>
       </c>
       <c r="F24" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="H24" s="2" t="s">
-        <v>202</v>
+        <v>107</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>377</v>
+        <v>291</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5846,31 +4835,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>378</v>
+        <v>292</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>378</v>
+        <v>292</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>379</v>
+        <v>293</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>295</v>
+        <v>147</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>380</v>
+        <v>294</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5878,31 +4867,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>381</v>
+        <v>295</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>381</v>
+        <v>295</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>382</v>
+        <v>296</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>383</v>
+        <v>297</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5910,31 +4899,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>384</v>
+        <v>298</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>384</v>
+        <v>298</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>385</v>
+        <v>299</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>295</v>
+        <v>177</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>386</v>
+        <v>300</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5942,31 +4931,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>387</v>
+        <v>301</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>387</v>
+        <v>301</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>388</v>
+        <v>302</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>202</v>
+        <v>147</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>389</v>
+        <v>303</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5974,31 +4963,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>390</v>
+        <v>304</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>390</v>
+        <v>304</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>391</v>
+        <v>305</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>392</v>
+        <v>306</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6006,31 +4995,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>393</v>
+        <v>307</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>393</v>
+        <v>307</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>394</v>
+        <v>308</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>295</v>
+        <v>147</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>395</v>
+        <v>309</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6038,31 +5027,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>396</v>
+        <v>310</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>396</v>
+        <v>310</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>397</v>
+        <v>311</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>398</v>
+        <v>147</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>399</v>
+        <v>312</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6106,6 +5095,1017 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J30"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
@@ -6169,13 +6169,13 @@
         <v>401</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>402</v>
@@ -6189,7 +6189,7 @@
         <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>49</v>
@@ -6201,13 +6201,13 @@
         <v>403</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>235</v>
+        <v>88</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>404</v>
@@ -6233,13 +6233,13 @@
         <v>406</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>407</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>408</v>
@@ -6253,7 +6253,7 @@
         <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>409</v>
@@ -6265,13 +6265,13 @@
         <v>410</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>112</v>
+        <v>236</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>411</v>
@@ -6285,7 +6285,7 @@
         <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>412</v>
@@ -6297,13 +6297,13 @@
         <v>413</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>112</v>
+        <v>236</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>414</v>
@@ -6317,7 +6317,7 @@
         <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>415</v>
@@ -6329,13 +6329,13 @@
         <v>416</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>112</v>
+        <v>236</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>417</v>
@@ -6361,13 +6361,13 @@
         <v>419</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>420</v>
@@ -6381,7 +6381,7 @@
         <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>421</v>
@@ -6393,13 +6393,13 @@
         <v>422</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>407</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>423</v>
@@ -6413,7 +6413,7 @@
         <v>42</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>424</v>
@@ -6425,13 +6425,13 @@
         <v>425</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>426</v>
@@ -6457,13 +6457,13 @@
         <v>428</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>429</v>
@@ -6477,7 +6477,7 @@
         <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>430</v>
@@ -6489,13 +6489,13 @@
         <v>431</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>432</v>
@@ -6509,7 +6509,7 @@
         <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>433</v>
@@ -6521,13 +6521,13 @@
         <v>434</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>435</v>
@@ -6541,7 +6541,7 @@
         <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>436</v>
@@ -6553,13 +6553,13 @@
         <v>437</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>438</v>
@@ -6573,7 +6573,7 @@
         <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>439</v>
@@ -6585,13 +6585,13 @@
         <v>440</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>441</v>
@@ -6605,7 +6605,7 @@
         <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>442</v>
@@ -6617,13 +6617,13 @@
         <v>443</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>444</v>
@@ -6637,7 +6637,7 @@
         <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>445</v>
@@ -6649,13 +6649,13 @@
         <v>446</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>447</v>
@@ -6669,7 +6669,7 @@
         <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>448</v>
@@ -6681,13 +6681,13 @@
         <v>449</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>450</v>
@@ -6713,13 +6713,13 @@
         <v>452</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>453</v>
@@ -6745,13 +6745,13 @@
         <v>455</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>456</v>
@@ -6777,13 +6777,13 @@
         <v>458</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>459</v>
@@ -6797,7 +6797,7 @@
         <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>460</v>
@@ -6809,13 +6809,13 @@
         <v>461</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>462</v>
@@ -6829,7 +6829,7 @@
         <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>463</v>
@@ -6841,13 +6841,13 @@
         <v>464</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>465</v>
@@ -6861,7 +6861,7 @@
         <v>42</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>466</v>
@@ -6873,13 +6873,13 @@
         <v>467</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>468</v>
@@ -6893,7 +6893,7 @@
         <v>42</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>469</v>
@@ -6905,13 +6905,13 @@
         <v>470</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>471</v>
@@ -6925,7 +6925,7 @@
         <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>472</v>
@@ -6937,13 +6937,13 @@
         <v>473</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>474</v>
@@ -6957,7 +6957,7 @@
         <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>475</v>
@@ -6969,13 +6969,13 @@
         <v>476</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>407</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>477</v>
@@ -6989,7 +6989,7 @@
         <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>478</v>
@@ -7001,13 +7001,13 @@
         <v>479</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>480</v>
@@ -7021,7 +7021,7 @@
         <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>481</v>
@@ -7033,13 +7033,13 @@
         <v>482</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>228</v>
+        <v>321</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>483</v>
@@ -7053,7 +7053,7 @@
         <v>42</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>484</v>
@@ -7065,13 +7065,13 @@
         <v>485</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>486</v>
@@ -7085,7 +7085,7 @@
         <v>42</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>487</v>
@@ -7097,13 +7097,13 @@
         <v>488</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>295</v>
+        <v>186</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>489</v>
@@ -7214,19 +7214,19 @@
         <v>491</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>235</v>
+        <v>88</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>492</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -7234,7 +7234,7 @@
         <v>50</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>493</v>
@@ -7246,19 +7246,19 @@
         <v>494</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>235</v>
+        <v>88</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>495</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -7278,19 +7278,19 @@
         <v>496</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>189</v>
+        <v>87</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>235</v>
+        <v>88</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>497</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -7298,7 +7298,7 @@
         <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>498</v>
@@ -7310,19 +7310,19 @@
         <v>499</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>500</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -7330,7 +7330,7 @@
         <v>50</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>501</v>
@@ -7342,19 +7342,19 @@
         <v>502</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>503</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -7362,7 +7362,7 @@
         <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>504</v>
@@ -7374,19 +7374,19 @@
         <v>505</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>125</v>
+        <v>246</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>506</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -7406,19 +7406,19 @@
         <v>508</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>509</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -7426,7 +7426,7 @@
         <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>510</v>
@@ -7438,19 +7438,19 @@
         <v>511</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>512</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -7458,7 +7458,7 @@
         <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>513</v>
@@ -7470,19 +7470,19 @@
         <v>514</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>515</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -7502,19 +7502,19 @@
         <v>517</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>518</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -7522,7 +7522,7 @@
         <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>519</v>
@@ -7534,19 +7534,19 @@
         <v>520</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>295</v>
+        <v>186</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>521</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -7554,7 +7554,7 @@
         <v>50</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>522</v>
@@ -7566,19 +7566,19 @@
         <v>523</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>524</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -7586,7 +7586,7 @@
         <v>50</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>525</v>
@@ -7598,19 +7598,19 @@
         <v>526</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>527</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -7618,7 +7618,7 @@
         <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>528</v>
@@ -7630,19 +7630,19 @@
         <v>529</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>530</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -7650,7 +7650,7 @@
         <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>531</v>
@@ -7662,19 +7662,19 @@
         <v>532</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>228</v>
+        <v>321</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>533</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -7682,7 +7682,7 @@
         <v>50</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>534</v>
@@ -7694,19 +7694,19 @@
         <v>535</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>295</v>
+        <v>186</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>536</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -7714,7 +7714,7 @@
         <v>50</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>537</v>
@@ -7726,19 +7726,19 @@
         <v>538</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>539</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -7758,19 +7758,19 @@
         <v>541</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>295</v>
+        <v>186</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>542</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -7790,19 +7790,19 @@
         <v>544</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>295</v>
+        <v>186</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>545</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -7822,19 +7822,19 @@
         <v>547</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>398</v>
+        <v>220</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>548</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -7842,7 +7842,7 @@
         <v>50</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>549</v>
@@ -7854,19 +7854,19 @@
         <v>550</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>398</v>
+        <v>220</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>551</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -7874,7 +7874,7 @@
         <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>552</v>
@@ -7886,19 +7886,19 @@
         <v>553</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>398</v>
+        <v>220</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>554</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -7906,7 +7906,7 @@
         <v>50</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>555</v>
@@ -7918,7 +7918,7 @@
         <v>556</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>100</v>
@@ -7930,7 +7930,7 @@
         <v>558</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -7938,7 +7938,7 @@
         <v>50</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>559</v>
@@ -7950,19 +7950,19 @@
         <v>560</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>398</v>
+        <v>220</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>561</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -7970,7 +7970,7 @@
         <v>50</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>562</v>
@@ -7982,19 +7982,19 @@
         <v>563</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>295</v>
+        <v>186</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>564</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -8002,7 +8002,7 @@
         <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>565</v>
@@ -8014,19 +8014,19 @@
         <v>566</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>228</v>
+        <v>321</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>398</v>
+        <v>220</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>567</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -8034,7 +8034,7 @@
         <v>50</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>568</v>
@@ -8046,7 +8046,7 @@
         <v>569</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>100</v>
@@ -8058,7 +8058,7 @@
         <v>571</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -8066,7 +8066,7 @@
         <v>50</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>572</v>
@@ -8078,10 +8078,10 @@
         <v>573</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>574</v>
@@ -8090,7 +8090,7 @@
         <v>575</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -8098,7 +8098,7 @@
         <v>50</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>576</v>
@@ -8110,7 +8110,7 @@
         <v>577</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>100</v>
@@ -8122,7 +8122,7 @@
         <v>579</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -8226,19 +8226,19 @@
         <v>581</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>228</v>
+        <v>321</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>112</v>
+        <v>236</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>582</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -8246,7 +8246,7 @@
         <v>58</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>583</v>
@@ -8258,19 +8258,19 @@
         <v>584</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>585</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -8290,19 +8290,19 @@
         <v>587</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>588</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -8310,7 +8310,7 @@
         <v>58</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>589</v>
@@ -8322,19 +8322,19 @@
         <v>590</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>228</v>
+        <v>321</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>591</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -8342,7 +8342,7 @@
         <v>58</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>58</v>
@@ -8354,19 +8354,19 @@
         <v>592</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>593</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -8374,7 +8374,7 @@
         <v>58</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>594</v>
@@ -8386,19 +8386,19 @@
         <v>595</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>295</v>
+        <v>186</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>596</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -8418,19 +8418,19 @@
         <v>598</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>599</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -8438,7 +8438,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>600</v>
@@ -8450,7 +8450,7 @@
         <v>601</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>100</v>
@@ -8462,7 +8462,7 @@
         <v>602</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -8470,7 +8470,7 @@
         <v>58</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>603</v>
@@ -8482,7 +8482,7 @@
         <v>604</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>100</v>
@@ -8494,7 +8494,7 @@
         <v>605</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -8514,19 +8514,19 @@
         <v>607</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>398</v>
+        <v>220</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>608</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -8534,7 +8534,7 @@
         <v>58</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>609</v>
@@ -8546,19 +8546,19 @@
         <v>610</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>398</v>
+        <v>220</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>611</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -8566,7 +8566,7 @@
         <v>58</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>612</v>
@@ -8578,10 +8578,10 @@
         <v>613</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>557</v>
@@ -8590,7 +8590,7 @@
         <v>614</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -8598,7 +8598,7 @@
         <v>58</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>615</v>
@@ -8610,19 +8610,19 @@
         <v>616</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>398</v>
+        <v>220</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>617</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -8630,7 +8630,7 @@
         <v>58</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>618</v>
@@ -8642,10 +8642,10 @@
         <v>619</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>570</v>
@@ -8654,7 +8654,7 @@
         <v>620</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -8662,7 +8662,7 @@
         <v>58</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>621</v>
@@ -8674,7 +8674,7 @@
         <v>622</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>100</v>
@@ -8686,7 +8686,7 @@
         <v>623</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -8694,7 +8694,7 @@
         <v>58</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>624</v>
@@ -8706,10 +8706,10 @@
         <v>625</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>574</v>
@@ -8718,7 +8718,7 @@
         <v>626</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -8726,7 +8726,7 @@
         <v>58</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>627</v>
@@ -8738,10 +8738,10 @@
         <v>628</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>570</v>
@@ -8750,7 +8750,7 @@
         <v>629</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -8770,7 +8770,7 @@
         <v>631</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>100</v>
@@ -8782,7 +8782,7 @@
         <v>632</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -8802,10 +8802,10 @@
         <v>634</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>570</v>
@@ -8814,7 +8814,7 @@
         <v>635</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -8834,10 +8834,10 @@
         <v>637</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>313</v>
+        <v>94</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>574</v>
@@ -8846,7 +8846,7 @@
         <v>638</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -8854,7 +8854,7 @@
         <v>58</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>639</v>
@@ -8866,10 +8866,10 @@
         <v>640</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>570</v>
@@ -8878,7 +8878,7 @@
         <v>641</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -8886,7 +8886,7 @@
         <v>58</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>642</v>
@@ -8898,7 +8898,7 @@
         <v>643</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>100</v>
@@ -8910,7 +8910,7 @@
         <v>644</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -8918,7 +8918,7 @@
         <v>58</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>645</v>
@@ -8930,10 +8930,10 @@
         <v>646</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>570</v>
@@ -8942,7 +8942,7 @@
         <v>647</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -8950,7 +8950,7 @@
         <v>58</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>648</v>
@@ -8962,7 +8962,7 @@
         <v>649</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>100</v>
@@ -8974,7 +8974,7 @@
         <v>651</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -8982,7 +8982,7 @@
         <v>58</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>652</v>
@@ -8994,7 +8994,7 @@
         <v>653</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>100</v>
@@ -9006,7 +9006,7 @@
         <v>654</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -9014,7 +9014,7 @@
         <v>58</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>655</v>
@@ -9026,10 +9026,10 @@
         <v>656</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>570</v>
@@ -9038,7 +9038,7 @@
         <v>657</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -9046,7 +9046,7 @@
         <v>58</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>658</v>
@@ -9058,7 +9058,7 @@
         <v>659</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>100</v>
@@ -9070,7 +9070,7 @@
         <v>660</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -9078,7 +9078,7 @@
         <v>58</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>661</v>
@@ -9090,10 +9090,10 @@
         <v>662</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>650</v>
@@ -9102,7 +9102,7 @@
         <v>663</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -9110,7 +9110,7 @@
         <v>58</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>66</v>
@@ -9122,10 +9122,10 @@
         <v>664</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>313</v>
+        <v>94</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>578</v>
@@ -9134,7 +9134,7 @@
         <v>665</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -9142,7 +9142,7 @@
         <v>58</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>666</v>
@@ -9154,10 +9154,10 @@
         <v>667</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>578</v>
@@ -9166,7 +9166,7 @@
         <v>668</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -9270,13 +9270,13 @@
         <v>670</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>228</v>
+        <v>321</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>235</v>
+        <v>88</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>671</v>
@@ -9290,7 +9290,7 @@
         <v>67</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>672</v>
@@ -9302,13 +9302,13 @@
         <v>673</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>398</v>
+        <v>220</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>674</v>
@@ -9334,13 +9334,13 @@
         <v>676</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>295</v>
+        <v>186</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>677</v>
@@ -9354,7 +9354,7 @@
         <v>67</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>678</v>
@@ -9366,7 +9366,7 @@
         <v>679</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>100</v>
@@ -9386,7 +9386,7 @@
         <v>67</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>681</v>
@@ -9398,7 +9398,7 @@
         <v>682</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>100</v>
@@ -9418,7 +9418,7 @@
         <v>67</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>684</v>
@@ -9430,10 +9430,10 @@
         <v>685</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>407</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>574</v>
@@ -9462,7 +9462,7 @@
         <v>688</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>407</v>
@@ -9482,7 +9482,7 @@
         <v>67</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>690</v>
@@ -9494,10 +9494,10 @@
         <v>691</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>189</v>
+        <v>407</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>574</v>
@@ -9514,7 +9514,7 @@
         <v>67</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>693</v>
@@ -9526,10 +9526,10 @@
         <v>694</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>313</v>
+        <v>94</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>574</v>
@@ -9558,10 +9558,10 @@
         <v>697</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>574</v>
@@ -9578,7 +9578,7 @@
         <v>67</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>699</v>
@@ -9590,10 +9590,10 @@
         <v>700</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>650</v>
@@ -9610,7 +9610,7 @@
         <v>67</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>702</v>
@@ -9622,7 +9622,7 @@
         <v>703</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>407</v>
@@ -9642,7 +9642,7 @@
         <v>67</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>705</v>
@@ -9654,7 +9654,7 @@
         <v>706</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>100</v>
@@ -9674,7 +9674,7 @@
         <v>67</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>708</v>
@@ -9686,13 +9686,13 @@
         <v>709</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>574</v>
+        <v>650</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>710</v>
@@ -9706,7 +9706,7 @@
         <v>67</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>711</v>
@@ -9718,10 +9718,10 @@
         <v>712</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>650</v>
@@ -9738,7 +9738,7 @@
         <v>67</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>714</v>
@@ -9750,13 +9750,13 @@
         <v>715</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>716</v>
@@ -9770,7 +9770,7 @@
         <v>67</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>717</v>
@@ -9782,13 +9782,13 @@
         <v>718</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>100</v>
+        <v>203</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>650</v>
+        <v>578</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>719</v>
@@ -9814,10 +9814,10 @@
         <v>721</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>650</v>
@@ -9846,7 +9846,7 @@
         <v>724</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>100</v>
@@ -9878,10 +9878,10 @@
         <v>727</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>650</v>
@@ -9898,7 +9898,7 @@
         <v>67</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>729</v>
@@ -9910,10 +9910,10 @@
         <v>730</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>228</v>
+        <v>321</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>650</v>
@@ -9930,7 +9930,7 @@
         <v>67</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>732</v>
@@ -9942,10 +9942,10 @@
         <v>733</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>650</v>
@@ -9962,7 +9962,7 @@
         <v>67</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>735</v>
@@ -9974,10 +9974,10 @@
         <v>736</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>578</v>
@@ -9994,7 +9994,7 @@
         <v>67</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>75</v>
@@ -10006,10 +10006,10 @@
         <v>738</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>313</v>
+        <v>94</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>578</v>
@@ -10026,7 +10026,7 @@
         <v>67</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>740</v>
@@ -10038,10 +10038,10 @@
         <v>741</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>742</v>
@@ -10058,7 +10058,7 @@
         <v>67</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>744</v>
@@ -10070,10 +10070,10 @@
         <v>745</v>
       </c>
       <c r="F27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>742</v>
@@ -10090,7 +10090,7 @@
         <v>67</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>747</v>
@@ -10102,10 +10102,10 @@
         <v>748</v>
       </c>
       <c r="F28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>749</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -9,29 +9,29 @@
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
-    <sheet name="만영" sheetId="3" r:id="rId3"/>
-    <sheet name="든솔" sheetId="4" r:id="rId4"/>
-    <sheet name="지존길드" sheetId="5" r:id="rId5"/>
-    <sheet name="따숨" sheetId="6" r:id="rId6"/>
-    <sheet name="바텀" sheetId="7" r:id="rId7"/>
+    <sheet name="바텀" sheetId="3" r:id="rId3"/>
+    <sheet name="지존길드" sheetId="4" r:id="rId4"/>
+    <sheet name="든솔" sheetId="5" r:id="rId5"/>
+    <sheet name="만영" sheetId="6" r:id="rId6"/>
+    <sheet name="따숨" sheetId="7" r:id="rId7"/>
     <sheet name="더위사냥" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">더위사냥!$A$1:$J$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">든솔!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">따숨!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">만영!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">바텀!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">든솔!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">따숨!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">만영!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">바텀!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">지존길드!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">지존길드!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2234" uniqueCount="755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2224" uniqueCount="752">
   <si>
     <t>guild_name</t>
   </si>
@@ -84,7 +84,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>426</t>
+    <t>428</t>
   </si>
   <si>
     <t>13위</t>
@@ -96,7 +96,7 @@
     <t>29명</t>
   </si>
   <si>
-    <t>4경 9072조 6890억 7407만</t>
+    <t>4경 9478조 6064억 3410만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -105,7 +105,82 @@
     <t>자유이용껀</t>
   </si>
   <si>
-    <t>2026.09.18</t>
+    <t>2026.09.19</t>
+  </si>
+  <si>
+    <t>바텀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%94%ED%85%80</t>
+  </si>
+  <si>
+    <t>Scania 29</t>
+  </si>
+  <si>
+    <t>435</t>
+  </si>
+  <si>
+    <t>14위</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>4경 7416조 1386억 8900만</t>
+  </si>
+  <si>
+    <t>바텀에서 캐리하실분! (톡방필수)</t>
+  </si>
+  <si>
+    <t>딜폿</t>
+  </si>
+  <si>
+    <t>지존길드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A7%80%EC%A1%B4%EA%B8%B8%EB%93%9C</t>
+  </si>
+  <si>
+    <t>Scania 4</t>
+  </si>
+  <si>
+    <t>440</t>
+  </si>
+  <si>
+    <t>11위</t>
+  </si>
+  <si>
+    <t>4경 6445조 2840억 90만</t>
+  </si>
+  <si>
+    <t>지존길드 공지용 오픈채팅 필수참여입니다.</t>
+  </si>
+  <si>
+    <t>지존순찌</t>
+  </si>
+  <si>
+    <t>든솔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%93%A0%EC%86%94</t>
+  </si>
+  <si>
+    <t>Scania 13</t>
+  </si>
+  <si>
+    <t>433</t>
+  </si>
+  <si>
+    <t>10위</t>
+  </si>
+  <si>
+    <t>4경 7933조 6785억 9956만</t>
+  </si>
+  <si>
+    <t>투력 300조이상,미접 1일 추방,매일 무료 업글필수,길드 컨텐츠 필수 참여,공지방 필수 참여, 게임에 열정있으신 분 환영/가입문의 현뇸.강필구.v박효신v</t>
+  </si>
+  <si>
+    <t>현뇸</t>
   </si>
   <si>
     <t>만영</t>
@@ -117,13 +192,13 @@
     <t>Scania 23</t>
   </si>
   <si>
-    <t>451</t>
+    <t>453</t>
   </si>
   <si>
     <t>8위</t>
   </si>
   <si>
-    <t>4경 2530조 1804억 6169만</t>
+    <t>4경 2629조 6634억 4875만</t>
   </si>
   <si>
     <t>가입신청 문의주세요.(정기유무 / 무곽)</t>
@@ -132,57 +207,6 @@
     <t>정기유무</t>
   </si>
   <si>
-    <t>든솔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%93%A0%EC%86%94</t>
-  </si>
-  <si>
-    <t>Scania 13</t>
-  </si>
-  <si>
-    <t>433</t>
-  </si>
-  <si>
-    <t>10위</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>4경 7158조 1930억 258만</t>
-  </si>
-  <si>
-    <t>투력 300조이상,미접 1일 추방,매일 무료 업글필수,길드 컨텐츠 필수 참여,공지방 필수 참여, 게임에 열정있으신 분 환영/가입문의 현뇸.강필구.v박효신v</t>
-  </si>
-  <si>
-    <t>현뇸</t>
-  </si>
-  <si>
-    <t>지존길드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A7%80%EC%A1%B4%EA%B8%B8%EB%93%9C</t>
-  </si>
-  <si>
-    <t>Scania 4</t>
-  </si>
-  <si>
-    <t>440</t>
-  </si>
-  <si>
-    <t>11위</t>
-  </si>
-  <si>
-    <t>4경 5576조 5195억 8399만</t>
-  </si>
-  <si>
-    <t>지존길드 공지용 오픈채팅 필수참여입니다.</t>
-  </si>
-  <si>
-    <t>지존순찌</t>
-  </si>
-  <si>
     <t>따숨</t>
   </si>
   <si>
@@ -192,13 +216,13 @@
     <t>Scania 3</t>
   </si>
   <si>
-    <t>463</t>
+    <t>460</t>
   </si>
   <si>
     <t>15위</t>
   </si>
   <si>
-    <t>4경 583조 5038억 2994만</t>
+    <t>4경 1275조 6508억 5891만</t>
   </si>
   <si>
     <t>길드건물/길드콘텐츠/길드톡방 필수이며 같이 재밌게 게임해요! 가입문의 김가원,호르몬,뚜징,김슴줌1에게 귓주세요</t>
@@ -207,30 +231,6 @@
     <t>호르몬</t>
   </si>
   <si>
-    <t>바텀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%94%ED%85%80</t>
-  </si>
-  <si>
-    <t>Scania 29</t>
-  </si>
-  <si>
-    <t>432</t>
-  </si>
-  <si>
-    <t>14위</t>
-  </si>
-  <si>
-    <t>4경 7161조 296억 2491만</t>
-  </si>
-  <si>
-    <t>바텀에서 캐리하실분! (톡방필수)</t>
-  </si>
-  <si>
-    <t>딜폿</t>
-  </si>
-  <si>
     <t>더위사냥</t>
   </si>
   <si>
@@ -240,7 +240,7 @@
     <t>Scania 50</t>
   </si>
   <si>
-    <t>442</t>
+    <t>438</t>
   </si>
   <si>
     <t>4위</t>
@@ -252,7 +252,7 @@
     <t>27명</t>
   </si>
   <si>
-    <t>4경 5413조 9919억 4137만</t>
+    <t>4경 6786조 8045억 8500만</t>
   </si>
   <si>
     <t>전투력 150 이상 용사님 언제든 환영합니다/궁금하신점 언제든 밍키비키 귓주세요/ 1일 접속,길드건물 업그레이드 필수/길드 콘텐츠 참가 필수/ 꾸준히 함께하실 용사님들 대환영합니다</t>
@@ -303,7 +303,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>8558조 231억 7162만</t>
+    <t>8570조 3175억 8447만</t>
   </si>
   <si>
     <t>2</t>
@@ -336,7 +336,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>4268조 343억 8957만</t>
+    <t>4344조 479억 3534만</t>
   </si>
   <si>
     <t>4</t>
@@ -396,7 +396,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>2794조 5874억 3077만</t>
+    <t>2838조 8556억 6943만</t>
   </si>
   <si>
     <t>8</t>
@@ -408,7 +408,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>2062조 5674억 3493만</t>
+    <t>2125조 1120억 4939만</t>
   </si>
   <si>
     <t>9</t>
@@ -432,7 +432,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
   </si>
   <si>
-    <t>1576조 8511억 519만</t>
+    <t>1606조 9335억 6930만</t>
   </si>
   <si>
     <t>11</t>
@@ -459,49 +459,49 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
   </si>
   <si>
+    <t>1178조 4809억 5968만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>불보독지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>1101조 795억 6833만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>채무조정</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
+  </si>
+  <si>
+    <t>972조 2153억 1957만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>우후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>1178조 4809억 5968만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>불보독지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>1045조 9073억 3017만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>채무조정</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
-  </si>
-  <si>
-    <t>972조 2153억 1957만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>우후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
-  </si>
-  <si>
-    <t>942조 6419억 6063만</t>
+    <t>971조 2607억 4284만</t>
   </si>
   <si>
     <t>16</t>
@@ -516,7 +516,7 @@
     <t>섀도어</t>
   </si>
   <si>
-    <t>925조 2980억 4556만</t>
+    <t>926조 4709억 657만</t>
   </si>
   <si>
     <t>17</t>
@@ -576,100 +576,100 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
+    <t>485조 354억 533만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>플로우00</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
+  </si>
+  <si>
+    <t>391조 5629억 3601만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>384조 814억 6223만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>솔인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>356조 443억 1139만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>박준우2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
+  </si>
+  <si>
     <t>109</t>
   </si>
   <si>
-    <t>460조 1881억 9462만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>플로우00</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
-  </si>
-  <si>
-    <t>386조 4288억 9793만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>372조 6896억 8563만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>솔인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>354조 6601억 9194만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>박준우2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
-  </si>
-  <si>
-    <t>328조 1595억 1568만</t>
+    <t>329조 8887억 57만</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
+    <t>꼬북빵야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
+  </si>
+  <si>
+    <t>240조 453억 6127만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>226조 9385억 6222만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
     <t>아르미느</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>222조 5602억 4740만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>여눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
-  </si>
-  <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>215조 3909억 7501만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>꼬북빵야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
-  </si>
-  <si>
-    <t>206조 9922억 631만</t>
+    <t>224조 7388억 729만</t>
   </si>
   <si>
     <t>29</t>
@@ -684,7 +684,820 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>194조 4027억 9180만</t>
+    <t>198조 8873억 6281만</t>
+  </si>
+  <si>
+    <t>전액할부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%95%A1%ED%95%A0%EB%B6%80</t>
+  </si>
+  <si>
+    <t>8468조 4686억 7667만</t>
+  </si>
+  <si>
+    <t>사랑향</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%96%A5</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>6527조 2315억 1292만</t>
+  </si>
+  <si>
+    <t>힐폿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%ED%8F%BF</t>
+  </si>
+  <si>
+    <t>4145조 1069억 1568만</t>
+  </si>
+  <si>
+    <t>례전</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%80%EC%A0%84</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>3374조 618억 7162만</t>
+  </si>
+  <si>
+    <t>숭타이준</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%ED%83%80%EC%9D%B4%EC%A4%80</t>
+  </si>
+  <si>
+    <t>2267조 4656억 338만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%9C%ED%8F%BF</t>
+  </si>
+  <si>
+    <t>2069조 6682억 9082만</t>
+  </si>
+  <si>
+    <t>뮬이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AE%AC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1498조 4072억 7555만</t>
+  </si>
+  <si>
+    <t>77S2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=77S2</t>
+  </si>
+  <si>
+    <t>1444조 8641억 2882만</t>
+  </si>
+  <si>
+    <t>지존빵수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%B5%EC%88%98</t>
+  </si>
+  <si>
+    <t>1344조 9709억 5378만</t>
+  </si>
+  <si>
+    <t>문제적남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EC%A0%9C%EC%A0%81%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>1250조 9156억 7530만</t>
+  </si>
+  <si>
+    <t>탱폿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%8F%BF</t>
+  </si>
+  <si>
+    <t>1240조 4023억 3426만</t>
+  </si>
+  <si>
+    <t>야키산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%82%A4%EC%82%B0</t>
+  </si>
+  <si>
+    <t>1239조 4722억 2107만</t>
+  </si>
+  <si>
+    <t>우즈2텐겐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%A6%882%ED%85%90%EA%B2%90</t>
+  </si>
+  <si>
+    <t>1216조 1916억 2414만</t>
+  </si>
+  <si>
+    <t>아이리쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EB%A6%AC%EC%89%AC</t>
+  </si>
+  <si>
+    <t>1201조 5056억 9678만</t>
+  </si>
+  <si>
+    <t>독스케</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%8A%A4%EC%BC%80</t>
+  </si>
+  <si>
+    <t>1064조 4633억 8858만</t>
+  </si>
+  <si>
+    <t>우월별하</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9B%94%EB%B3%84%ED%95%98</t>
+  </si>
+  <si>
+    <t>922조 8577억 2728만</t>
+  </si>
+  <si>
+    <t>화둥에불낸년</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EB%91%A5%EC%97%90%EB%B6%88%EB%82%B8%EB%85%84</t>
+  </si>
+  <si>
+    <t>864조 4672억 2142만</t>
+  </si>
+  <si>
+    <t>기똥찬벌레</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%98%A5%EC%B0%AC%EB%B2%8C%EB%A0%88</t>
+  </si>
+  <si>
+    <t>717조 5782억 3399만</t>
+  </si>
+  <si>
+    <t>JJuna</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=JJuna</t>
+  </si>
+  <si>
+    <t>711조 601억 6569만</t>
+  </si>
+  <si>
+    <t>이게용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B2%8C%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>694조 6475억 554만</t>
+  </si>
+  <si>
+    <t>난센</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EC%84%BC</t>
+  </si>
+  <si>
+    <t>662조 680억 9838만</t>
+  </si>
+  <si>
+    <t>매화로이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%ED%99%94%EB%A1%9C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>649조 2631억 5583만</t>
+  </si>
+  <si>
+    <t>콜리셰마드르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%9C%EB%A6%AC%EC%85%B0%EB%A7%88%EB%93%9C%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>640조 4995억 9917만</t>
+  </si>
+  <si>
+    <t>퇴근이마렵다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%87%B4%EA%B7%BC%EC%9D%B4%EB%A7%88%EB%A0%B5%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>552조 3852억 676만</t>
+  </si>
+  <si>
+    <t>구도류</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%8F%84%EB%A5%98</t>
+  </si>
+  <si>
+    <t>526조 9101억 9078만</t>
+  </si>
+  <si>
+    <t>유채아버지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%B1%84%EC%95%84%EB%B2%84%EC%A7%80</t>
+  </si>
+  <si>
+    <t>484조 1099억 9114만</t>
+  </si>
+  <si>
+    <t>에프람</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%ED%94%84%EB%9E%8C</t>
+  </si>
+  <si>
+    <t>473조 8921억 7583만</t>
+  </si>
+  <si>
+    <t>조단23</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%8B%A823</t>
+  </si>
+  <si>
+    <t>456조 6055억 5640만</t>
+  </si>
+  <si>
+    <t>아콩린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BD%A9%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>432조 1699억 4429만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>별루루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A3%A8%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>274조 4277억 4696만</t>
+  </si>
+  <si>
+    <t>지존쫀파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>6757조 5035억 879만</t>
+  </si>
+  <si>
+    <t>협의</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%91%EC%9D%98</t>
+  </si>
+  <si>
+    <t>4158조 8546억 7008만</t>
+  </si>
+  <si>
+    <t>포항엄석대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
+  </si>
+  <si>
+    <t>3872조 369억 891만</t>
+  </si>
+  <si>
+    <t>타개</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
+  </si>
+  <si>
+    <t>2495조 7634억 7223만</t>
+  </si>
+  <si>
+    <t>포항가자미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>2269조 2449억 6902만</t>
+  </si>
+  <si>
+    <t>기뽐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%BD%90</t>
+  </si>
+  <si>
+    <t>2259조 1663억 8382만</t>
+  </si>
+  <si>
+    <t>지존빼앙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
+  </si>
+  <si>
+    <t>2004조 2057억 1924만</t>
+  </si>
+  <si>
+    <t>변신술사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
+  </si>
+  <si>
+    <t>1888조 3627억 818만</t>
+  </si>
+  <si>
+    <t>댜니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>1739조 5479억 2768만</t>
+  </si>
+  <si>
+    <t>뿡쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
+  </si>
+  <si>
+    <t>1707조 2709억 6232만</t>
+  </si>
+  <si>
+    <t>온백</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
+  </si>
+  <si>
+    <t>1491조 2311억 2507만</t>
+  </si>
+  <si>
+    <t>파울</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
+  </si>
+  <si>
+    <t>1425조 4762억 1692만</t>
+  </si>
+  <si>
+    <t>엘르가든</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
+  </si>
+  <si>
+    <t>1400조 9926억 8431만</t>
+  </si>
+  <si>
+    <t>마카롱롱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
+  </si>
+  <si>
+    <t>1391조 2010억 3776만</t>
+  </si>
+  <si>
+    <t>짱잘자쿨냥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%9E%98%EC%9E%90%EC%BF%A8%EB%83%A5</t>
+  </si>
+  <si>
+    <t>1027조 6078억 1748만</t>
+  </si>
+  <si>
+    <t>대좀이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>978조 3640억 5389만</t>
+  </si>
+  <si>
+    <t>모짜리코베르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>956조 6204억 8172만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
+  </si>
+  <si>
+    <t>951조 2060억 9725만</t>
+  </si>
+  <si>
+    <t>김허덕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
+  </si>
+  <si>
+    <t>882조 7278억 5282만</t>
+  </si>
+  <si>
+    <t>마갤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
+  </si>
+  <si>
+    <t>826조 8046억 9936만</t>
+  </si>
+  <si>
+    <t>기본이리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>824조 2609억 4999만</t>
+  </si>
+  <si>
+    <t>냐은</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EC%9D%80</t>
+  </si>
+  <si>
+    <t>810조 1567억 9854만</t>
+  </si>
+  <si>
+    <t>오옹나이스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%B9%EB%82%98%EC%9D%B4%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>787조 4728억 4596만</t>
+  </si>
+  <si>
+    <t>전산봉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%B0%EB%B4%89</t>
+  </si>
+  <si>
+    <t>671조 6340억 2972만</t>
+  </si>
+  <si>
+    <t>Doham</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Doham</t>
+  </si>
+  <si>
+    <t>627조 8627억 9090만</t>
+  </si>
+  <si>
+    <t>고숨도칭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
+  </si>
+  <si>
+    <t>584조 3143억 9077만</t>
+  </si>
+  <si>
+    <t>태코찡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
+  </si>
+  <si>
+    <t>547조 9327억 8104만</t>
+  </si>
+  <si>
+    <t>유플러스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%94%8C%EB%9F%AC%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>482조 8831억 8288만</t>
+  </si>
+  <si>
+    <t>진성팔퀴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%84%B1%ED%8C%94%ED%80%B4</t>
+  </si>
+  <si>
+    <t>347조 5732억 9309만</t>
+  </si>
+  <si>
+    <t>빵후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%ED%9B%84</t>
+  </si>
+  <si>
+    <t>277조 36억 4103만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EB%87%B8</t>
+  </si>
+  <si>
+    <t>5203조 5412억 3960만</t>
+  </si>
+  <si>
+    <t>손챠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%90%EC%B1%A0</t>
+  </si>
+  <si>
+    <t>4575조 5000억 9644만</t>
+  </si>
+  <si>
+    <t>GOD날두</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=GOD%EB%82%A0%EB%91%90</t>
+  </si>
+  <si>
+    <t>3907조 618억 9021만</t>
+  </si>
+  <si>
+    <t>강필구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%84%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>3886조 2944억 7368만</t>
+  </si>
+  <si>
+    <t>알배기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%8C%EB%B0%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>3214조 2193억 3893만</t>
+  </si>
+  <si>
+    <t>러브포티</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%B8%8C%ED%8F%AC%ED%8B%B0</t>
+  </si>
+  <si>
+    <t>2525조 3900억 9711만</t>
+  </si>
+  <si>
+    <t>테이킷슬로우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%85%8C%EC%9D%B4%ED%82%B7%EC%8A%AC%EB%A1%9C%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>2367조 6141억 542만</t>
+  </si>
+  <si>
+    <t>주요엘농산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%9A%94%EC%97%98%EB%86%8D%EC%82%B0</t>
+  </si>
+  <si>
+    <t>2128조 4643억 3752만</t>
+  </si>
+  <si>
+    <t>하찌바리이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B0%8C%EB%B0%94%EB%A6%AC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2120조 5849억 6712만</t>
+  </si>
+  <si>
+    <t>88치킨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=88%EC%B9%98%ED%82%A8</t>
+  </si>
+  <si>
+    <t>1621조 3630억 3601만</t>
+  </si>
+  <si>
+    <t>탕비실도우미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%95%EB%B9%84%EC%8B%A4%EB%8F%84%EC%9A%B0%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>1449조 9858억 2106만</t>
+  </si>
+  <si>
+    <t>Darken</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Darken</t>
+  </si>
+  <si>
+    <t>1428조 2881억 4391만</t>
+  </si>
+  <si>
+    <t>서늘한그늘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%8A%98%ED%95%9C%EA%B7%B8%EB%8A%98</t>
+  </si>
+  <si>
+    <t>1402조 805억 8만</t>
+  </si>
+  <si>
+    <t>하이하로하라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9D%B4%ED%95%98%EB%A1%9C%ED%95%98%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>1123조 1256억 7302만</t>
+  </si>
+  <si>
+    <t>차보이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EB%B3%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1005조 6484억 9494만</t>
+  </si>
+  <si>
+    <t>도레오</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%88%EC%98%A4</t>
+  </si>
+  <si>
+    <t>985조 3833억 8106만</t>
+  </si>
+  <si>
+    <t>여릿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%A6%BF</t>
+  </si>
+  <si>
+    <t>970조 8021억 203만</t>
+  </si>
+  <si>
+    <t>초읍사나이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%8D%EC%82%AC%EB%82%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>898조 9050억 2855만</t>
+  </si>
+  <si>
+    <t>v박효신v</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=v%EB%B0%95%ED%9A%A8%EC%8B%A0v</t>
+  </si>
+  <si>
+    <t>877조 8674억 153만</t>
+  </si>
+  <si>
+    <t>시간이돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B0%84%EC%9D%B4%EB%8F%88</t>
+  </si>
+  <si>
+    <t>818조 3610억 7891만</t>
+  </si>
+  <si>
+    <t>고으농</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%9C%BC%EB%86%8D</t>
+  </si>
+  <si>
+    <t>709조 2564억 5573만</t>
+  </si>
+  <si>
+    <t>영구짱구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%81%EA%B5%AC%EC%A7%B1%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>708조 6531억 8974만</t>
+  </si>
+  <si>
+    <t>다둉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>655조 928억 6795만</t>
+  </si>
+  <si>
+    <t>도사랑화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%82%AC%EB%9E%91%ED%99%94</t>
+  </si>
+  <si>
+    <t>599조 3582억 8395만</t>
+  </si>
+  <si>
+    <t>뜌미누</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9C%8C%EB%AF%B8%EB%88%84</t>
+  </si>
+  <si>
+    <t>576조 4166억 7025만</t>
+  </si>
+  <si>
+    <t>발진</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%9C%EC%A7%84</t>
+  </si>
+  <si>
+    <t>559조 8595억 2848만</t>
+  </si>
+  <si>
+    <t>익뇸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%87%B8</t>
+  </si>
+  <si>
+    <t>469조 5981억 3531만</t>
+  </si>
+  <si>
+    <t>하엘이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%97%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>390조 8622억 7970만</t>
+  </si>
+  <si>
+    <t>나는배불러요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%8A%94%EB%B0%B0%EB%B6%88%EB%9F%AC%EC%9A%94</t>
+  </si>
+  <si>
+    <t>380조 861억 5166만</t>
+  </si>
+  <si>
+    <t>아리미쿵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A6%AC%EB%AF%B8%EC%BF%B5</t>
+  </si>
+  <si>
+    <t>374조 138억 2953만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EA%B8%B0%EC%9C%A0%EB%AC%B4</t>
@@ -735,9 +1548,6 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%85%8C%ED%86%A0%EC%9D%BC%EB%82%A8</t>
   </si>
   <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
     <t>1679조 550억 6110만</t>
   </si>
   <si>
@@ -747,7 +1557,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EA%BD%81%EB%83%89%EB%B2%95</t>
   </si>
   <si>
-    <t>1587조 2460억 5224만</t>
+    <t>1592조 4211억 6015만</t>
   </si>
   <si>
     <t>라쥬르</t>
@@ -765,7 +1575,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EA%B8%B0%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>1292조 1441억 1279만</t>
+    <t>1294조 966억 5266만</t>
   </si>
   <si>
     <t>브네</t>
@@ -774,7 +1584,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%84%A4</t>
   </si>
   <si>
-    <t>1197조 672억 1023만</t>
+    <t>1228조 4840억 9179만</t>
   </si>
   <si>
     <t>빙율</t>
@@ -783,7 +1593,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%99%EC%9C%A8</t>
   </si>
   <si>
-    <t>1001조 5912억 7083만</t>
+    <t>1003조 4784억 1839만</t>
   </si>
   <si>
     <t>33세배장호</t>
@@ -810,7 +1620,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%81%EC%A0%B9%EC%A0%81</t>
   </si>
   <si>
-    <t>772조 6540억 6836만</t>
+    <t>782조 8871억 195만</t>
   </si>
   <si>
     <t>최빵쭈</t>
@@ -828,9 +1638,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EB%AF%B8%EC%9E%88%EA%B2%8C%EB%86%80%EB%9E%98</t>
   </si>
   <si>
-    <t>캡틴</t>
-  </si>
-  <si>
     <t>693조 8487억 9863만</t>
   </si>
   <si>
@@ -840,7 +1647,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%88%EB%B2%BD%EB%86%80%EB%9E%98</t>
   </si>
   <si>
-    <t>667조 6256억 2612만</t>
+    <t>672조 6764억 5352만</t>
   </si>
   <si>
     <t>가덴</t>
@@ -849,7 +1656,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%8D%B4</t>
   </si>
   <si>
-    <t>658조 7298억 4446만</t>
+    <t>671조 304억 1814만</t>
   </si>
   <si>
     <t>타뤽</t>
@@ -858,7 +1665,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%A4%BD</t>
   </si>
   <si>
-    <t>654조 5879억 6291만</t>
+    <t>656조 4235억 6293만</t>
   </si>
   <si>
     <t>무르스</t>
@@ -867,7 +1674,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%A5%B4%EC%8A%A4</t>
   </si>
   <si>
-    <t>550조 9943억 2132만</t>
+    <t>551조 750억 2587만</t>
   </si>
   <si>
     <t>채황새</t>
@@ -885,7 +1692,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%AC%EC%83%B7</t>
   </si>
   <si>
-    <t>444조 5177억 1036만</t>
+    <t>445조 1131억 3507만</t>
   </si>
   <si>
     <t>럭키루키</t>
@@ -894,7 +1701,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%AD%ED%82%A4%EB%A3%A8%ED%82%A4</t>
   </si>
   <si>
-    <t>441조 6478억 9292만</t>
+    <t>442조 4965억 5609만</t>
   </si>
   <si>
     <t>박도란</t>
@@ -921,7 +1728,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
   </si>
   <si>
-    <t>372조 1824억 4173만</t>
+    <t>375조 2668억 3844만</t>
   </si>
   <si>
     <t>뿌앵뿌앵</t>
@@ -930,7 +1737,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EC%95%B5%EB%BF%8C%EC%95%B5</t>
   </si>
   <si>
-    <t>299조 649억 3921만</t>
+    <t>319조 6901억 743만</t>
   </si>
   <si>
     <t>냥홍이</t>
@@ -948,1105 +1755,298 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EB%B9%B5%EC%AD%88</t>
   </si>
   <si>
-    <t>신궁</t>
+    <t>217조 8780억 2602만</t>
+  </si>
+  <si>
+    <t>꺄꽁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BA%84%EA%BD%81</t>
+  </si>
+  <si>
+    <t>6901조 9733억 8619만</t>
+  </si>
+  <si>
+    <t>별쌥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A5</t>
+  </si>
+  <si>
+    <t>5132조 1321억 7494만</t>
+  </si>
+  <si>
+    <t>진욱이에요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9A%B1%EC%9D%B4%EC%97%90%EC%9A%94</t>
+  </si>
+  <si>
+    <t>3955조 6580억 3551만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A5%B4%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>2836조 4957억 4786만</t>
+  </si>
+  <si>
+    <t>낭만황금망치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%ED%99%A9%EA%B8%88%EB%A7%9D%EC%B9%98</t>
+  </si>
+  <si>
+    <t>2725조 47억 9055만</t>
+  </si>
+  <si>
+    <t>김슴줌1</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%8A%B4%EC%A4%8C1</t>
+  </si>
+  <si>
+    <t>2463조 8467억 9186만</t>
+  </si>
+  <si>
+    <t>천달</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EB%8B%AC</t>
+  </si>
+  <si>
+    <t>2141조 9784억 7690만</t>
+  </si>
+  <si>
+    <t>호두와감자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%91%90%EC%99%80%EA%B0%90%EC%9E%90</t>
+  </si>
+  <si>
+    <t>2096조 549억 4046만</t>
+  </si>
+  <si>
+    <t>쿠댜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EB%8C%9C</t>
+  </si>
+  <si>
+    <t>1782조 5964억 7721만</t>
+  </si>
+  <si>
+    <t>뚜징</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EC%A7%95</t>
+  </si>
+  <si>
+    <t>1477조 1901억 1245만</t>
+  </si>
+  <si>
+    <t>활용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%9C%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>1464조 2603억 2227만</t>
+  </si>
+  <si>
+    <t>별곡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EA%B3%A1</t>
+  </si>
+  <si>
+    <t>891조 5989억 2514만</t>
+  </si>
+  <si>
+    <t>턍ol</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%84%8Dol</t>
+  </si>
+  <si>
+    <t>663조 7250억 2403만</t>
+  </si>
+  <si>
+    <t>게렬곰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%EB%A0%AC%EA%B3%B0</t>
+  </si>
+  <si>
+    <t>654조 1115억 5671만</t>
+  </si>
+  <si>
+    <t>까쿠미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EC%BF%A0%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>646조 6992억 8304만</t>
+  </si>
+  <si>
+    <t>동래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%9E%98</t>
+  </si>
+  <si>
+    <t>640조 1455억 8439만</t>
+  </si>
+  <si>
+    <t>띠우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%A0%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>606조 7449억 8996만</t>
+  </si>
+  <si>
+    <t>별쌤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A4</t>
+  </si>
+  <si>
+    <t>605조 135억 1888만</t>
+  </si>
+  <si>
+    <t>초이레</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%B4%EB%A0%88</t>
+  </si>
+  <si>
+    <t>483조 5947억 1837만</t>
+  </si>
+  <si>
+    <t>민족고대감자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%A1%B1%EA%B3%A0%EB%8C%80%EA%B0%90%EC%9E%90</t>
+  </si>
+  <si>
+    <t>447조 5787억 6359만</t>
+  </si>
+  <si>
+    <t>승아의하루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%EC%95%84%EC%9D%98%ED%95%98%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>419조 8392억 5458만</t>
+  </si>
+  <si>
+    <t>끄챰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%81%84%EC%B1%B0</t>
+  </si>
+  <si>
+    <t>412조 7920억 6036만</t>
+  </si>
+  <si>
+    <t>쿠까미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EA%B9%8C%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>407조 1167억 2176만</t>
+  </si>
+  <si>
+    <t>택Ol</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%9DOl</t>
+  </si>
+  <si>
+    <t>281조 8647억 7498만</t>
+  </si>
+  <si>
+    <t>08217</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=08217</t>
+  </si>
+  <si>
+    <t>275조 3869억 9547만</t>
+  </si>
+  <si>
+    <t>툼스데이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%88%BC%EC%8A%A4%EB%8D%B0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>246조 9543억 8317만</t>
+  </si>
+  <si>
+    <t>왕단단이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EB%8B%A8%EB%8B%A8%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>236조 4461억 1753만</t>
+  </si>
+  <si>
+    <t>루이쥔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%9D%B4%EC%A5%94</t>
+  </si>
+  <si>
+    <t>219조 8367억 8039만</t>
+  </si>
+  <si>
+    <t>꾸현</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%ED%98%84</t>
+  </si>
+  <si>
+    <t>88조 3966억 6293만</t>
+  </si>
+  <si>
+    <t>달갸뤼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EA%B0%B8%EB%A4%BC</t>
+  </si>
+  <si>
+    <t>70조 6134억 8727만</t>
+  </si>
+  <si>
+    <t>교주만두</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%90%EC%A3%BC%EB%A7%8C%EB%91%90</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>4경 5919조 3484억 4327만</t>
+  </si>
+  <si>
+    <t>할바이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%B0%94%EC%9D%B4</t>
   </si>
   <si>
     <t>107</t>
   </si>
   <si>
-    <t>213조 4811억 791만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>zzingco</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=zzingco</t>
-  </si>
-  <si>
-    <t>198조 5322억 1400만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EB%87%B8</t>
-  </si>
-  <si>
-    <t>5203조 5412억 3960만</t>
-  </si>
-  <si>
-    <t>손챠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%90%EC%B1%A0</t>
-  </si>
-  <si>
-    <t>4575조 5000억 9644만</t>
-  </si>
-  <si>
-    <t>GOD날두</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=GOD%EB%82%A0%EB%91%90</t>
-  </si>
-  <si>
-    <t>3904조 5928억 3449만</t>
-  </si>
-  <si>
-    <t>강필구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%84%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>3886조 2944억 7368만</t>
-  </si>
-  <si>
-    <t>알배기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%8C%EB%B0%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>3214조 2193억 3893만</t>
-  </si>
-  <si>
-    <t>러브포티</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%B8%8C%ED%8F%AC%ED%8B%B0</t>
-  </si>
-  <si>
-    <t>2476조 7754억 5692만</t>
-  </si>
-  <si>
-    <t>테이킷슬로우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%85%8C%EC%9D%B4%ED%82%B7%EC%8A%AC%EB%A1%9C%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>2367조 6141억 542만</t>
-  </si>
-  <si>
-    <t>하찌바리이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B0%8C%EB%B0%94%EB%A6%AC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2120조 5849억 6712만</t>
-  </si>
-  <si>
-    <t>주요엘농산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%9A%94%EC%97%98%EB%86%8D%EC%82%B0</t>
-  </si>
-  <si>
-    <t>2108조 9859억 3747만</t>
-  </si>
-  <si>
-    <t>88치킨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=88%EC%B9%98%ED%82%A8</t>
-  </si>
-  <si>
-    <t>1511조 3601억 3371만</t>
-  </si>
-  <si>
-    <t>탕비실도우미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%95%EB%B9%84%EC%8B%A4%EB%8F%84%EC%9A%B0%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>1449조 9858억 2106만</t>
-  </si>
-  <si>
-    <t>Darken</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Darken</t>
-  </si>
-  <si>
-    <t>1422조 9623억 7266만</t>
-  </si>
-  <si>
-    <t>서늘한그늘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%8A%98%ED%95%9C%EA%B7%B8%EB%8A%98</t>
-  </si>
-  <si>
-    <t>1193조 4587억 5172만</t>
-  </si>
-  <si>
-    <t>하이하로하라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9D%B4%ED%95%98%EB%A1%9C%ED%95%98%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>1123조 1256억 7302만</t>
-  </si>
-  <si>
-    <t>차보이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EB%B3%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1002조 2468억 8962만</t>
-  </si>
-  <si>
-    <t>여릿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%A6%BF</t>
-  </si>
-  <si>
-    <t>970조 8021억 203만</t>
-  </si>
-  <si>
-    <t>v박효신v</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=v%EB%B0%95%ED%9A%A8%EC%8B%A0v</t>
-  </si>
-  <si>
-    <t>877조 8674억 153만</t>
-  </si>
-  <si>
-    <t>초읍사나이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%8D%EC%82%AC%EB%82%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>863조 6528억 8432만</t>
-  </si>
-  <si>
-    <t>시간이돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B0%84%EC%9D%B4%EB%8F%88</t>
-  </si>
-  <si>
-    <t>818조 3610억 7891만</t>
-  </si>
-  <si>
-    <t>고으농</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%9C%BC%EB%86%8D</t>
-  </si>
-  <si>
-    <t>709조 2564억 5573만</t>
-  </si>
-  <si>
-    <t>영구짱구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%81%EA%B5%AC%EC%A7%B1%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>708조 6531억 8974만</t>
-  </si>
-  <si>
-    <t>도레오</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%88%EC%98%A4</t>
-  </si>
-  <si>
-    <t>687조 9142억 124만</t>
-  </si>
-  <si>
-    <t>다둉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>655조 928억 6795만</t>
-  </si>
-  <si>
-    <t>도사랑화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%82%AC%EB%9E%91%ED%99%94</t>
-  </si>
-  <si>
-    <t>598조 9913억 4613만</t>
-  </si>
-  <si>
-    <t>뜌미누</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9C%8C%EB%AF%B8%EB%88%84</t>
-  </si>
-  <si>
-    <t>576조 4166억 7025만</t>
-  </si>
-  <si>
-    <t>발진</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%9C%EC%A7%84</t>
-  </si>
-  <si>
-    <t>559조 8595억 2848만</t>
-  </si>
-  <si>
-    <t>익뇸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%87%B8</t>
-  </si>
-  <si>
-    <t>469조 5981억 3531만</t>
-  </si>
-  <si>
-    <t>나는배불러요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%8A%94%EB%B0%B0%EB%B6%88%EB%9F%AC%EC%9A%94</t>
-  </si>
-  <si>
-    <t>373조 936억 7624만</t>
-  </si>
-  <si>
-    <t>아리미쿵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A6%AC%EB%AF%B8%EC%BF%B5</t>
-  </si>
-  <si>
-    <t>364조 8123억 9912만</t>
-  </si>
-  <si>
-    <t>하엘이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%97%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>362조 5729억 7362만</t>
-  </si>
-  <si>
-    <t>지존쫀파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>6757조 5035억 879만</t>
-  </si>
-  <si>
-    <t>협의</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%91%EC%9D%98</t>
-  </si>
-  <si>
-    <t>4151조 7828억 7756만</t>
-  </si>
-  <si>
-    <t>포항엄석대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
-  </si>
-  <si>
-    <t>3857조 9291억 1450만</t>
-  </si>
-  <si>
-    <t>타개</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
-  </si>
-  <si>
-    <t>2486조 9079억 1586만</t>
-  </si>
-  <si>
-    <t>포항가자미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>2263조 1140억 8844만</t>
-  </si>
-  <si>
-    <t>기뽐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%BD%90</t>
-  </si>
-  <si>
-    <t>2259조 1663억 8382만</t>
-  </si>
-  <si>
-    <t>지존빼앙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
-  </si>
-  <si>
-    <t>1951조 5767억 8833만</t>
-  </si>
-  <si>
-    <t>댜니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>1738조 4296억 7283만</t>
-  </si>
-  <si>
-    <t>뿡쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
-  </si>
-  <si>
-    <t>1545조 4817억 4956만</t>
-  </si>
-  <si>
-    <t>온백</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
-  </si>
-  <si>
-    <t>1482조 8951억 781만</t>
-  </si>
-  <si>
-    <t>파울</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
-  </si>
-  <si>
-    <t>1419조 9260억 2582만</t>
-  </si>
-  <si>
-    <t>엘르가든</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
-  </si>
-  <si>
-    <t>1400조 9926억 8431만</t>
-  </si>
-  <si>
-    <t>변신술사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
-  </si>
-  <si>
-    <t>1395조 8897억 1304만</t>
-  </si>
-  <si>
-    <t>마카롱롱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
-  </si>
-  <si>
-    <t>1391조 2010억 3776만</t>
-  </si>
-  <si>
-    <t>짱잘자쿨냥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%9E%98%EC%9E%90%EC%BF%A8%EB%83%A5</t>
-  </si>
-  <si>
-    <t>1027조 6078억 1748만</t>
-  </si>
-  <si>
-    <t>대좀이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>971조 5267억 8902만</t>
-  </si>
-  <si>
-    <t>모짜리코베르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>952조 8262억 4047만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
-  </si>
-  <si>
-    <t>940조 3059억 3341만</t>
-  </si>
-  <si>
-    <t>김허덕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
-  </si>
-  <si>
-    <t>882조 7278억 5282만</t>
-  </si>
-  <si>
-    <t>마갤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
-  </si>
-  <si>
-    <t>826조 8046억 9936만</t>
-  </si>
-  <si>
-    <t>기본이리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>824조 2609억 4999만</t>
-  </si>
-  <si>
-    <t>냐은</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EC%9D%80</t>
-  </si>
-  <si>
-    <t>810조 1567억 9854만</t>
-  </si>
-  <si>
-    <t>오옹나이스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%B9%EB%82%98%EC%9D%B4%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>787조 4728억 4596만</t>
-  </si>
-  <si>
-    <t>전산봉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%B0%EB%B4%89</t>
-  </si>
-  <si>
-    <t>647조 9759억 4435만</t>
-  </si>
-  <si>
-    <t>고숨도칭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
-  </si>
-  <si>
-    <t>584조 3143억 9077만</t>
-  </si>
-  <si>
-    <t>Doham</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Doham</t>
-  </si>
-  <si>
-    <t>562조 3497억 5522만</t>
-  </si>
-  <si>
-    <t>태코찡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
-  </si>
-  <si>
-    <t>547조 9327억 8104만</t>
-  </si>
-  <si>
-    <t>유플러스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%94%8C%EB%9F%AC%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>482조 8831억 8288만</t>
-  </si>
-  <si>
-    <t>진성팔퀴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%84%B1%ED%8C%94%ED%80%B4</t>
-  </si>
-  <si>
-    <t>347조 5732억 9309만</t>
-  </si>
-  <si>
-    <t>빵후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%ED%9B%84</t>
-  </si>
-  <si>
-    <t>277조 36억 4103만</t>
-  </si>
-  <si>
-    <t>꺄꽁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BA%84%EA%BD%81</t>
-  </si>
-  <si>
-    <t>6887조 6667억 3366만</t>
-  </si>
-  <si>
-    <t>별쌥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A5</t>
-  </si>
-  <si>
-    <t>5024조 2686억 8129만</t>
-  </si>
-  <si>
-    <t>진욱이에요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9A%B1%EC%9D%B4%EC%97%90%EC%9A%94</t>
-  </si>
-  <si>
-    <t>3955조 6580억 3551만</t>
-  </si>
-  <si>
-    <t>낭만황금망치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%ED%99%A9%EA%B8%88%EB%A7%9D%EC%B9%98</t>
-  </si>
-  <si>
-    <t>2665조 3773억 2315만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A5%B4%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>2663조 6348억 8142만</t>
-  </si>
-  <si>
-    <t>김슴줌1</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%8A%B4%EC%A4%8C1</t>
-  </si>
-  <si>
-    <t>2427조 261억 7995만</t>
-  </si>
-  <si>
-    <t>천달</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EB%8B%AC</t>
-  </si>
-  <si>
-    <t>2141조 3106억 9974만</t>
-  </si>
-  <si>
-    <t>호두와감자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%91%90%EC%99%80%EA%B0%90%EC%9E%90</t>
-  </si>
-  <si>
-    <t>2096조 549억 4046만</t>
-  </si>
-  <si>
-    <t>쿠댜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EB%8C%9C</t>
-  </si>
-  <si>
-    <t>1782조 5964억 7721만</t>
-  </si>
-  <si>
-    <t>뚜징</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EC%A7%95</t>
-  </si>
-  <si>
-    <t>1477조 1901억 1245만</t>
-  </si>
-  <si>
-    <t>활용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%9C%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>1383조 715억 1152만</t>
-  </si>
-  <si>
-    <t>별곡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EA%B3%A1</t>
-  </si>
-  <si>
-    <t>878조 4432억 5200만</t>
-  </si>
-  <si>
-    <t>턍ol</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%84%8Dol</t>
-  </si>
-  <si>
-    <t>658조 2553억 1664만</t>
-  </si>
-  <si>
-    <t>게렬곰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%EB%A0%AC%EA%B3%B0</t>
-  </si>
-  <si>
-    <t>654조 80억 8812만</t>
-  </si>
-  <si>
-    <t>까쿠미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EC%BF%A0%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>646조 6992억 8304만</t>
-  </si>
-  <si>
-    <t>동래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%9E%98</t>
-  </si>
-  <si>
-    <t>609조 2026억 9761만</t>
-  </si>
-  <si>
-    <t>띠우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%A0%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>575조 1568억 2284만</t>
-  </si>
-  <si>
-    <t>별쌤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A4</t>
-  </si>
-  <si>
-    <t>527조 5495억 7336만</t>
-  </si>
-  <si>
-    <t>초이레</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%B4%EB%A0%88</t>
-  </si>
-  <si>
-    <t>464조 4040억 924만</t>
-  </si>
-  <si>
-    <t>민족고대감자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%A1%B1%EA%B3%A0%EB%8C%80%EA%B0%90%EC%9E%90</t>
-  </si>
-  <si>
-    <t>424조 85억 3229만</t>
-  </si>
-  <si>
-    <t>승아의하루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%EC%95%84%EC%9D%98%ED%95%98%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>419조 8392억 5458만</t>
-  </si>
-  <si>
-    <t>끄챰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%81%84%EC%B1%B0</t>
-  </si>
-  <si>
-    <t>408조 4724억 3423만</t>
-  </si>
-  <si>
-    <t>쿠까미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EA%B9%8C%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>394조 6595억 7259만</t>
-  </si>
-  <si>
-    <t>택Ol</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%9DOl</t>
-  </si>
-  <si>
-    <t>281조 8647억 7498만</t>
-  </si>
-  <si>
-    <t>08217</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=08217</t>
-  </si>
-  <si>
-    <t>274조 9362억 9646만</t>
-  </si>
-  <si>
-    <t>툼스데이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%88%BC%EC%8A%A4%EB%8D%B0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>246조 9543억 8317만</t>
-  </si>
-  <si>
-    <t>왕단단이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EB%8B%A8%EB%8B%A8%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>236조 4461억 1753만</t>
-  </si>
-  <si>
-    <t>루이쥔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%9D%B4%EC%A5%94</t>
-  </si>
-  <si>
-    <t>219조 7888억 2922만</t>
-  </si>
-  <si>
-    <t>꾸현</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%ED%98%84</t>
-  </si>
-  <si>
-    <t>88조 3966억 6293만</t>
-  </si>
-  <si>
-    <t>달갸뤼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EA%B0%B8%EB%A4%BC</t>
-  </si>
-  <si>
-    <t>70조 5623억 5258만</t>
-  </si>
-  <si>
-    <t>전액할부</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%95%A1%ED%95%A0%EB%B6%80</t>
-  </si>
-  <si>
-    <t>8468조 4686억 7667만</t>
-  </si>
-  <si>
-    <t>사랑향</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%96%A5</t>
-  </si>
-  <si>
-    <t>6469조 5626억 9365만</t>
-  </si>
-  <si>
-    <t>힐폿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%ED%8F%BF</t>
-  </si>
-  <si>
-    <t>4145조 1069억 1568만</t>
-  </si>
-  <si>
-    <t>례전</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%80%EC%A0%84</t>
-  </si>
-  <si>
-    <t>3368조 5231억 8431만</t>
-  </si>
-  <si>
-    <t>숭타이준</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%ED%83%80%EC%9D%B4%EC%A4%80</t>
-  </si>
-  <si>
-    <t>2267조 4656억 338만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%9C%ED%8F%BF</t>
-  </si>
-  <si>
-    <t>2027조 4295억 2482만</t>
-  </si>
-  <si>
-    <t>뮬이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AE%AC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1498조 4072억 7555만</t>
-  </si>
-  <si>
-    <t>77S2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=77S2</t>
-  </si>
-  <si>
-    <t>1444조 8641억 2882만</t>
-  </si>
-  <si>
-    <t>지존빵수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%B5%EC%88%98</t>
-  </si>
-  <si>
-    <t>1344조 9709억 5378만</t>
-  </si>
-  <si>
-    <t>문제적남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EC%A0%9C%EC%A0%81%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>1250조 9156억 7530만</t>
-  </si>
-  <si>
-    <t>탱폿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%8F%BF</t>
-  </si>
-  <si>
-    <t>1240조 4023억 3426만</t>
-  </si>
-  <si>
-    <t>야키산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%82%A4%EC%82%B0</t>
-  </si>
-  <si>
-    <t>1239조 4722억 2107만</t>
-  </si>
-  <si>
-    <t>우즈2텐겐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%A6%882%ED%85%90%EA%B2%90</t>
-  </si>
-  <si>
-    <t>1216조 1916억 2414만</t>
-  </si>
-  <si>
-    <t>아이리쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EB%A6%AC%EC%89%AC</t>
-  </si>
-  <si>
-    <t>1200조 9503억 5332만</t>
-  </si>
-  <si>
-    <t>독스케</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%8A%A4%EC%BC%80</t>
-  </si>
-  <si>
-    <t>1062조 6671억 995만</t>
-  </si>
-  <si>
-    <t>우월별하</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9B%94%EB%B3%84%ED%95%98</t>
-  </si>
-  <si>
-    <t>922조 8577억 2728만</t>
-  </si>
-  <si>
-    <t>화둥에불낸년</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EB%91%A5%EC%97%90%EB%B6%88%EB%82%B8%EB%85%84</t>
-  </si>
-  <si>
-    <t>824조 8049억 3182만</t>
-  </si>
-  <si>
-    <t>기똥찬벌레</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%98%A5%EC%B0%AC%EB%B2%8C%EB%A0%88</t>
-  </si>
-  <si>
-    <t>716조 6452억 3159만</t>
-  </si>
-  <si>
-    <t>JJuna</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=JJuna</t>
-  </si>
-  <si>
-    <t>703조 5638억 6657만</t>
-  </si>
-  <si>
-    <t>이게용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B2%8C%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>664조 1343억 3622만</t>
-  </si>
-  <si>
-    <t>난센</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EC%84%BC</t>
-  </si>
-  <si>
-    <t>662조 680억 9838만</t>
-  </si>
-  <si>
-    <t>매화로이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%ED%99%94%EB%A1%9C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>648조 5977억 2760만</t>
-  </si>
-  <si>
-    <t>콜리셰마드르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%9C%EB%A6%AC%EC%85%B0%EB%A7%88%EB%93%9C%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>640조 4995억 9917만</t>
-  </si>
-  <si>
-    <t>퇴근이마렵다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%87%B4%EA%B7%BC%EC%9D%B4%EB%A7%88%EB%A0%B5%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>551조 8209억 9940만</t>
-  </si>
-  <si>
-    <t>구도류</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%8F%84%EB%A5%98</t>
-  </si>
-  <si>
-    <t>526조 1877억 3406만</t>
-  </si>
-  <si>
-    <t>유채아버지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%B1%84%EC%95%84%EB%B2%84%EC%A7%80</t>
-  </si>
-  <si>
-    <t>480조 4995억 2392만</t>
-  </si>
-  <si>
-    <t>조단23</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%8B%A823</t>
-  </si>
-  <si>
-    <t>456조 614억 6073만</t>
-  </si>
-  <si>
-    <t>에프람</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%ED%94%84%EB%9E%8C</t>
-  </si>
-  <si>
-    <t>435조 3046억 1077만</t>
-  </si>
-  <si>
-    <t>아콩린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BD%A9%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>408조 3210억 7894만</t>
-  </si>
-  <si>
-    <t>별루루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A3%A8%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>274조 2644억 2361만</t>
-  </si>
-  <si>
-    <t>교주만두</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%90%EC%A3%BC%EB%A7%8C%EB%91%90</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>4경 4587조 9543억 369만</t>
+    <t>184조 9307억 32만</t>
   </si>
   <si>
     <t>섹밍</t>
@@ -2055,28 +2055,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B9%EB%B0%8D</t>
   </si>
   <si>
-    <t>177조 9378억 6263만</t>
-  </si>
-  <si>
-    <t>할바이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%B0%94%EC%9D%B4</t>
+    <t>179조 4697억 6535만</t>
+  </si>
+  <si>
+    <t>대구남성</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EA%B5%AC%EB%82%A8%EC%84%B1</t>
   </si>
   <si>
     <t>106</t>
   </si>
   <si>
-    <t>168조 4928억 3883만</t>
-  </si>
-  <si>
-    <t>대구남성</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EA%B5%AC%EB%82%A8%EC%84%B1</t>
-  </si>
-  <si>
-    <t>51조 393억 3494만</t>
+    <t>56조 7587억 2852만</t>
   </si>
   <si>
     <t>KR#0P7W5X70V4</t>
@@ -2085,7 +2076,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%230P7W5X70V4</t>
   </si>
   <si>
-    <t>46조 1562억 2176만</t>
+    <t>50조 5199억 3451만</t>
   </si>
   <si>
     <t>코잉코잉</t>
@@ -2100,13 +2091,31 @@
     <t>30조 7088억 1566만</t>
   </si>
   <si>
+    <t>낭랑28세</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%9E%9128%EC%84%B8</t>
+  </si>
+  <si>
+    <t>27조 8185억 4451만</t>
+  </si>
+  <si>
     <t>토벤숍이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%B2%A4%EC%88%8D%EC%9D%B4</t>
   </si>
   <si>
-    <t>27조 2106억 7631만</t>
+    <t>27조 7454억 2342만</t>
+  </si>
+  <si>
+    <t>뭐하는게임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AD%90%ED%95%98%EB%8A%94%EA%B2%8C%EC%9E%84</t>
+  </si>
+  <si>
+    <t>26조 7249억 7710만</t>
   </si>
   <si>
     <t>돈성</t>
@@ -2118,22 +2127,13 @@
     <t>26조 6536억 9041만</t>
   </si>
   <si>
-    <t>낭랑28세</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%9E%9128%EC%84%B8</t>
-  </si>
-  <si>
-    <t>25조 7650억 65만</t>
-  </si>
-  <si>
-    <t>뭐하는게임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AD%90%ED%95%98%EB%8A%94%EA%B2%8C%EC%9E%84</t>
-  </si>
-  <si>
-    <t>24조 7724억 4883만</t>
+    <t>오스띤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%8A%A4%EB%9D%A4</t>
+  </si>
+  <si>
+    <t>25조 294억 3111만</t>
   </si>
   <si>
     <t>빵신궁</t>
@@ -2166,13 +2166,13 @@
     <t>19조 5230억 2961만</t>
   </si>
   <si>
-    <t>오스띤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%8A%A4%EB%9D%A4</t>
-  </si>
-  <si>
-    <t>19조 2억 7120만</t>
+    <t>킬혁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%AC%ED%98%81</t>
+  </si>
+  <si>
+    <t>19조 227억 3114만</t>
   </si>
   <si>
     <t>고통받는갈비</t>
@@ -2181,7 +2181,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%ED%86%B5%EB%B0%9B%EB%8A%94%EA%B0%88%EB%B9%84</t>
   </si>
   <si>
-    <t>18조 8551억 7813만</t>
+    <t>19조 124억 8712만</t>
   </si>
   <si>
     <t>우루차</t>
@@ -2190,16 +2190,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%A3%A8%EC%B0%A8</t>
   </si>
   <si>
-    <t>18조 5834억 9740만</t>
-  </si>
-  <si>
-    <t>킬혁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%AC%ED%98%81</t>
-  </si>
-  <si>
-    <t>18조 2918억 509만</t>
+    <t>18조 6278억 5908만</t>
   </si>
   <si>
     <t>밀초크코</t>
@@ -2211,6 +2202,15 @@
     <t>17조 3335억 2558만</t>
   </si>
   <si>
+    <t>썬콜우체국</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9A%B0%EC%B2%B4%EA%B5%AD</t>
+  </si>
+  <si>
+    <t>16조 9302억 5236만</t>
+  </si>
+  <si>
     <t>배렛나루왁서</t>
   </si>
   <si>
@@ -2220,15 +2220,6 @@
     <t>16조 4047억 5178만</t>
   </si>
   <si>
-    <t>썬콜우체국</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9A%B0%EC%B2%B4%EA%B5%AD</t>
-  </si>
-  <si>
-    <t>15조 9829억 3646만</t>
-  </si>
-  <si>
     <t>문보겨엉</t>
   </si>
   <si>
@@ -2247,7 +2238,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%95%A1%EC%9A%94%EB%82%98%ED%90%81</t>
   </si>
   <si>
-    <t>12조 2595억 5342만</t>
+    <t>12조 2637억 8958만</t>
   </si>
   <si>
     <t>썬콜법사ss</t>
@@ -2292,10 +2283,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A6%88%EB%82%98%EB%8B%88</t>
   </si>
   <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>2조 4831억 2314만</t>
+    <t>100</t>
+  </si>
+  <si>
+    <t>2조 6392억 203만</t>
   </si>
 </sst>
 </file>
@@ -2782,16 +2773,16 @@
         <v>19</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>24</v>
@@ -2799,31 +2790,31 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>39</v>
@@ -2864,7 +2855,7 @@
         <v>19</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>47</v>
@@ -2905,7 +2896,7 @@
         <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>55</v>
@@ -2946,7 +2937,7 @@
         <v>19</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>63</v>
@@ -3438,10 +3429,10 @@
         <v>137</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3452,28 +3443,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3484,16 +3475,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
@@ -3505,7 +3496,7 @@
         <v>115</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3516,16 +3507,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
@@ -3534,7 +3525,7 @@
         <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>156</v>
@@ -3566,7 +3557,7 @@
         <v>160</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>161</v>
@@ -3662,7 +3653,7 @@
         <v>94</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>173</v>
@@ -3694,7 +3685,7 @@
         <v>94</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>177</v>
@@ -3726,10 +3717,10 @@
         <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3740,16 +3731,16 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
@@ -3758,10 +3749,10 @@
         <v>137</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3772,16 +3763,16 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
@@ -3790,10 +3781,10 @@
         <v>94</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3804,16 +3795,16 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
@@ -3822,10 +3813,10 @@
         <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3836,16 +3827,16 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
@@ -3854,7 +3845,7 @@
         <v>94</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>199</v>
@@ -3883,10 +3874,10 @@
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>203</v>
@@ -3918,7 +3909,7 @@
         <v>207</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>208</v>
@@ -3947,10 +3938,10 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>212</v>
@@ -3982,7 +3973,7 @@
         <v>216</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>217</v>
@@ -4083,25 +4074,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>32</v>
+        <v>218</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>218</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4115,25 +4106,25 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>94</v>
+        <v>223</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4147,25 +4138,25 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4179,25 +4170,25 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>95</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4211,13 +4202,13 @@
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
@@ -4226,10 +4217,10 @@
         <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4243,25 +4234,25 @@
         <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>232</v>
+        <v>33</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>232</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>234</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4275,13 +4266,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
@@ -4293,7 +4284,7 @@
         <v>120</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4307,25 +4298,25 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4339,25 +4330,25 @@
         <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>94</v>
+        <v>160</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4371,25 +4362,25 @@
         <v>130</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4403,25 +4394,25 @@
         <v>134</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>94</v>
+        <v>207</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>142</v>
+        <v>95</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4435,13 +4426,13 @@
         <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
@@ -4450,10 +4441,10 @@
         <v>94</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4464,28 +4455,28 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4496,28 +4487,28 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4528,28 +4519,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>207</v>
+        <v>160</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4563,22 +4554,22 @@
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>265</v>
+        <v>94</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>266</v>
@@ -4607,10 +4598,10 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>269</v>
@@ -4639,10 +4630,10 @@
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>265</v>
+        <v>100</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>272</v>
@@ -4671,10 +4662,10 @@
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>207</v>
+        <v>137</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>275</v>
@@ -4703,10 +4694,10 @@
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>278</v>
@@ -4735,10 +4726,10 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>181</v>
+        <v>115</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>281</v>
@@ -4752,7 +4743,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>282</v>
@@ -4767,10 +4758,10 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>137</v>
+        <v>207</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>284</v>
@@ -4784,7 +4775,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>285</v>
@@ -4799,10 +4790,10 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>265</v>
+        <v>160</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>287</v>
@@ -4816,7 +4807,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>288</v>
@@ -4834,7 +4825,7 @@
         <v>94</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>142</v>
+        <v>198</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>290</v>
@@ -4848,7 +4839,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>291</v>
@@ -4863,10 +4854,10 @@
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>137</v>
+        <v>207</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>293</v>
@@ -4895,10 +4886,10 @@
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>94</v>
+        <v>160</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>296</v>
@@ -4927,7 +4918,7 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>216</v>
+        <v>94</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>115</v>
@@ -4959,10 +4950,10 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>94</v>
+        <v>230</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>302</v>
@@ -4991,13 +4982,13 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5008,16 +4999,16 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>87</v>
@@ -5026,10 +5017,10 @@
         <v>94</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5122,31 +5113,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>41</v>
+        <v>310</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>41</v>
+        <v>310</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>313</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5154,31 +5145,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>316</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5186,19 +5177,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>318</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
@@ -5207,10 +5198,10 @@
         <v>160</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5218,31 +5209,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>321</v>
-      </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>95</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5250,31 +5241,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>324</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>325</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5282,31 +5273,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>327</v>
-      </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5314,31 +5305,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>331</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5346,31 +5337,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5378,31 +5369,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>336</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>337</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5410,19 +5401,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
@@ -5434,7 +5425,7 @@
         <v>115</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5442,31 +5433,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>343</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5474,31 +5465,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>345</v>
-      </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>110</v>
+        <v>207</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5506,31 +5497,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>349</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5538,19 +5529,19 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
@@ -5559,10 +5550,10 @@
         <v>94</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5570,19 +5561,19 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>354</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
@@ -5591,10 +5582,10 @@
         <v>94</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5602,31 +5593,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>357</v>
-      </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>94</v>
+        <v>223</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5634,31 +5625,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>360</v>
-      </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>216</v>
+        <v>94</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5666,31 +5657,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>166</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>364</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5698,31 +5689,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5730,31 +5721,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>147</v>
+        <v>94</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5762,19 +5753,19 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
@@ -5783,10 +5774,10 @@
         <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>181</v>
+        <v>120</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5794,31 +5785,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>376</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5826,31 +5817,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>147</v>
+        <v>88</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5858,19 +5849,19 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
@@ -5879,10 +5870,10 @@
         <v>94</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5890,19 +5881,19 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
@@ -5911,10 +5902,10 @@
         <v>160</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5922,31 +5913,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>388</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5954,31 +5945,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>391</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5986,31 +5977,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="H29" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6018,31 +6009,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>213</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>397</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6050,31 +6041,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>399</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>400</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6173,25 +6164,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>401</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6205,25 +6196,25 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>404</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>406</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6237,13 +6228,13 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
@@ -6252,10 +6243,10 @@
         <v>160</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6269,25 +6260,25 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>94</v>
+        <v>160</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>95</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6301,25 +6292,25 @@
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>415</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6333,25 +6324,25 @@
         <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6365,25 +6356,25 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>421</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6397,25 +6388,25 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>422</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>424</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6429,25 +6420,25 @@
         <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>427</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6461,25 +6452,25 @@
         <v>130</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>428</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>430</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6493,25 +6484,25 @@
         <v>134</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>433</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6525,25 +6516,25 @@
         <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>436</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6554,28 +6545,28 @@
         <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>439</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6586,16 +6577,16 @@
         <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
@@ -6604,10 +6595,10 @@
         <v>94</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6618,16 +6609,16 @@
         <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
@@ -6636,10 +6627,10 @@
         <v>94</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6653,25 +6644,25 @@
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>265</v>
+        <v>160</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6685,13 +6676,13 @@
         <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
@@ -6703,7 +6694,7 @@
         <v>115</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6717,25 +6708,25 @@
         <v>166</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>49</v>
+        <v>450</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>49</v>
+        <v>450</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>453</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6749,25 +6740,25 @@
         <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>455</v>
-      </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>94</v>
+        <v>216</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6781,25 +6772,25 @@
         <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>459</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6813,25 +6804,25 @@
         <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6842,28 +6833,28 @@
         <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>465</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6874,28 +6865,28 @@
         <v>42</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6906,16 +6897,16 @@
         <v>42</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>469</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>470</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
@@ -6924,10 +6915,10 @@
         <v>94</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>181</v>
+        <v>115</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6938,28 +6929,28 @@
         <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>473</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>474</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6973,25 +6964,25 @@
         <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>477</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7005,25 +6996,25 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>479</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>480</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7037,25 +7028,25 @@
         <v>209</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>483</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7069,25 +7060,25 @@
         <v>213</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>485</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>486</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -7098,28 +7089,28 @@
         <v>42</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>488</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>489</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -7165,7 +7156,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -7218,25 +7209,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>492</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -7250,25 +7241,25 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -7282,25 +7273,25 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>207</v>
+        <v>100</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>95</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -7314,13 +7305,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
@@ -7329,10 +7320,10 @@
         <v>100</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -7346,25 +7337,25 @@
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>57</v>
+        <v>500</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>57</v>
+        <v>500</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -7378,25 +7369,25 @@
         <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -7410,13 +7401,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>508</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
@@ -7428,7 +7419,7 @@
         <v>120</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -7442,25 +7433,25 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>511</v>
-      </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -7474,13 +7465,13 @@
         <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>513</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>514</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
@@ -7489,10 +7480,10 @@
         <v>94</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -7506,25 +7497,25 @@
         <v>130</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>517</v>
-      </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -7538,25 +7529,25 @@
         <v>134</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>521</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -7570,25 +7561,25 @@
         <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>523</v>
-      </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -7599,28 +7590,28 @@
         <v>50</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>526</v>
-      </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -7631,28 +7622,28 @@
         <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>529</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>530</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7663,16 +7654,16 @@
         <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>531</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>532</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
@@ -7681,10 +7672,10 @@
         <v>207</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7698,25 +7689,25 @@
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>535</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>536</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7730,25 +7721,25 @@
         <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>538</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>539</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7762,25 +7753,25 @@
         <v>166</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>541</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>542</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7794,25 +7785,25 @@
         <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>544</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>545</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7826,25 +7817,25 @@
         <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>547</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>548</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7858,25 +7849,25 @@
         <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7887,28 +7878,28 @@
         <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>553</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>554</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7919,28 +7910,28 @@
         <v>50</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>556</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>557</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7951,28 +7942,28 @@
         <v>50</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>559</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>560</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7983,28 +7974,28 @@
         <v>50</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>562</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>563</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -8018,13 +8009,13 @@
         <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>564</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>565</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
@@ -8033,10 +8024,10 @@
         <v>94</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -8050,25 +8041,25 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>568</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>569</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -8082,13 +8073,13 @@
         <v>209</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>570</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>571</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
@@ -8097,10 +8088,10 @@
         <v>94</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -8114,64 +8105,32 @@
         <v>213</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>575</v>
-      </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -8202,7 +8161,6 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8263,25 +8221,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8295,25 +8253,25 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>265</v>
+        <v>160</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8327,25 +8285,25 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>110</v>
+        <v>207</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8359,25 +8317,25 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>588</v>
+        <v>65</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>588</v>
+        <v>65</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>234</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>95</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8391,25 +8349,25 @@
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8423,25 +8381,25 @@
         <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>65</v>
+        <v>589</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>65</v>
+        <v>589</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>230</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8455,13 +8413,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
@@ -8473,7 +8431,7 @@
         <v>120</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8487,25 +8445,25 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8519,25 +8477,25 @@
         <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8551,13 +8509,13 @@
         <v>130</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
@@ -8566,10 +8524,10 @@
         <v>94</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8583,25 +8541,25 @@
         <v>134</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>207</v>
+        <v>88</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8615,25 +8573,25 @@
         <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>94</v>
+        <v>160</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8644,16 +8602,16 @@
         <v>58</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
@@ -8665,7 +8623,7 @@
         <v>115</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8676,16 +8634,16 @@
         <v>58</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
@@ -8694,10 +8652,10 @@
         <v>94</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8708,28 +8666,28 @@
         <v>58</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8743,13 +8701,13 @@
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
@@ -8758,10 +8716,10 @@
         <v>94</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8775,13 +8733,13 @@
         <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
@@ -8790,10 +8748,10 @@
         <v>94</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>142</v>
+        <v>198</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8807,25 +8765,25 @@
         <v>166</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8839,25 +8797,25 @@
         <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8871,25 +8829,25 @@
         <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>137</v>
+        <v>392</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>142</v>
+        <v>198</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8903,25 +8861,25 @@
         <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>207</v>
+        <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8932,28 +8890,28 @@
         <v>58</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>207</v>
+        <v>100</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8964,28 +8922,28 @@
         <v>58</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>115</v>
+        <v>193</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -8996,28 +8954,28 @@
         <v>58</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9028,28 +8986,28 @@
         <v>58</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>207</v>
+        <v>94</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>142</v>
+        <v>198</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9063,25 +9021,25 @@
         <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>142</v>
+        <v>198</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -9095,25 +9053,25 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>142</v>
+        <v>198</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9127,13 +9085,13 @@
         <v>209</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
@@ -9142,10 +9100,10 @@
         <v>94</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -9159,13 +9117,13 @@
         <v>213</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
@@ -9174,10 +9132,10 @@
         <v>94</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -9188,28 +9146,28 @@
         <v>58</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>94</v>
+        <v>160</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -9263,7 +9221,7 @@
     <col min="3" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9307,13 +9265,13 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
@@ -9322,10 +9280,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -9339,25 +9297,25 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>194</v>
+        <v>670</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -9371,25 +9329,25 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>94</v>
+        <v>160</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>677</v>
+        <v>193</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -9403,13 +9361,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
@@ -9421,7 +9379,7 @@
         <v>677</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -9435,13 +9393,13 @@
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
@@ -9453,7 +9411,7 @@
         <v>677</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -9467,25 +9425,25 @@
         <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>685</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>688</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -9499,25 +9457,25 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>265</v>
+        <v>392</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -9531,25 +9489,25 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -9563,25 +9521,25 @@
         <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>305</v>
+        <v>88</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -9595,25 +9553,25 @@
         <v>130</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>88</v>
+        <v>230</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -9627,25 +9585,25 @@
         <v>134</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>305</v>
+        <v>160</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -9659,25 +9617,25 @@
         <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>88</v>
+        <v>392</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>706</v>
+        <v>684</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9688,28 +9646,28 @@
         <v>66</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>216</v>
+        <v>88</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>687</v>
+        <v>706</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9720,28 +9678,28 @@
         <v>66</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>160</v>
+        <v>216</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9752,28 +9710,28 @@
         <v>66</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>94</v>
+        <v>160</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>706</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9787,13 +9745,13 @@
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
@@ -9805,7 +9763,7 @@
         <v>706</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9819,25 +9777,25 @@
         <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>706</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9851,13 +9809,13 @@
         <v>166</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
@@ -9869,7 +9827,7 @@
         <v>706</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9883,25 +9841,25 @@
         <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>110</v>
+        <v>216</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>706</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9915,25 +9873,25 @@
         <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>216</v>
+        <v>110</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>706</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9947,13 +9905,13 @@
         <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
@@ -9962,10 +9920,10 @@
         <v>207</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9976,16 +9934,16 @@
         <v>66</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
@@ -9997,7 +9955,7 @@
         <v>706</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -10008,16 +9966,16 @@
         <v>66</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
@@ -10029,7 +9987,7 @@
         <v>706</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -10040,7 +9998,7 @@
         <v>66</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>75</v>
@@ -10049,19 +10007,19 @@
         <v>75</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>159</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -10072,16 +10030,16 @@
         <v>66</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
@@ -10090,10 +10048,10 @@
         <v>207</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -10107,25 +10065,25 @@
         <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>265</v>
+        <v>223</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -10139,25 +10097,25 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>751</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>754</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -8,30 +8,30 @@
   </bookViews>
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
-    <sheet name="빅딜" sheetId="2" r:id="rId2"/>
-    <sheet name="바텀" sheetId="3" r:id="rId3"/>
-    <sheet name="지존길드" sheetId="4" r:id="rId4"/>
-    <sheet name="든솔" sheetId="5" r:id="rId5"/>
+    <sheet name="바텀" sheetId="2" r:id="rId2"/>
+    <sheet name="빅딜" sheetId="3" r:id="rId3"/>
+    <sheet name="든솔" sheetId="4" r:id="rId4"/>
+    <sheet name="지존길드" sheetId="5" r:id="rId5"/>
     <sheet name="만영" sheetId="6" r:id="rId6"/>
     <sheet name="따숨" sheetId="7" r:id="rId7"/>
     <sheet name="더위사냥" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">더위사냥!$A$1:$J$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">든솔!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">더위사냥!$A$1:$J$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">든솔!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">따숨!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">만영!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">바텀!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">지존길드!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">바텀!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">빅딜!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">지존길드!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2224" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2214" uniqueCount="749">
   <si>
     <t>guild_name</t>
   </si>
@@ -72,31 +72,61 @@
     <t>data_date</t>
   </si>
   <si>
+    <t>바텀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%94%ED%85%80</t>
+  </si>
+  <si>
+    <t>Scania</t>
+  </si>
+  <si>
+    <t>Scania 29</t>
+  </si>
+  <si>
+    <t>435</t>
+  </si>
+  <si>
+    <t>14위</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>4경 7638조 4057억 173만</t>
+  </si>
+  <si>
+    <t>바텀에서 캐리하실분! (톡방필수)</t>
+  </si>
+  <si>
+    <t>딜폿</t>
+  </si>
+  <si>
+    <t>2026.09.20</t>
+  </si>
+  <si>
     <t>빅딜</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%85%EB%94%9C</t>
   </si>
   <si>
-    <t>Scania</t>
-  </si>
-  <si>
     <t>Scania 2</t>
   </si>
   <si>
-    <t>428</t>
+    <t>426</t>
   </si>
   <si>
     <t>13위</t>
   </si>
   <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
     <t>29명</t>
   </si>
   <si>
-    <t>4경 9478조 6064억 3410만</t>
+    <t>5경 26조 6494억 6590만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -105,34 +135,28 @@
     <t>자유이용껀</t>
   </si>
   <si>
-    <t>2026.09.19</t>
-  </si>
-  <si>
-    <t>바텀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%94%ED%85%80</t>
-  </si>
-  <si>
-    <t>Scania 29</t>
-  </si>
-  <si>
-    <t>435</t>
-  </si>
-  <si>
-    <t>14위</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>4경 7416조 1386억 8900만</t>
-  </si>
-  <si>
-    <t>바텀에서 캐리하실분! (톡방필수)</t>
-  </si>
-  <si>
-    <t>딜폿</t>
+    <t>든솔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%93%A0%EC%86%94</t>
+  </si>
+  <si>
+    <t>Scania 13</t>
+  </si>
+  <si>
+    <t>429</t>
+  </si>
+  <si>
+    <t>10위</t>
+  </si>
+  <si>
+    <t>4경 9515조 7755억 5964만</t>
+  </si>
+  <si>
+    <t>투력 300조이상,미접 1일 추방,매일 무료 업글필수,길드 컨텐츠 필수 참여,공지방 필수 참여, 게임에 열정있으신 분 환영/가입문의 현뇸.강필구.v박효신v</t>
+  </si>
+  <si>
+    <t>현뇸</t>
   </si>
   <si>
     <t>지존길드</t>
@@ -144,13 +168,13 @@
     <t>Scania 4</t>
   </si>
   <si>
-    <t>440</t>
+    <t>437</t>
   </si>
   <si>
     <t>11위</t>
   </si>
   <si>
-    <t>4경 6445조 2840억 90만</t>
+    <t>4경 7116조 5949억 2207만</t>
   </si>
   <si>
     <t>지존길드 공지용 오픈채팅 필수참여입니다.</t>
@@ -159,30 +183,6 @@
     <t>지존순찌</t>
   </si>
   <si>
-    <t>든솔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%93%A0%EC%86%94</t>
-  </si>
-  <si>
-    <t>Scania 13</t>
-  </si>
-  <si>
-    <t>433</t>
-  </si>
-  <si>
-    <t>10위</t>
-  </si>
-  <si>
-    <t>4경 7933조 6785억 9956만</t>
-  </si>
-  <si>
-    <t>투력 300조이상,미접 1일 추방,매일 무료 업글필수,길드 컨텐츠 필수 참여,공지방 필수 참여, 게임에 열정있으신 분 환영/가입문의 현뇸.강필구.v박효신v</t>
-  </si>
-  <si>
-    <t>현뇸</t>
-  </si>
-  <si>
     <t>만영</t>
   </si>
   <si>
@@ -192,13 +192,13 @@
     <t>Scania 23</t>
   </si>
   <si>
-    <t>453</t>
+    <t>451</t>
   </si>
   <si>
     <t>8위</t>
   </si>
   <si>
-    <t>4경 2629조 6634억 4875만</t>
+    <t>4경 2779조 8854억 531만</t>
   </si>
   <si>
     <t>가입신청 문의주세요.(정기유무 / 무곽)</t>
@@ -222,7 +222,7 @@
     <t>15위</t>
   </si>
   <si>
-    <t>4경 1275조 6508억 5891만</t>
+    <t>4경 1796조 8029억 8549만</t>
   </si>
   <si>
     <t>길드건물/길드콘텐츠/길드톡방 필수이며 같이 재밌게 게임해요! 가입문의 김가원,호르몬,뚜징,김슴줌1에게 귓주세요</t>
@@ -240,7 +240,7 @@
     <t>Scania 50</t>
   </si>
   <si>
-    <t>438</t>
+    <t>434</t>
   </si>
   <si>
     <t>4위</t>
@@ -249,10 +249,10 @@
     <t>Lv.7</t>
   </si>
   <si>
-    <t>27명</t>
-  </si>
-  <si>
-    <t>4경 6786조 8045억 8500만</t>
+    <t>26명</t>
+  </si>
+  <si>
+    <t>4경 7770조 9992억 1980만</t>
   </si>
   <si>
     <t>전투력 150 이상 용사님 언제든 환영합니다/궁금하신점 언제든 밍키비키 귓주세요/ 1일 접속,길드건물 업그레이드 필수/길드 콘텐츠 참가 필수/ 꾸준히 함께하실 용사님들 대환영합니다</t>
@@ -288,25 +288,421 @@
     <t>1</t>
   </si>
   <si>
+    <t>전액할부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%95%A1%ED%95%A0%EB%B6%80</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>8468조 4686억 7667만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>사랑향</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%96%A5</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>6527조 2315억 1292만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>힐폿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%ED%8F%BF</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>4145조 1069억 1568만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>례전</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%80%EC%A0%84</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>3379조 3767억 1551만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>숭타이준</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%ED%83%80%EC%9D%B4%EC%A4%80</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>2267조 4656억 338만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%9C%ED%8F%BF</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>2069조 6682억 9082만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>뮬이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AE%AC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1503조 8814억 8612만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>77S2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=77S2</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>1444조 8641억 2882만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>지존빵수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%B5%EC%88%98</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>1385조 1109억 8만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>문제적남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EC%A0%9C%EC%A0%81%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>1250조 9156억 7530만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>탱폿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%8F%BF</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>1242조 596억 4552만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>야키산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%82%A4%EC%82%B0</t>
+  </si>
+  <si>
+    <t>1239조 4722억 2107만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>우즈2텐겐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%A6%882%ED%85%90%EA%B2%90</t>
+  </si>
+  <si>
+    <t>1216조 1916억 2414만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>아이리쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EB%A6%AC%EC%89%AC</t>
+  </si>
+  <si>
+    <t>1202조 1798억 4628만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>독스케</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%8A%A4%EC%BC%80</t>
+  </si>
+  <si>
+    <t>1066조 4523억 4836만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>우월별하</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9B%94%EB%B3%84%ED%95%98</t>
+  </si>
+  <si>
+    <t>1032조 7712억 9061만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>화둥에불낸년</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EB%91%A5%EC%97%90%EB%B6%88%EB%82%B8%EB%85%84</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>864조 4672억 2142만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>기똥찬벌레</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%98%A5%EC%B0%AC%EB%B2%8C%EB%A0%88</t>
+  </si>
+  <si>
+    <t>719조 8209억 3386만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>JJuna</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=JJuna</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>711조 601억 6569만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>이게용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B2%8C%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>694조 7664억 410만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>난센</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EC%84%BC</t>
+  </si>
+  <si>
+    <t>662조 680억 9838만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>매화로이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%ED%99%94%EB%A1%9C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>651조 9269억 9659만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>콜리셰마드르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%9C%EB%A6%AC%EC%85%B0%EB%A7%88%EB%93%9C%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>645조 9298억 1219만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>퇴근이마렵다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%87%B4%EA%B7%BC%EC%9D%B4%EB%A7%88%EB%A0%B5%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>561조 27억 9719만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>구도류</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%8F%84%EB%A5%98</t>
+  </si>
+  <si>
+    <t>527조 8961억 264만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>유채아버지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%B1%84%EC%95%84%EB%B2%84%EC%A7%80</t>
+  </si>
+  <si>
+    <t>484조 1099억 9114만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>에프람</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%ED%94%84%EB%9E%8C</t>
+  </si>
+  <si>
+    <t>474조 8988억 5123만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>조단23</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%8B%A823</t>
+  </si>
+  <si>
+    <t>463조 9824억 4952만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>아콩린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BD%A9%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>439조 5500억 5260만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>별루루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A3%A8%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>286조 6694억 3367만</t>
+  </si>
+  <si>
     <t>김치싸대기</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>히어로</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>8570조 3175억 8447만</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>8574조 1501억 5135만</t>
   </si>
   <si>
     <t>굴러가는일상</t>
@@ -315,31 +711,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
   </si>
   <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>5571조 2990억 750만</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>두향</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%91%90%ED%96%A5</t>
   </si>
   <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>4344조 479억 3534만</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>4349조 3566억 3215만</t>
   </si>
   <si>
     <t>몽호</t>
@@ -354,22 +735,13 @@
     <t>3674조 8409억 1914만</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>대방어조아</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>3334조 8639억 6043만</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>3437조 4377억 392만</t>
   </si>
   <si>
     <t>흑두부</t>
@@ -378,28 +750,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>3314조 3423억 3688만</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>엘라임</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>2838조 8556억 6943만</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>2839조 1366억 4961만</t>
   </si>
   <si>
     <t>서포터즈</t>
@@ -408,10 +768,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>2125조 1120억 4939만</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>2125조 3498억 9185만</t>
+  </si>
+  <si>
+    <t>퍼퓸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
+  </si>
+  <si>
+    <t>1912조 9606억 5811만</t>
   </si>
   <si>
     <t>KR#TAKIN9CP37</t>
@@ -420,22 +786,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>1738조 4910억 368만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>퍼퓸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
-  </si>
-  <si>
-    <t>1606조 9335억 6930만</t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>1808조 1569억 2798만</t>
   </si>
   <si>
     <t>야가다</t>
@@ -444,15 +795,9 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
   </si>
   <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
     <t>1508조 7420억 3377만</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>뻥뻥</t>
   </si>
   <si>
@@ -462,9 +807,6 @@
     <t>1178조 4809억 5968만</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>불보독지</t>
   </si>
   <si>
@@ -474,10 +816,7 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>1101조 795억 6833만</t>
-  </si>
-  <si>
-    <t>14</t>
+    <t>1102조 6798억 2352만</t>
   </si>
   <si>
     <t>채무조정</t>
@@ -489,39 +828,21 @@
     <t>972조 2153억 1957만</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>우후</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>971조 2607억 4284만</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
     <t>926조 4709억 657만</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>호우기</t>
   </si>
   <si>
@@ -531,9 +852,6 @@
     <t>838조 1381억 1843만</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>정태준</t>
   </si>
   <si>
@@ -543,9 +861,6 @@
     <t>747조 6479억 4857만</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
     <t>좀치는형님</t>
   </si>
   <si>
@@ -555,9 +870,6 @@
     <t>738조 8585억 6928만</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>팡대지</t>
   </si>
   <si>
@@ -567,19 +879,13 @@
     <t>539조 3853억 2223만</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>민들레꽃</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>485조 354억 533만</t>
-  </si>
-  <si>
-    <t>22</t>
+    <t>486조 5354억 4811만</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -588,10 +894,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
   </si>
   <si>
-    <t>391조 5629억 3601만</t>
-  </si>
-  <si>
-    <t>23</t>
+    <t>398조 4483억 503만</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -603,7 +906,13 @@
     <t>384조 814억 6223만</t>
   </si>
   <si>
-    <t>24</t>
+    <t>박준우2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
+  </si>
+  <si>
+    <t>380조 192억 2246만</t>
   </si>
   <si>
     <t>솔인</t>
@@ -612,30 +921,9 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
   </si>
   <si>
-    <t>108</t>
-  </si>
-  <si>
     <t>356조 443억 1139만</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>박준우2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>329조 8887억 57만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
     <t>꼬북빵야</t>
   </si>
   <si>
@@ -645,24 +933,15 @@
     <t>240조 453억 6127만</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
     <t>여눈</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
   </si>
   <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
     <t>226조 9385억 6222만</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
     <t>아르미느</t>
   </si>
   <si>
@@ -672,9 +951,6 @@
     <t>224조 7388억 729만</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
     <t>꾸르꾸르</t>
   </si>
   <si>
@@ -687,280 +963,274 @@
     <t>198조 8873억 6281만</t>
   </si>
   <si>
-    <t>전액할부</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%95%A1%ED%95%A0%EB%B6%80</t>
-  </si>
-  <si>
-    <t>8468조 4686억 7667만</t>
-  </si>
-  <si>
-    <t>사랑향</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%96%A5</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>6527조 2315억 1292만</t>
-  </si>
-  <si>
-    <t>힐폿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%ED%8F%BF</t>
-  </si>
-  <si>
-    <t>4145조 1069억 1568만</t>
-  </si>
-  <si>
-    <t>례전</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%80%EC%A0%84</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>3374조 618억 7162만</t>
-  </si>
-  <si>
-    <t>숭타이준</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%ED%83%80%EC%9D%B4%EC%A4%80</t>
-  </si>
-  <si>
-    <t>2267조 4656억 338만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%9C%ED%8F%BF</t>
-  </si>
-  <si>
-    <t>2069조 6682억 9082만</t>
-  </si>
-  <si>
-    <t>뮬이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AE%AC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1498조 4072억 7555만</t>
-  </si>
-  <si>
-    <t>77S2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=77S2</t>
-  </si>
-  <si>
-    <t>1444조 8641억 2882만</t>
-  </si>
-  <si>
-    <t>지존빵수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%B5%EC%88%98</t>
-  </si>
-  <si>
-    <t>1344조 9709억 5378만</t>
-  </si>
-  <si>
-    <t>문제적남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EC%A0%9C%EC%A0%81%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>1250조 9156억 7530만</t>
-  </si>
-  <si>
-    <t>탱폿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%8F%BF</t>
-  </si>
-  <si>
-    <t>1240조 4023억 3426만</t>
-  </si>
-  <si>
-    <t>야키산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%82%A4%EC%82%B0</t>
-  </si>
-  <si>
-    <t>1239조 4722억 2107만</t>
-  </si>
-  <si>
-    <t>우즈2텐겐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%A6%882%ED%85%90%EA%B2%90</t>
-  </si>
-  <si>
-    <t>1216조 1916억 2414만</t>
-  </si>
-  <si>
-    <t>아이리쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EB%A6%AC%EC%89%AC</t>
-  </si>
-  <si>
-    <t>1201조 5056억 9678만</t>
-  </si>
-  <si>
-    <t>독스케</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%8A%A4%EC%BC%80</t>
-  </si>
-  <si>
-    <t>1064조 4633억 8858만</t>
-  </si>
-  <si>
-    <t>우월별하</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9B%94%EB%B3%84%ED%95%98</t>
-  </si>
-  <si>
-    <t>922조 8577억 2728만</t>
-  </si>
-  <si>
-    <t>화둥에불낸년</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EB%91%A5%EC%97%90%EB%B6%88%EB%82%B8%EB%85%84</t>
-  </si>
-  <si>
-    <t>864조 4672억 2142만</t>
-  </si>
-  <si>
-    <t>기똥찬벌레</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%98%A5%EC%B0%AC%EB%B2%8C%EB%A0%88</t>
-  </si>
-  <si>
-    <t>717조 5782억 3399만</t>
-  </si>
-  <si>
-    <t>JJuna</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=JJuna</t>
-  </si>
-  <si>
-    <t>711조 601억 6569만</t>
-  </si>
-  <si>
-    <t>이게용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B2%8C%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>694조 6475억 554만</t>
-  </si>
-  <si>
-    <t>난센</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EC%84%BC</t>
-  </si>
-  <si>
-    <t>662조 680억 9838만</t>
-  </si>
-  <si>
-    <t>매화로이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%ED%99%94%EB%A1%9C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>649조 2631억 5583만</t>
-  </si>
-  <si>
-    <t>콜리셰마드르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%9C%EB%A6%AC%EC%85%B0%EB%A7%88%EB%93%9C%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>640조 4995억 9917만</t>
-  </si>
-  <si>
-    <t>퇴근이마렵다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%87%B4%EA%B7%BC%EC%9D%B4%EB%A7%88%EB%A0%B5%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>552조 3852억 676만</t>
-  </si>
-  <si>
-    <t>구도류</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%8F%84%EB%A5%98</t>
-  </si>
-  <si>
-    <t>526조 9101억 9078만</t>
-  </si>
-  <si>
-    <t>유채아버지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%B1%84%EC%95%84%EB%B2%84%EC%A7%80</t>
-  </si>
-  <si>
-    <t>484조 1099억 9114만</t>
-  </si>
-  <si>
-    <t>에프람</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%ED%94%84%EB%9E%8C</t>
-  </si>
-  <si>
-    <t>473조 8921억 7583만</t>
-  </si>
-  <si>
-    <t>조단23</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%8B%A823</t>
-  </si>
-  <si>
-    <t>456조 6055억 5640만</t>
-  </si>
-  <si>
-    <t>아콩린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BD%A9%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>432조 1699억 4429만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>별루루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A3%A8%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>274조 4277억 4696만</t>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EB%87%B8</t>
+  </si>
+  <si>
+    <t>5590조 1893억 1428만</t>
+  </si>
+  <si>
+    <t>손챠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%90%EC%B1%A0</t>
+  </si>
+  <si>
+    <t>4727조 3461억 4993만</t>
+  </si>
+  <si>
+    <t>강필구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%84%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>4550조 9774억 5040만</t>
+  </si>
+  <si>
+    <t>GOD날두</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=GOD%EB%82%A0%EB%91%90</t>
+  </si>
+  <si>
+    <t>3909조 7173억 706만</t>
+  </si>
+  <si>
+    <t>알배기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%8C%EB%B0%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>3214조 2193억 3893만</t>
+  </si>
+  <si>
+    <t>러브포티</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%B8%8C%ED%8F%AC%ED%8B%B0</t>
+  </si>
+  <si>
+    <t>2531조 2493억 3579만</t>
+  </si>
+  <si>
+    <t>테이킷슬로우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%85%8C%EC%9D%B4%ED%82%B7%EC%8A%AC%EB%A1%9C%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>2367조 6141억 542만</t>
+  </si>
+  <si>
+    <t>하찌바리이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B0%8C%EB%B0%94%EB%A6%AC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2204조 7560억 5453만</t>
+  </si>
+  <si>
+    <t>주요엘농산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%9A%94%EC%97%98%EB%86%8D%EC%82%B0</t>
+  </si>
+  <si>
+    <t>2135조 1941억 762만</t>
+  </si>
+  <si>
+    <t>88치킨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=88%EC%B9%98%ED%82%A8</t>
+  </si>
+  <si>
+    <t>1621조 3630억 3601만</t>
+  </si>
+  <si>
+    <t>탕비실도우미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%95%EB%B9%84%EC%8B%A4%EB%8F%84%EC%9A%B0%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>1449조 9858억 2106만</t>
+  </si>
+  <si>
+    <t>Darken</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Darken</t>
+  </si>
+  <si>
+    <t>1430조 3705억 8146만</t>
+  </si>
+  <si>
+    <t>서늘한그늘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%8A%98%ED%95%9C%EA%B7%B8%EB%8A%98</t>
+  </si>
+  <si>
+    <t>1402조 805억 8만</t>
+  </si>
+  <si>
+    <t>하이하로하라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9D%B4%ED%95%98%EB%A1%9C%ED%95%98%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>1212조 8331억 8391만</t>
+  </si>
+  <si>
+    <t>차보이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EB%B3%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1056조 4395억 4897만</t>
+  </si>
+  <si>
+    <t>도레오</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%88%EC%98%A4</t>
+  </si>
+  <si>
+    <t>985조 3833억 8106만</t>
+  </si>
+  <si>
+    <t>여릿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%A6%BF</t>
+  </si>
+  <si>
+    <t>974조 6489억 1819만</t>
+  </si>
+  <si>
+    <t>초읍사나이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%8D%EC%82%AC%EB%82%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>900조 5079억 3229만</t>
+  </si>
+  <si>
+    <t>v박효신v</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=v%EB%B0%95%ED%9A%A8%EC%8B%A0v</t>
+  </si>
+  <si>
+    <t>897조 7782억 7489만</t>
+  </si>
+  <si>
+    <t>시간이돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B0%84%EC%9D%B4%EB%8F%88</t>
+  </si>
+  <si>
+    <t>845조 3828억 1795만</t>
+  </si>
+  <si>
+    <t>고으농</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%9C%BC%EB%86%8D</t>
+  </si>
+  <si>
+    <t>709조 2564억 5573만</t>
+  </si>
+  <si>
+    <t>영구짱구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%81%EA%B5%AC%EC%A7%B1%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>708조 6531억 8974만</t>
+  </si>
+  <si>
+    <t>다둉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>655조 928억 6795만</t>
+  </si>
+  <si>
+    <t>도사랑화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%82%AC%EB%9E%91%ED%99%94</t>
+  </si>
+  <si>
+    <t>651조 1571억 2030만</t>
+  </si>
+  <si>
+    <t>뜌미누</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9C%8C%EB%AF%B8%EB%88%84</t>
+  </si>
+  <si>
+    <t>576조 4166억 7025만</t>
+  </si>
+  <si>
+    <t>발진</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%9C%EC%A7%84</t>
+  </si>
+  <si>
+    <t>559조 8595억 2848만</t>
+  </si>
+  <si>
+    <t>익뇸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%87%B8</t>
+  </si>
+  <si>
+    <t>469조 5981억 3531만</t>
+  </si>
+  <si>
+    <t>나는배불러요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%8A%94%EB%B0%B0%EB%B6%88%EB%9F%AC%EC%9A%94</t>
+  </si>
+  <si>
+    <t>412조 5859억 5045만</t>
+  </si>
+  <si>
+    <t>하엘이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%97%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>390조 8622억 7970만</t>
+  </si>
+  <si>
+    <t>아리미쿵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A6%AC%EB%AF%B8%EC%BF%B5</t>
+  </si>
+  <si>
+    <t>387조 6260억 3394만</t>
   </si>
   <si>
     <t>지존쫀파</t>
@@ -978,7 +1248,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%91%EC%9D%98</t>
   </si>
   <si>
-    <t>4158조 8546억 7008만</t>
+    <t>4245조 3598억 1665만</t>
   </si>
   <si>
     <t>포항엄석대</t>
@@ -987,7 +1257,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
   </si>
   <si>
-    <t>3872조 369억 891만</t>
+    <t>4022조 9259억 9763만</t>
   </si>
   <si>
     <t>타개</t>
@@ -996,7 +1266,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
   </si>
   <si>
-    <t>2495조 7634억 7223만</t>
+    <t>2546조 9231억 8482만</t>
   </si>
   <si>
     <t>포항가자미</t>
@@ -1005,7 +1275,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
   </si>
   <si>
-    <t>2269조 2449억 6902만</t>
+    <t>2275조 975억 942만</t>
   </si>
   <si>
     <t>기뽐</t>
@@ -1023,7 +1293,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
   </si>
   <si>
-    <t>2004조 2057억 1924만</t>
+    <t>2083조 2761억 2150만</t>
   </si>
   <si>
     <t>변신술사</t>
@@ -1035,22 +1305,22 @@
     <t>1888조 3627억 818만</t>
   </si>
   <si>
+    <t>뿡쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
+  </si>
+  <si>
+    <t>1799조 246억 9846만</t>
+  </si>
+  <si>
     <t>댜니</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>1739조 5479억 2768만</t>
-  </si>
-  <si>
-    <t>뿡쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
-  </si>
-  <si>
-    <t>1707조 2709억 6232만</t>
+    <t>1757조 1363억 1880만</t>
   </si>
   <si>
     <t>온백</t>
@@ -1059,7 +1329,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
   </si>
   <si>
-    <t>1491조 2311억 2507만</t>
+    <t>1491조 3442억 3139만</t>
+  </si>
+  <si>
+    <t>엘르가든</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
+  </si>
+  <si>
+    <t>1483조 2810억 4011만</t>
   </si>
   <si>
     <t>파울</t>
@@ -1068,16 +1347,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
   </si>
   <si>
-    <t>1425조 4762억 1692만</t>
-  </si>
-  <si>
-    <t>엘르가든</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
-  </si>
-  <si>
-    <t>1400조 9926억 8431만</t>
+    <t>1431조 346억 5059만</t>
   </si>
   <si>
     <t>마카롱롱</t>
@@ -1086,7 +1356,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
   </si>
   <si>
-    <t>1391조 2010억 3776만</t>
+    <t>1426조 665억 2214만</t>
   </si>
   <si>
     <t>짱잘자쿨냥</t>
@@ -1095,7 +1365,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%9E%98%EC%9E%90%EC%BF%A8%EB%83%A5</t>
   </si>
   <si>
-    <t>1027조 6078억 1748만</t>
+    <t>1052조 292억 883만</t>
   </si>
   <si>
     <t>대좀이</t>
@@ -1104,7 +1374,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>978조 3640억 5389만</t>
+    <t>978조 7832억 9889만</t>
   </si>
   <si>
     <t>모짜리코베르</t>
@@ -1119,7 +1389,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
   </si>
   <si>
-    <t>951조 2060억 9725만</t>
+    <t>953조 6362억 3238만</t>
   </si>
   <si>
     <t>김허덕</t>
@@ -1128,7 +1398,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
   </si>
   <si>
-    <t>882조 7278억 5282만</t>
+    <t>916조 5073억 5513만</t>
   </si>
   <si>
     <t>마갤</t>
@@ -1182,7 +1452,7 @@
     <t>https://mgf.gg/contents/character.php?n=Doham</t>
   </si>
   <si>
-    <t>627조 8627억 9090만</t>
+    <t>628조 6146억 917만</t>
   </si>
   <si>
     <t>고숨도칭</t>
@@ -1200,7 +1470,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
   </si>
   <si>
-    <t>547조 9327억 8104만</t>
+    <t>548조 5072억 4464만</t>
   </si>
   <si>
     <t>유플러스</t>
@@ -1209,10 +1479,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%94%8C%EB%9F%AC%EC%8A%A4</t>
   </si>
   <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>482조 8831억 8288만</t>
+    <t>486조 1731억 5041만</t>
   </si>
   <si>
     <t>진성팔퀴</t>
@@ -1233,273 +1500,6 @@
     <t>277조 36억 4103만</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EB%87%B8</t>
-  </si>
-  <si>
-    <t>5203조 5412억 3960만</t>
-  </si>
-  <si>
-    <t>손챠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%90%EC%B1%A0</t>
-  </si>
-  <si>
-    <t>4575조 5000억 9644만</t>
-  </si>
-  <si>
-    <t>GOD날두</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=GOD%EB%82%A0%EB%91%90</t>
-  </si>
-  <si>
-    <t>3907조 618억 9021만</t>
-  </si>
-  <si>
-    <t>강필구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%84%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>3886조 2944억 7368만</t>
-  </si>
-  <si>
-    <t>알배기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%8C%EB%B0%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>3214조 2193억 3893만</t>
-  </si>
-  <si>
-    <t>러브포티</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%B8%8C%ED%8F%AC%ED%8B%B0</t>
-  </si>
-  <si>
-    <t>2525조 3900억 9711만</t>
-  </si>
-  <si>
-    <t>테이킷슬로우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%85%8C%EC%9D%B4%ED%82%B7%EC%8A%AC%EB%A1%9C%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>2367조 6141억 542만</t>
-  </si>
-  <si>
-    <t>주요엘농산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%9A%94%EC%97%98%EB%86%8D%EC%82%B0</t>
-  </si>
-  <si>
-    <t>2128조 4643억 3752만</t>
-  </si>
-  <si>
-    <t>하찌바리이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B0%8C%EB%B0%94%EB%A6%AC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2120조 5849억 6712만</t>
-  </si>
-  <si>
-    <t>88치킨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=88%EC%B9%98%ED%82%A8</t>
-  </si>
-  <si>
-    <t>1621조 3630억 3601만</t>
-  </si>
-  <si>
-    <t>탕비실도우미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%95%EB%B9%84%EC%8B%A4%EB%8F%84%EC%9A%B0%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>1449조 9858억 2106만</t>
-  </si>
-  <si>
-    <t>Darken</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Darken</t>
-  </si>
-  <si>
-    <t>1428조 2881억 4391만</t>
-  </si>
-  <si>
-    <t>서늘한그늘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%8A%98%ED%95%9C%EA%B7%B8%EB%8A%98</t>
-  </si>
-  <si>
-    <t>1402조 805억 8만</t>
-  </si>
-  <si>
-    <t>하이하로하라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9D%B4%ED%95%98%EB%A1%9C%ED%95%98%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>1123조 1256억 7302만</t>
-  </si>
-  <si>
-    <t>차보이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EB%B3%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1005조 6484억 9494만</t>
-  </si>
-  <si>
-    <t>도레오</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%88%EC%98%A4</t>
-  </si>
-  <si>
-    <t>985조 3833억 8106만</t>
-  </si>
-  <si>
-    <t>여릿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%A6%BF</t>
-  </si>
-  <si>
-    <t>970조 8021억 203만</t>
-  </si>
-  <si>
-    <t>초읍사나이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%8D%EC%82%AC%EB%82%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>898조 9050억 2855만</t>
-  </si>
-  <si>
-    <t>v박효신v</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=v%EB%B0%95%ED%9A%A8%EC%8B%A0v</t>
-  </si>
-  <si>
-    <t>877조 8674억 153만</t>
-  </si>
-  <si>
-    <t>시간이돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B0%84%EC%9D%B4%EB%8F%88</t>
-  </si>
-  <si>
-    <t>818조 3610억 7891만</t>
-  </si>
-  <si>
-    <t>고으농</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%9C%BC%EB%86%8D</t>
-  </si>
-  <si>
-    <t>709조 2564억 5573만</t>
-  </si>
-  <si>
-    <t>영구짱구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%81%EA%B5%AC%EC%A7%B1%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>708조 6531억 8974만</t>
-  </si>
-  <si>
-    <t>다둉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>655조 928억 6795만</t>
-  </si>
-  <si>
-    <t>도사랑화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%82%AC%EB%9E%91%ED%99%94</t>
-  </si>
-  <si>
-    <t>599조 3582억 8395만</t>
-  </si>
-  <si>
-    <t>뜌미누</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9C%8C%EB%AF%B8%EB%88%84</t>
-  </si>
-  <si>
-    <t>576조 4166억 7025만</t>
-  </si>
-  <si>
-    <t>발진</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%9C%EC%A7%84</t>
-  </si>
-  <si>
-    <t>559조 8595억 2848만</t>
-  </si>
-  <si>
-    <t>익뇸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%87%B8</t>
-  </si>
-  <si>
-    <t>469조 5981억 3531만</t>
-  </si>
-  <si>
-    <t>하엘이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%97%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>390조 8622억 7970만</t>
-  </si>
-  <si>
-    <t>나는배불러요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%8A%94%EB%B0%B0%EB%B6%88%EB%9F%AC%EC%9A%94</t>
-  </si>
-  <si>
-    <t>380조 861억 5166만</t>
-  </si>
-  <si>
-    <t>아리미쿵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A6%AC%EB%AF%B8%EC%BF%B5</t>
-  </si>
-  <si>
-    <t>374조 138억 2953만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EA%B8%B0%EC%9C%A0%EB%AC%B4</t>
   </si>
   <si>
@@ -1530,7 +1530,7 @@
     <t>https://mgf.gg/contents/character.php?n=2%EB%B2%88%EC%A7%B8%EC%BA%90%EB%A6%AD</t>
   </si>
   <si>
-    <t>2958조 1473억 9921만</t>
+    <t>3011조 6164억 1039만</t>
   </si>
   <si>
     <t>장뱁새</t>
@@ -1557,7 +1557,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EA%BD%81%EB%83%89%EB%B2%95</t>
   </si>
   <si>
-    <t>1592조 4211억 6015만</t>
+    <t>1592조 5197억 2855만</t>
   </si>
   <si>
     <t>라쥬르</t>
@@ -1575,7 +1575,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EA%B8%B0%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>1294조 966억 5266만</t>
+    <t>1296조 9411억 8740만</t>
   </si>
   <si>
     <t>브네</t>
@@ -1584,7 +1584,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%84%A4</t>
   </si>
   <si>
-    <t>1228조 4840억 9179만</t>
+    <t>1236조 4698억 7192만</t>
   </si>
   <si>
     <t>빙율</t>
@@ -1593,7 +1593,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%99%EC%9C%A8</t>
   </si>
   <si>
-    <t>1003조 4784억 1839만</t>
+    <t>1031조 5997억 5573만</t>
   </si>
   <si>
     <t>33세배장호</t>
@@ -1656,7 +1656,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%8D%B4</t>
   </si>
   <si>
-    <t>671조 304억 1814만</t>
+    <t>672조 1832억 1101만</t>
   </si>
   <si>
     <t>타뤽</t>
@@ -1683,7 +1683,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%ED%99%A9%EC%83%88</t>
   </si>
   <si>
-    <t>482조 7128억 6384만</t>
+    <t>522조 356억 75만</t>
+  </si>
+  <si>
+    <t>럭키루키</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9F%AD%ED%82%A4%EB%A3%A8%ED%82%A4</t>
+  </si>
+  <si>
+    <t>448조 9818억 5133만</t>
   </si>
   <si>
     <t>넬샷</t>
@@ -1692,16 +1701,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%AC%EC%83%B7</t>
   </si>
   <si>
-    <t>445조 1131억 3507만</t>
-  </si>
-  <si>
-    <t>럭키루키</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9F%AD%ED%82%A4%EB%A3%A8%ED%82%A4</t>
-  </si>
-  <si>
-    <t>442조 4965억 5609만</t>
+    <t>445조 7566억 761만</t>
   </si>
   <si>
     <t>박도란</t>
@@ -1728,7 +1728,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
   </si>
   <si>
-    <t>375조 2668억 3844만</t>
+    <t>375조 3772억 9734만</t>
   </si>
   <si>
     <t>뿌앵뿌앵</t>
@@ -1746,7 +1746,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%ED%99%8D%EC%9D%B4</t>
   </si>
   <si>
-    <t>223조 4994억 6998만</t>
+    <t>233조 3745억 9305만</t>
   </si>
   <si>
     <t>윤빵쭈</t>
@@ -1755,7 +1755,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EB%B9%B5%EC%AD%88</t>
   </si>
   <si>
-    <t>217조 8780억 2602만</t>
+    <t>217조 9908억 7127만</t>
   </si>
   <si>
     <t>꺄꽁</t>
@@ -1764,7 +1764,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BA%84%EA%BD%81</t>
   </si>
   <si>
-    <t>6901조 9733억 8619만</t>
+    <t>6904조 481억 4485만</t>
   </si>
   <si>
     <t>별쌥</t>
@@ -1773,7 +1773,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A5</t>
   </si>
   <si>
-    <t>5132조 1321억 7494만</t>
+    <t>5154조 7176억 1397만</t>
   </si>
   <si>
     <t>진욱이에요</t>
@@ -1788,7 +1788,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A5%B4%EB%AA%AC</t>
   </si>
   <si>
-    <t>2836조 4957억 4786만</t>
+    <t>2964조 9616억 8154만</t>
   </si>
   <si>
     <t>낭만황금망치</t>
@@ -1797,7 +1797,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%ED%99%A9%EA%B8%88%EB%A7%9D%EC%B9%98</t>
   </si>
   <si>
-    <t>2725조 47억 9055만</t>
+    <t>2756조 5810억 8494만</t>
   </si>
   <si>
     <t>김슴줌1</t>
@@ -1806,7 +1806,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%8A%B4%EC%A4%8C1</t>
   </si>
   <si>
-    <t>2463조 8467억 9186만</t>
+    <t>2521조 9561억 5399만</t>
+  </si>
+  <si>
+    <t>호두와감자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%91%90%EC%99%80%EA%B0%90%EC%9E%90</t>
+  </si>
+  <si>
+    <t>2152조 1249억 4826만</t>
   </si>
   <si>
     <t>천달</t>
@@ -1815,16 +1824,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EB%8B%AC</t>
   </si>
   <si>
-    <t>2141조 9784억 7690만</t>
-  </si>
-  <si>
-    <t>호두와감자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%91%90%EC%99%80%EA%B0%90%EC%9E%90</t>
-  </si>
-  <si>
-    <t>2096조 549억 4046만</t>
+    <t>2149조 1188억 9046만</t>
   </si>
   <si>
     <t>쿠댜</t>
@@ -1842,7 +1842,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EC%A7%95</t>
   </si>
   <si>
-    <t>1477조 1901억 1245만</t>
+    <t>1583조 6911억 8361만</t>
   </si>
   <si>
     <t>활용</t>
@@ -1860,7 +1860,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EA%B3%A1</t>
   </si>
   <si>
-    <t>891조 5989억 2514만</t>
+    <t>898조 1648억 6794만</t>
   </si>
   <si>
     <t>턍ol</t>
@@ -1869,7 +1869,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%84%8Dol</t>
   </si>
   <si>
-    <t>663조 7250억 2403만</t>
+    <t>667조 2327억 3215만</t>
   </si>
   <si>
     <t>게렬곰</t>
@@ -1878,7 +1878,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%EB%A0%AC%EA%B3%B0</t>
   </si>
   <si>
-    <t>654조 1115억 5671만</t>
+    <t>654조 8716억 3599만</t>
   </si>
   <si>
     <t>까쿠미</t>
@@ -1899,6 +1899,15 @@
     <t>640조 1455억 8439만</t>
   </si>
   <si>
+    <t>별쌤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A4</t>
+  </si>
+  <si>
+    <t>622조 5518억 5064만</t>
+  </si>
+  <si>
     <t>띠우</t>
   </si>
   <si>
@@ -1908,22 +1917,13 @@
     <t>606조 7449억 8996만</t>
   </si>
   <si>
-    <t>별쌤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A4</t>
-  </si>
-  <si>
-    <t>605조 135억 1888만</t>
-  </si>
-  <si>
     <t>초이레</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%B4%EB%A0%88</t>
   </si>
   <si>
-    <t>483조 5947억 1837만</t>
+    <t>495조 5334억 8326만</t>
   </si>
   <si>
     <t>민족고대감자</t>
@@ -1935,6 +1935,15 @@
     <t>447조 5787억 6359만</t>
   </si>
   <si>
+    <t>끄챰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%81%84%EC%B1%B0</t>
+  </si>
+  <si>
+    <t>433조 1790억 4867만</t>
+  </si>
+  <si>
     <t>승아의하루</t>
   </si>
   <si>
@@ -1944,22 +1953,22 @@
     <t>419조 8392억 5458만</t>
   </si>
   <si>
-    <t>끄챰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%81%84%EC%B1%B0</t>
-  </si>
-  <si>
-    <t>412조 7920억 6036만</t>
-  </si>
-  <si>
     <t>쿠까미</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EA%B9%8C%EB%AF%B8</t>
   </si>
   <si>
-    <t>407조 1167억 2176만</t>
+    <t>415조 5101억 5476만</t>
+  </si>
+  <si>
+    <t>툼스데이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%88%BC%EC%8A%A4%EB%8D%B0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>285조 1117억 8099만</t>
   </si>
   <si>
     <t>택Ol</t>
@@ -1977,16 +1986,7 @@
     <t>https://mgf.gg/contents/character.php?n=08217</t>
   </si>
   <si>
-    <t>275조 3869억 9547만</t>
-  </si>
-  <si>
-    <t>툼스데이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%88%BC%EC%8A%A4%EB%8D%B0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>246조 9543억 8317만</t>
+    <t>275조 8660억 7908만</t>
   </si>
   <si>
     <t>왕단단이</t>
@@ -2004,7 +2004,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%9D%B4%EC%A5%94</t>
   </si>
   <si>
-    <t>219조 8367억 8039만</t>
+    <t>220조 7378억 9699만</t>
   </si>
   <si>
     <t>꾸현</t>
@@ -2034,7 +2034,7 @@
     <t>116</t>
   </si>
   <si>
-    <t>4경 5919조 3484억 4327만</t>
+    <t>4경 6916조 5364억 277만</t>
   </si>
   <si>
     <t>할바이</t>
@@ -2046,7 +2046,7 @@
     <t>107</t>
   </si>
   <si>
-    <t>184조 9307억 32만</t>
+    <t>185조 510억 1212만</t>
   </si>
   <si>
     <t>섹밍</t>
@@ -2055,7 +2055,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B9%EB%B0%8D</t>
   </si>
   <si>
-    <t>179조 4697억 6535만</t>
+    <t>182조 8452억 2024만</t>
   </si>
   <si>
     <t>대구남성</t>
@@ -2088,7 +2088,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>30조 7088억 1566만</t>
+    <t>31조 9616억 1520만</t>
   </si>
   <si>
     <t>낭랑28세</t>
@@ -2109,15 +2109,6 @@
     <t>27조 7454억 2342만</t>
   </si>
   <si>
-    <t>뭐하는게임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AD%90%ED%95%98%EB%8A%94%EA%B2%8C%EC%9E%84</t>
-  </si>
-  <si>
-    <t>26조 7249억 7710만</t>
-  </si>
-  <si>
     <t>돈성</t>
   </si>
   <si>
@@ -2127,22 +2118,22 @@
     <t>26조 6536억 9041만</t>
   </si>
   <si>
+    <t>빵신궁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EC%8B%A0%EA%B6%81</t>
+  </si>
+  <si>
+    <t>25조 8899억 815만</t>
+  </si>
+  <si>
     <t>오스띤</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%8A%A4%EB%9D%A4</t>
   </si>
   <si>
-    <t>25조 294억 3111만</t>
-  </si>
-  <si>
-    <t>빵신궁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EC%8B%A0%EA%B6%81</t>
-  </si>
-  <si>
-    <t>23조 2234억 7980만</t>
+    <t>25조 1534억 6428만</t>
   </si>
   <si>
     <t>씅놈</t>
@@ -2154,7 +2145,16 @@
     <t>103</t>
   </si>
   <si>
-    <t>21조 4758억 2277만</t>
+    <t>21조 5414억 9145만</t>
+  </si>
+  <si>
+    <t>고통받는갈비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%ED%86%B5%EB%B0%9B%EB%8A%94%EA%B0%88%EB%B9%84</t>
+  </si>
+  <si>
+    <t>19조 5947억 2985만</t>
   </si>
   <si>
     <t>마키맛키마</t>
@@ -2166,22 +2166,22 @@
     <t>19조 5230억 2961만</t>
   </si>
   <si>
+    <t>밀초크코</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%EC%B4%88%ED%81%AC%EC%BD%94</t>
+  </si>
+  <si>
+    <t>19조 5171억 2730만</t>
+  </si>
+  <si>
     <t>킬혁</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%82%AC%ED%98%81</t>
   </si>
   <si>
-    <t>19조 227억 3114만</t>
-  </si>
-  <si>
-    <t>고통받는갈비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%ED%86%B5%EB%B0%9B%EB%8A%94%EA%B0%88%EB%B9%84</t>
-  </si>
-  <si>
-    <t>19조 124억 8712만</t>
+    <t>19조 1678억 560만</t>
   </si>
   <si>
     <t>우루차</t>
@@ -2190,16 +2190,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%A3%A8%EC%B0%A8</t>
   </si>
   <si>
-    <t>18조 6278억 5908만</t>
-  </si>
-  <si>
-    <t>밀초크코</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%EC%B4%88%ED%81%AC%EC%BD%94</t>
-  </si>
-  <si>
-    <t>17조 3335억 2558만</t>
+    <t>18조 9074억 3093만</t>
   </si>
   <si>
     <t>썬콜우체국</t>
@@ -2208,7 +2199,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9A%B0%EC%B2%B4%EA%B5%AD</t>
   </si>
   <si>
-    <t>16조 9302억 5236만</t>
+    <t>17조 80억 6779만</t>
   </si>
   <si>
     <t>배렛나루왁서</t>
@@ -2238,7 +2229,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%95%A1%EC%9A%94%EB%82%98%ED%90%81</t>
   </si>
   <si>
-    <t>12조 2637억 8958만</t>
+    <t>12조 2790억 7295만</t>
   </si>
   <si>
     <t>썬콜법사ss</t>
@@ -2250,22 +2241,22 @@
     <t>11조 4563억 4132만</t>
   </si>
   <si>
+    <t>포디케이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%94%94%EC%BC%80%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>7조 4410억 1237만</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%ED%82%A4%EB%B9%84%ED%82%A4</t>
   </si>
   <si>
-    <t>5조 8535억 6831만</t>
-  </si>
-  <si>
-    <t>포디케이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%94%94%EC%BC%80%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>5조 4032억 1370만</t>
+    <t>6조 864억 9467만</t>
   </si>
   <si>
     <t>경기도인</t>
@@ -2814,7 +2805,7 @@
         <v>19</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>39</v>
@@ -2855,7 +2846,7 @@
         <v>19</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>47</v>
@@ -2896,7 +2887,7 @@
         <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>55</v>
@@ -2937,7 +2928,7 @@
         <v>19</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>63</v>
@@ -3010,1017 +3001,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J30"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -4068,31 +3048,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>218</v>
+        <v>85</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>218</v>
+        <v>85</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>219</v>
+        <v>86</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4100,31 +3080,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>221</v>
+        <v>92</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>221</v>
+        <v>92</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>222</v>
+        <v>93</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>223</v>
+        <v>94</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>224</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4132,31 +3112,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>225</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>225</v>
+        <v>97</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>226</v>
+        <v>98</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>227</v>
+        <v>101</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4164,31 +3144,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>228</v>
+        <v>103</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>228</v>
+        <v>103</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>229</v>
+        <v>104</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>230</v>
+        <v>105</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>231</v>
+        <v>106</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4196,31 +3176,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>232</v>
+        <v>108</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>232</v>
+        <v>108</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>233</v>
+        <v>109</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>234</v>
+        <v>111</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4228,31 +3208,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>235</v>
+        <v>113</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>236</v>
+        <v>116</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4260,31 +3240,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>237</v>
+        <v>118</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>237</v>
+        <v>118</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>238</v>
+        <v>119</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4292,31 +3272,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>240</v>
+        <v>122</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>241</v>
+        <v>123</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>242</v>
+        <v>125</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4324,31 +3304,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>243</v>
+        <v>127</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>243</v>
+        <v>127</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>244</v>
+        <v>128</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>245</v>
+        <v>130</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4356,31 +3336,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>246</v>
+        <v>132</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>246</v>
+        <v>132</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>247</v>
+        <v>133</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>248</v>
+        <v>134</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4388,31 +3368,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>249</v>
+        <v>136</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>249</v>
+        <v>136</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>250</v>
+        <v>137</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>207</v>
+        <v>138</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>251</v>
+        <v>139</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4420,31 +3400,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>252</v>
+        <v>141</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>252</v>
+        <v>141</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>253</v>
+        <v>142</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>254</v>
+        <v>143</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4452,31 +3432,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>255</v>
+        <v>145</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>255</v>
+        <v>145</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>256</v>
+        <v>146</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>257</v>
+        <v>147</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4484,31 +3464,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>258</v>
+        <v>149</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>258</v>
+        <v>149</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>259</v>
+        <v>150</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>260</v>
+        <v>151</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4516,31 +3496,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>261</v>
+        <v>153</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>261</v>
+        <v>153</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>262</v>
+        <v>154</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>263</v>
+        <v>155</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4548,31 +3528,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>264</v>
-      </c>
       <c r="D17" s="2" t="s">
-        <v>264</v>
+        <v>157</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>265</v>
+        <v>158</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>266</v>
+        <v>159</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4580,31 +3560,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>268</v>
-      </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>269</v>
+        <v>164</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4612,31 +3592,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>270</v>
+        <v>166</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>271</v>
+        <v>167</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>272</v>
+        <v>168</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4644,31 +3624,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>273</v>
-      </c>
       <c r="D20" s="2" t="s">
-        <v>273</v>
+        <v>170</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>274</v>
+        <v>171</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>275</v>
+        <v>173</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4676,31 +3656,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>276</v>
+        <v>175</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>276</v>
+        <v>175</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>277</v>
+        <v>176</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>278</v>
+        <v>177</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4708,31 +3688,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>279</v>
+        <v>179</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>279</v>
+        <v>179</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>280</v>
+        <v>180</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>207</v>
+        <v>138</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>281</v>
+        <v>181</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4740,31 +3720,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>282</v>
+        <v>183</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>282</v>
+        <v>183</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>283</v>
+        <v>184</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>207</v>
+        <v>138</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>284</v>
+        <v>185</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4772,31 +3752,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>285</v>
+        <v>187</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>285</v>
+        <v>187</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>286</v>
+        <v>188</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>287</v>
+        <v>189</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4804,31 +3784,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>288</v>
+        <v>191</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>288</v>
+        <v>191</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>289</v>
+        <v>192</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>290</v>
+        <v>194</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4836,31 +3816,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>195</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>291</v>
+        <v>196</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>291</v>
+        <v>196</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>292</v>
+        <v>197</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>207</v>
+        <v>138</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>293</v>
+        <v>198</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4868,31 +3848,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>294</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>294</v>
+        <v>200</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>295</v>
+        <v>201</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>296</v>
+        <v>202</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4900,31 +3880,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>297</v>
-      </c>
       <c r="D28" s="2" t="s">
-        <v>297</v>
+        <v>204</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>298</v>
+        <v>205</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>299</v>
+        <v>206</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4932,31 +3912,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>301</v>
-      </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>230</v>
+        <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>302</v>
+        <v>210</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4964,31 +3944,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>304</v>
-      </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>305</v>
+        <v>214</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4996,31 +3976,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>306</v>
+        <v>215</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>307</v>
+        <v>216</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>307</v>
+        <v>216</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>308</v>
+        <v>217</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>309</v>
+        <v>219</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5064,6 +4044,1017 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J30"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
@@ -5119,25 +5110,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>311</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5151,25 +5142,25 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>314</v>
-      </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>207</v>
+        <v>129</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5180,28 +5171,28 @@
         <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>318</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5215,25 +5206,25 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>321</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5247,25 +5238,25 @@
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>323</v>
-      </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5279,25 +5270,25 @@
         <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>327</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5311,25 +5302,25 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>329</v>
-      </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>223</v>
+        <v>260</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5340,28 +5331,28 @@
         <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>333</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5375,25 +5366,25 @@
         <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>336</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5404,28 +5395,28 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5436,25 +5427,25 @@
         <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>342</v>
@@ -5468,7 +5459,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>343</v>
@@ -5483,10 +5474,10 @@
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>207</v>
+        <v>99</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>345</v>
@@ -5500,7 +5491,7 @@
         <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>346</v>
@@ -5515,10 +5506,10 @@
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>216</v>
+        <v>129</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>348</v>
@@ -5547,10 +5538,10 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>351</v>
@@ -5579,10 +5570,10 @@
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>354</v>
@@ -5596,7 +5587,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>355</v>
@@ -5611,10 +5602,10 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>223</v>
+        <v>129</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>357</v>
@@ -5628,7 +5619,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>358</v>
@@ -5643,7 +5634,7 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>115</v>
@@ -5660,28 +5651,28 @@
         <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>41</v>
+        <v>361</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>41</v>
+        <v>361</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5692,28 +5683,28 @@
         <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>94</v>
+        <v>308</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5727,13 +5718,13 @@
         <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
@@ -5742,10 +5733,10 @@
         <v>94</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5759,25 +5750,25 @@
         <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>94</v>
+        <v>260</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5791,25 +5782,25 @@
         <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>207</v>
+        <v>110</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5823,25 +5814,25 @@
         <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>88</v>
+        <v>260</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5855,25 +5846,25 @@
         <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>198</v>
+        <v>124</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5887,25 +5878,25 @@
         <v>195</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5916,28 +5907,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>230</v>
+        <v>138</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>198</v>
+        <v>124</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5948,28 +5939,28 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5980,25 +5971,25 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>392</v>
+        <v>172</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>393</v>
@@ -6012,7 +6003,7 @@
         <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>394</v>
@@ -6027,10 +6018,10 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>230</v>
+        <v>341</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>396</v>
@@ -6044,7 +6035,7 @@
         <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>306</v>
+        <v>215</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>397</v>
@@ -6059,10 +6050,10 @@
         <v>87</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>207</v>
+        <v>99</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>198</v>
+        <v>163</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>399</v>
@@ -6164,25 +6155,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>49</v>
+        <v>400</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>400</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6196,25 +6187,25 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6225,28 +6216,28 @@
         <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6260,25 +6251,25 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6292,25 +6283,25 @@
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6324,25 +6315,25 @@
         <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6356,25 +6347,25 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>146</v>
+        <v>94</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6385,28 +6376,28 @@
         <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6420,25 +6411,25 @@
         <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>160</v>
+        <v>308</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6449,28 +6440,28 @@
         <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>216</v>
+        <v>110</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6481,28 +6472,28 @@
         <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>392</v>
+        <v>222</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6513,28 +6504,28 @@
         <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>110</v>
+        <v>308</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6545,28 +6536,28 @@
         <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6580,25 +6571,25 @@
         <v>148</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6612,25 +6603,25 @@
         <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6641,28 +6632,28 @@
         <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6673,28 +6664,28 @@
         <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6705,25 +6696,25 @@
         <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>450</v>
+        <v>49</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>450</v>
+        <v>49</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>451</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>452</v>
@@ -6737,7 +6728,7 @@
         <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>453</v>
@@ -6752,10 +6743,10 @@
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>216</v>
+        <v>110</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>455</v>
@@ -6784,10 +6775,10 @@
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>223</v>
+        <v>110</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>458</v>
@@ -6816,7 +6807,7 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>146</v>
+        <v>110</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>115</v>
@@ -6848,10 +6839,10 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>198</v>
+        <v>163</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>464</v>
@@ -6880,10 +6871,10 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>146</v>
+        <v>222</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>467</v>
@@ -6912,10 +6903,10 @@
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>115</v>
+        <v>193</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>470</v>
@@ -6944,10 +6935,10 @@
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>198</v>
+        <v>163</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>473</v>
@@ -6961,7 +6952,7 @@
         <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>474</v>
@@ -6976,10 +6967,10 @@
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>207</v>
+        <v>105</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>115</v>
+        <v>193</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>476</v>
@@ -6993,7 +6984,7 @@
         <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>477</v>
@@ -7011,7 +7002,7 @@
         <v>110</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>198</v>
+        <v>163</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>479</v>
@@ -7025,7 +7016,7 @@
         <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>480</v>
@@ -7040,10 +7031,10 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>392</v>
+        <v>341</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>482</v>
@@ -7057,7 +7048,7 @@
         <v>42</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>483</v>
@@ -7072,10 +7063,10 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>485</v>
@@ -7089,7 +7080,7 @@
         <v>42</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>306</v>
+        <v>215</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>486</v>
@@ -7104,10 +7095,10 @@
         <v>87</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>488</v>
@@ -7218,13 +7209,13 @@
         <v>489</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>490</v>
@@ -7253,10 +7244,10 @@
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>89</v>
+        <v>232</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>493</v>
@@ -7270,7 +7261,7 @@
         <v>50</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>494</v>
@@ -7285,10 +7276,10 @@
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>496</v>
@@ -7317,10 +7308,10 @@
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>499</v>
@@ -7349,10 +7340,10 @@
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>502</v>
@@ -7381,10 +7372,10 @@
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>230</v>
+        <v>105</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>505</v>
@@ -7413,10 +7404,10 @@
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>508</v>
@@ -7430,7 +7421,7 @@
         <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>509</v>
@@ -7445,10 +7436,10 @@
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>146</v>
+        <v>260</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>511</v>
@@ -7477,10 +7468,10 @@
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>514</v>
@@ -7494,7 +7485,7 @@
         <v>50</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>515</v>
@@ -7509,10 +7500,10 @@
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>517</v>
@@ -7526,7 +7517,7 @@
         <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>518</v>
@@ -7541,10 +7532,10 @@
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>520</v>
@@ -7558,7 +7549,7 @@
         <v>50</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>521</v>
@@ -7573,10 +7564,10 @@
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>523</v>
@@ -7590,7 +7581,7 @@
         <v>50</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>524</v>
@@ -7605,10 +7596,10 @@
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>526</v>
@@ -7637,10 +7628,10 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>88</v>
+        <v>222</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>529</v>
@@ -7669,10 +7660,10 @@
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>207</v>
+        <v>138</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>532</v>
@@ -7686,7 +7677,7 @@
         <v>50</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>533</v>
@@ -7701,10 +7692,10 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>223</v>
+        <v>94</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>535</v>
@@ -7718,7 +7709,7 @@
         <v>50</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>536</v>
@@ -7733,10 +7724,10 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>538</v>
@@ -7750,7 +7741,7 @@
         <v>50</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>539</v>
@@ -7765,10 +7756,10 @@
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>223</v>
+        <v>94</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>541</v>
@@ -7782,7 +7773,7 @@
         <v>50</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>542</v>
@@ -7797,10 +7788,10 @@
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>207</v>
+        <v>138</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>544</v>
@@ -7829,10 +7820,10 @@
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>547</v>
@@ -7861,10 +7852,10 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>550</v>
@@ -7893,10 +7884,10 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>198</v>
+        <v>163</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>553</v>
@@ -7925,10 +7916,10 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>556</v>
@@ -7957,10 +7948,10 @@
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>559</v>
@@ -7989,10 +7980,10 @@
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>562</v>
@@ -8006,7 +7997,7 @@
         <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>563</v>
@@ -8021,10 +8012,10 @@
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>565</v>
@@ -8038,7 +8029,7 @@
         <v>50</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>566</v>
@@ -8053,10 +8044,10 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>216</v>
+        <v>308</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>568</v>
@@ -8070,7 +8061,7 @@
         <v>50</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>569</v>
@@ -8085,10 +8076,10 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>571</v>
@@ -8102,7 +8093,7 @@
         <v>50</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>572</v>
@@ -8117,10 +8108,10 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>392</v>
+        <v>341</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>574</v>
@@ -8233,10 +8224,10 @@
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>577</v>
@@ -8265,10 +8256,10 @@
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>580</v>
@@ -8282,7 +8273,7 @@
         <v>58</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>581</v>
@@ -8297,10 +8288,10 @@
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>207</v>
+        <v>138</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>583</v>
@@ -8326,13 +8317,13 @@
         <v>584</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>585</v>
@@ -8361,10 +8352,10 @@
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>588</v>
@@ -8393,10 +8384,10 @@
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>230</v>
+        <v>105</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>591</v>
@@ -8425,10 +8416,10 @@
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>594</v>
@@ -8442,7 +8433,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>595</v>
@@ -8457,10 +8448,10 @@
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>597</v>
@@ -8489,10 +8480,10 @@
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>600</v>
@@ -8506,7 +8497,7 @@
         <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>601</v>
@@ -8521,10 +8512,10 @@
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>603</v>
@@ -8538,7 +8529,7 @@
         <v>58</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>604</v>
@@ -8553,10 +8544,10 @@
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>88</v>
+        <v>222</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>606</v>
@@ -8570,7 +8561,7 @@
         <v>58</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>607</v>
@@ -8585,10 +8576,10 @@
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>609</v>
@@ -8602,7 +8593,7 @@
         <v>58</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>610</v>
@@ -8617,10 +8608,10 @@
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>612</v>
@@ -8649,10 +8640,10 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>615</v>
@@ -8681,10 +8672,10 @@
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>207</v>
+        <v>138</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>618</v>
@@ -8698,7 +8689,7 @@
         <v>58</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>619</v>
@@ -8713,10 +8704,10 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>621</v>
@@ -8730,7 +8721,7 @@
         <v>58</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>622</v>
@@ -8745,10 +8736,10 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>198</v>
+        <v>124</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>624</v>
@@ -8762,7 +8753,7 @@
         <v>58</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>625</v>
@@ -8777,10 +8768,10 @@
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>115</v>
+        <v>193</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>627</v>
@@ -8794,7 +8785,7 @@
         <v>58</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>628</v>
@@ -8809,10 +8800,10 @@
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>630</v>
@@ -8841,10 +8832,10 @@
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>392</v>
+        <v>341</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>633</v>
@@ -8873,10 +8864,10 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>198</v>
+        <v>163</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>636</v>
@@ -8905,10 +8896,10 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>639</v>
@@ -8937,10 +8928,10 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>642</v>
@@ -8969,10 +8960,10 @@
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>645</v>
@@ -9001,10 +8992,10 @@
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>94</v>
+        <v>222</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>648</v>
@@ -9018,7 +9009,7 @@
         <v>58</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>649</v>
@@ -9033,10 +9024,10 @@
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>651</v>
@@ -9050,7 +9041,7 @@
         <v>58</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>652</v>
@@ -9065,10 +9056,10 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>230</v>
+        <v>105</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>654</v>
@@ -9082,7 +9073,7 @@
         <v>58</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>655</v>
@@ -9097,10 +9088,10 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>657</v>
@@ -9114,7 +9105,7 @@
         <v>58</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>658</v>
@@ -9129,10 +9120,10 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>660</v>
@@ -9146,7 +9137,7 @@
         <v>58</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>306</v>
+        <v>215</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>661</v>
@@ -9161,10 +9152,10 @@
         <v>87</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>663</v>
@@ -9213,7 +9204,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -9221,7 +9212,7 @@
     <col min="3" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9277,7 +9268,7 @@
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>666</v>
@@ -9309,7 +9300,7 @@
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>670</v>
@@ -9326,7 +9317,7 @@
         <v>66</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>672</v>
@@ -9341,10 +9332,10 @@
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>674</v>
@@ -9373,7 +9364,7 @@
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>677</v>
@@ -9405,7 +9396,7 @@
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>677</v>
@@ -9437,7 +9428,7 @@
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>392</v>
+        <v>341</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>684</v>
@@ -9469,7 +9460,7 @@
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>392</v>
+        <v>341</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>684</v>
@@ -9486,7 +9477,7 @@
         <v>66</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>689</v>
@@ -9501,7 +9492,7 @@
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>223</v>
+        <v>94</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>684</v>
@@ -9533,7 +9524,7 @@
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>684</v>
@@ -9550,7 +9541,7 @@
         <v>66</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>695</v>
@@ -9565,7 +9556,7 @@
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>230</v>
+        <v>341</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>684</v>
@@ -9582,7 +9573,7 @@
         <v>66</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>698</v>
@@ -9597,7 +9588,7 @@
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>684</v>
@@ -9614,7 +9605,7 @@
         <v>66</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>701</v>
@@ -9629,13 +9620,13 @@
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>392</v>
+        <v>222</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>684</v>
+        <v>703</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9646,25 +9637,25 @@
         <v>66</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>707</v>
@@ -9693,7 +9684,7 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>216</v>
+        <v>308</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>684</v>
@@ -9725,10 +9716,10 @@
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>713</v>
@@ -9742,7 +9733,7 @@
         <v>66</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>714</v>
@@ -9757,10 +9748,10 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>716</v>
@@ -9774,7 +9765,7 @@
         <v>66</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>717</v>
@@ -9789,10 +9780,10 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>719</v>
@@ -9806,7 +9797,7 @@
         <v>66</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>720</v>
@@ -9821,10 +9812,10 @@
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>94</v>
+        <v>308</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>722</v>
@@ -9838,7 +9829,7 @@
         <v>66</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>723</v>
@@ -9853,10 +9844,10 @@
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>216</v>
+        <v>99</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>725</v>
@@ -9885,13 +9876,13 @@
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>706</v>
+        <v>728</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9905,22 +9896,22 @@
         <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>207</v>
+        <v>88</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>731</v>
+        <v>703</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>732</v>
@@ -9949,10 +9940,10 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>100</v>
+        <v>308</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>735</v>
@@ -9981,13 +9972,13 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>216</v>
+        <v>138</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>706</v>
+        <v>738</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -10007,19 +9998,19 @@
         <v>75</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>230</v>
+        <v>105</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -10033,22 +10024,22 @@
         <v>195</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>207</v>
+        <v>94</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>744</v>
@@ -10062,7 +10053,7 @@
         <v>66</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>745</v>
@@ -10077,52 +10068,20 @@
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>223</v>
+        <v>94</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>748</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>748</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J28"/>
+  <autoFilter ref="A1:J27"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -10150,7 +10109,6 @@
     <hyperlink ref="E25" r:id="rId24"/>
     <hyperlink ref="E26" r:id="rId25"/>
     <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -231,7 +231,7 @@
     <t>5경 985조 128억 1537만</t>
   </si>
   <si>
-    <t>셀린느2군 IN 300위분들   귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
+    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
   </si>
   <si>
     <t>자유이용껀</t>
@@ -309,7 +309,7 @@
     <t>117</t>
   </si>
   <si>
-    <t>6경 6141조 4,657억 3,898만</t>
+    <t>6경 6141조 4657억 3898만</t>
   </si>
   <si>
     <t>2</t>
@@ -327,7 +327,7 @@
     <t>116</t>
   </si>
   <si>
-    <t>2경 8747조 2,524억 6,858만</t>
+    <t>2경 8747조 2524억 6858만</t>
   </si>
   <si>
     <t>3</t>
@@ -345,7 +345,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>1경 630조 4,441억 5,868만</t>
+    <t>1경 630조 4441억 5868만</t>
   </si>
   <si>
     <t>4</t>
@@ -363,7 +363,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>6327조 503억 4,939만</t>
+    <t>6327조 503억 4939만</t>
   </si>
   <si>
     <t>5</t>
@@ -375,7 +375,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%90%EC%B1%A0</t>
   </si>
   <si>
-    <t>4842조 8,830억 3,283만</t>
+    <t>4842조 8830억 3283만</t>
   </si>
   <si>
     <t>6</t>
@@ -387,7 +387,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%84%EA%B5%AC</t>
   </si>
   <si>
-    <t>4808조 4,650억 4,072만</t>
+    <t>4808조 4650억 4072만</t>
   </si>
   <si>
     <t>7</t>
@@ -399,7 +399,7 @@
     <t>https://mgf.gg/contents/character.php?n=GOD%EB%82%A0%EB%91%90</t>
   </si>
   <si>
-    <t>4260조 3,079억 8,728만</t>
+    <t>4260조 3079억 8728만</t>
   </si>
   <si>
     <t>8</t>
@@ -414,7 +414,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>3846조 9,002억 873만</t>
+    <t>3846조 9002억 873만</t>
   </si>
   <si>
     <t>9</t>
@@ -429,7 +429,7 @@
     <t>111</t>
   </si>
   <si>
-    <t>3339조 7,819억 8,470만</t>
+    <t>3339조 7819억 8470만</t>
   </si>
   <si>
     <t>10</t>
@@ -441,7 +441,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B0%8C%EB%B0%94%EB%A6%AC%EC%9D%B4</t>
   </si>
   <si>
-    <t>2938조 9,566억 7,745만</t>
+    <t>2938조 9566억 7745만</t>
   </si>
   <si>
     <t>11</t>
@@ -453,7 +453,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%B8%8C%ED%8F%AC%ED%8B%B0</t>
   </si>
   <si>
-    <t>2805조 7,388억 7,122만</t>
+    <t>2805조 7388억 7122만</t>
   </si>
   <si>
     <t>12</t>
@@ -468,7 +468,7 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>2367조 6,141억 542만</t>
+    <t>2367조 6141억 542만</t>
   </si>
   <si>
     <t>13</t>
@@ -480,7 +480,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EA%B8%88%EC%96%B4%EA%B8%88%EB%8B%88</t>
   </si>
   <si>
-    <t>2171조 2,630억 8,147만</t>
+    <t>2171조 2630억 8147만</t>
   </si>
   <si>
     <t>14</t>
@@ -495,7 +495,7 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>1860조 7,967억 6,835만</t>
+    <t>1860조 7967억 6835만</t>
   </si>
   <si>
     <t>15</t>
@@ -510,7 +510,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>1752조 4,338억 1,823만</t>
+    <t>1752조 4338억 1823만</t>
   </si>
   <si>
     <t>16</t>
@@ -525,7 +525,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>1692조 2,004억 4,089만</t>
+    <t>1692조 2004억 4089만</t>
   </si>
   <si>
     <t>17</t>
@@ -537,7 +537,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%8A%98%ED%95%9C%EA%B7%B8%EB%8A%98</t>
   </si>
   <si>
-    <t>1574조 1,606억 2,965만</t>
+    <t>1574조 1606억 2965만</t>
   </si>
   <si>
     <t>18</t>
@@ -549,7 +549,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9D%B4%ED%95%98%EB%A1%9C%ED%95%98%EB%9D%BC</t>
   </si>
   <si>
-    <t>1536조 9,319억 6,510만</t>
+    <t>1536조 9319억 6510만</t>
   </si>
   <si>
     <t>19</t>
@@ -561,7 +561,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EB%B3%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>1224조 930억 2,497만</t>
+    <t>1224조 930억 2497만</t>
   </si>
   <si>
     <t>20</t>
@@ -573,7 +573,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%A6%BF</t>
   </si>
   <si>
-    <t>1114조 7,266억 7,195만</t>
+    <t>1114조 7266억 7195만</t>
   </si>
   <si>
     <t>21</t>
@@ -591,7 +591,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>1038조 1,690억 5,557만</t>
+    <t>1038조 1690억 5557만</t>
   </si>
   <si>
     <t>22</t>
@@ -603,7 +603,7 @@
     <t>https://mgf.gg/contents/character.php?n=v%EB%B0%95%ED%9A%A8%EC%8B%A0v</t>
   </si>
   <si>
-    <t>1037조 494억 3,376만</t>
+    <t>1037조 494억 3376만</t>
   </si>
   <si>
     <t>23</t>
@@ -615,7 +615,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%88%EC%98%A4</t>
   </si>
   <si>
-    <t>985조 3,833억 8,106만</t>
+    <t>985조 3833억 8106만</t>
   </si>
   <si>
     <t>24</t>
@@ -630,7 +630,7 @@
     <t>캡틴</t>
   </si>
   <si>
-    <t>948조 2,787억 2,895만</t>
+    <t>948조 2787억 2895만</t>
   </si>
   <si>
     <t>25</t>
@@ -642,7 +642,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
   </si>
   <si>
-    <t>862조 9,981억 2,406만</t>
+    <t>862조 9981억 2406만</t>
   </si>
   <si>
     <t>26</t>
@@ -654,7 +654,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%9C%BC%EB%86%8D</t>
   </si>
   <si>
-    <t>782조 5,974억 6,272만</t>
+    <t>782조 5974억 6272만</t>
   </si>
   <si>
     <t>27</t>
@@ -666,7 +666,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%87%B8</t>
   </si>
   <si>
-    <t>545조 140억 3,857만</t>
+    <t>545조 140억 3857만</t>
   </si>
   <si>
     <t>28</t>
@@ -681,7 +681,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>501조 2,685억 7,899만</t>
+    <t>501조 2685억 7899만</t>
   </si>
   <si>
     <t>29</t>
@@ -693,7 +693,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A6%AC%EB%AF%B8%EC%BF%B5</t>
   </si>
   <si>
-    <t>496조 7,292억 3,016만</t>
+    <t>496조 7292억 3016만</t>
   </si>
   <si>
     <t>30</t>
@@ -705,7 +705,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%8A%94%EB%B0%B0%EB%B6%88%EB%9F%AC%EC%9A%94</t>
   </si>
   <si>
-    <t>438조 6,576억 9,723만</t>
+    <t>438조 6576억 9723만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EA%B8%B0%EC%9C%A0%EB%AC%B4</t>
@@ -714,7 +714,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>1경 1162조 1,533억 1,870만</t>
+    <t>1경 1162조 1533억 1870만</t>
   </si>
   <si>
     <t>무곽</t>
@@ -723,7 +723,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EA%B3%BD</t>
   </si>
   <si>
-    <t>1경 185조 1,642억 4,847만</t>
+    <t>1경 185조 1642억 4847만</t>
   </si>
   <si>
     <t>형팡팡이</t>
@@ -732,7 +732,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%95%ED%8C%A1%ED%8C%A1%EC%9D%B4</t>
   </si>
   <si>
-    <t>4996조 5,941억 3,100만</t>
+    <t>4996조 5941억 3100만</t>
   </si>
   <si>
     <t>2번째캐릭</t>
@@ -741,7 +741,7 @@
     <t>https://mgf.gg/contents/character.php?n=2%EB%B2%88%EC%A7%B8%EC%BA%90%EB%A6%AD</t>
   </si>
   <si>
-    <t>3247조 628억 2,570만</t>
+    <t>3247조 628억 2570만</t>
   </si>
   <si>
     <t>붉은모자</t>
@@ -750,7 +750,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%89%EC%9D%80%EB%AA%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>3233조 3,396억 9,304만</t>
+    <t>3233조 3396억 9304만</t>
   </si>
   <si>
     <t>장뱁새</t>
@@ -759,7 +759,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B1%81%EC%83%88</t>
   </si>
   <si>
-    <t>3031조 5,264억 7,495만</t>
+    <t>3031조 5264억 7495만</t>
   </si>
   <si>
     <t>꽁꽁냉법</t>
@@ -768,7 +768,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EA%BD%81%EB%83%89%EB%B2%95</t>
   </si>
   <si>
-    <t>2333조 4,544억 8,833만</t>
+    <t>2333조 4544억 8833만</t>
   </si>
   <si>
     <t>테토일남</t>
@@ -780,7 +780,7 @@
     <t>다크나이트</t>
   </si>
   <si>
-    <t>1985조 8,710억 9,334만</t>
+    <t>1985조 8710억 9334만</t>
   </si>
   <si>
     <t>뚜기파파</t>
@@ -789,7 +789,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EA%B8%B0%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>1746조 6,215억 912만</t>
+    <t>1746조 6215억 912만</t>
   </si>
   <si>
     <t>브네</t>
@@ -798,7 +798,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%84%A4</t>
   </si>
   <si>
-    <t>1584조 5,973억 6,962만</t>
+    <t>1584조 5973억 6962만</t>
   </si>
   <si>
     <t>라쥬르</t>
@@ -807,7 +807,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%A5%AC%EB%A5%B4</t>
   </si>
   <si>
-    <t>1528조 947억 6,864만</t>
+    <t>1528조 947억 6864만</t>
   </si>
   <si>
     <t>빙율</t>
@@ -816,7 +816,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%99%EC%9C%A8</t>
   </si>
   <si>
-    <t>1193조 4,056억 8,035만</t>
+    <t>1193조 4056억 8035만</t>
   </si>
   <si>
     <t>33세배장호</t>
@@ -834,7 +834,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%81%EC%A0%B9%EC%A0%81</t>
   </si>
   <si>
-    <t>1018조 1,956억 6,161만</t>
+    <t>1018조 1956억 6161만</t>
   </si>
   <si>
     <t>재미있게놀래</t>
@@ -843,7 +843,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EB%AF%B8%EC%9E%88%EA%B2%8C%EB%86%80%EB%9E%98</t>
   </si>
   <si>
-    <t>960조 3,899억 5,166만</t>
+    <t>960조 3899억 5166만</t>
   </si>
   <si>
     <t>가덴</t>
@@ -852,7 +852,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%8D%B4</t>
   </si>
   <si>
-    <t>856조 2,582억 8,336만</t>
+    <t>856조 2582억 8336만</t>
   </si>
   <si>
     <t>정기휴므</t>
@@ -861,7 +861,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EA%B8%B0%ED%9C%B4%EB%AF%80</t>
   </si>
   <si>
-    <t>826조 7,863억 3,978만</t>
+    <t>826조 7863억 3978만</t>
   </si>
   <si>
     <t>최빵쭈</t>
@@ -873,7 +873,7 @@
     <t>바이퍼</t>
   </si>
   <si>
-    <t>783조 5,993억 9,157만</t>
+    <t>783조 5993억 9157만</t>
   </si>
   <si>
     <t>타뤽</t>
@@ -882,7 +882,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%A4%BD</t>
   </si>
   <si>
-    <t>759조 1,590억 8,137만</t>
+    <t>759조 1590억 8137만</t>
   </si>
   <si>
     <t>무르스</t>
@@ -891,7 +891,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%A5%B4%EC%8A%A4</t>
   </si>
   <si>
-    <t>722조 8,101억 454만</t>
+    <t>722조 8101억 454만</t>
   </si>
   <si>
     <t>새벽놀래</t>
@@ -900,7 +900,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%88%EB%B2%BD%EB%86%80%EB%9E%98</t>
   </si>
   <si>
-    <t>721조 9,101억 319만</t>
+    <t>721조 9101억 319만</t>
   </si>
   <si>
     <t>채황새</t>
@@ -918,7 +918,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%AD%ED%82%A4%EB%A3%A8%ED%82%A4</t>
   </si>
   <si>
-    <t>536조 2,111억 8,984만</t>
+    <t>536조 2111억 8984만</t>
   </si>
   <si>
     <t>저기휴무</t>
@@ -927,7 +927,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%80%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
   </si>
   <si>
-    <t>520조 5,128억</t>
+    <t>520조 5128억</t>
   </si>
   <si>
     <t>넬샷</t>
@@ -936,7 +936,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%AC%EC%83%B7</t>
   </si>
   <si>
-    <t>494조 6,391억 6,864만</t>
+    <t>494조 6391억 6864만</t>
   </si>
   <si>
     <t>박도란</t>
@@ -945,7 +945,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%8F%84%EB%9E%80</t>
   </si>
   <si>
-    <t>423조 4,561억 9,991만</t>
+    <t>423조 4561억 9991만</t>
   </si>
   <si>
     <t>장기휴무</t>
@@ -954,7 +954,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
   </si>
   <si>
-    <t>410조 8,040억 472만</t>
+    <t>410조 8040억 472만</t>
   </si>
   <si>
     <t>뿌앵뿌앵</t>
@@ -963,7 +963,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EC%95%B5%EB%BF%8C%EC%95%B5</t>
   </si>
   <si>
-    <t>392조 7,676억 5,327만</t>
+    <t>392조 7676억 5327만</t>
   </si>
   <si>
     <t>윤빵쭈</t>
@@ -975,7 +975,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>279조 8,923억 8,669만</t>
+    <t>279조 8923억 8669만</t>
   </si>
   <si>
     <t>냥홍이</t>
@@ -984,7 +984,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%ED%99%8D%EC%9D%B4</t>
   </si>
   <si>
-    <t>268조 9,505억 6,629만</t>
+    <t>268조 9505억 6629만</t>
   </si>
   <si>
     <t>지존쫀파</t>
@@ -993,7 +993,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
   </si>
   <si>
-    <t>8188조 1,046억 1,273만</t>
+    <t>8188조 1046억 1273만</t>
   </si>
   <si>
     <t>수텍</t>
@@ -1002,7 +1002,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%ED%85%8D</t>
   </si>
   <si>
-    <t>6992조 3,764억 4,633만</t>
+    <t>6992조 3764억 4633만</t>
   </si>
   <si>
     <t>협의</t>
@@ -1011,7 +1011,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%91%EC%9D%98</t>
   </si>
   <si>
-    <t>4402조 1,032억 4,015만</t>
+    <t>4402조 1032억 4015만</t>
   </si>
   <si>
     <t>포항엄석대</t>
@@ -1020,7 +1020,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
   </si>
   <si>
-    <t>4094조 124억 4,985만</t>
+    <t>4094조 124억 4985만</t>
   </si>
   <si>
     <t>기뽐</t>
@@ -1029,7 +1029,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%BD%90</t>
   </si>
   <si>
-    <t>3303조 6,174억 3,840만</t>
+    <t>3303조 6174억 3840만</t>
   </si>
   <si>
     <t>타개</t>
@@ -1038,7 +1038,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
   </si>
   <si>
-    <t>2988조 9,066억 1,886만</t>
+    <t>2988조 9066억 1886만</t>
   </si>
   <si>
     <t>포항가자미</t>
@@ -1047,7 +1047,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
   </si>
   <si>
-    <t>2424조 9,978억 2,159만</t>
+    <t>2424조 9978억 2159만</t>
   </si>
   <si>
     <t>변신술사</t>
@@ -1056,7 +1056,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
   </si>
   <si>
-    <t>2269조 6,121억 182만</t>
+    <t>2290조 8654억 1226만</t>
+  </si>
+  <si>
+    <t>뿡쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
+  </si>
+  <si>
+    <t>2279조 9226억 7885만</t>
   </si>
   <si>
     <t>지존빼앙</t>
@@ -1065,16 +1074,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
   </si>
   <si>
-    <t>2224조 5,091억 9,296만</t>
-  </si>
-  <si>
-    <t>뿡쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
-  </si>
-  <si>
-    <t>2182조 5,730억 5,749만</t>
+    <t>2224조 5091억 9296만</t>
   </si>
   <si>
     <t>엘르가든</t>
@@ -1083,7 +1083,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
   </si>
   <si>
-    <t>1978조 8,306억 8,833만</t>
+    <t>1978조 8306억 8833만</t>
   </si>
   <si>
     <t>댜니</t>
@@ -1092,7 +1092,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>1831조 4,812억 8,418만</t>
+    <t>1831조 4812억 8418만</t>
   </si>
   <si>
     <t>온백</t>
@@ -1101,7 +1101,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
   </si>
   <si>
-    <t>1814조 2,226억 6,845만</t>
+    <t>1814조 2226억 6845만</t>
   </si>
   <si>
     <t>파울</t>
@@ -1110,7 +1110,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
   </si>
   <si>
-    <t>1766조 7,006억 9,923만</t>
+    <t>1766조 7006억 9923만</t>
   </si>
   <si>
     <t>마카롱롱</t>
@@ -1119,7 +1119,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
   </si>
   <si>
-    <t>1596조 5,749억 9,080만</t>
+    <t>1596조 5749억 9080만</t>
   </si>
   <si>
     <t>모짜리코베르</t>
@@ -1128,13 +1128,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
   </si>
   <si>
-    <t>1240조 6,809억 9,149만</t>
+    <t>1240조 6809억 9149만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
   </si>
   <si>
-    <t>1213조 7,003억 6,444만</t>
+    <t>1213조 7003억 6444만</t>
   </si>
   <si>
     <t>짱잘자쿨냥</t>
@@ -1143,7 +1143,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%9E%98%EC%9E%90%EC%BF%A8%EB%83%A5</t>
   </si>
   <si>
-    <t>1149조 8,047억 287만</t>
+    <t>1149조 8047억 287만</t>
   </si>
   <si>
     <t>대좀이</t>
@@ -1152,7 +1152,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>1091조 9,888억 5,564만</t>
+    <t>1091조 9888억 5564만</t>
   </si>
   <si>
     <t>기본이리</t>
@@ -1161,7 +1161,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
   </si>
   <si>
-    <t>1050조 4,181억 3,112만</t>
+    <t>1050조 4181억 3112만</t>
   </si>
   <si>
     <t>김허덕</t>
@@ -1170,7 +1170,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
   </si>
   <si>
-    <t>1046조 865억 5,975만</t>
+    <t>1046조 865억 5975만</t>
   </si>
   <si>
     <t>냐은</t>
@@ -1179,7 +1179,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EC%9D%80</t>
   </si>
   <si>
-    <t>1033조 7,202억 5,586만</t>
+    <t>1033조 7202억 5586만</t>
   </si>
   <si>
     <t>마갤</t>
@@ -1188,7 +1188,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
   </si>
   <si>
-    <t>1015조 5,704억 3,498만</t>
+    <t>1015조 5704억 3498만</t>
   </si>
   <si>
     <t>오옹나이스</t>
@@ -1197,7 +1197,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%B9%EB%82%98%EC%9D%B4%EC%8A%A4</t>
   </si>
   <si>
-    <t>799조 5,234억 8,229만</t>
+    <t>799조 5234억 8229만</t>
   </si>
   <si>
     <t>고숨도칭</t>
@@ -1206,7 +1206,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
   </si>
   <si>
-    <t>796조 5,685억 5,174만</t>
+    <t>796조 5685억 5174만</t>
   </si>
   <si>
     <t>전산봉</t>
@@ -1215,7 +1215,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%B0%EB%B4%89</t>
   </si>
   <si>
-    <t>765조 9,289억 1,162만</t>
+    <t>765조 9289억 1162만</t>
   </si>
   <si>
     <t>Doham</t>
@@ -1224,7 +1224,7 @@
     <t>https://mgf.gg/contents/character.php?n=Doham</t>
   </si>
   <si>
-    <t>747조 6,533억 1,496만</t>
+    <t>747조 6533억 1496만</t>
   </si>
   <si>
     <t>태코찡</t>
@@ -1233,7 +1233,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
   </si>
   <si>
-    <t>665조 2,579억 6,198만</t>
+    <t>665조 2579억 6198만</t>
   </si>
   <si>
     <t>유플러스</t>
@@ -1242,7 +1242,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%94%8C%EB%9F%AC%EC%8A%A4</t>
   </si>
   <si>
-    <t>649조 5,527억 6,316만</t>
+    <t>649조 5527억 6316만</t>
   </si>
   <si>
     <t>빵후</t>
@@ -1251,7 +1251,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%ED%9B%84</t>
   </si>
   <si>
-    <t>277조 36억 4,103만</t>
+    <t>277조 36억 4103만</t>
   </si>
   <si>
     <t>전액할부</t>
@@ -1260,7 +1260,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%95%A1%ED%95%A0%EB%B6%80</t>
   </si>
   <si>
-    <t>1경 556조 6,511억 5,477만</t>
+    <t>1경 556조 6511억 5477만</t>
   </si>
   <si>
     <t>사랑향</t>
@@ -1269,7 +1269,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%96%A5</t>
   </si>
   <si>
-    <t>7984조 7,938억 2,458만</t>
+    <t>7984조 7938억 2458만</t>
   </si>
   <si>
     <t>힐폿</t>
@@ -1287,7 +1287,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%80%EC%A0%84</t>
   </si>
   <si>
-    <t>3668조 9,031억 8,187만</t>
+    <t>3668조 9031억 8187만</t>
   </si>
   <si>
     <t>숭타이준</t>
@@ -1296,13 +1296,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%ED%83%80%EC%9D%B4%EC%A4%80</t>
   </si>
   <si>
-    <t>3001조 7,702억 6,620만</t>
+    <t>3001조 7702억 6620만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%94%9C%ED%8F%BF</t>
   </si>
   <si>
-    <t>2598조 7,115억 1,793만</t>
+    <t>2598조 7115억 1793만</t>
   </si>
   <si>
     <t>뻑걸</t>
@@ -1311,7 +1311,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%91%EA%B1%B8</t>
   </si>
   <si>
-    <t>1867조 5,966억 1,163만</t>
+    <t>1867조 5966억 1163만</t>
   </si>
   <si>
     <t>뮬이</t>
@@ -1320,7 +1320,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AE%AC%EC%9D%B4</t>
   </si>
   <si>
-    <t>1618조 7,801억 3,460만</t>
+    <t>1618조 7801억 3460만</t>
   </si>
   <si>
     <t>지존빵수</t>
@@ -1329,7 +1329,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%B5%EC%88%98</t>
   </si>
   <si>
-    <t>1610조 953억 6,364만</t>
+    <t>1610조 953억 6364만</t>
   </si>
   <si>
     <t>야키산</t>
@@ -1338,7 +1338,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%82%A4%EC%82%B0</t>
   </si>
   <si>
-    <t>1576조 9,887억 2,494만</t>
+    <t>1576조 9887억 2494만</t>
   </si>
   <si>
     <t>문제적남자</t>
@@ -1347,7 +1347,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EC%A0%9C%EC%A0%81%EB%82%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>1447조 754억 2,073만</t>
+    <t>1447조 754억 2073만</t>
   </si>
   <si>
     <t>탱폿</t>
@@ -1356,7 +1356,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%8F%BF</t>
   </si>
   <si>
-    <t>1399조 9,788억 4,010만</t>
+    <t>1399조 9788억 4010만</t>
   </si>
   <si>
     <t>우즈2텐겐</t>
@@ -1365,7 +1365,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%A6%882%ED%85%90%EA%B2%90</t>
   </si>
   <si>
-    <t>1317조 4,439억 6,807만</t>
+    <t>1317조 4439억 6807만</t>
   </si>
   <si>
     <t>아이리쉬</t>
@@ -1374,7 +1374,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EB%A6%AC%EC%89%AC</t>
   </si>
   <si>
-    <t>1252조 7,283억 7,526만</t>
+    <t>1252조 7283억 7526만</t>
   </si>
   <si>
     <t>독스케</t>
@@ -1383,7 +1383,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%8A%A4%EC%BC%80</t>
   </si>
   <si>
-    <t>1150조 9,844억 1,359만</t>
+    <t>1150조 9844억 1359만</t>
   </si>
   <si>
     <t>우월별하</t>
@@ -1392,7 +1392,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9B%94%EB%B3%84%ED%95%98</t>
   </si>
   <si>
-    <t>1032조 7,712억 9,061만</t>
+    <t>1032조 7712억 9061만</t>
   </si>
   <si>
     <t>화둥에불낸년</t>
@@ -1401,7 +1401,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EB%91%A5%EC%97%90%EB%B6%88%EB%82%B8%EB%85%84</t>
   </si>
   <si>
-    <t>1004조 9,588억 8,909만</t>
+    <t>1004조 9588억 8909만</t>
   </si>
   <si>
     <t>이게용</t>
@@ -1410,7 +1410,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B2%8C%EC%9A%A9</t>
   </si>
   <si>
-    <t>978조 4,612억 6,155만</t>
+    <t>978조 4612억 6155만</t>
   </si>
   <si>
     <t>기똥찬벌레</t>
@@ -1419,7 +1419,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%98%A5%EC%B0%AC%EB%B2%8C%EB%A0%88</t>
   </si>
   <si>
-    <t>951조 8,281억 4,925만</t>
+    <t>951조 8281억 4925만</t>
   </si>
   <si>
     <t>매화로이</t>
@@ -1428,7 +1428,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%ED%99%94%EB%A1%9C%EC%9D%B4</t>
   </si>
   <si>
-    <t>888조 3,912억 9,246만</t>
+    <t>888조 3912억 9246만</t>
   </si>
   <si>
     <t>JJuna</t>
@@ -1437,7 +1437,7 @@
     <t>https://mgf.gg/contents/character.php?n=JJuna</t>
   </si>
   <si>
-    <t>820조 1,636억 7,645만</t>
+    <t>820조 1636억 7645만</t>
   </si>
   <si>
     <t>에프람</t>
@@ -1446,7 +1446,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%ED%94%84%EB%9E%8C</t>
   </si>
   <si>
-    <t>762조 4,036억 3,352만</t>
+    <t>762조 4036억 3352만</t>
   </si>
   <si>
     <t>콜리셰마드르</t>
@@ -1455,7 +1455,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%9C%EB%A6%AC%EC%85%B0%EB%A7%88%EB%93%9C%EB%A5%B4</t>
   </si>
   <si>
-    <t>722조 8,675억 2,990만</t>
+    <t>722조 8675억 2990만</t>
   </si>
   <si>
     <t>난센</t>
@@ -1464,7 +1464,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EC%84%BC</t>
   </si>
   <si>
-    <t>712조 8,834억 5,919만</t>
+    <t>712조 8834억 5919만</t>
   </si>
   <si>
     <t>구도류</t>
@@ -1473,7 +1473,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%8F%84%EB%A5%98</t>
   </si>
   <si>
-    <t>597조 4,814억 267만</t>
+    <t>597조 4814억 267만</t>
   </si>
   <si>
     <t>조단23</t>
@@ -1482,7 +1482,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%8B%A823</t>
   </si>
   <si>
-    <t>547조 1,752억 7,480만</t>
+    <t>547조 1752억 7480만</t>
   </si>
   <si>
     <t>유채아버지</t>
@@ -1491,7 +1491,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%B1%84%EC%95%84%EB%B2%84%EC%A7%80</t>
   </si>
   <si>
-    <t>539조 4,690억 5,456만</t>
+    <t>539조 4690억 5456만</t>
   </si>
   <si>
     <t>아콩린</t>
@@ -1500,7 +1500,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BD%A9%EB%A6%B0</t>
   </si>
   <si>
-    <t>531조 5,593억 3,139만</t>
+    <t>531조 5593억 3139만</t>
   </si>
   <si>
     <t>별루루</t>
@@ -1509,7 +1509,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A3%A8%EB%A3%A8</t>
   </si>
   <si>
-    <t>424조 6,674억 8,815만</t>
+    <t>424조 6674억 8815만</t>
   </si>
   <si>
     <t>꺄꽁</t>
@@ -1518,7 +1518,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BA%84%EA%BD%81</t>
   </si>
   <si>
-    <t>7135조 6,187억 3,211만</t>
+    <t>7278조 8334억 8539만</t>
   </si>
   <si>
     <t>별쌥</t>
@@ -1527,7 +1527,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A5</t>
   </si>
   <si>
-    <t>5960조 7,320억 2,376만</t>
+    <t>5960조 7320억 2376만</t>
   </si>
   <si>
     <t>진욱이에요</t>
@@ -1536,13 +1536,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9A%B1%EC%9D%B4%EC%97%90%EC%9A%94</t>
   </si>
   <si>
-    <t>4550조 1,468억 5,509만</t>
+    <t>4550조 1468억 5509만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A5%B4%EB%AA%AC</t>
   </si>
   <si>
-    <t>3646조 653억 8,697만</t>
+    <t>3646조 653억 8697만</t>
   </si>
   <si>
     <t>낭만황금망치</t>
@@ -1551,7 +1551,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%ED%99%A9%EA%B8%88%EB%A7%9D%EC%B9%98</t>
   </si>
   <si>
-    <t>3488조 4,591억 2,770만</t>
+    <t>3489조 5165억 7352만</t>
   </si>
   <si>
     <t>김슴줌1</t>
@@ -1560,7 +1560,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%8A%B4%EC%A4%8C1</t>
   </si>
   <si>
-    <t>3270조 2,257억 1,209만</t>
+    <t>3270조 2257억 1209만</t>
   </si>
   <si>
     <t>천달</t>
@@ -1569,7 +1569,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EB%8B%AC</t>
   </si>
   <si>
-    <t>2717조 9,833억 6,552만</t>
+    <t>2717조 9833억 6552만</t>
   </si>
   <si>
     <t>호두와감자</t>
@@ -1578,7 +1578,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%91%90%EC%99%80%EA%B0%90%EC%9E%90</t>
   </si>
   <si>
-    <t>2525조 8,587억 8,102만</t>
+    <t>2525조 8587억 8102만</t>
+  </si>
+  <si>
+    <t>활용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%9C%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>2013조 908억 8266만</t>
   </si>
   <si>
     <t>쿠댜</t>
@@ -1587,16 +1596,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EB%8C%9C</t>
   </si>
   <si>
-    <t>1916조 9,415억 6,270만</t>
-  </si>
-  <si>
-    <t>활용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%9C%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>1867조 7,074억 9,904만</t>
+    <t>1966조 5445억 7393만</t>
   </si>
   <si>
     <t>뚜징</t>
@@ -1605,7 +1605,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EC%A7%95</t>
   </si>
   <si>
-    <t>1806조 9,134억 8,019만</t>
+    <t>1806조 9134억 8019만</t>
   </si>
   <si>
     <t>별곡</t>
@@ -1614,7 +1614,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EA%B3%A1</t>
   </si>
   <si>
-    <t>969조 8,456억 4,768만</t>
+    <t>969조 8456억 4768만</t>
   </si>
   <si>
     <t>까쿠미</t>
@@ -1623,7 +1623,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EC%BF%A0%EB%AF%B8</t>
   </si>
   <si>
-    <t>861조 9,064억 5,984만</t>
+    <t>861조 9064억 5984만</t>
   </si>
   <si>
     <t>턍ol</t>
@@ -1632,7 +1632,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%84%8Dol</t>
   </si>
   <si>
-    <t>788조 6,038억 6,835만</t>
+    <t>788조 6038억 6835만</t>
   </si>
   <si>
     <t>동래</t>
@@ -1641,7 +1641,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%9E%98</t>
   </si>
   <si>
-    <t>788조 3,697억 1,727만</t>
+    <t>788조 3697억 1727만</t>
   </si>
   <si>
     <t>별쌤</t>
@@ -1650,7 +1650,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A4</t>
   </si>
   <si>
-    <t>738조 5,918억 5,801만</t>
+    <t>738조 5918억 5801만</t>
   </si>
   <si>
     <t>게렬곰</t>
@@ -1659,7 +1659,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%EB%A0%AC%EA%B3%B0</t>
   </si>
   <si>
-    <t>729조 1,853억 3,020만</t>
+    <t>729조 1853억 3020만</t>
   </si>
   <si>
     <t>초이레</t>
@@ -1668,7 +1668,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%B4%EB%A0%88</t>
   </si>
   <si>
-    <t>651조 5,939억 4,000만</t>
+    <t>651조 5939억 4000만</t>
   </si>
   <si>
     <t>띠우</t>
@@ -1686,7 +1686,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%81%84%EC%B1%B0</t>
   </si>
   <si>
-    <t>473조 8,542억 7,621만</t>
+    <t>475조 4236억 4624만</t>
   </si>
   <si>
     <t>민족고대감자</t>
@@ -1695,7 +1695,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%A1%B1%EA%B3%A0%EB%8C%80%EA%B0%90%EC%9E%90</t>
   </si>
   <si>
-    <t>447조 5,787억 6,359만</t>
+    <t>447조 5787억 6359만</t>
   </si>
   <si>
     <t>쿠까미</t>
@@ -1704,7 +1704,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EA%B9%8C%EB%AF%B8</t>
   </si>
   <si>
-    <t>442조 874억 8,170만</t>
+    <t>442조 874억 8170만</t>
   </si>
   <si>
     <t>승아의하루</t>
@@ -1713,7 +1713,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%EC%95%84%EC%9D%98%ED%95%98%EB%A3%A8</t>
   </si>
   <si>
-    <t>419조 8,392억 5,458만</t>
+    <t>419조 8392억 5458만</t>
   </si>
   <si>
     <t>왕단단이</t>
@@ -1722,7 +1722,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EB%8B%A8%EB%8B%A8%EC%9D%B4</t>
   </si>
   <si>
-    <t>374조 1,106억 1,593만</t>
+    <t>374조 1106억 1593만</t>
   </si>
   <si>
     <t>택Ol</t>
@@ -1731,7 +1731,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9DOl</t>
   </si>
   <si>
-    <t>343조 8,584억 7,876만</t>
+    <t>343조 8584억 7876만</t>
   </si>
   <si>
     <t>08217</t>
@@ -1740,7 +1740,7 @@
     <t>https://mgf.gg/contents/character.php?n=08217</t>
   </si>
   <si>
-    <t>328조 6,713억 6,296만</t>
+    <t>328조 6713억 6296만</t>
   </si>
   <si>
     <t>루이쥔</t>
@@ -1749,7 +1749,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%9D%B4%EC%A5%94</t>
   </si>
   <si>
-    <t>312조 422억 7,493만</t>
+    <t>312조 422억 7493만</t>
   </si>
   <si>
     <t>툼스데이</t>
@@ -1758,7 +1758,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%88%BC%EC%8A%A4%EB%8D%B0%EC%9D%B4</t>
   </si>
   <si>
-    <t>285조 1,117억 8,099만</t>
+    <t>285조 1117억 8099만</t>
   </si>
   <si>
     <t>꾸현</t>
@@ -1767,7 +1767,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%ED%98%84</t>
   </si>
   <si>
-    <t>88조 3,966억 6,293만</t>
+    <t>88조 3966억 6293만</t>
   </si>
   <si>
     <t>달갸뤼</t>
@@ -1776,7 +1776,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EA%B0%B8%EB%A4%BC</t>
   </si>
   <si>
-    <t>73조 4,903억 3,576만</t>
+    <t>73조 4903억 3576만</t>
   </si>
   <si>
     <t>김치싸대기</t>
@@ -1785,7 +1785,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
   </si>
   <si>
-    <t>9713조 4,850억 8,781만</t>
+    <t>9713조 4850억 8781만</t>
   </si>
   <si>
     <t>굴러가는일상</t>
@@ -1794,7 +1794,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
   </si>
   <si>
-    <t>6465조 5,267억 4,688만</t>
+    <t>6465조 5267억 4688만</t>
   </si>
   <si>
     <t>흑두부</t>
@@ -1803,7 +1803,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>3686조 3,442억 6,715만</t>
+    <t>3686조 3442억 6715만</t>
   </si>
   <si>
     <t>대방어조아</t>
@@ -1812,7 +1812,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>3586조 4,643억 9,612만</t>
+    <t>3586조 4643억 9612만</t>
   </si>
   <si>
     <t>엘라임</t>
@@ -1821,7 +1821,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
   </si>
   <si>
-    <t>3469조 8,887억 4,598만</t>
+    <t>3469조 8887억 4598만</t>
   </si>
   <si>
     <t>퍼퓸</t>
@@ -1830,7 +1830,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
   </si>
   <si>
-    <t>2483조 8,452억 3,773만</t>
+    <t>2483조 8452억 3773만</t>
   </si>
   <si>
     <t>서포터즈</t>
@@ -1839,7 +1839,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>2417조 4,217억 703만</t>
+    <t>2431조 544억 4930만</t>
   </si>
   <si>
     <t>KR#TAKIN9CP37</t>
@@ -1848,13 +1848,13 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>1905조 4,587억 3,879만</t>
+    <t>1905조 4587억 3879만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
   </si>
   <si>
-    <t>1831조 3,912억 3,225만</t>
+    <t>1831조 3912억 3225만</t>
   </si>
   <si>
     <t>뻥뻥</t>
@@ -1863,7 +1863,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
   </si>
   <si>
-    <t>1825조 2,398억 5,085만</t>
+    <t>1825조 2398억 5085만</t>
   </si>
   <si>
     <t>야가다</t>
@@ -1872,7 +1872,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
   </si>
   <si>
-    <t>1697조 755억 7,134만</t>
+    <t>1697조 755억 7134만</t>
   </si>
   <si>
     <t>불보독지</t>
@@ -1881,7 +1881,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
   </si>
   <si>
-    <t>1259조 8,128억 5,685만</t>
+    <t>1259조 8128억 5685만</t>
   </si>
   <si>
     <t>우후</t>
@@ -1890,7 +1890,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>1058조 2,431억 2,633만</t>
+    <t>1058조 2431억 2633만</t>
   </si>
   <si>
     <t>호우기</t>
@@ -1899,7 +1899,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>1052조 9,891억 7,693만</t>
+    <t>1052조 9891억 7693만</t>
   </si>
   <si>
     <t>채무조정</t>
@@ -1908,7 +1908,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
   </si>
   <si>
-    <t>1006조 7,349억 1,730만</t>
+    <t>1006조 7349억 1730만</t>
   </si>
   <si>
     <t>단풍카우</t>
@@ -1917,7 +1917,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>987조 2,843억 9,824만</t>
+    <t>987조 2843억 9824만</t>
   </si>
   <si>
     <t>좀치는형님</t>
@@ -1926,7 +1926,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
   </si>
   <si>
-    <t>926조 2,055억 4,066만</t>
+    <t>928조 8138억 6047만</t>
   </si>
   <si>
     <t>뽀송히</t>
@@ -1935,7 +1935,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
   </si>
   <si>
-    <t>914조 9,534억 4,237만</t>
+    <t>914조 9534억 4237만</t>
   </si>
   <si>
     <t>정태준</t>
@@ -1944,7 +1944,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
   </si>
   <si>
-    <t>864조 6,290억 5,998만</t>
+    <t>864조 6290억 5998만</t>
   </si>
   <si>
     <t>팡대지</t>
@@ -1953,7 +1953,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
   </si>
   <si>
-    <t>560조 1,285억 7,637만</t>
+    <t>560조 1285억 7637만</t>
   </si>
   <si>
     <t>민들레꽃</t>
@@ -1962,7 +1962,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>532조 1,581억 8,976만</t>
+    <t>532조 1581억 8976만</t>
   </si>
   <si>
     <t>박준우2</t>
@@ -1971,7 +1971,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
   </si>
   <si>
-    <t>459조 5,489억 3,382만</t>
+    <t>459조 5489억 3382만</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -1980,7 +1980,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
   </si>
   <si>
-    <t>420조 8,785억 9,592만</t>
+    <t>420조 8785억 9592만</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -1989,7 +1989,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>410조 5,852억 7,919만</t>
+    <t>410조 5852억 7919만</t>
   </si>
   <si>
     <t>솔인</t>
@@ -1998,7 +1998,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
   </si>
   <si>
-    <t>372조 4,821억 9,681만</t>
+    <t>372조 4821억 9681만</t>
   </si>
   <si>
     <t>꼬북빵야</t>
@@ -2007,7 +2007,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
   </si>
   <si>
-    <t>275조 6,869억 3,523만</t>
+    <t>275조 6869억 3523만</t>
   </si>
   <si>
     <t>여눈</t>
@@ -2016,7 +2016,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
   </si>
   <si>
-    <t>249조 9,325억 1,140만</t>
+    <t>249조 9325억 1140만</t>
   </si>
   <si>
     <t>아르미느</t>
@@ -2025,7 +2025,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>245조 4,859억 3,395만</t>
+    <t>245조 4859억 3395만</t>
   </si>
   <si>
     <t>교주만두</t>
@@ -2034,7 +2034,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%90%EC%A3%BC%EB%A7%8C%EB%91%90</t>
   </si>
   <si>
-    <t>6경 4821조 8,677억 1,103만</t>
+    <t>6경 4821조 8677억 1103만</t>
   </si>
   <si>
     <t>할바이</t>
@@ -2046,7 +2046,7 @@
     <t>107</t>
   </si>
   <si>
-    <t>231조 2,461억 1,057만</t>
+    <t>231조 2461억 1057만</t>
   </si>
   <si>
     <t>섹밍</t>
@@ -2055,7 +2055,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B9%EB%B0%8D</t>
   </si>
   <si>
-    <t>211조 4,498억 8,225만</t>
+    <t>211조 4498억 8225만</t>
   </si>
   <si>
     <t>대구남성</t>
@@ -2067,7 +2067,7 @@
     <t>106</t>
   </si>
   <si>
-    <t>73조 3,158억 3,342만</t>
+    <t>73조 3158억 3342만</t>
   </si>
   <si>
     <t>코잉코잉</t>
@@ -2079,7 +2079,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>39조 280억 1,146만</t>
+    <t>39조 280억 1146만</t>
   </si>
   <si>
     <t>토벤숍이</t>
@@ -2088,7 +2088,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%B2%A4%EC%88%8D%EC%9D%B4</t>
   </si>
   <si>
-    <t>36조 4,537억 6,794만</t>
+    <t>36조 4537억 6794만</t>
   </si>
   <si>
     <t>낭랑28세</t>
@@ -2097,7 +2097,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%9E%9128%EC%84%B8</t>
   </si>
   <si>
-    <t>36조 3,976억 1,339만</t>
+    <t>36조 3976억 1339만</t>
   </si>
   <si>
     <t>빵신궁</t>
@@ -2106,7 +2106,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EC%8B%A0%EA%B6%81</t>
   </si>
   <si>
-    <t>30조 7,181억 324만</t>
+    <t>30조 7181억 324만</t>
   </si>
   <si>
     <t>오스띤</t>
@@ -2115,7 +2115,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%8A%A4%EB%9D%A4</t>
   </si>
   <si>
-    <t>29조 9,499억 3,058만</t>
+    <t>29조 9499억 3058만</t>
   </si>
   <si>
     <t>밀초크코</t>
@@ -2124,7 +2124,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%EC%B4%88%ED%81%AC%EC%BD%94</t>
   </si>
   <si>
-    <t>28조 1,153억 4,015만</t>
+    <t>28조 1153억 4015만</t>
   </si>
   <si>
     <t>마키맛키마</t>
@@ -2136,7 +2136,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>27조 2,464억 4,277만</t>
+    <t>27조 2464억 4277만</t>
   </si>
   <si>
     <t>킬혁</t>
@@ -2145,7 +2145,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%AC%ED%98%81</t>
   </si>
   <si>
-    <t>25조 4,433억 6,581만</t>
+    <t>25조 4433억 6581만</t>
   </si>
   <si>
     <t>썬콜우체국</t>
@@ -2157,7 +2157,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>25조 787억 2,808만</t>
+    <t>25조 787억 2808만</t>
   </si>
   <si>
     <t>문보겨엉</t>
@@ -2169,7 +2169,7 @@
     <t>102</t>
   </si>
   <si>
-    <t>24조 1,864억 5,790만</t>
+    <t>24조 1864억 5790만</t>
   </si>
   <si>
     <t>고통받는갈비</t>
@@ -2178,7 +2178,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%ED%86%B5%EB%B0%9B%EB%8A%94%EA%B0%88%EB%B9%84</t>
   </si>
   <si>
-    <t>23조 9,956억 4,822만</t>
+    <t>23조 9956억 4822만</t>
   </si>
   <si>
     <t>씅놈</t>
@@ -2187,7 +2187,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%94%85%EB%86%88</t>
   </si>
   <si>
-    <t>22조 1,653억 9,791만</t>
+    <t>22조 1653억 9791만</t>
   </si>
   <si>
     <t>배렛나루왁서</t>
@@ -2196,7 +2196,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%EB%A0%9B%EB%82%98%EB%A3%A8%EC%99%81%EC%84%9C</t>
   </si>
   <si>
-    <t>20조 6,218억 5,190만</t>
+    <t>20조 6218억 5190만</t>
   </si>
   <si>
     <t>땡요나퐁</t>
@@ -2205,7 +2205,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%95%A1%EC%9A%94%EB%82%98%ED%90%81</t>
   </si>
   <si>
-    <t>20조 2,598억 1,813만</t>
+    <t>20조 2598억 1813만</t>
   </si>
   <si>
     <t>썬콜법사ss</t>
@@ -2214,7 +2214,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%ACss</t>
   </si>
   <si>
-    <t>19조 4,439억 6,528만</t>
+    <t>19조 4439억 6528만</t>
   </si>
   <si>
     <t>포디케이</t>
@@ -2223,13 +2223,13 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%94%94%EC%BC%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>9조 5,884억 9,293만</t>
+    <t>9조 5884억 9293만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%ED%82%A4%EB%B9%84%ED%82%A4</t>
   </si>
   <si>
-    <t>6조 3,603억 7,229만</t>
+    <t>6조 3603억 7229만</t>
   </si>
   <si>
     <t>경기도인</t>
@@ -2241,7 +2241,7 @@
     <t>101</t>
   </si>
   <si>
-    <t>5조 6,702억 2,764만</t>
+    <t>5조 6702억 2764만</t>
   </si>
   <si>
     <t>즈나니</t>
@@ -2253,7 +2253,7 @@
     <t>100</t>
   </si>
   <si>
-    <t>3조 2,857억 8,721만</t>
+    <t>3조 2857억 8721만</t>
   </si>
 </sst>
 </file>
@@ -2986,7 +2986,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4031,7 +4031,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5076,7 +5076,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5388,7 +5388,7 @@
         <v>89</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>131</v>
@@ -5420,7 +5420,7 @@
         <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>131</v>
@@ -6121,7 +6121,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7133,7 +7133,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7445,10 +7445,10 @@
         <v>89</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>518</v>
@@ -7477,10 +7477,10 @@
         <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>521</v>
@@ -8177,7 +8177,7 @@
     <col min="3" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9156,7 +9156,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -84,7 +84,7 @@
     <t>Scania 13</t>
   </si>
   <si>
-    <t>848</t>
+    <t>855</t>
   </si>
   <si>
     <t>33위</t>
@@ -117,10 +117,10 @@
     <t>Scania 23</t>
   </si>
   <si>
-    <t>909</t>
-  </si>
-  <si>
-    <t>13위</t>
+    <t>916</t>
+  </si>
+  <si>
+    <t>12위</t>
   </si>
   <si>
     <t>29명</t>
@@ -147,7 +147,7 @@
     <t>Scania 4</t>
   </si>
   <si>
-    <t>858</t>
+    <t>864</t>
   </si>
   <si>
     <t>31위</t>
@@ -177,7 +177,7 @@
     <t>Scania 29</t>
   </si>
   <si>
-    <t>877</t>
+    <t>876</t>
   </si>
   <si>
     <t>16위</t>
@@ -201,7 +201,7 @@
     <t>Scania 3</t>
   </si>
   <si>
-    <t>905</t>
+    <t>911</t>
   </si>
   <si>
     <t>37위</t>
@@ -225,7 +225,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>841</t>
+    <t>845</t>
   </si>
   <si>
     <t>5경 985조 128억 1537만</t>
@@ -309,7 +309,7 @@
     <t>117</t>
   </si>
   <si>
-    <t>6경 6141조 4657억 3898만</t>
+    <t>6경 6264조 2325억 5474만</t>
   </si>
   <si>
     <t>2</t>
@@ -363,7 +363,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>6327조 503억 4939만</t>
+    <t>6643조 5956억 2880만</t>
   </si>
   <si>
     <t>5</t>
@@ -375,7 +375,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%90%EC%B1%A0</t>
   </si>
   <si>
-    <t>4842조 8830억 3283만</t>
+    <t>5044조 7555억 8867만</t>
   </si>
   <si>
     <t>6</t>
@@ -387,7 +387,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%84%EA%B5%AC</t>
   </si>
   <si>
-    <t>4808조 4650억 4072만</t>
+    <t>4999조 315억 4310만</t>
   </si>
   <si>
     <t>7</t>
@@ -399,7 +399,7 @@
     <t>https://mgf.gg/contents/character.php?n=GOD%EB%82%A0%EB%91%90</t>
   </si>
   <si>
-    <t>4260조 3079억 8728만</t>
+    <t>4592조 8710억 8469만</t>
   </si>
   <si>
     <t>8</t>
@@ -426,94 +426,106 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%9A%94%EC%97%98%EB%86%8D%EC%82%B0</t>
   </si>
   <si>
+    <t>3339조 7819억 8470만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>테이킷슬로우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%85%8C%EC%9D%B4%ED%82%B7%EC%8A%AC%EB%A1%9C%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>3050조 3867억 6933만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>하찌바리이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B0%8C%EB%B0%94%EB%A6%AC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2949조 7637억 2309만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>러브포티</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%B8%8C%ED%8F%AC%ED%8B%B0</t>
+  </si>
+  <si>
+    <t>2805조 7388억 7122만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>황금어금니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EA%B8%88%EC%96%B4%EA%B8%88%EB%8B%88</t>
+  </si>
+  <si>
+    <t>2437조 3344억 6767만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>서늘한그늘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%8A%98%ED%95%9C%EA%B7%B8%EB%8A%98</t>
+  </si>
+  <si>
+    <t>1877조 8513억 6254만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Darken</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Darken</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>1871조 5805억 9718만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>88치킨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=88%EC%B9%98%ED%82%A8</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>3339조 7819억 8470만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>하찌바리이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B0%8C%EB%B0%94%EB%A6%AC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2938조 9566억 7745만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>러브포티</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%B8%8C%ED%8F%AC%ED%8B%B0</t>
-  </si>
-  <si>
-    <t>2805조 7388억 7122만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>테이킷슬로우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%85%8C%EC%9D%B4%ED%82%B7%EC%8A%AC%EB%A1%9C%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>2367조 6141억 542만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>황금어금니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EA%B8%88%EC%96%B4%EA%B8%88%EB%8B%88</t>
-  </si>
-  <si>
-    <t>2171조 2630억 8147만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Darken</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Darken</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>1860조 7967억 6835만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>88치킨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=88%EC%B9%98%ED%82%A8</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
     <t>1752조 4338억 1823만</t>
   </si>
   <si>
-    <t>16</t>
+    <t>17</t>
   </si>
   <si>
     <t>탕비실도우미</t>
@@ -528,18 +540,6 @@
     <t>1692조 2004억 4089만</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>서늘한그늘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%8A%98%ED%95%9C%EA%B7%B8%EB%8A%98</t>
-  </si>
-  <si>
-    <t>1574조 1606억 2965만</t>
-  </si>
-  <si>
     <t>18</t>
   </si>
   <si>
@@ -549,7 +549,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9D%B4%ED%95%98%EB%A1%9C%ED%95%98%EB%9D%BC</t>
   </si>
   <si>
-    <t>1536조 9319억 6510만</t>
+    <t>1568조 9673억 9173만</t>
   </si>
   <si>
     <t>19</t>
@@ -561,7 +561,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EB%B3%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>1224조 930억 2497만</t>
+    <t>1421조 9976억 815만</t>
   </si>
   <si>
     <t>20</t>
@@ -573,7 +573,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%A6%BF</t>
   </si>
   <si>
-    <t>1114조 7266억 7195만</t>
+    <t>1123조 5970억 5035만</t>
   </si>
   <si>
     <t>21</t>
@@ -591,7 +591,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>1038조 1690억 5557만</t>
+    <t>1045조 6661억 447만</t>
   </si>
   <si>
     <t>22</t>
@@ -603,7 +603,7 @@
     <t>https://mgf.gg/contents/character.php?n=v%EB%B0%95%ED%9A%A8%EC%8B%A0v</t>
   </si>
   <si>
-    <t>1037조 494억 3376만</t>
+    <t>1045조 5076억 8642만</t>
   </si>
   <si>
     <t>23</t>
@@ -654,7 +654,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%9C%BC%EB%86%8D</t>
   </si>
   <si>
-    <t>782조 5974억 6272만</t>
+    <t>790조 9426억 8960만</t>
   </si>
   <si>
     <t>27</t>
@@ -666,12 +666,24 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%87%B8</t>
   </si>
   <si>
-    <t>545조 140억 3857만</t>
+    <t>545조 4194억 1165만</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
+    <t>아리미쿵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A6%AC%EB%AF%B8%EC%BF%B5</t>
+  </si>
+  <si>
+    <t>521조 8718억 5001만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
     <t>하엘이</t>
   </si>
   <si>
@@ -684,18 +696,6 @@
     <t>501조 2685억 7899만</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>아리미쿵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A6%AC%EB%AF%B8%EC%BF%B5</t>
-  </si>
-  <si>
-    <t>496조 7292억 3016만</t>
-  </si>
-  <si>
     <t>30</t>
   </si>
   <si>
@@ -705,7 +705,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%8A%94%EB%B0%B0%EB%B6%88%EB%9F%AC%EC%9A%94</t>
   </si>
   <si>
-    <t>438조 6576억 9723만</t>
+    <t>461조 2828억 9976만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EA%B8%B0%EC%9C%A0%EB%AC%B4</t>
@@ -714,7 +714,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>1경 1162조 1533억 1870만</t>
+    <t>1경 1263조 6150억 2344만</t>
   </si>
   <si>
     <t>무곽</t>
@@ -732,7 +732,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%95%ED%8C%A1%ED%8C%A1%EC%9D%B4</t>
   </si>
   <si>
-    <t>4996조 5941억 3100만</t>
+    <t>5205조 6865억 52만</t>
   </si>
   <si>
     <t>2번째캐릭</t>
@@ -741,7 +741,7 @@
     <t>https://mgf.gg/contents/character.php?n=2%EB%B2%88%EC%A7%B8%EC%BA%90%EB%A6%AD</t>
   </si>
   <si>
-    <t>3247조 628억 2570만</t>
+    <t>3585조 5411억 4772만</t>
   </si>
   <si>
     <t>붉은모자</t>
@@ -750,7 +750,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%89%EC%9D%80%EB%AA%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>3233조 3396억 9304만</t>
+    <t>3310조 9315억 971만</t>
   </si>
   <si>
     <t>장뱁새</t>
@@ -759,7 +759,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B1%81%EC%83%88</t>
   </si>
   <si>
-    <t>3031조 5264억 7495만</t>
+    <t>3211조 7684억 4650만</t>
   </si>
   <si>
     <t>꽁꽁냉법</t>
@@ -789,7 +789,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EA%B8%B0%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>1746조 6215억 912만</t>
+    <t>1797조 9273억 1994만</t>
   </si>
   <si>
     <t>브네</t>
@@ -807,7 +807,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%A5%AC%EB%A5%B4</t>
   </si>
   <si>
-    <t>1528조 947억 6864만</t>
+    <t>1549조 5880억 9660만</t>
   </si>
   <si>
     <t>빙율</t>
@@ -816,7 +816,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%99%EC%9C%A8</t>
   </si>
   <si>
-    <t>1193조 4056억 8035만</t>
+    <t>1277조 9168억 9349만</t>
   </si>
   <si>
     <t>33세배장호</t>
@@ -843,7 +843,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EB%AF%B8%EC%9E%88%EA%B2%8C%EB%86%80%EB%9E%98</t>
   </si>
   <si>
-    <t>960조 3899억 5166만</t>
+    <t>1014조 8151억 8461만</t>
   </si>
   <si>
     <t>가덴</t>
@@ -873,7 +873,7 @@
     <t>바이퍼</t>
   </si>
   <si>
-    <t>783조 5993억 9157만</t>
+    <t>798조 7907억 2903만</t>
   </si>
   <si>
     <t>타뤽</t>
@@ -882,7 +882,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%A4%BD</t>
   </si>
   <si>
-    <t>759조 1590억 8137만</t>
+    <t>767조 4778억 1368만</t>
   </si>
   <si>
     <t>무르스</t>
@@ -891,7 +891,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%A5%B4%EC%8A%A4</t>
   </si>
   <si>
-    <t>722조 8101억 454만</t>
+    <t>724조 3437억 8634만</t>
   </si>
   <si>
     <t>새벽놀래</t>
@@ -909,7 +909,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%ED%99%A9%EC%83%88</t>
   </si>
   <si>
-    <t>620조 528억 618만</t>
+    <t>637조 1040억 9649만</t>
   </si>
   <si>
     <t>럭키루키</t>
@@ -918,7 +918,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%AD%ED%82%A4%EB%A3%A8%ED%82%A4</t>
   </si>
   <si>
-    <t>536조 2111억 8984만</t>
+    <t>545조 5633억 510만</t>
+  </si>
+  <si>
+    <t>넬샷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%AC%EC%83%B7</t>
+  </si>
+  <si>
+    <t>522조 1544억 7993만</t>
   </si>
   <si>
     <t>저기휴무</t>
@@ -930,15 +939,6 @@
     <t>520조 5128억</t>
   </si>
   <si>
-    <t>넬샷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%AC%EC%83%B7</t>
-  </si>
-  <si>
-    <t>494조 6391억 6864만</t>
-  </si>
-  <si>
     <t>박도란</t>
   </si>
   <si>
@@ -954,7 +954,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
   </si>
   <si>
-    <t>410조 8040억 472만</t>
+    <t>411조 997억 9396만</t>
   </si>
   <si>
     <t>뿌앵뿌앵</t>
@@ -975,7 +975,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>279조 8923억 8669만</t>
+    <t>280조 4315억 8147만</t>
   </si>
   <si>
     <t>냥홍이</t>
@@ -984,7 +984,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%ED%99%8D%EC%9D%B4</t>
   </si>
   <si>
-    <t>268조 9505억 6629만</t>
+    <t>270조 1480억 937만</t>
   </si>
   <si>
     <t>지존쫀파</t>
@@ -993,7 +993,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
   </si>
   <si>
-    <t>8188조 1046억 1273만</t>
+    <t>8217조 5797억 1907만</t>
   </si>
   <si>
     <t>수텍</t>
@@ -1002,7 +1002,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%ED%85%8D</t>
   </si>
   <si>
-    <t>6992조 3764억 4633만</t>
+    <t>7449조 4009억 54만</t>
   </si>
   <si>
     <t>협의</t>
@@ -1038,7 +1038,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
   </si>
   <si>
-    <t>2988조 9066억 1886만</t>
+    <t>2993조 5억 2522만</t>
+  </si>
+  <si>
+    <t>변신술사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
+  </si>
+  <si>
+    <t>2465조 3877억 3257만</t>
   </si>
   <si>
     <t>포항가자미</t>
@@ -1047,16 +1056,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
   </si>
   <si>
-    <t>2424조 9978억 2159만</t>
-  </si>
-  <si>
-    <t>변신술사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
-  </si>
-  <si>
-    <t>2290조 8654억 1226만</t>
+    <t>2432조 7584억 4757만</t>
   </si>
   <si>
     <t>뿡쓰</t>
@@ -1074,7 +1074,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
   </si>
   <si>
-    <t>2224조 5091억 9296만</t>
+    <t>2255조 9124억 1422만</t>
   </si>
   <si>
     <t>엘르가든</t>
@@ -1092,7 +1092,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>1831조 4812억 8418만</t>
+    <t>1833조 7180억 5399만</t>
   </si>
   <si>
     <t>온백</t>
@@ -1101,7 +1101,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
   </si>
   <si>
-    <t>1814조 2226억 6845만</t>
+    <t>1830조 1973억 356만</t>
   </si>
   <si>
     <t>파울</t>
@@ -1119,7 +1119,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
   </si>
   <si>
-    <t>1596조 5749억 9080만</t>
+    <t>1725조 492억 8770만</t>
   </si>
   <si>
     <t>모짜리코베르</t>
@@ -1152,7 +1152,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>1091조 9888억 5564만</t>
+    <t>1101조 5798억 4738만</t>
   </si>
   <si>
     <t>기본이리</t>
@@ -1161,7 +1161,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
   </si>
   <si>
-    <t>1050조 4181억 3112만</t>
+    <t>1050조 6512억 3068만</t>
   </si>
   <si>
     <t>김허덕</t>
@@ -1170,7 +1170,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
   </si>
   <si>
-    <t>1046조 865억 5975만</t>
+    <t>1047조 2041억 8654만</t>
   </si>
   <si>
     <t>냐은</t>
@@ -1188,7 +1188,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
   </si>
   <si>
-    <t>1015조 5704억 3498만</t>
+    <t>1018조 127억 2969만</t>
   </si>
   <si>
     <t>오옹나이스</t>
@@ -1197,7 +1197,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%B9%EB%82%98%EC%9D%B4%EC%8A%A4</t>
   </si>
   <si>
-    <t>799조 5234억 8229만</t>
+    <t>826조 4642억 7332만</t>
   </si>
   <si>
     <t>고숨도칭</t>
@@ -1206,7 +1206,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
   </si>
   <si>
-    <t>796조 5685억 5174만</t>
+    <t>819조 1516억 3816만</t>
   </si>
   <si>
     <t>전산봉</t>
@@ -1269,7 +1269,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%96%A5</t>
   </si>
   <si>
-    <t>7984조 7938억 2458만</t>
+    <t>8009조 8453억 8152만</t>
   </si>
   <si>
     <t>힐폿</t>
@@ -1287,7 +1287,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%80%EC%A0%84</t>
   </si>
   <si>
-    <t>3668조 9031억 8187만</t>
+    <t>3781조 9068억 199만</t>
   </si>
   <si>
     <t>숭타이준</t>
@@ -1311,7 +1311,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%91%EA%B1%B8</t>
   </si>
   <si>
-    <t>1867조 5966억 1163만</t>
+    <t>1881조 7876억 680만</t>
+  </si>
+  <si>
+    <t>탱폿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%8F%BF</t>
+  </si>
+  <si>
+    <t>1730조 2233억 310만</t>
+  </si>
+  <si>
+    <t>아이리쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EB%A6%AC%EC%89%AC</t>
+  </si>
+  <si>
+    <t>1673조 8707억 7898만</t>
   </si>
   <si>
     <t>뮬이</t>
@@ -1320,7 +1338,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AE%AC%EC%9D%B4</t>
   </si>
   <si>
-    <t>1618조 7801억 3460만</t>
+    <t>1653조 6593억 5059만</t>
   </si>
   <si>
     <t>지존빵수</t>
@@ -1329,7 +1347,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%B5%EC%88%98</t>
   </si>
   <si>
-    <t>1610조 953억 6364만</t>
+    <t>1611조 3008억 2919만</t>
   </si>
   <si>
     <t>야키산</t>
@@ -1350,15 +1368,6 @@
     <t>1447조 754억 2073만</t>
   </si>
   <si>
-    <t>탱폿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%8F%BF</t>
-  </si>
-  <si>
-    <t>1399조 9788억 4010만</t>
-  </si>
-  <si>
     <t>우즈2텐겐</t>
   </si>
   <si>
@@ -1368,15 +1377,6 @@
     <t>1317조 4439억 6807만</t>
   </si>
   <si>
-    <t>아이리쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EB%A6%AC%EC%89%AC</t>
-  </si>
-  <si>
-    <t>1252조 7283억 7526만</t>
-  </si>
-  <si>
     <t>독스케</t>
   </si>
   <si>
@@ -1386,6 +1386,15 @@
     <t>1150조 9844억 1359만</t>
   </si>
   <si>
+    <t>화둥에불낸년</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EB%91%A5%EC%97%90%EB%B6%88%EB%82%B8%EB%85%84</t>
+  </si>
+  <si>
+    <t>1100조 4777억 6755만</t>
+  </si>
+  <si>
     <t>우월별하</t>
   </si>
   <si>
@@ -1395,22 +1404,13 @@
     <t>1032조 7712억 9061만</t>
   </si>
   <si>
-    <t>화둥에불낸년</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EB%91%A5%EC%97%90%EB%B6%88%EB%82%B8%EB%85%84</t>
-  </si>
-  <si>
-    <t>1004조 9588억 8909만</t>
-  </si>
-  <si>
     <t>이게용</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B2%8C%EC%9A%A9</t>
   </si>
   <si>
-    <t>978조 4612억 6155만</t>
+    <t>978조 7638억 9111만</t>
   </si>
   <si>
     <t>기똥찬벌레</t>
@@ -1419,7 +1419,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%98%A5%EC%B0%AC%EB%B2%8C%EB%A0%88</t>
   </si>
   <si>
-    <t>951조 8281억 4925만</t>
+    <t>954조 2646억 6683만</t>
   </si>
   <si>
     <t>매화로이</t>
@@ -1428,7 +1428,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%ED%99%94%EB%A1%9C%EC%9D%B4</t>
   </si>
   <si>
-    <t>888조 3912억 9246만</t>
+    <t>918조 4009억 4487만</t>
   </si>
   <si>
     <t>JJuna</t>
@@ -1437,7 +1437,7 @@
     <t>https://mgf.gg/contents/character.php?n=JJuna</t>
   </si>
   <si>
-    <t>820조 1636억 7645만</t>
+    <t>833조 3992억 7722만</t>
   </si>
   <si>
     <t>에프람</t>
@@ -1449,22 +1449,22 @@
     <t>762조 4036억 3352만</t>
   </si>
   <si>
+    <t>난센</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EC%84%BC</t>
+  </si>
+  <si>
+    <t>723조 9121억 925만</t>
+  </si>
+  <si>
     <t>콜리셰마드르</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%9C%EB%A6%AC%EC%85%B0%EB%A7%88%EB%93%9C%EB%A5%B4</t>
   </si>
   <si>
-    <t>722조 8675억 2990만</t>
-  </si>
-  <si>
-    <t>난센</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EC%84%BC</t>
-  </si>
-  <si>
-    <t>712조 8834억 5919만</t>
+    <t>723조 8606억 2545만</t>
   </si>
   <si>
     <t>구도류</t>
@@ -1473,7 +1473,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%8F%84%EB%A5%98</t>
   </si>
   <si>
-    <t>597조 4814억 267만</t>
+    <t>662조 9337억 5072만</t>
   </si>
   <si>
     <t>조단23</t>
@@ -1482,7 +1482,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%8B%A823</t>
   </si>
   <si>
-    <t>547조 1752억 7480만</t>
+    <t>573조 6230억 4015만</t>
   </si>
   <si>
     <t>유채아버지</t>
@@ -1491,7 +1491,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%B1%84%EC%95%84%EB%B2%84%EC%A7%80</t>
   </si>
   <si>
-    <t>539조 4690억 5456만</t>
+    <t>544조 6860억 9144만</t>
   </si>
   <si>
     <t>아콩린</t>
@@ -1518,7 +1518,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BA%84%EA%BD%81</t>
   </si>
   <si>
-    <t>7278조 8334억 8539만</t>
+    <t>7363조 2391억 4894만</t>
   </si>
   <si>
     <t>별쌥</t>
@@ -1527,7 +1527,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A5</t>
   </si>
   <si>
-    <t>5960조 7320억 2376만</t>
+    <t>6085조 5153억 7648만</t>
   </si>
   <si>
     <t>진욱이에요</t>
@@ -1536,7 +1536,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9A%B1%EC%9D%B4%EC%97%90%EC%9A%94</t>
   </si>
   <si>
-    <t>4550조 1468억 5509만</t>
+    <t>4592조 7796억 1562만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A5%B4%EB%AA%AC</t>
@@ -1551,7 +1551,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%ED%99%A9%EA%B8%88%EB%A7%9D%EC%B9%98</t>
   </si>
   <si>
-    <t>3489조 5165억 7352만</t>
+    <t>3642조 356억 9080만</t>
   </si>
   <si>
     <t>김슴줌1</t>
@@ -1560,7 +1560,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%8A%B4%EC%A4%8C1</t>
   </si>
   <si>
-    <t>3270조 2257억 1209만</t>
+    <t>3276조 9644억 1607만</t>
   </si>
   <si>
     <t>천달</t>
@@ -1569,7 +1569,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EB%8B%AC</t>
   </si>
   <si>
-    <t>2717조 9833억 6552만</t>
+    <t>2815조 1272억 2796만</t>
   </si>
   <si>
     <t>호두와감자</t>
@@ -1581,22 +1581,22 @@
     <t>2525조 8587억 8102만</t>
   </si>
   <si>
+    <t>쿠댜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EB%8C%9C</t>
+  </si>
+  <si>
+    <t>2034조 9527억 9371만</t>
+  </si>
+  <si>
     <t>활용</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%99%9C%EC%9A%A9</t>
   </si>
   <si>
-    <t>2013조 908억 8266만</t>
-  </si>
-  <si>
-    <t>쿠댜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EB%8C%9C</t>
-  </si>
-  <si>
-    <t>1966조 5445억 7393만</t>
+    <t>2022조 1053억 9832만</t>
   </si>
   <si>
     <t>뚜징</t>
@@ -1605,7 +1605,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EC%A7%95</t>
   </si>
   <si>
-    <t>1806조 9134억 8019만</t>
+    <t>1821조 6787억 9932만</t>
   </si>
   <si>
     <t>별곡</t>
@@ -1614,7 +1614,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EA%B3%A1</t>
   </si>
   <si>
-    <t>969조 8456억 4768만</t>
+    <t>973조 5203억 5375만</t>
+  </si>
+  <si>
+    <t>동래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%9E%98</t>
+  </si>
+  <si>
+    <t>873조 7569억 2406만</t>
   </si>
   <si>
     <t>까쿠미</t>
@@ -1632,16 +1641,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%84%8Dol</t>
   </si>
   <si>
-    <t>788조 6038억 6835만</t>
-  </si>
-  <si>
-    <t>동래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%9E%98</t>
-  </si>
-  <si>
-    <t>788조 3697억 1727만</t>
+    <t>803조 9673억 2722만</t>
   </si>
   <si>
     <t>별쌤</t>
@@ -1650,7 +1650,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A4</t>
   </si>
   <si>
-    <t>738조 5918억 5801만</t>
+    <t>751조 3939억 6610만</t>
   </si>
   <si>
     <t>게렬곰</t>
@@ -1668,7 +1668,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%B4%EB%A0%88</t>
   </si>
   <si>
-    <t>651조 5939억 4000만</t>
+    <t>653조 2456억 6776만</t>
   </si>
   <si>
     <t>띠우</t>
@@ -1680,13 +1680,22 @@
     <t>611조 703억 208만</t>
   </si>
   <si>
+    <t>쿠까미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EA%B9%8C%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>568조 5865억 5732만</t>
+  </si>
+  <si>
     <t>끄챰</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%81%84%EC%B1%B0</t>
   </si>
   <si>
-    <t>475조 4236억 4624만</t>
+    <t>476조 6108억 9450만</t>
   </si>
   <si>
     <t>민족고대감자</t>
@@ -1698,22 +1707,13 @@
     <t>447조 5787억 6359만</t>
   </si>
   <si>
-    <t>쿠까미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EA%B9%8C%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>442조 874억 8170만</t>
-  </si>
-  <si>
     <t>승아의하루</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%EC%95%84%EC%9D%98%ED%95%98%EB%A3%A8</t>
   </si>
   <si>
-    <t>419조 8392억 5458만</t>
+    <t>426조 3736억 2690만</t>
   </si>
   <si>
     <t>왕단단이</t>
@@ -1722,7 +1722,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EB%8B%A8%EB%8B%A8%EC%9D%B4</t>
   </si>
   <si>
-    <t>374조 1106억 1593만</t>
+    <t>386조 7828억 5660만</t>
   </si>
   <si>
     <t>택Ol</t>
@@ -1740,7 +1740,7 @@
     <t>https://mgf.gg/contents/character.php?n=08217</t>
   </si>
   <si>
-    <t>328조 6713억 6296만</t>
+    <t>329조 3953억 9225만</t>
   </si>
   <si>
     <t>루이쥔</t>
@@ -1749,7 +1749,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%9D%B4%EC%A5%94</t>
   </si>
   <si>
-    <t>312조 422억 7493만</t>
+    <t>322조 5434억 4404만</t>
   </si>
   <si>
     <t>툼스데이</t>
@@ -1761,6 +1761,15 @@
     <t>285조 1117억 8099만</t>
   </si>
   <si>
+    <t>달갸뤼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EA%B0%B8%EB%A4%BC</t>
+  </si>
+  <si>
+    <t>110조 2393억 7850만</t>
+  </si>
+  <si>
     <t>꾸현</t>
   </si>
   <si>
@@ -1770,15 +1779,6 @@
     <t>88조 3966억 6293만</t>
   </si>
   <si>
-    <t>달갸뤼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EA%B0%B8%EB%A4%BC</t>
-  </si>
-  <si>
-    <t>73조 4903억 3576만</t>
-  </si>
-  <si>
     <t>김치싸대기</t>
   </si>
   <si>
@@ -1812,7 +1812,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>3586조 4643억 9612만</t>
+    <t>3648조 8531억 6875만</t>
   </si>
   <si>
     <t>엘라임</t>
@@ -1821,7 +1821,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
   </si>
   <si>
-    <t>3469조 8887억 4598만</t>
+    <t>3531조 2793억 8113만</t>
   </si>
   <si>
     <t>퍼퓸</t>
@@ -1830,7 +1830,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
   </si>
   <si>
-    <t>2483조 8452억 3773만</t>
+    <t>2484조 5237억 5157만</t>
   </si>
   <si>
     <t>서포터즈</t>
@@ -1839,7 +1839,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>2431조 544억 4930만</t>
+    <t>2443조 1439억 5824만</t>
+  </si>
+  <si>
+    <t>뻥뻥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
+  </si>
+  <si>
+    <t>2043조 9656억 4336만</t>
   </si>
   <si>
     <t>KR#TAKIN9CP37</t>
@@ -1848,7 +1857,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>1905조 4587억 3879만</t>
+    <t>1905조 6059억 8847만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
@@ -1857,15 +1866,6 @@
     <t>1831조 3912억 3225만</t>
   </si>
   <si>
-    <t>뻥뻥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
-  </si>
-  <si>
-    <t>1825조 2398억 5085만</t>
-  </si>
-  <si>
     <t>야가다</t>
   </si>
   <si>
@@ -1881,7 +1881,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
   </si>
   <si>
-    <t>1259조 8128억 5685만</t>
+    <t>1265조 7396억 7046만</t>
+  </si>
+  <si>
+    <t>채무조정</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
+  </si>
+  <si>
+    <t>1065조 650억 5642만</t>
+  </si>
+  <si>
+    <t>호우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>1062조 1444억 674만</t>
   </si>
   <si>
     <t>우후</t>
@@ -1890,25 +1908,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>1058조 2431억 2633만</t>
-  </si>
-  <si>
-    <t>호우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>1052조 9891억 7693만</t>
-  </si>
-  <si>
-    <t>채무조정</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
-  </si>
-  <si>
-    <t>1006조 7349억 1730만</t>
+    <t>1058조 5051억 8293만</t>
   </si>
   <si>
     <t>단풍카우</t>
@@ -1926,7 +1926,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
   </si>
   <si>
-    <t>928조 8138억 6047만</t>
+    <t>930조 1939억 3217만</t>
   </si>
   <si>
     <t>뽀송히</t>
@@ -1953,7 +1953,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
   </si>
   <si>
-    <t>560조 1285억 7637만</t>
+    <t>560조 3492억 2985만</t>
   </si>
   <si>
     <t>민들레꽃</t>
@@ -1971,7 +1971,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
   </si>
   <si>
-    <t>459조 5489억 3382만</t>
+    <t>524조 8468억 7860만</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>440조 6040억 4040만</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -1980,16 +1989,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
   </si>
   <si>
-    <t>420조 8785억 9592만</t>
-  </si>
-  <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>410조 5852억 7919만</t>
+    <t>425조 1582억 57만</t>
   </si>
   <si>
     <t>솔인</t>
@@ -1998,7 +1998,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
   </si>
   <si>
-    <t>372조 4821억 9681만</t>
+    <t>420조 9657억 7177만</t>
+  </si>
+  <si>
+    <t>아르미느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
+  </si>
+  <si>
+    <t>325조 1469억 5466만</t>
   </si>
   <si>
     <t>꼬북빵야</t>
@@ -2016,16 +2025,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
   </si>
   <si>
-    <t>249조 9325억 1140만</t>
-  </si>
-  <si>
-    <t>아르미느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
-  </si>
-  <si>
-    <t>245조 4859억 3395만</t>
+    <t>254조 6783억 7167만</t>
   </si>
   <si>
     <t>교주만두</t>
@@ -2034,7 +2034,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%90%EC%A3%BC%EB%A7%8C%EB%91%90</t>
   </si>
   <si>
-    <t>6경 4821조 8677억 1103만</t>
+    <t>6경 5777조 9196억 9550만</t>
   </si>
   <si>
     <t>할바이</t>
@@ -2046,7 +2046,7 @@
     <t>107</t>
   </si>
   <si>
-    <t>231조 2461억 1057만</t>
+    <t>231조 4036억 4133만</t>
   </si>
   <si>
     <t>섹밍</t>
@@ -2055,7 +2055,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B9%EB%B0%8D</t>
   </si>
   <si>
-    <t>211조 4498억 8225만</t>
+    <t>212조 2384억 7803만</t>
   </si>
   <si>
     <t>대구남성</t>
@@ -2079,7 +2079,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>39조 280억 1146만</t>
+    <t>40조 2826억 5542만</t>
   </si>
   <si>
     <t>토벤숍이</t>
@@ -2088,7 +2088,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%B2%A4%EC%88%8D%EC%9D%B4</t>
   </si>
   <si>
-    <t>36조 4537억 6794만</t>
+    <t>37조 303억 5299만</t>
   </si>
   <si>
     <t>낭랑28세</t>
@@ -2100,22 +2100,46 @@
     <t>36조 3976억 1339만</t>
   </si>
   <si>
+    <t>오스띤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%8A%A4%EB%9D%A4</t>
+  </si>
+  <si>
+    <t>34조 9341억 2338만</t>
+  </si>
+  <si>
     <t>빵신궁</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EC%8B%A0%EA%B6%81</t>
   </si>
   <si>
-    <t>30조 7181억 324만</t>
-  </si>
-  <si>
-    <t>오스띤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%8A%A4%EB%9D%A4</t>
-  </si>
-  <si>
-    <t>29조 9499억 3058만</t>
+    <t>32조 6484억 713만</t>
+  </si>
+  <si>
+    <t>썬콜우체국</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9A%B0%EC%B2%B4%EA%B5%AD</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>29조 1746억 7908만</t>
+  </si>
+  <si>
+    <t>마키맛키마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%82%A4%EB%A7%9B%ED%82%A4%EB%A7%88</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>28조 4286억 5242만</t>
   </si>
   <si>
     <t>밀초크코</t>
@@ -2127,37 +2151,13 @@
     <t>28조 1153억 4015만</t>
   </si>
   <si>
-    <t>마키맛키마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%82%A4%EB%A7%9B%ED%82%A4%EB%A7%88</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>27조 2464억 4277만</t>
-  </si>
-  <si>
     <t>킬혁</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%82%AC%ED%98%81</t>
   </si>
   <si>
-    <t>25조 4433억 6581만</t>
-  </si>
-  <si>
-    <t>썬콜우체국</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9A%B0%EC%B2%B4%EA%B5%AD</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>25조 787억 2808만</t>
+    <t>26조 1938억 4246만</t>
   </si>
   <si>
     <t>문보겨엉</t>
@@ -2181,6 +2181,15 @@
     <t>23조 9956억 4822만</t>
   </si>
   <si>
+    <t>땡요나퐁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%95%A1%EC%9A%94%EB%82%98%ED%90%81</t>
+  </si>
+  <si>
+    <t>23조 7753억 377만</t>
+  </si>
+  <si>
     <t>씅놈</t>
   </si>
   <si>
@@ -2190,31 +2199,22 @@
     <t>22조 1653억 9791만</t>
   </si>
   <si>
+    <t>썬콜법사ss</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%ACss</t>
+  </si>
+  <si>
+    <t>20조 7784억 5647만</t>
+  </si>
+  <si>
     <t>배렛나루왁서</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%EB%A0%9B%EB%82%98%EB%A3%A8%EC%99%81%EC%84%9C</t>
   </si>
   <si>
-    <t>20조 6218억 5190만</t>
-  </si>
-  <si>
-    <t>땡요나퐁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%95%A1%EC%9A%94%EB%82%98%ED%90%81</t>
-  </si>
-  <si>
-    <t>20조 2598억 1813만</t>
-  </si>
-  <si>
-    <t>썬콜법사ss</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%ACss</t>
-  </si>
-  <si>
-    <t>19조 4439억 6528만</t>
+    <t>20조 7626억 7590만</t>
   </si>
   <si>
     <t>포디케이</t>
@@ -2223,25 +2223,13 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%94%94%EC%BC%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>9조 5884억 9293만</t>
+    <t>9조 8785억 6273만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%ED%82%A4%EB%B9%84%ED%82%A4</t>
   </si>
   <si>
-    <t>6조 3603억 7229만</t>
-  </si>
-  <si>
-    <t>경기도인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EA%B8%B0%EB%8F%84%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>5조 6702억 2764만</t>
+    <t>7조 5757억 9871만</t>
   </si>
   <si>
     <t>즈나니</t>
@@ -2253,7 +2241,19 @@
     <t>100</t>
   </si>
   <si>
-    <t>3조 2857억 8721만</t>
+    <t>3조 3723억 2727만</t>
+  </si>
+  <si>
+    <t>닝윤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%9D%EC%9C%A4</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>3조 2786억 3256만</t>
   </si>
 </sst>
 </file>
@@ -3301,10 +3301,10 @@
         <v>102</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3315,22 +3315,22 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>109</v>
@@ -3362,7 +3362,7 @@
         <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>109</v>
@@ -3394,13 +3394,13 @@
         <v>89</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>109</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3411,16 +3411,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>89</v>
@@ -3432,7 +3432,7 @@
         <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3443,28 +3443,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3475,28 +3475,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="H16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3507,28 +3507,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3539,25 +3539,25 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>168</v>
@@ -3589,7 +3589,7 @@
         <v>90</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>172</v>
@@ -3621,7 +3621,7 @@
         <v>90</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>176</v>
@@ -3714,10 +3714,10 @@
         <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>190</v>
@@ -3749,7 +3749,7 @@
         <v>102</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>194</v>
@@ -3781,7 +3781,7 @@
         <v>198</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>199</v>
@@ -3810,7 +3810,7 @@
         <v>89</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>126</v>
@@ -3842,10 +3842,10 @@
         <v>89</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>207</v>
@@ -3874,7 +3874,7 @@
         <v>89</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>185</v>
@@ -3906,13 +3906,13 @@
         <v>89</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3923,25 +3923,25 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>220</v>
@@ -4087,7 +4087,7 @@
         <v>107</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>226</v>
@@ -4314,7 +4314,7 @@
         <v>248</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>249</v>
@@ -4360,7 +4360,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>253</v>
@@ -4407,7 +4407,7 @@
         <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>109</v>
@@ -4442,7 +4442,7 @@
         <v>90</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>261</v>
@@ -4456,7 +4456,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>262</v>
@@ -4474,7 +4474,7 @@
         <v>90</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>264</v>
@@ -4488,7 +4488,7 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>265</v>
@@ -4506,7 +4506,7 @@
         <v>96</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>267</v>
@@ -4520,7 +4520,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>268</v>
@@ -4538,7 +4538,7 @@
         <v>198</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>270</v>
@@ -4552,7 +4552,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>271</v>
@@ -4584,7 +4584,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>274</v>
@@ -4602,7 +4602,7 @@
         <v>108</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>276</v>
@@ -4634,7 +4634,7 @@
         <v>279</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>280</v>
@@ -4698,7 +4698,7 @@
         <v>102</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>286</v>
@@ -4730,7 +4730,7 @@
         <v>102</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>289</v>
@@ -4762,7 +4762,7 @@
         <v>102</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>215</v>
+        <v>185</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>292</v>
@@ -4794,7 +4794,7 @@
         <v>198</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>295</v>
@@ -4826,7 +4826,7 @@
         <v>184</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>298</v>
@@ -4858,7 +4858,7 @@
         <v>184</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>301</v>
@@ -4951,10 +4951,10 @@
         <v>89</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>310</v>
@@ -4968,7 +4968,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>311</v>
@@ -4983,7 +4983,7 @@
         <v>89</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>313</v>
@@ -5132,7 +5132,7 @@
         <v>89</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>103</v>
@@ -5324,10 +5324,10 @@
         <v>89</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>108</v>
+        <v>198</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>338</v>
@@ -5356,10 +5356,10 @@
         <v>89</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>198</v>
+        <v>108</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>341</v>
@@ -5388,10 +5388,10 @@
         <v>89</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>344</v>
@@ -5405,7 +5405,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>345</v>
@@ -5423,7 +5423,7 @@
         <v>198</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>347</v>
@@ -5452,7 +5452,7 @@
         <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>109</v>
@@ -5501,7 +5501,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>354</v>
@@ -5533,7 +5533,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>357</v>
@@ -5565,7 +5565,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>360</v>
@@ -5597,7 +5597,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>363</v>
@@ -5615,7 +5615,7 @@
         <v>90</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>365</v>
@@ -5629,7 +5629,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>43</v>
@@ -5647,7 +5647,7 @@
         <v>198</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>367</v>
@@ -5711,7 +5711,7 @@
         <v>198</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>373</v>
@@ -5775,7 +5775,7 @@
         <v>90</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>379</v>
@@ -5807,7 +5807,7 @@
         <v>279</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>382</v>
@@ -5871,7 +5871,7 @@
         <v>96</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>388</v>
@@ -5935,7 +5935,7 @@
         <v>90</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>394</v>
@@ -5999,7 +5999,7 @@
         <v>90</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>400</v>
@@ -6013,7 +6013,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>401</v>
@@ -6028,10 +6028,10 @@
         <v>89</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>403</v>
@@ -6063,7 +6063,7 @@
         <v>279</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>406</v>
@@ -6241,7 +6241,7 @@
         <v>89</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>103</v>
@@ -6401,7 +6401,7 @@
         <v>89</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>90</v>
+        <v>279</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>109</v>
@@ -6433,10 +6433,10 @@
         <v>89</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>432</v>
@@ -6450,7 +6450,7 @@
         <v>45</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>433</v>
@@ -6468,7 +6468,7 @@
         <v>90</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>435</v>
@@ -6497,7 +6497,7 @@
         <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>126</v>
@@ -6529,10 +6529,10 @@
         <v>89</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>279</v>
+        <v>90</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>441</v>
@@ -6546,7 +6546,7 @@
         <v>45</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>442</v>
@@ -6561,10 +6561,10 @@
         <v>89</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>444</v>
@@ -6578,7 +6578,7 @@
         <v>45</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>445</v>
@@ -6593,10 +6593,10 @@
         <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>447</v>
@@ -6610,7 +6610,7 @@
         <v>45</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>448</v>
@@ -6628,7 +6628,7 @@
         <v>102</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>450</v>
@@ -6642,7 +6642,7 @@
         <v>45</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>451</v>
@@ -6660,7 +6660,7 @@
         <v>90</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>453</v>
@@ -6674,7 +6674,7 @@
         <v>45</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>454</v>
@@ -6692,7 +6692,7 @@
         <v>90</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>456</v>
@@ -6724,7 +6724,7 @@
         <v>184</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>459</v>
@@ -6756,7 +6756,7 @@
         <v>108</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>462</v>
@@ -6788,7 +6788,7 @@
         <v>279</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>465</v>
@@ -6852,7 +6852,7 @@
         <v>90</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>471</v>
@@ -6881,10 +6881,10 @@
         <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>102</v>
+        <v>279</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>474</v>
@@ -6913,10 +6913,10 @@
         <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>279</v>
+        <v>102</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>477</v>
@@ -6948,7 +6948,7 @@
         <v>279</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>480</v>
@@ -7044,7 +7044,7 @@
         <v>90</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>489</v>
@@ -7058,7 +7058,7 @@
         <v>45</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>490</v>
@@ -7076,7 +7076,7 @@
         <v>90</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>492</v>
@@ -7445,10 +7445,10 @@
         <v>89</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>518</v>
@@ -7462,7 +7462,7 @@
         <v>53</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>519</v>
@@ -7477,10 +7477,10 @@
         <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>521</v>
@@ -7544,7 +7544,7 @@
         <v>102</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>527</v>
@@ -7558,7 +7558,7 @@
         <v>53</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>528</v>
@@ -7573,10 +7573,10 @@
         <v>89</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>279</v>
+        <v>90</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>530</v>
@@ -7590,7 +7590,7 @@
         <v>53</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>531</v>
@@ -7605,10 +7605,10 @@
         <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>102</v>
+        <v>279</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>533</v>
@@ -7622,7 +7622,7 @@
         <v>53</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>534</v>
@@ -7637,10 +7637,10 @@
         <v>89</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>536</v>
@@ -7654,7 +7654,7 @@
         <v>53</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>537</v>
@@ -7672,7 +7672,7 @@
         <v>90</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>539</v>
@@ -7686,7 +7686,7 @@
         <v>53</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>540</v>
@@ -7704,7 +7704,7 @@
         <v>90</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>542</v>
@@ -7797,10 +7797,10 @@
         <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>551</v>
@@ -7829,7 +7829,7 @@
         <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>185</v>
@@ -7861,10 +7861,10 @@
         <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>90</v>
+        <v>167</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>313</v>
+        <v>185</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>557</v>
@@ -7896,7 +7896,7 @@
         <v>90</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>560</v>
@@ -7928,7 +7928,7 @@
         <v>248</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>215</v>
+        <v>185</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>563</v>
@@ -7960,7 +7960,7 @@
         <v>96</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>566</v>
@@ -7992,7 +7992,7 @@
         <v>90</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>569</v>
@@ -8024,7 +8024,7 @@
         <v>90</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>572</v>
@@ -8070,7 +8070,7 @@
         <v>53</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>576</v>
@@ -8085,7 +8085,7 @@
         <v>89</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>313</v>
@@ -8117,7 +8117,7 @@
         <v>89</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>313</v>
@@ -8300,7 +8300,7 @@
         <v>90</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>590</v>
@@ -8329,7 +8329,7 @@
         <v>89</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>109</v>
@@ -8425,7 +8425,7 @@
         <v>89</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>126</v>
@@ -8457,10 +8457,10 @@
         <v>89</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>605</v>
@@ -8477,25 +8477,25 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>67</v>
+        <v>606</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>67</v>
+        <v>606</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>44</v>
@@ -8506,25 +8506,25 @@
         <v>61</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>608</v>
+        <v>67</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>608</v>
+        <v>67</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>609</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>184</v>
+        <v>102</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>610</v>
@@ -8585,10 +8585,10 @@
         <v>89</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>616</v>
@@ -8602,7 +8602,7 @@
         <v>61</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>617</v>
@@ -8617,10 +8617,10 @@
         <v>89</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>185</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>619</v>
@@ -8634,7 +8634,7 @@
         <v>61</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>620</v>
@@ -8649,7 +8649,7 @@
         <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>126</v>
@@ -8666,7 +8666,7 @@
         <v>61</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>623</v>
@@ -8681,10 +8681,10 @@
         <v>89</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>131</v>
+        <v>185</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>625</v>
@@ -8698,7 +8698,7 @@
         <v>61</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>626</v>
@@ -8716,7 +8716,7 @@
         <v>96</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>628</v>
@@ -8730,7 +8730,7 @@
         <v>61</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>629</v>
@@ -8777,10 +8777,10 @@
         <v>89</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>634</v>
@@ -8812,7 +8812,7 @@
         <v>90</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>637</v>
@@ -8908,7 +8908,7 @@
         <v>90</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>646</v>
@@ -8937,7 +8937,7 @@
         <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>184</v>
+        <v>90</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>185</v>
@@ -8969,7 +8969,7 @@
         <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>90</v>
+        <v>184</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>185</v>
@@ -9004,7 +9004,7 @@
         <v>108</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>655</v>
@@ -9033,10 +9033,10 @@
         <v>89</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>215</v>
+        <v>313</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>658</v>
@@ -9065,10 +9065,10 @@
         <v>89</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>279</v>
+        <v>90</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>661</v>
@@ -9097,10 +9097,10 @@
         <v>89</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>96</v>
+        <v>279</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>313</v>
+        <v>219</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>664</v>
@@ -9279,7 +9279,7 @@
         <v>102</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>674</v>
@@ -9340,7 +9340,7 @@
         <v>89</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>681</v>
@@ -9404,7 +9404,7 @@
         <v>89</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>681</v>
@@ -9436,7 +9436,7 @@
         <v>89</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>163</v>
+        <v>102</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>681</v>
@@ -9468,7 +9468,7 @@
         <v>89</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>681</v>
@@ -9485,7 +9485,7 @@
         <v>68</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>695</v>
@@ -9500,13 +9500,13 @@
         <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>681</v>
+        <v>697</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -9520,25 +9520,25 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -9552,25 +9552,25 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>681</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -9581,25 +9581,25 @@
         <v>68</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>707</v>
+        <v>681</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>708</v>
@@ -9613,7 +9613,7 @@
         <v>68</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>709</v>
@@ -9645,7 +9645,7 @@
         <v>68</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>713</v>
@@ -9677,7 +9677,7 @@
         <v>68</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>716</v>
@@ -9692,7 +9692,7 @@
         <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>681</v>
@@ -9709,7 +9709,7 @@
         <v>68</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>719</v>
@@ -9724,7 +9724,7 @@
         <v>89</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>153</v>
+        <v>96</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>681</v>
@@ -9756,7 +9756,7 @@
         <v>89</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>108</v>
+        <v>161</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>681</v>
@@ -9788,7 +9788,7 @@
         <v>89</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>681</v>
@@ -9855,7 +9855,7 @@
         <v>248</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>732</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -84,7 +84,7 @@
     <t>Scania 13</t>
   </si>
   <si>
-    <t>857</t>
+    <t>859</t>
   </si>
   <si>
     <t>34위</t>
@@ -117,7 +117,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>850</t>
+    <t>851</t>
   </si>
   <si>
     <t>38위</t>
@@ -147,7 +147,7 @@
     <t>Scania 23</t>
   </si>
   <si>
-    <t>922</t>
+    <t>924</t>
   </si>
   <si>
     <t>12위</t>
@@ -201,7 +201,7 @@
     <t>Scania 3</t>
   </si>
   <si>
-    <t>918</t>
+    <t>919</t>
   </si>
   <si>
     <t>37위</t>
@@ -2046,7 +2046,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%90%EC%A3%BC%EB%A7%8C%EB%91%90</t>
   </si>
   <si>
-    <t>6경 6938조 7858억 839만</t>
+    <t>6경 7863조 6241억 5421만</t>
   </si>
   <si>
     <t>할바이</t>
@@ -2067,7 +2067,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B9%EB%B0%8D</t>
   </si>
   <si>
-    <t>222조 5745억 8968만</t>
+    <t>225조 7858억 6277만</t>
   </si>
   <si>
     <t>대구남성</t>
@@ -2103,6 +2103,15 @@
     <t>40조 2826억 5542만</t>
   </si>
   <si>
+    <t>오스띤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%8A%A4%EB%9D%A4</t>
+  </si>
+  <si>
+    <t>39조 7598억 3127만</t>
+  </si>
+  <si>
     <t>토벤숍이</t>
   </si>
   <si>
@@ -2112,15 +2121,6 @@
     <t>37조 9497억 6922만</t>
   </si>
   <si>
-    <t>오스띤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%8A%A4%EB%9D%A4</t>
-  </si>
-  <si>
-    <t>35조 12억 8580만</t>
-  </si>
-  <si>
     <t>빵신궁</t>
   </si>
   <si>
@@ -2139,7 +2139,16 @@
     <t>103</t>
   </si>
   <si>
-    <t>29조 4514억 132만</t>
+    <t>30조 3004억 723만</t>
+  </si>
+  <si>
+    <t>밀초크코</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%EC%B4%88%ED%81%AC%EC%BD%94</t>
+  </si>
+  <si>
+    <t>30조 642억 2549만</t>
   </si>
   <si>
     <t>마키맛키마</t>
@@ -2154,15 +2163,6 @@
     <t>28조 4370억 1152만</t>
   </si>
   <si>
-    <t>밀초크코</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%EC%B4%88%ED%81%AC%EC%BD%94</t>
-  </si>
-  <si>
-    <t>28조 1153억 4015만</t>
-  </si>
-  <si>
     <t>킬혁</t>
   </si>
   <si>
@@ -2178,7 +2178,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%ED%86%B5%EB%B0%9B%EB%8A%94%EA%B0%88%EB%B9%84</t>
   </si>
   <si>
-    <t>25조 4971억 9716만</t>
+    <t>25조 5115억 6680만</t>
   </si>
   <si>
     <t>문보겨엉</t>
@@ -2226,7 +2226,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%EB%A0%9B%EB%82%98%EB%A3%A8%EC%99%81%EC%84%9C</t>
   </si>
   <si>
-    <t>20조 7626억 7590만</t>
+    <t>21조 1749억 5773만</t>
   </si>
   <si>
     <t>페프릭2</t>
@@ -2250,7 +2250,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%ED%82%A4%EB%B9%84%ED%82%A4</t>
   </si>
   <si>
-    <t>7조 6325억 4371만</t>
+    <t>8조 2642억 6569만</t>
   </si>
   <si>
     <t>즈나니</t>
@@ -2262,7 +2262,7 @@
     <t>100</t>
   </si>
   <si>
-    <t>3조 3723억 2727만</t>
+    <t>3조 6189억 1745만</t>
   </si>
   <si>
     <t>닝윤</t>
@@ -9207,7 +9207,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9455,7 +9455,7 @@
         <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>203</v>
+        <v>103</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>685</v>
@@ -9487,7 +9487,7 @@
         <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>103</v>
+        <v>203</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>685</v>
@@ -9583,13 +9583,13 @@
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>168</v>
+        <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>705</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>706</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>43</v>
@@ -9603,22 +9603,22 @@
         <v>142</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>708</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>685</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>709</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -18,12 +18,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">더위사냥!$A$1:$J$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">더위사냥!$A$1:$J$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">든솔!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">따숨!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">만영!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">바텀!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">빅딜!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">바텀!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">빅딜!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">지존길드!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2174" uniqueCount="740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2194" uniqueCount="747">
   <si>
     <t>guild_name</t>
   </si>
@@ -84,7 +84,7 @@
     <t>Scania 13</t>
   </si>
   <si>
-    <t>869</t>
+    <t>873</t>
   </si>
   <si>
     <t>36위</t>
@@ -117,7 +117,7 @@
     <t>Scania 23</t>
   </si>
   <si>
-    <t>934</t>
+    <t>941</t>
   </si>
   <si>
     <t>12위</t>
@@ -147,7 +147,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>863</t>
+    <t>866</t>
   </si>
   <si>
     <t>39위</t>
@@ -174,7 +174,7 @@
     <t>Scania 4</t>
   </si>
   <si>
-    <t>877</t>
+    <t>883</t>
   </si>
   <si>
     <t>30위</t>
@@ -201,7 +201,7 @@
     <t>Scania 29</t>
   </si>
   <si>
-    <t>890</t>
+    <t>892</t>
   </si>
   <si>
     <t>16위</t>
@@ -225,7 +225,10 @@
     <t>Scania 3</t>
   </si>
   <si>
-    <t>930</t>
+    <t>936</t>
+  </si>
+  <si>
+    <t>40위</t>
   </si>
   <si>
     <t>4경 3027조 2732억 9013만</t>
@@ -246,7 +249,7 @@
     <t>Scania 50</t>
   </si>
   <si>
-    <t>889</t>
+    <t>891</t>
   </si>
   <si>
     <t>4위</t>
@@ -309,7 +312,7 @@
     <t>117</t>
   </si>
   <si>
-    <t>7경 4395조 6344억 2201만</t>
+    <t>8경 955조 5504억 1622만</t>
   </si>
   <si>
     <t>2</t>
@@ -327,7 +330,7 @@
     <t>116</t>
   </si>
   <si>
-    <t>3경 756조 9441억 3344만</t>
+    <t>3경 4454조 1771억 441만</t>
   </si>
   <si>
     <t>3</t>
@@ -360,76 +363,88 @@
     <t>팔라딘</t>
   </si>
   <si>
+    <t>7320조 9731억 42만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>손챠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%90%EC%B1%A0</t>
+  </si>
+  <si>
+    <t>6566조 8993억 2840만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>강필구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%84%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>5795조 243억 391만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>GOD날두</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=GOD%EB%82%A0%EB%91%90</t>
+  </si>
+  <si>
+    <t>5152조 2929억 580만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>알배기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%8C%EB%B0%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>4412조 4638억 6313만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>주요엘농산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%9A%94%EC%97%98%EB%86%8D%EC%82%B0</t>
+  </si>
+  <si>
+    <t>3371조 1631억 8076만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>러브포티</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%B8%8C%ED%8F%AC%ED%8B%B0</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>6825조 1952억 7444만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>강필구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%84%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>5477조 8071억 911만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>GOD날두</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=GOD%EB%82%A0%EB%91%90</t>
-  </si>
-  <si>
-    <t>5152조 2929억 580만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>손챠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%90%EC%B1%A0</t>
-  </si>
-  <si>
-    <t>5113조 9402억 283만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>알배기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%8C%EB%B0%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>4185조 3566억 9153만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>주요엘농산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%9A%94%EC%97%98%EB%86%8D%EC%82%B0</t>
-  </si>
-  <si>
-    <t>3339조 7819억 8470만</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>3245조 2928억 8407만</t>
+  </si>
+  <si>
+    <t>11</t>
   </si>
   <si>
     <t>하찌바리이</t>
@@ -438,10 +453,10 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B0%8C%EB%B0%94%EB%A6%AC%EC%9D%B4</t>
   </si>
   <si>
-    <t>3106조 702억 2689만</t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>3200조 4397억 9454만</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>테이킷슬로우</t>
@@ -456,18 +471,6 @@
     <t>3050조 3867억 6933만</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>러브포티</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%B8%8C%ED%8F%AC%ED%8B%B0</t>
-  </si>
-  <si>
-    <t>3010조 3158억 3827만</t>
-  </si>
-  <si>
     <t>13</t>
   </si>
   <si>
@@ -477,7 +480,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EA%B8%88%EC%96%B4%EA%B8%88%EB%8B%88</t>
   </si>
   <si>
-    <t>2437조 3344억 6767만</t>
+    <t>2449조 7623억 409만</t>
   </si>
   <si>
     <t>14</t>
@@ -501,6 +504,21 @@
     <t>15</t>
   </si>
   <si>
+    <t>Darken</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Darken</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>2028조 1280억 6282만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>88치킨</t>
   </si>
   <si>
@@ -513,21 +531,6 @@
     <t>1978조 8045억 2544만</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Darken</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Darken</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>1968조 5365억 2474만</t>
-  </si>
-  <si>
     <t>17</t>
   </si>
   <si>
@@ -549,7 +552,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9D%B4%ED%95%98%EB%A1%9C%ED%95%98%EB%9D%BC</t>
   </si>
   <si>
-    <t>1568조 9673억 9173만</t>
+    <t>1698조 5982억 3367만</t>
   </si>
   <si>
     <t>19</t>
@@ -561,36 +564,51 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EB%B3%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>1421조 9976억 815만</t>
+    <t>1479조 8061억 8067만</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
+    <t>v박효신v</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=v%EB%B0%95%ED%9A%A8%EC%8B%A0v</t>
+  </si>
+  <si>
+    <t>1320조 8273억 6704만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>여릿</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%A6%BF</t>
   </si>
   <si>
-    <t>1175조 5517억 762만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>v박효신v</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=v%EB%B0%95%ED%9A%A8%EC%8B%A0v</t>
-  </si>
-  <si>
-    <t>1173조 6935억 8320만</t>
+    <t>1215조 5892억 2562만</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
+    <t>시간이돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B0%84%EC%9D%B4%EB%8F%88</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>1175조 7749억 1807만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
     <t>초읍사나이</t>
   </si>
   <si>
@@ -603,10 +621,22 @@
     <t>110</t>
   </si>
   <si>
-    <t>1054조 640억 21만</t>
-  </si>
-  <si>
-    <t>23</t>
+    <t>1149조 8254억 2838만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>다둉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1051조 8745억 8180만</t>
+  </si>
+  <si>
+    <t>25</t>
   </si>
   <si>
     <t>도레오</t>
@@ -618,33 +648,6 @@
     <t>985조 3833억 8106만</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>다둉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>959조 2659억 2007만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>시간이돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B0%84%EC%9D%B4%EB%8F%88</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>948조 2787억 2895만</t>
-  </si>
-  <si>
     <t>26</t>
   </si>
   <si>
@@ -654,7 +657,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%9C%BC%EB%86%8D</t>
   </si>
   <si>
-    <t>830조 8939억 1801만</t>
+    <t>886조 1045억 1505만</t>
   </si>
   <si>
     <t>27</t>
@@ -666,12 +669,27 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%87%B8</t>
   </si>
   <si>
-    <t>586조 8982억 274만</t>
+    <t>656조 2458억 3631만</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
+    <t>하엘이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%97%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>613조 4694억 3249만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
     <t>아리미쿵</t>
   </si>
   <si>
@@ -681,21 +699,6 @@
     <t>540조 9494억 6800만</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>하엘이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%97%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>539조 9235억 1149만</t>
-  </si>
-  <si>
     <t>30</t>
   </si>
   <si>
@@ -705,7 +708,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%8A%94%EB%B0%B0%EB%B6%88%EB%9F%AC%EC%9A%94</t>
   </si>
   <si>
-    <t>500조 4379억 2093만</t>
+    <t>500조 5054억 5138만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EA%B8%B0%EC%9C%A0%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>1경 2732조 8456억 7264만</t>
   </si>
   <si>
     <t>무곽</t>
@@ -717,13 +726,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>1경 2113조 7010억 9109만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EA%B8%B0%EC%9C%A0%EB%AC%B4</t>
-  </si>
-  <si>
-    <t>1경 1403조 4889억 5224만</t>
+    <t>1경 2526조 6847억 9408만</t>
   </si>
   <si>
     <t>형팡팡이</t>
@@ -735,22 +738,22 @@
     <t>5209조 9277억 4214만</t>
   </si>
   <si>
+    <t>붉은모자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%89%EC%9D%80%EB%AA%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>3702조 4677억 8853만</t>
+  </si>
+  <si>
     <t>2번째캐릭</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=2%EB%B2%88%EC%A7%B8%EC%BA%90%EB%A6%AD</t>
   </si>
   <si>
-    <t>3640조 9694억 6763만</t>
-  </si>
-  <si>
-    <t>붉은모자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%89%EC%9D%80%EB%AA%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>3624조 6368억 4218만</t>
+    <t>3695조 8405억 1988만</t>
   </si>
   <si>
     <t>장뱁새</t>
@@ -759,7 +762,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B1%81%EC%83%88</t>
   </si>
   <si>
-    <t>3393조 171억 298만</t>
+    <t>3484조 3912억 6973만</t>
+  </si>
+  <si>
+    <t>히테라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%85%8C%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>3360조 7324억 4501만</t>
   </si>
   <si>
     <t>꽁꽁냉법</t>
@@ -768,7 +780,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EA%BD%81%EB%83%89%EB%B2%95</t>
   </si>
   <si>
-    <t>2411조 2417억 4395만</t>
+    <t>2565조 4438억 9218만</t>
   </si>
   <si>
     <t>테토일남</t>
@@ -783,6 +795,15 @@
     <t>2294조 4627억 6705만</t>
   </si>
   <si>
+    <t>뚜기파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EA%B8%B0%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>2025조 6243억 9048만</t>
+  </si>
+  <si>
     <t>브네</t>
   </si>
   <si>
@@ -792,22 +813,22 @@
     <t>1928조 5981억 7061만</t>
   </si>
   <si>
-    <t>뚜기파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EA%B8%B0%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>1826조 4933억 5622만</t>
-  </si>
-  <si>
     <t>라쥬르</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%A5%AC%EB%A5%B4</t>
   </si>
   <si>
-    <t>1607조 8256억 3694만</t>
+    <t>1625조 4762억 9577만</t>
+  </si>
+  <si>
+    <t>재미있게놀래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EB%AF%B8%EC%9E%88%EA%B2%8C%EB%86%80%EB%9E%98</t>
+  </si>
+  <si>
+    <t>1364조 9796억 5823만</t>
   </si>
   <si>
     <t>빙율</t>
@@ -816,7 +837,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%99%EC%9C%A8</t>
   </si>
   <si>
-    <t>1279조 7202억 6968만</t>
+    <t>1314조 7187억 8022만</t>
   </si>
   <si>
     <t>33세배장호</t>
@@ -825,16 +846,7 @@
     <t>https://mgf.gg/contents/character.php?n=33%EC%84%B8%EB%B0%B0%EC%9E%A5%ED%98%B8</t>
   </si>
   <si>
-    <t>1195조 7981억 4943만</t>
-  </si>
-  <si>
-    <t>재미있게놀래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EB%AF%B8%EC%9E%88%EA%B2%8C%EB%86%80%EB%9E%98</t>
-  </si>
-  <si>
-    <t>1147조 3293억 1346만</t>
+    <t>1243조 6726억 369만</t>
   </si>
   <si>
     <t>적젹적</t>
@@ -843,7 +855,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%81%EC%A0%B9%EC%A0%81</t>
   </si>
   <si>
-    <t>1071조 4528억 148만</t>
+    <t>1155조 2525억 2408만</t>
   </si>
   <si>
     <t>가덴</t>
@@ -864,7 +876,7 @@
     <t>바이퍼</t>
   </si>
   <si>
-    <t>867조 4036억 7417만</t>
+    <t>939조 4028억 5874만</t>
   </si>
   <si>
     <t>정기휴므</t>
@@ -882,7 +894,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%A4%BD</t>
   </si>
   <si>
-    <t>793조 1390억 7569만</t>
+    <t>804조 8666억 5004만</t>
   </si>
   <si>
     <t>무르스</t>
@@ -891,16 +903,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%A5%B4%EC%8A%A4</t>
   </si>
   <si>
-    <t>755조 4291억 9052만</t>
-  </si>
-  <si>
-    <t>새벽놀래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%88%EB%B2%BD%EB%86%80%EB%9E%98</t>
-  </si>
-  <si>
-    <t>721조 9101억 319만</t>
+    <t>781조 786억 3030만</t>
   </si>
   <si>
     <t>채황새</t>
@@ -909,7 +912,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%ED%99%A9%EC%83%88</t>
   </si>
   <si>
-    <t>704조 7281억 1323만</t>
+    <t>748조 9237억 7147만</t>
   </si>
   <si>
     <t>럭키루키</t>
@@ -918,7 +921,34 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%AD%ED%82%A4%EB%A3%A8%ED%82%A4</t>
   </si>
   <si>
-    <t>687조 5308억 5856만</t>
+    <t>726조 2461억 3618만</t>
+  </si>
+  <si>
+    <t>저기휴무</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%80%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>699조 6704억 9749만</t>
+  </si>
+  <si>
+    <t>박도란</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%8F%84%EB%9E%80</t>
+  </si>
+  <si>
+    <t>631조 424억 363만</t>
+  </si>
+  <si>
+    <t>장기휴무</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>539조 87억 1816만</t>
   </si>
   <si>
     <t>넬샷</t>
@@ -930,40 +960,13 @@
     <t>534조 5433억 6031만</t>
   </si>
   <si>
-    <t>저기휴무</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%80%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
-  </si>
-  <si>
-    <t>520조 5128억</t>
-  </si>
-  <si>
-    <t>박도란</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%8F%84%EB%9E%80</t>
-  </si>
-  <si>
-    <t>423조 6857억 6542만</t>
-  </si>
-  <si>
-    <t>장기휴무</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
-  </si>
-  <si>
-    <t>414조 2163억 1053만</t>
-  </si>
-  <si>
     <t>뿌앵뿌앵</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EC%95%B5%EB%BF%8C%EC%95%B5</t>
   </si>
   <si>
-    <t>395조 8266억 4000만</t>
+    <t>407조 2779억 5092만</t>
   </si>
   <si>
     <t>냥홍이</t>
@@ -972,7 +975,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%ED%99%8D%EC%9D%B4</t>
   </si>
   <si>
-    <t>302조 2704억 7085만</t>
+    <t>325조 5988억 9275만</t>
   </si>
   <si>
     <t>윤빵쭈</t>
@@ -1002,7 +1005,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
   </si>
   <si>
-    <t>7601조 6815억 1984만</t>
+    <t>7915조 5233억 4019만</t>
   </si>
   <si>
     <t>흑두부</t>
@@ -1011,7 +1014,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>3977조 6444억 4078만</t>
+    <t>4261조 8121억 2145만</t>
   </si>
   <si>
     <t>대방어조아</t>
@@ -1029,7 +1032,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
   </si>
   <si>
-    <t>3762조 2211억 2278만</t>
+    <t>3855조 7457억 7793만</t>
   </si>
   <si>
     <t>퍼퓸</t>
@@ -1038,7 +1041,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
   </si>
   <si>
-    <t>2728조 3700억 7437만</t>
+    <t>2845조 5542억 8706만</t>
   </si>
   <si>
     <t>서포터즈</t>
@@ -1047,7 +1050,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>2631조 6453억 5245만</t>
+    <t>2746조 3871억 2532만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
+    <t>2284조 2891억 4675만</t>
+  </si>
+  <si>
+    <t>KR#TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>2119조 8987억 8050만</t>
   </si>
   <si>
     <t>뻥뻥</t>
@@ -1059,21 +1077,6 @@
     <t>2043조 9656억 4336만</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
-  </si>
-  <si>
-    <t>1989조 7824억 6125만</t>
-  </si>
-  <si>
-    <t>KR#TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>1905조 6059억 8847만</t>
-  </si>
-  <si>
     <t>야가다</t>
   </si>
   <si>
@@ -1089,7 +1092,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
   </si>
   <si>
-    <t>1315조 5220억 4669만</t>
+    <t>1322조 8716억 7240만</t>
+  </si>
+  <si>
+    <t>단풍카우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>1128조 7710억 7257만</t>
+  </si>
+  <si>
+    <t>호우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>1123조 2521억 2655만</t>
   </si>
   <si>
     <t>우후</t>
@@ -1101,24 +1122,6 @@
     <t>1109조 9165억 9489만</t>
   </si>
   <si>
-    <t>호우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>1108조 180억 2351만</t>
-  </si>
-  <si>
-    <t>단풍카우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>1073조 5649억 8462만</t>
-  </si>
-  <si>
     <t>채무조정</t>
   </si>
   <si>
@@ -1128,6 +1131,15 @@
     <t>1065조 650억 5642만</t>
   </si>
   <si>
+    <t>뽀송히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
+  </si>
+  <si>
+    <t>1037조 6022억 9430만</t>
+  </si>
+  <si>
     <t>좀치는형님</t>
   </si>
   <si>
@@ -1137,22 +1149,22 @@
     <t>1035조 3847억 2058만</t>
   </si>
   <si>
-    <t>뽀송히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
-  </si>
-  <si>
-    <t>1004조 8036억 1662만</t>
-  </si>
-  <si>
     <t>정태준</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
   </si>
   <si>
-    <t>945조 4753억 8997만</t>
+    <t>970조 2899억 6670만</t>
+  </si>
+  <si>
+    <t>라탱호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%ED%83%B1%ED%98%B8</t>
+  </si>
+  <si>
+    <t>839조 136억 3753만</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -1161,7 +1173,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>694조 9328억 4347만</t>
+    <t>771조 110억 9890만</t>
+  </si>
+  <si>
+    <t>짤똘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%A4%EB%98%98</t>
+  </si>
+  <si>
+    <t>671조 4394억 5627만</t>
   </si>
   <si>
     <t>팡대지</t>
@@ -1197,7 +1218,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
   </si>
   <si>
-    <t>465조 5751억 1115만</t>
+    <t>467조 3553억 7499만</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -1206,7 +1227,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
   </si>
   <si>
-    <t>435조 2837억 6019만</t>
+    <t>445조 8279억 8293만</t>
   </si>
   <si>
     <t>아르미느</t>
@@ -1215,7 +1236,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>326조 4698억 2146만</t>
+    <t>327조 8098억 2654만</t>
+  </si>
+  <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>290조 6954억 7448만</t>
   </si>
   <si>
     <t>꼬북빵야</t>
@@ -1227,22 +1257,13 @@
     <t>275조 6869억 3523만</t>
   </si>
   <si>
-    <t>여눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
-  </si>
-  <si>
-    <t>270조 8495억 5221만</t>
-  </si>
-  <si>
     <t>지존쫀파</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
   </si>
   <si>
-    <t>8623조 4455억 698만</t>
+    <t>9094조 7371억 4105만</t>
   </si>
   <si>
     <t>수텍</t>
@@ -1251,7 +1272,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%ED%85%8D</t>
   </si>
   <si>
-    <t>7468조 2422억 4958만</t>
+    <t>7571조 6718억 4695만</t>
   </si>
   <si>
     <t>포항엄석대</t>
@@ -1260,7 +1281,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
   </si>
   <si>
-    <t>4453조 8085억 1203만</t>
+    <t>4469조 9154억 1147만</t>
   </si>
   <si>
     <t>협의</t>
@@ -1272,6 +1293,15 @@
     <t>4402조 1032억 4015만</t>
   </si>
   <si>
+    <t>타개</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
+  </si>
+  <si>
+    <t>3686조 6135억 2383만</t>
+  </si>
+  <si>
     <t>기뽐</t>
   </si>
   <si>
@@ -1281,22 +1311,13 @@
     <t>3303조 6174억 3840만</t>
   </si>
   <si>
-    <t>타개</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
-  </si>
-  <si>
-    <t>3074조 9670억 3069만</t>
-  </si>
-  <si>
     <t>댜니</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>2719조 7474억 1743만</t>
+    <t>2840조 4958억 3412만</t>
   </si>
   <si>
     <t>포항가자미</t>
@@ -1305,7 +1326,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
   </si>
   <si>
-    <t>2581조 6429억 5864만</t>
+    <t>2582조 4683억 1990만</t>
+  </si>
+  <si>
+    <t>뿡쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
+  </si>
+  <si>
+    <t>2517조 3409억 1416만</t>
   </si>
   <si>
     <t>지존빼앙</t>
@@ -1326,15 +1356,6 @@
     <t>2465조 3877억 3257만</t>
   </si>
   <si>
-    <t>뿡쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
-  </si>
-  <si>
-    <t>2441조 2925억 1424만</t>
-  </si>
-  <si>
     <t>엘르가든</t>
   </si>
   <si>
@@ -1350,7 +1371,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
   </si>
   <si>
-    <t>2255조 4974억 667만</t>
+    <t>2287조 747억 2820만</t>
+  </si>
+  <si>
+    <t>파울</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
+  </si>
+  <si>
+    <t>1901조 6768억 6078만</t>
   </si>
   <si>
     <t>마카롱롱</t>
@@ -1362,28 +1392,28 @@
     <t>1889조 8524억 3410만</t>
   </si>
   <si>
-    <t>파울</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
-  </si>
-  <si>
-    <t>1802조 8305억 7088만</t>
+    <t>오옹나이스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%B9%EB%82%98%EC%9D%B4%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>1379조 1810억 4031만</t>
+  </si>
+  <si>
+    <t>대좀이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1328조 7104억 3097만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
   </si>
   <si>
-    <t>1303조 7925억 4494만</t>
-  </si>
-  <si>
-    <t>대좀이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1293조 7161억 8573만</t>
+    <t>1316조 2657억 6833만</t>
   </si>
   <si>
     <t>모짜리코베르</t>
@@ -1392,7 +1422,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
   </si>
   <si>
-    <t>1247조 6075억 2806만</t>
+    <t>1263조 2766억 1030만</t>
+  </si>
+  <si>
+    <t>마갤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
+  </si>
+  <si>
+    <t>1200조 1472억 1769만</t>
   </si>
   <si>
     <t>짱잘자쿨냥</t>
@@ -1410,7 +1449,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
   </si>
   <si>
-    <t>1083조 3384억 3846만</t>
+    <t>1140조 9567억 8620만</t>
   </si>
   <si>
     <t>기본이리</t>
@@ -1431,31 +1470,13 @@
     <t>1068조 2571억 1131만</t>
   </si>
   <si>
-    <t>마갤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
-  </si>
-  <si>
-    <t>1060조 3768억 2296만</t>
-  </si>
-  <si>
     <t>전산봉</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%B0%EB%B4%89</t>
   </si>
   <si>
-    <t>925조 3542억 1411만</t>
-  </si>
-  <si>
-    <t>오옹나이스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%B9%EB%82%98%EC%9D%B4%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>883조 1176억 6134만</t>
+    <t>952조 4188억 521만</t>
   </si>
   <si>
     <t>고숨도칭</t>
@@ -1464,7 +1485,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
   </si>
   <si>
-    <t>849조 971억 5090만</t>
+    <t>864조 3912억 902만</t>
+  </si>
+  <si>
+    <t>태코찡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
+  </si>
+  <si>
+    <t>845조 9463억 6641만</t>
   </si>
   <si>
     <t>Doham</t>
@@ -1473,16 +1503,7 @@
     <t>https://mgf.gg/contents/character.php?n=Doham</t>
   </si>
   <si>
-    <t>793조 748억 2183만</t>
-  </si>
-  <si>
-    <t>태코찡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
-  </si>
-  <si>
-    <t>775조 1513억 6255만</t>
+    <t>803조 7038억 6082만</t>
   </si>
   <si>
     <t>유플러스</t>
@@ -1500,7 +1521,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%ED%9B%84</t>
   </si>
   <si>
-    <t>286조 3410억 357만</t>
+    <t>355조 5297억 5157만</t>
   </si>
   <si>
     <t>전액할부</t>
@@ -1509,7 +1530,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%95%A1%ED%95%A0%EB%B6%80</t>
   </si>
   <si>
-    <t>1경 556조 6511억 5477만</t>
+    <t>1경 2872조 7013억 2041만</t>
   </si>
   <si>
     <t>사랑향</t>
@@ -1518,16 +1539,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%96%A5</t>
   </si>
   <si>
-    <t>8677조 6078억 7904만</t>
-  </si>
-  <si>
-    <t>힐폿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%ED%8F%BF</t>
-  </si>
-  <si>
-    <t>8445조 3983억 8202만</t>
+    <t>9352조 8862억 9035만</t>
   </si>
   <si>
     <t>례전</t>
@@ -1536,7 +1548,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%80%EC%A0%84</t>
   </si>
   <si>
-    <t>4054조 2763억 1511만</t>
+    <t>4537조 7475억 1863만</t>
   </si>
   <si>
     <t>숭타이준</t>
@@ -1545,7 +1557,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%ED%83%80%EC%9D%B4%EC%A4%80</t>
   </si>
   <si>
-    <t>3334조 9718억 8229만</t>
+    <t>3569조 1779억 1697만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%94%9C%ED%8F%BF</t>
@@ -1554,6 +1566,15 @@
     <t>2598조 7115억 1793만</t>
   </si>
   <si>
+    <t>뻑걸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%91%EA%B1%B8</t>
+  </si>
+  <si>
+    <t>2401조 9715억 7435만</t>
+  </si>
+  <si>
     <t>지존빵수</t>
   </si>
   <si>
@@ -1563,13 +1584,31 @@
     <t>2308조 4760억 1242만</t>
   </si>
   <si>
-    <t>뻑걸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%91%EA%B1%B8</t>
-  </si>
-  <si>
-    <t>2282조 2546억 2222만</t>
+    <t>탱폿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%8F%BF</t>
+  </si>
+  <si>
+    <t>1888조 1422억 7967만</t>
+  </si>
+  <si>
+    <t>뮬이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AE%AC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1776조 1606억 9310만</t>
+  </si>
+  <si>
+    <t>야키산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%82%A4%EC%82%B0</t>
+  </si>
+  <si>
+    <t>1773조 2884억 5347만</t>
   </si>
   <si>
     <t>문제적남자</t>
@@ -1581,40 +1620,22 @@
     <t>1758조 5739억 8468만</t>
   </si>
   <si>
-    <t>탱폿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%8F%BF</t>
-  </si>
-  <si>
-    <t>1733조 8932억 3463만</t>
-  </si>
-  <si>
     <t>아이리쉬</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EB%A6%AC%EC%89%AC</t>
   </si>
   <si>
-    <t>1719조 1348억 46만</t>
-  </si>
-  <si>
-    <t>뮬이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AE%AC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1702조 7512억 2154만</t>
-  </si>
-  <si>
-    <t>야키산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%82%A4%EC%82%B0</t>
-  </si>
-  <si>
-    <t>1617조 1851억 6253만</t>
+    <t>1720조 9654억 9587만</t>
+  </si>
+  <si>
+    <t>화둥에불낸년</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EB%91%A5%EC%97%90%EB%B6%88%EB%82%B8%EB%85%84</t>
+  </si>
+  <si>
+    <t>1459조 5948억 5940만</t>
   </si>
   <si>
     <t>우즈2텐겐</t>
@@ -1626,22 +1647,22 @@
     <t>1317조 4439억 6807만</t>
   </si>
   <si>
-    <t>화둥에불낸년</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EB%91%A5%EC%97%90%EB%B6%88%EB%82%B8%EB%85%84</t>
-  </si>
-  <si>
-    <t>1253조 7419억 3226만</t>
-  </si>
-  <si>
     <t>독스케</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%8A%A4%EC%BC%80</t>
   </si>
   <si>
-    <t>1192조 8780억 6899만</t>
+    <t>1307조 8641억 6141만</t>
+  </si>
+  <si>
+    <t>이게용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B2%8C%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>1077조 2244억 2379만</t>
   </si>
   <si>
     <t>우월별하</t>
@@ -1653,13 +1674,22 @@
     <t>1032조 7712억 9061만</t>
   </si>
   <si>
-    <t>이게용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B2%8C%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>1015조 196억 2603만</t>
+    <t>매화로이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%ED%99%94%EB%A1%9C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1009조 7400억 8966만</t>
+  </si>
+  <si>
+    <t>구도류</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%8F%84%EB%A5%98</t>
+  </si>
+  <si>
+    <t>1004조 3247억 5882만</t>
   </si>
   <si>
     <t>기똥찬벌레</t>
@@ -1671,15 +1701,6 @@
     <t>996조 5921억 5383만</t>
   </si>
   <si>
-    <t>매화로이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%ED%99%94%EB%A1%9C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>983조 6230억 4444만</t>
-  </si>
-  <si>
     <t>JJuna</t>
   </si>
   <si>
@@ -1689,22 +1710,22 @@
     <t>846조 2980억 4433만</t>
   </si>
   <si>
+    <t>난센</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EC%84%BC</t>
+  </si>
+  <si>
+    <t>796조 7724억 80만</t>
+  </si>
+  <si>
     <t>에프람</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%ED%94%84%EB%9E%8C</t>
   </si>
   <si>
-    <t>793조 5041억 3232만</t>
-  </si>
-  <si>
-    <t>난센</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EC%84%BC</t>
-  </si>
-  <si>
-    <t>739조 5353억 7477만</t>
+    <t>793조 9880억 7830만</t>
   </si>
   <si>
     <t>콜리셰마드르</t>
@@ -1713,16 +1734,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%9C%EB%A6%AC%EC%85%B0%EB%A7%88%EB%93%9C%EB%A5%B4</t>
   </si>
   <si>
-    <t>729조 7279억 783만</t>
-  </si>
-  <si>
-    <t>구도류</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%8F%84%EB%A5%98</t>
-  </si>
-  <si>
-    <t>725조 6359억 435만</t>
+    <t>775조 3471억 4564만</t>
   </si>
   <si>
     <t>유채아버지</t>
@@ -1731,7 +1743,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%B1%84%EC%95%84%EB%B2%84%EC%A7%80</t>
   </si>
   <si>
-    <t>601조 3317억 4770만</t>
+    <t>666조 1493억 2746만</t>
   </si>
   <si>
     <t>조단23</t>
@@ -1740,7 +1752,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%8B%A823</t>
   </si>
   <si>
-    <t>591조 2509억 8646만</t>
+    <t>664조 5237억 9537만</t>
   </si>
   <si>
     <t>아콩린</t>
@@ -1749,7 +1761,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BD%A9%EB%A6%B0</t>
   </si>
   <si>
-    <t>539조 6116억 4533만</t>
+    <t>567조 831억 836만</t>
   </si>
   <si>
     <t>별루루</t>
@@ -1767,7 +1779,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BA%84%EA%BD%81</t>
   </si>
   <si>
-    <t>8172조 2992억 1061만</t>
+    <t>9113조 5821억 4815만</t>
   </si>
   <si>
     <t>별쌥</t>
@@ -1776,7 +1788,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A5</t>
   </si>
   <si>
-    <t>6358조 8584억 2408만</t>
+    <t>7374조 3275억 4141만</t>
   </si>
   <si>
     <t>진욱이에요</t>
@@ -1788,19 +1800,19 @@
     <t>4749조 892억 3024만</t>
   </si>
   <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A5%B4%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>3978조 8791억 1664만</t>
+  </si>
+  <si>
     <t>낭만황금망치</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%ED%99%A9%EA%B8%88%EB%A7%9D%EC%B9%98</t>
   </si>
   <si>
-    <t>3734조 9281억 7965만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A5%B4%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>3716조 6477억 1542만</t>
+    <t>3964조 9837억 1147만</t>
   </si>
   <si>
     <t>김슴줌1</t>
@@ -1809,7 +1821,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%8A%B4%EC%A4%8C1</t>
   </si>
   <si>
-    <t>3442조 4879억 1385만</t>
+    <t>3490조 3012억 4881만</t>
   </si>
   <si>
     <t>천달</t>
@@ -1818,7 +1830,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EB%8B%AC</t>
   </si>
   <si>
-    <t>2980조 1759억 9294만</t>
+    <t>3179조 1126억 5293만</t>
   </si>
   <si>
     <t>호두와감자</t>
@@ -1857,13 +1869,31 @@
     <t>1975조 6421억 1426만</t>
   </si>
   <si>
+    <t>게렬곰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%EB%A0%AC%EA%B3%B0</t>
+  </si>
+  <si>
+    <t>1092조 4657억 282만</t>
+  </si>
+  <si>
     <t>별곡</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EA%B3%A1</t>
   </si>
   <si>
-    <t>1047조 4304억 3414만</t>
+    <t>1052조 607억 2317만</t>
+  </si>
+  <si>
+    <t>턍ol</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%84%8Dol</t>
+  </si>
+  <si>
+    <t>945조 3772억 7776만</t>
   </si>
   <si>
     <t>동래</t>
@@ -1875,15 +1905,6 @@
     <t>903조 5825억 2349만</t>
   </si>
   <si>
-    <t>턍ol</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%84%8Dol</t>
-  </si>
-  <si>
-    <t>891조 6667억 5260만</t>
-  </si>
-  <si>
     <t>까쿠미</t>
   </si>
   <si>
@@ -1893,22 +1914,22 @@
     <t>891조 610억 5144만</t>
   </si>
   <si>
+    <t>초이레</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%B4%EB%A0%88</t>
+  </si>
+  <si>
+    <t>863조 1058억 6521만</t>
+  </si>
+  <si>
     <t>별쌤</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A4</t>
   </si>
   <si>
-    <t>806조 6006억 4020만</t>
-  </si>
-  <si>
-    <t>게렬곰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%EB%A0%AC%EA%B3%B0</t>
-  </si>
-  <si>
-    <t>729조 1853억 3020만</t>
+    <t>839조 4891억 2876만</t>
   </si>
   <si>
     <t>띠우</t>
@@ -1917,16 +1938,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%A0%EC%9A%B0</t>
   </si>
   <si>
-    <t>695조 7955억 384만</t>
-  </si>
-  <si>
-    <t>초이레</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%B4%EB%A0%88</t>
-  </si>
-  <si>
-    <t>694조 3405억 3293만</t>
+    <t>724조 6318억 7556만</t>
   </si>
   <si>
     <t>쿠까미</t>
@@ -1935,7 +1947,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EA%B9%8C%EB%AF%B8</t>
   </si>
   <si>
-    <t>580조 4879억 4595만</t>
+    <t>639조 2231억 5295만</t>
   </si>
   <si>
     <t>민족고대감자</t>
@@ -1956,31 +1968,31 @@
     <t>479조 7098억 5560만</t>
   </si>
   <si>
+    <t>승아의하루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%EC%95%84%EC%9D%98%ED%95%98%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>451조 854억 6819만</t>
+  </si>
+  <si>
+    <t>08217</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=08217</t>
+  </si>
+  <si>
+    <t>447조 4288억 7860만</t>
+  </si>
+  <si>
     <t>왕단단이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EB%8B%A8%EB%8B%A8%EC%9D%B4</t>
   </si>
   <si>
-    <t>431조 7974억 1574만</t>
-  </si>
-  <si>
-    <t>승아의하루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%EC%95%84%EC%9D%98%ED%95%98%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>430조 9231억 1376만</t>
-  </si>
-  <si>
-    <t>08217</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=08217</t>
-  </si>
-  <si>
-    <t>374조 5422억 822만</t>
+    <t>438조 9996억 5330만</t>
   </si>
   <si>
     <t>루이쥔</t>
@@ -1989,7 +2001,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%9D%B4%EC%A5%94</t>
   </si>
   <si>
-    <t>359조 2005억 1909만</t>
+    <t>368조 1850억 3501만</t>
   </si>
   <si>
     <t>택Ol</t>
@@ -1998,7 +2010,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9DOl</t>
   </si>
   <si>
-    <t>343조 8584억 7876만</t>
+    <t>344조 1217억 6727만</t>
   </si>
   <si>
     <t>툼스데이</t>
@@ -2016,7 +2028,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EA%B0%B8%EB%A4%BC</t>
   </si>
   <si>
-    <t>118조 8230억 3317만</t>
+    <t>167조 517억 2138만</t>
   </si>
   <si>
     <t>꾸현</t>
@@ -2034,7 +2046,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%90%EC%A3%BC%EB%A7%8C%EB%91%90</t>
   </si>
   <si>
-    <t>7경 3515조 8288억 192만</t>
+    <t>8경 2362조 3435억 4962만</t>
+  </si>
+  <si>
+    <t>할바이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%B0%94%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>249조 9358억 1984만</t>
   </si>
   <si>
     <t>섹밍</t>
@@ -2046,18 +2070,6 @@
     <t>242조 6051억 9884만</t>
   </si>
   <si>
-    <t>할바이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%B0%94%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>238조 4911억 5752만</t>
-  </si>
-  <si>
     <t>대구남성</t>
   </si>
   <si>
@@ -2067,7 +2079,19 @@
     <t>106</t>
   </si>
   <si>
-    <t>73조 3158억 3342만</t>
+    <t>74조 4621억 8540만</t>
+  </si>
+  <si>
+    <t>낭랑28세</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%9E%9128%EC%84%B8</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>53조 5707억 3136만</t>
   </si>
   <si>
     <t>코잉코잉</t>
@@ -2076,19 +2100,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%9E%89%EC%BD%94%EC%9E%89</t>
   </si>
   <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>47조 6427억 7411만</t>
-  </si>
-  <si>
-    <t>낭랑28세</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%9E%9128%EC%84%B8</t>
-  </si>
-  <si>
-    <t>46조 6894억 5588만</t>
+    <t>105</t>
+  </si>
+  <si>
+    <t>52조 4162억 5487만</t>
   </si>
   <si>
     <t>오스띤</t>
@@ -2097,7 +2112,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%8A%A4%EB%9D%A4</t>
   </si>
   <si>
-    <t>41조 8461억 875만</t>
+    <t>46조 6669억 1509만</t>
   </si>
   <si>
     <t>빵신궁</t>
@@ -2127,7 +2142,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>32조 3695억 51만</t>
+    <t>33조 9631억 9118만</t>
   </si>
   <si>
     <t>밀초크코</t>
@@ -2145,7 +2160,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%ED%86%B5%EB%B0%9B%EB%8A%94%EA%B0%88%EB%B9%84</t>
   </si>
   <si>
-    <t>29조 6158억 5168만</t>
+    <t>30조 3417억 9621만</t>
   </si>
   <si>
     <t>마키맛키마</t>
@@ -2154,10 +2169,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%82%A4%EB%A7%9B%ED%82%A4%EB%A7%88</t>
   </si>
   <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>29조 4040억 8926만</t>
+    <t>29조 5158억 9903만</t>
   </si>
   <si>
     <t>킬혁</t>
@@ -2190,6 +2202,15 @@
     <t>24조 2392억 8962만</t>
   </si>
   <si>
+    <t>배렛나루왁서</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%EB%A0%9B%EB%82%98%EB%A3%A8%EC%99%81%EC%84%9C</t>
+  </si>
+  <si>
+    <t>22조 7587억 8669만</t>
+  </si>
+  <si>
     <t>썬콜법사ss</t>
   </si>
   <si>
@@ -2199,22 +2220,13 @@
     <t>22조 1581억 577만</t>
   </si>
   <si>
-    <t>배렛나루왁서</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%EB%A0%9B%EB%82%98%EB%A3%A8%EC%99%81%EC%84%9C</t>
-  </si>
-  <si>
-    <t>21조 3374억 1402만</t>
-  </si>
-  <si>
     <t>페프릭2</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%8E%98%ED%94%84%EB%A6%AD2</t>
   </si>
   <si>
-    <t>16조 3082억 9287만</t>
+    <t>21조 1071억 3891만</t>
   </si>
   <si>
     <t>포디케이</t>
@@ -2223,13 +2235,34 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%94%94%EC%BC%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>10조 185억 7755만</t>
+    <t>11조 8245억 1379만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%ED%82%A4%EB%B9%84%ED%82%A4</t>
   </si>
   <si>
-    <t>8조 2771억 7725만</t>
+    <t>9조 2258억 9744만</t>
+  </si>
+  <si>
+    <t>갈음</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%88%EC%9D%8C</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>4조 2142억 3853만</t>
+  </si>
+  <si>
+    <t>즈나니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A6%88%EB%82%98%EB%8B%88</t>
+  </si>
+  <si>
+    <t>4조 1149억 2956만</t>
   </si>
   <si>
     <t>닝윤</t>
@@ -2238,19 +2271,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%9D%EC%9C%A4</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
     <t>4조 360억 3466만</t>
-  </si>
-  <si>
-    <t>즈나니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A6%88%EB%82%98%EB%8B%88</t>
-  </si>
-  <si>
-    <t>3조 9091억 3113만</t>
   </si>
 </sst>
 </file>
@@ -2895,7 +2916,7 @@
         <v>64</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>19</v>
@@ -2904,13 +2925,13 @@
         <v>49</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>43</v>
@@ -2918,40 +2939,40 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>34</v>
@@ -2983,7 +3004,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2992,28 +3013,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3024,28 +3045,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3056,28 +3077,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3088,28 +3109,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3120,7 +3141,7 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>23</v>
@@ -3129,16 +3150,16 @@
         <v>23</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>110</v>
@@ -3164,13 +3185,13 @@
         <v>113</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>114</v>
@@ -3196,13 +3217,13 @@
         <v>117</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>118</v>
@@ -3228,13 +3249,13 @@
         <v>121</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>122</v>
@@ -3260,10 +3281,10 @@
         <v>125</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>126</v>
@@ -3292,10 +3313,10 @@
         <v>130</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>126</v>
@@ -3324,16 +3345,16 @@
         <v>134</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3344,25 +3365,25 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>140</v>
@@ -3388,16 +3409,16 @@
         <v>143</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3408,28 +3429,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3440,28 +3461,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3472,28 +3493,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3504,28 +3525,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>109</v>
+        <v>154</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3536,28 +3557,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3568,28 +3589,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3600,28 +3621,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3632,28 +3653,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3664,28 +3685,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>158</v>
+        <v>91</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3696,25 +3717,25 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>190</v>
@@ -3740,16 +3761,16 @@
         <v>193</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>102</v>
+        <v>194</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3760,28 +3781,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3792,28 +3813,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>202</v>
+        <v>103</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3824,28 +3845,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3856,28 +3877,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3888,28 +3909,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3920,28 +3941,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3952,28 +3973,28 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -4037,28 +4058,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4069,28 +4090,28 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>225</v>
+        <v>33</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>225</v>
+        <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>226</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>228</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -4101,28 +4122,28 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>33</v>
+        <v>228</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>33</v>
+        <v>228</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>229</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>163</v>
+        <v>91</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>97</v>
+        <v>230</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -4133,28 +4154,28 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -4165,28 +4186,28 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>108</v>
+        <v>189</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -4200,25 +4221,25 @@
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>202</v>
+        <v>109</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -4232,25 +4253,25 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -4264,25 +4285,25 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -4296,19 +4317,19 @@
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>248</v>
+        <v>91</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>126</v>
@@ -4337,16 +4358,16 @@
         <v>251</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>108</v>
+        <v>252</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -4360,25 +4381,25 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -4389,28 +4410,28 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -4424,25 +4445,25 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -4453,28 +4474,28 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>90</v>
+        <v>189</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -4485,28 +4506,28 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>202</v>
+        <v>91</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -4517,28 +4538,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -4549,28 +4570,28 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -4581,25 +4602,25 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>276</v>
+        <v>189</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>277</v>
@@ -4613,7 +4634,7 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>278</v>
@@ -4625,16 +4646,16 @@
         <v>279</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>108</v>
+        <v>280</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -4645,28 +4666,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>276</v>
+        <v>109</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -4677,28 +4698,28 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>102</v>
+        <v>280</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -4709,28 +4730,28 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -4741,28 +4762,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -4776,25 +4797,25 @@
         <v>191</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -4805,28 +4826,28 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -4837,28 +4858,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>188</v>
+        <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -4869,28 +4890,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -4901,28 +4922,28 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>90</v>
+        <v>194</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -4933,28 +4954,28 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -4965,28 +4986,28 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -4997,28 +5018,28 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>34</v>
@@ -5064,7 +5085,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5081,28 +5102,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5113,28 +5134,28 @@
         <v>35</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>43</v>
@@ -5145,28 +5166,28 @@
         <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>43</v>
@@ -5177,28 +5198,28 @@
         <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>43</v>
@@ -5209,28 +5230,28 @@
         <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>43</v>
@@ -5244,25 +5265,25 @@
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>43</v>
@@ -5276,25 +5297,25 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>43</v>
@@ -5308,25 +5329,25 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>43</v>
@@ -5340,22 +5361,22 @@
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>339</v>
+        <v>42</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>339</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>340</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>341</v>
@@ -5372,25 +5393,25 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>42</v>
+        <v>342</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>42</v>
+        <v>342</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>43</v>
@@ -5404,25 +5425,25 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>43</v>
@@ -5433,28 +5454,28 @@
         <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>43</v>
@@ -5468,25 +5489,25 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>43</v>
@@ -5497,28 +5518,28 @@
         <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>43</v>
@@ -5529,28 +5550,28 @@
         <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>43</v>
@@ -5561,28 +5582,28 @@
         <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>126</v>
+        <v>195</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>43</v>
@@ -5593,28 +5614,28 @@
         <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>43</v>
@@ -5625,28 +5646,28 @@
         <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>43</v>
@@ -5657,28 +5678,28 @@
         <v>35</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>158</v>
+        <v>91</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>43</v>
@@ -5689,28 +5710,28 @@
         <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>43</v>
@@ -5721,28 +5742,28 @@
         <v>35</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>43</v>
@@ -5753,28 +5774,28 @@
         <v>35</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>43</v>
@@ -5785,28 +5806,28 @@
         <v>35</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>43</v>
@@ -5820,25 +5841,25 @@
         <v>191</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>43</v>
@@ -5849,28 +5870,28 @@
         <v>35</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="I25" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>43</v>
@@ -5881,28 +5902,28 @@
         <v>35</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>188</v>
+        <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>43</v>
@@ -5913,28 +5934,28 @@
         <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>316</v>
+        <v>216</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>43</v>
@@ -5945,28 +5966,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>90</v>
+        <v>194</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>43</v>
@@ -5977,35 +5998,99 @@
         <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>276</v>
+        <v>97</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>219</v>
+        <v>317</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>43</v>
       </c>
     </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -6035,6 +6120,8 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6060,28 +6147,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6092,28 +6179,28 @@
         <v>44</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>43</v>
@@ -6124,28 +6211,28 @@
         <v>44</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>43</v>
@@ -6156,28 +6243,28 @@
         <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>43</v>
@@ -6188,28 +6275,28 @@
         <v>44</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>43</v>
@@ -6223,25 +6310,25 @@
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>43</v>
@@ -6255,25 +6342,25 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>43</v>
@@ -6287,25 +6374,25 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>43</v>
@@ -6319,25 +6406,25 @@
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>43</v>
@@ -6351,25 +6438,25 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>43</v>
@@ -6383,25 +6470,25 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>43</v>
@@ -6412,28 +6499,28 @@
         <v>44</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>43</v>
@@ -6447,25 +6534,25 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>43</v>
@@ -6476,28 +6563,28 @@
         <v>44</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>43</v>
@@ -6508,28 +6595,28 @@
         <v>44</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>90</v>
+        <v>280</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>43</v>
@@ -6540,28 +6627,28 @@
         <v>44</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>276</v>
+        <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>43</v>
@@ -6572,28 +6659,28 @@
         <v>44</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>52</v>
+        <v>453</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>453</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>43</v>
@@ -6604,28 +6691,28 @@
         <v>44</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>43</v>
@@ -6636,28 +6723,28 @@
         <v>44</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>451</v>
+        <v>52</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>451</v>
+        <v>52</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>90</v>
+        <v>189</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>43</v>
@@ -6668,28 +6755,28 @@
         <v>44</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>43</v>
@@ -6700,28 +6787,28 @@
         <v>44</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>43</v>
@@ -6732,28 +6819,28 @@
         <v>44</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>43</v>
@@ -6764,28 +6851,28 @@
         <v>44</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>276</v>
+        <v>91</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>43</v>
@@ -6799,25 +6886,25 @@
         <v>191</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>43</v>
@@ -6828,28 +6915,28 @@
         <v>44</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>90</v>
+        <v>280</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>43</v>
@@ -6860,28 +6947,28 @@
         <v>44</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>126</v>
+        <v>195</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>43</v>
@@ -6892,28 +6979,28 @@
         <v>44</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>43</v>
@@ -6924,28 +7011,28 @@
         <v>44</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>43</v>
@@ -6956,28 +7043,28 @@
         <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>43</v>
@@ -6988,28 +7075,28 @@
         <v>44</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>43</v>
@@ -7020,28 +7107,28 @@
         <v>44</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>43</v>
@@ -7087,7 +7174,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -7096,7 +7183,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7105,28 +7192,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -7137,28 +7224,28 @@
         <v>53</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -7169,28 +7256,28 @@
         <v>53</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -7201,28 +7288,28 @@
         <v>53</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>163</v>
+        <v>252</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -7233,28 +7320,28 @@
         <v>53</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>248</v>
+        <v>91</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -7268,25 +7355,25 @@
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>502</v>
+        <v>60</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>502</v>
+        <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -7300,25 +7387,25 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>60</v>
+        <v>511</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>60</v>
+        <v>511</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>90</v>
+        <v>189</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -7332,25 +7419,25 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -7364,25 +7451,25 @@
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>202</v>
+        <v>280</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -7396,25 +7483,25 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -7428,25 +7515,25 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>276</v>
+        <v>91</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -7457,28 +7544,28 @@
         <v>53</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -7492,25 +7579,25 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -7521,28 +7608,28 @@
         <v>53</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -7553,28 +7640,28 @@
         <v>53</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -7585,28 +7672,28 @@
         <v>53</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -7617,28 +7704,28 @@
         <v>53</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>102</v>
+        <v>194</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -7649,28 +7736,28 @@
         <v>53</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -7681,28 +7768,28 @@
         <v>53</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>188</v>
+        <v>280</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -7713,28 +7800,28 @@
         <v>53</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>108</v>
+        <v>280</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -7745,28 +7832,28 @@
         <v>53</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>276</v>
+        <v>109</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -7777,28 +7864,28 @@
         <v>53</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -7809,28 +7896,28 @@
         <v>53</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>90</v>
+        <v>280</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -7844,25 +7931,25 @@
         <v>191</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>276</v>
+        <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -7873,28 +7960,28 @@
         <v>53</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -7905,28 +7992,28 @@
         <v>53</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>276</v>
+        <v>103</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -7937,28 +8024,28 @@
         <v>53</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>102</v>
+        <v>252</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -7969,28 +8056,28 @@
         <v>53</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>248</v>
+        <v>91</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -8001,67 +8088,35 @@
         <v>53</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J29"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -8091,7 +8146,6 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8117,28 +8171,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -8149,28 +8203,28 @@
         <v>61</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>43</v>
@@ -8181,28 +8235,28 @@
         <v>61</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>43</v>
@@ -8213,28 +8267,28 @@
         <v>61</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>43</v>
@@ -8245,28 +8299,28 @@
         <v>61</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>585</v>
+        <v>68</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>585</v>
+        <v>68</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>43</v>
@@ -8280,25 +8334,25 @@
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>67</v>
+        <v>591</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>67</v>
+        <v>591</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>43</v>
@@ -8312,25 +8366,25 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>43</v>
@@ -8344,25 +8398,25 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>43</v>
@@ -8376,25 +8430,25 @@
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>43</v>
@@ -8408,25 +8462,25 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>43</v>
@@ -8440,25 +8494,25 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>43</v>
@@ -8469,28 +8523,28 @@
         <v>61</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>43</v>
@@ -8504,25 +8558,25 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>43</v>
@@ -8533,28 +8587,28 @@
         <v>61</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>43</v>
@@ -8565,28 +8619,28 @@
         <v>61</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>43</v>
@@ -8597,28 +8651,28 @@
         <v>61</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>276</v>
+        <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>43</v>
@@ -8629,28 +8683,28 @@
         <v>61</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>90</v>
+        <v>280</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>43</v>
@@ -8661,28 +8715,28 @@
         <v>61</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>43</v>
@@ -8693,28 +8747,28 @@
         <v>61</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>43</v>
@@ -8725,28 +8779,28 @@
         <v>61</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>43</v>
@@ -8757,28 +8811,28 @@
         <v>61</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>43</v>
@@ -8789,28 +8843,28 @@
         <v>61</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>43</v>
@@ -8821,28 +8875,28 @@
         <v>61</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>43</v>
@@ -8856,25 +8910,25 @@
         <v>191</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>248</v>
+        <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>43</v>
@@ -8885,28 +8939,28 @@
         <v>61</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="I25" s="2" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>43</v>
@@ -8917,28 +8971,28 @@
         <v>61</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>90</v>
+        <v>252</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>43</v>
@@ -8949,28 +9003,28 @@
         <v>61</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>43</v>
@@ -8981,28 +9035,28 @@
         <v>61</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>43</v>
@@ -9013,28 +9067,28 @@
         <v>61</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>43</v>
@@ -9045,28 +9099,28 @@
         <v>61</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>43</v>
@@ -9077,28 +9131,28 @@
         <v>61</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>43</v>
@@ -9144,7 +9198,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -9153,7 +9207,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9162,28 +9216,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -9191,31 +9245,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -9223,31 +9277,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>219</v>
+        <v>674</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -9255,31 +9309,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>673</v>
+        <v>216</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -9287,31 +9341,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -9319,31 +9373,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -9351,31 +9405,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -9383,31 +9437,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -9415,31 +9469,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -9447,31 +9501,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -9479,31 +9533,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -9511,31 +9565,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -9543,31 +9597,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -9575,31 +9629,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>707</v>
+        <v>689</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -9607,31 +9661,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -9639,31 +9693,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -9671,31 +9725,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -9703,31 +9757,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -9735,31 +9789,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -9767,31 +9821,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -9799,31 +9853,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -9831,31 +9885,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -9863,31 +9917,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>202</v>
+        <v>91</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -9895,38 +9949,70 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
       </c>
     </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J24"/>
+  <autoFilter ref="A1:J25"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -9951,6 +10037,7 @@
     <hyperlink ref="E22" r:id="rId21"/>
     <hyperlink ref="E23" r:id="rId22"/>
     <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -12,18 +12,18 @@
     <sheet name="만영" sheetId="3" r:id="rId3"/>
     <sheet name="빅딜" sheetId="4" r:id="rId4"/>
     <sheet name="지존길드" sheetId="5" r:id="rId5"/>
-    <sheet name="바텀" sheetId="6" r:id="rId6"/>
-    <sheet name="따숨" sheetId="7" r:id="rId7"/>
+    <sheet name="따숨" sheetId="6" r:id="rId6"/>
+    <sheet name="바텀" sheetId="7" r:id="rId7"/>
     <sheet name="더위사냥" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">더위사냥!$A$1:$J$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">든솔!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">따숨!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">든솔!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">따숨!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">만영!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">바텀!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">빅딜!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">바텀!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">빅딜!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">지존길드!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2194" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2174" uniqueCount="741">
   <si>
     <t>guild_name</t>
   </si>
@@ -192,6 +192,30 @@
     <t>지존순찌</t>
   </si>
   <si>
+    <t>따숨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%94%B0%EC%88%A8</t>
+  </si>
+  <si>
+    <t>Scania 3</t>
+  </si>
+  <si>
+    <t>936</t>
+  </si>
+  <si>
+    <t>40위</t>
+  </si>
+  <si>
+    <t>4경 3027조 2732억 9013만</t>
+  </si>
+  <si>
+    <t>길드건물/길드콘텐츠/길드톡방 필수이며 같이 재밌게 게임해요! 가입문의 김가원,호르몬,뚜징,김슴줌1에게 귓주세요</t>
+  </si>
+  <si>
+    <t>호르몬</t>
+  </si>
+  <si>
     <t>바텀</t>
   </si>
   <si>
@@ -216,30 +240,6 @@
     <t>딜폿</t>
   </si>
   <si>
-    <t>따숨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%94%B0%EC%88%A8</t>
-  </si>
-  <si>
-    <t>Scania 3</t>
-  </si>
-  <si>
-    <t>936</t>
-  </si>
-  <si>
-    <t>40위</t>
-  </si>
-  <si>
-    <t>4경 3027조 2732억 9013만</t>
-  </si>
-  <si>
-    <t>길드건물/길드콘텐츠/길드톡방 필수이며 같이 재밌게 게임해요! 가입문의 김가원,호르몬,뚜징,김슴줌1에게 귓주세요</t>
-  </si>
-  <si>
-    <t>호르몬</t>
-  </si>
-  <si>
     <t>더위사냥</t>
   </si>
   <si>
@@ -312,7 +312,7 @@
     <t>117</t>
   </si>
   <si>
-    <t>8경 955조 5504억 1622만</t>
+    <t>8경 1141조 4236억 9441만</t>
   </si>
   <si>
     <t>2</t>
@@ -363,7 +363,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>7320조 9731억 42만</t>
+    <t>7477조 5337억 4346만</t>
   </si>
   <si>
     <t>5</t>
@@ -399,7 +399,7 @@
     <t>https://mgf.gg/contents/character.php?n=GOD%EB%82%A0%EB%91%90</t>
   </si>
   <si>
-    <t>5152조 2929억 580만</t>
+    <t>5267조 3069억 6491만</t>
   </si>
   <si>
     <t>8</t>
@@ -414,7 +414,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>4412조 4638억 6313만</t>
+    <t>4448조 4463억 2650만</t>
   </si>
   <si>
     <t>9</t>
@@ -426,7 +426,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%9A%94%EC%97%98%EB%86%8D%EC%82%B0</t>
   </si>
   <si>
-    <t>3371조 1631억 8076만</t>
+    <t>3372조 7251억 8925만</t>
   </si>
   <si>
     <t>10</t>
@@ -453,7 +453,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B0%8C%EB%B0%94%EB%A6%AC%EC%9D%B4</t>
   </si>
   <si>
-    <t>3200조 4397억 9454만</t>
+    <t>3236조 4179억 3396만</t>
   </si>
   <si>
     <t>12</t>
@@ -480,7 +480,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EA%B8%88%EC%96%B4%EA%B8%88%EB%8B%88</t>
   </si>
   <si>
-    <t>2449조 7623억 409만</t>
+    <t>2498조 4801억 4342만</t>
   </si>
   <si>
     <t>14</t>
@@ -504,480 +504,471 @@
     <t>15</t>
   </si>
   <si>
-    <t>Darken</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Darken</t>
+    <t>서늘한그늘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%8A%98%ED%95%9C%EA%B7%B8%EB%8A%98</t>
+  </si>
+  <si>
+    <t>2349조 6211억 5045만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>88치킨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=88%EC%B9%98%ED%82%A8</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>2134조 7264억 6794만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>하이하로하라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9D%B4%ED%95%98%EB%A1%9C%ED%95%98%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>1698조 5982억 3367만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>차보이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EB%B3%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1479조 8061억 8067만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>v박효신v</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=v%EB%B0%95%ED%9A%A8%EC%8B%A0v</t>
+  </si>
+  <si>
+    <t>1335조 2774억 3624만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>여릿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%A6%BF</t>
+  </si>
+  <si>
+    <t>1256조 4669억 2721만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>시간이돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B0%84%EC%9D%B4%EB%8F%88</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>1234조 123억 1646만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>초읍사나이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%8D%EC%82%AC%EB%82%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1153조 479억 7983만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>다둉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1056조 8727억 2763만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>고으농</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%9C%BC%EB%86%8D</t>
+  </si>
+  <si>
+    <t>992조 4375억 6722만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>도레오</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%88%EC%98%A4</t>
+  </si>
+  <si>
+    <t>985조 3833억 8106만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>익뇸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%87%B8</t>
   </si>
   <si>
     <t>나이트로드</t>
   </si>
   <si>
-    <t>2028조 1280억 6282만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>88치킨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=88%EC%B9%98%ED%82%A8</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>1978조 8045억 2544만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>서늘한그늘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%8A%98%ED%95%9C%EA%B7%B8%EB%8A%98</t>
-  </si>
-  <si>
-    <t>1877조 8513억 6254만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>하이하로하라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9D%B4%ED%95%98%EB%A1%9C%ED%95%98%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>1698조 5982억 3367만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>차보이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EB%B3%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1479조 8061억 8067만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>v박효신v</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=v%EB%B0%95%ED%9A%A8%EC%8B%A0v</t>
-  </si>
-  <si>
-    <t>1320조 8273억 6704만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>여릿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%A6%BF</t>
-  </si>
-  <si>
-    <t>1215조 5892억 2562만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>시간이돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B0%84%EC%9D%B4%EB%8F%88</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>1175조 7749억 1807만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>초읍사나이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%8D%EC%82%AC%EB%82%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>1149조 8254억 2838만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>다둉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1051조 8745억 8180만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>도레오</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%88%EC%98%A4</t>
-  </si>
-  <si>
-    <t>985조 3833억 8106만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>고으농</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%9C%BC%EB%86%8D</t>
-  </si>
-  <si>
-    <t>886조 1045억 1505만</t>
+    <t>713조 1621억 2270만</t>
   </si>
   <si>
     <t>27</t>
   </si>
   <si>
-    <t>익뇸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%87%B8</t>
-  </si>
-  <si>
-    <t>656조 2458억 3631만</t>
+    <t>하엘이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%97%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>613조 4694억 3249만</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
-    <t>하엘이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%97%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>613조 4694억 3249만</t>
+    <t>아리미쿵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A6%AC%EB%AF%B8%EC%BF%B5</t>
+  </si>
+  <si>
+    <t>540조 9494억 6800만</t>
   </si>
   <si>
     <t>29</t>
   </si>
   <si>
-    <t>아리미쿵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A6%AC%EB%AF%B8%EC%BF%B5</t>
-  </si>
-  <si>
-    <t>540조 9494억 6800만</t>
+    <t>나는배불러요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%8A%94%EB%B0%B0%EB%B6%88%EB%9F%AC%EC%9A%94</t>
+  </si>
+  <si>
+    <t>502조 1051억 5367만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EA%B8%B0%EC%9C%A0%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>1경 3183조 5333억 2516만</t>
+  </si>
+  <si>
+    <t>무곽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EA%B3%BD</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>1경 2526조 6847억 9408만</t>
+  </si>
+  <si>
+    <t>형팡팡이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%95%ED%8C%A1%ED%8C%A1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>5210조 3974억 4208만</t>
+  </si>
+  <si>
+    <t>붉은모자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%89%EC%9D%80%EB%AA%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>3716조 2349억 9071만</t>
+  </si>
+  <si>
+    <t>2번째캐릭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=2%EB%B2%88%EC%A7%B8%EC%BA%90%EB%A6%AD</t>
+  </si>
+  <si>
+    <t>3706조 3989억 6467만</t>
+  </si>
+  <si>
+    <t>장뱁새</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B1%81%EC%83%88</t>
+  </si>
+  <si>
+    <t>3484조 3912억 6973만</t>
+  </si>
+  <si>
+    <t>히테라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%85%8C%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>3388조 1795억 6만</t>
+  </si>
+  <si>
+    <t>꽁꽁냉법</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EA%BD%81%EB%83%89%EB%B2%95</t>
+  </si>
+  <si>
+    <t>2571조 2622억 8515만</t>
+  </si>
+  <si>
+    <t>테토일남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%85%8C%ED%86%A0%EC%9D%BC%EB%82%A8</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>2485조 8540억 6298만</t>
+  </si>
+  <si>
+    <t>뚜기파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EA%B8%B0%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>2025조 6243억 9048만</t>
+  </si>
+  <si>
+    <t>브네</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%84%A4</t>
+  </si>
+  <si>
+    <t>1928조 5981억 7061만</t>
+  </si>
+  <si>
+    <t>라쥬르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%A5%AC%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>1631조 7745억 9292만</t>
+  </si>
+  <si>
+    <t>초앤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%95%A4</t>
+  </si>
+  <si>
+    <t>1575조 5348억 5955만</t>
+  </si>
+  <si>
+    <t>재미있게놀래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EB%AF%B8%EC%9E%88%EA%B2%8C%EB%86%80%EB%9E%98</t>
+  </si>
+  <si>
+    <t>1384조 7511억 4574만</t>
+  </si>
+  <si>
+    <t>빙율</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%99%EC%9C%A8</t>
+  </si>
+  <si>
+    <t>1314조 7187억 8022만</t>
+  </si>
+  <si>
+    <t>33세배장호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=33%EC%84%B8%EB%B0%B0%EC%9E%A5%ED%98%B8</t>
+  </si>
+  <si>
+    <t>1247조 6774억 6373만</t>
+  </si>
+  <si>
+    <t>적젹적</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%81%EC%A0%B9%EC%A0%81</t>
+  </si>
+  <si>
+    <t>1155조 2525억 2408만</t>
+  </si>
+  <si>
+    <t>가덴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%8D%B4</t>
+  </si>
+  <si>
+    <t>1042조 615억 229만</t>
+  </si>
+  <si>
+    <t>최빵쭈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EB%B9%B5%EC%AD%88</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>980조 2953억 7066만</t>
+  </si>
+  <si>
+    <t>정기휴므</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EA%B8%B0%ED%9C%B4%EB%AF%80</t>
+  </si>
+  <si>
+    <t>891조 2847억 9662만</t>
+  </si>
+  <si>
+    <t>타뤽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%A4%BD</t>
+  </si>
+  <si>
+    <t>804조 8666억 5004만</t>
+  </si>
+  <si>
+    <t>무르스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%A5%B4%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>782조 4234억 7902만</t>
+  </si>
+  <si>
+    <t>채황새</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%ED%99%A9%EC%83%88</t>
+  </si>
+  <si>
+    <t>759조 9478억 7922만</t>
+  </si>
+  <si>
+    <t>저기휴무</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%80%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>699조 6704억 9749만</t>
+  </si>
+  <si>
+    <t>박도란</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%8F%84%EB%9E%80</t>
+  </si>
+  <si>
+    <t>631조 424억 363만</t>
+  </si>
+  <si>
+    <t>넬샷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%AC%EC%83%B7</t>
+  </si>
+  <si>
+    <t>540조 8323억 210만</t>
+  </si>
+  <si>
+    <t>장기휴무</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>539조 87억 1816만</t>
+  </si>
+  <si>
+    <t>뿌앵뿌앵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EC%95%B5%EB%BF%8C%EC%95%B5</t>
+  </si>
+  <si>
+    <t>418조 4422억 2130만</t>
+  </si>
+  <si>
+    <t>냥홍이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%ED%99%8D%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>325조 8254억 8546만</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>나는배불러요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%8A%94%EB%B0%B0%EB%B6%88%EB%9F%AC%EC%9A%94</t>
-  </si>
-  <si>
-    <t>500조 5054억 5138만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EA%B8%B0%EC%9C%A0%EB%AC%B4</t>
-  </si>
-  <si>
-    <t>1경 2732조 8456억 7264만</t>
-  </si>
-  <si>
-    <t>무곽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EA%B3%BD</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>1경 2526조 6847억 9408만</t>
-  </si>
-  <si>
-    <t>형팡팡이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%95%ED%8C%A1%ED%8C%A1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>5209조 9277억 4214만</t>
-  </si>
-  <si>
-    <t>붉은모자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%89%EC%9D%80%EB%AA%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>3702조 4677억 8853만</t>
-  </si>
-  <si>
-    <t>2번째캐릭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=2%EB%B2%88%EC%A7%B8%EC%BA%90%EB%A6%AD</t>
-  </si>
-  <si>
-    <t>3695조 8405억 1988만</t>
-  </si>
-  <si>
-    <t>장뱁새</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B1%81%EC%83%88</t>
-  </si>
-  <si>
-    <t>3484조 3912억 6973만</t>
-  </si>
-  <si>
-    <t>히테라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%85%8C%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>3360조 7324억 4501만</t>
-  </si>
-  <si>
-    <t>꽁꽁냉법</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EA%BD%81%EB%83%89%EB%B2%95</t>
-  </si>
-  <si>
-    <t>2565조 4438억 9218만</t>
-  </si>
-  <si>
-    <t>테토일남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%85%8C%ED%86%A0%EC%9D%BC%EB%82%A8</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>2294조 4627억 6705만</t>
-  </si>
-  <si>
-    <t>뚜기파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EA%B8%B0%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>2025조 6243억 9048만</t>
-  </si>
-  <si>
-    <t>브네</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%84%A4</t>
-  </si>
-  <si>
-    <t>1928조 5981억 7061만</t>
-  </si>
-  <si>
-    <t>라쥬르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%A5%AC%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>1625조 4762억 9577만</t>
-  </si>
-  <si>
-    <t>재미있게놀래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EB%AF%B8%EC%9E%88%EA%B2%8C%EB%86%80%EB%9E%98</t>
-  </si>
-  <si>
-    <t>1364조 9796억 5823만</t>
-  </si>
-  <si>
-    <t>빙율</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%99%EC%9C%A8</t>
-  </si>
-  <si>
-    <t>1314조 7187억 8022만</t>
-  </si>
-  <si>
-    <t>33세배장호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=33%EC%84%B8%EB%B0%B0%EC%9E%A5%ED%98%B8</t>
-  </si>
-  <si>
-    <t>1243조 6726억 369만</t>
-  </si>
-  <si>
-    <t>적젹적</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%81%EC%A0%B9%EC%A0%81</t>
-  </si>
-  <si>
-    <t>1155조 2525억 2408만</t>
-  </si>
-  <si>
-    <t>가덴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%8D%B4</t>
-  </si>
-  <si>
-    <t>1002조 2371억 1100만</t>
-  </si>
-  <si>
-    <t>최빵쭈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EB%B9%B5%EC%AD%88</t>
-  </si>
-  <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>939조 4028억 5874만</t>
-  </si>
-  <si>
-    <t>정기휴므</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EA%B8%B0%ED%9C%B4%EB%AF%80</t>
-  </si>
-  <si>
-    <t>826조 7863억 3978만</t>
-  </si>
-  <si>
-    <t>타뤽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%A4%BD</t>
-  </si>
-  <si>
-    <t>804조 8666억 5004만</t>
-  </si>
-  <si>
-    <t>무르스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%A5%B4%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>781조 786억 3030만</t>
-  </si>
-  <si>
-    <t>채황새</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%ED%99%A9%EC%83%88</t>
-  </si>
-  <si>
-    <t>748조 9237억 7147만</t>
-  </si>
-  <si>
-    <t>럭키루키</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9F%AD%ED%82%A4%EB%A3%A8%ED%82%A4</t>
-  </si>
-  <si>
-    <t>726조 2461억 3618만</t>
-  </si>
-  <si>
-    <t>저기휴무</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%80%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
-  </si>
-  <si>
-    <t>699조 6704억 9749만</t>
-  </si>
-  <si>
-    <t>박도란</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%8F%84%EB%9E%80</t>
-  </si>
-  <si>
-    <t>631조 424억 363만</t>
-  </si>
-  <si>
-    <t>장기휴무</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
-  </si>
-  <si>
-    <t>539조 87억 1816만</t>
-  </si>
-  <si>
-    <t>넬샷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%AC%EC%83%B7</t>
-  </si>
-  <si>
-    <t>534조 5433억 6031만</t>
-  </si>
-  <si>
-    <t>뿌앵뿌앵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EC%95%B5%EB%BF%8C%EC%95%B5</t>
-  </si>
-  <si>
-    <t>407조 2779억 5092만</t>
-  </si>
-  <si>
-    <t>냥홍이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%ED%99%8D%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>325조 5988억 9275만</t>
-  </si>
-  <si>
     <t>윤빵쭈</t>
   </si>
   <si>
@@ -996,7 +987,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
   </si>
   <si>
-    <t>2경 237조 9091억 2548만</t>
+    <t>2경 255조 6179억 2423만</t>
   </si>
   <si>
     <t>굴러가는일상</t>
@@ -1005,7 +996,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
   </si>
   <si>
-    <t>7915조 5233억 4019만</t>
+    <t>7944조 993억 9474만</t>
+  </si>
+  <si>
+    <t>엘라임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
+  </si>
+  <si>
+    <t>4704조 7804억 542만</t>
   </si>
   <si>
     <t>흑두부</t>
@@ -1026,13 +1026,13 @@
     <t>3924조 2536억 9340만</t>
   </si>
   <si>
-    <t>엘라임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
-  </si>
-  <si>
-    <t>3855조 7457억 7793만</t>
+    <t>서포터즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
+  </si>
+  <si>
+    <t>2958조 4121억 9385만</t>
   </si>
   <si>
     <t>퍼퓸</t>
@@ -1044,19 +1044,10 @@
     <t>2845조 5542억 8706만</t>
   </si>
   <si>
-    <t>서포터즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
-  </si>
-  <si>
-    <t>2746조 3871억 2532만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
   </si>
   <si>
-    <t>2284조 2891억 4675만</t>
+    <t>2301조 7318억 5637만</t>
   </si>
   <si>
     <t>KR#TAKIN9CP37</t>
@@ -1065,7 +1056,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>2119조 8987억 8050만</t>
+    <t>2155조 4511억 6887만</t>
   </si>
   <si>
     <t>뻥뻥</t>
@@ -1092,7 +1083,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
   </si>
   <si>
-    <t>1322조 8716억 7240만</t>
+    <t>1324조 9226억 3624만</t>
   </si>
   <si>
     <t>단풍카우</t>
@@ -1101,7 +1092,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>1128조 7710억 7257만</t>
+    <t>1134조 9932억 8765만</t>
   </si>
   <si>
     <t>호우기</t>
@@ -1110,7 +1101,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>1123조 2521억 2655만</t>
+    <t>1124조 2763억 6571만</t>
   </si>
   <si>
     <t>우후</t>
@@ -1128,7 +1119,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
   </si>
   <si>
-    <t>1065조 650억 5642만</t>
+    <t>1077조 4158억 5356만</t>
   </si>
   <si>
     <t>뽀송히</t>
@@ -1137,7 +1128,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
   </si>
   <si>
-    <t>1037조 6022억 9430만</t>
+    <t>1042조 2381억 369만</t>
   </si>
   <si>
     <t>좀치는형님</t>
@@ -1164,7 +1155,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%ED%83%B1%ED%98%B8</t>
   </si>
   <si>
-    <t>839조 136억 3753만</t>
+    <t>878조 9823억 5133만</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -1173,7 +1164,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>771조 110억 9890만</t>
+    <t>789조 2546억 9378만</t>
   </si>
   <si>
     <t>짤똘</t>
@@ -1182,7 +1173,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%A4%EB%98%98</t>
   </si>
   <si>
-    <t>671조 4394억 5627만</t>
+    <t>671조 5173억 6638만</t>
   </si>
   <si>
     <t>팡대지</t>
@@ -1200,7 +1191,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>551조 4586억 8525만</t>
+    <t>558조 368억 4937만</t>
   </si>
   <si>
     <t>박준우2</t>
@@ -1218,16 +1209,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
   </si>
   <si>
-    <t>467조 3553억 7499만</t>
-  </si>
-  <si>
-    <t>플로우00</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
-  </si>
-  <si>
-    <t>445조 8279억 8293만</t>
+    <t>468조 4891억 849만</t>
   </si>
   <si>
     <t>아르미느</t>
@@ -1236,7 +1218,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>327조 8098억 2654만</t>
+    <t>337조 7925억 8502만</t>
   </si>
   <si>
     <t>여눈</t>
@@ -1245,7 +1227,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
   </si>
   <si>
-    <t>290조 6954억 7448만</t>
+    <t>292조 9201억 6015만</t>
   </si>
   <si>
     <t>꼬북빵야</t>
@@ -1263,7 +1245,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
   </si>
   <si>
-    <t>9094조 7371억 4105만</t>
+    <t>9743조 813억 3813만</t>
   </si>
   <si>
     <t>수텍</t>
@@ -1272,7 +1254,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%ED%85%8D</t>
   </si>
   <si>
-    <t>7571조 6718억 4695만</t>
+    <t>7731조 8382억 7567만</t>
   </si>
   <si>
     <t>포항엄석대</t>
@@ -1281,7 +1263,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
   </si>
   <si>
-    <t>4469조 9154억 1147만</t>
+    <t>4492조 1878억 3268만</t>
   </si>
   <si>
     <t>협의</t>
@@ -1299,7 +1281,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
   </si>
   <si>
-    <t>3686조 6135억 2383만</t>
+    <t>3689조 8892억 3174만</t>
   </si>
   <si>
     <t>기뽐</t>
@@ -1335,7 +1317,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
   </si>
   <si>
-    <t>2517조 3409억 1416만</t>
+    <t>2530조 3491억 7461만</t>
   </si>
   <si>
     <t>지존빼앙</t>
@@ -1344,7 +1326,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
   </si>
   <si>
-    <t>2472조 8689억 2239만</t>
+    <t>2515조 2382억 6614만</t>
   </si>
   <si>
     <t>변신술사</t>
@@ -1371,7 +1353,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
   </si>
   <si>
-    <t>2287조 747억 2820만</t>
+    <t>2292조 9975억 215만</t>
   </si>
   <si>
     <t>파울</t>
@@ -1407,22 +1389,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>1328조 7104억 3097만</t>
+    <t>1338조 9567억 2031만</t>
+  </si>
+  <si>
+    <t>모짜리코베르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>1337조 9988억 6043만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
   </si>
   <si>
-    <t>1316조 2657억 6833만</t>
-  </si>
-  <si>
-    <t>모짜리코베르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>1263조 2766억 1030만</t>
+    <t>1316조 5131억 3303만</t>
   </si>
   <si>
     <t>마갤</t>
@@ -1434,6 +1416,15 @@
     <t>1200조 1472억 1769만</t>
   </si>
   <si>
+    <t>김허덕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
+  </si>
+  <si>
+    <t>1173조 7299억 1919만</t>
+  </si>
+  <si>
     <t>짱잘자쿨냥</t>
   </si>
   <si>
@@ -1443,22 +1434,13 @@
     <t>1149조 8047억 287만</t>
   </si>
   <si>
-    <t>김허덕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
-  </si>
-  <si>
-    <t>1140조 9567억 8620만</t>
-  </si>
-  <si>
     <t>기본이리</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
   </si>
   <si>
-    <t>1078조 6352억 6820만</t>
+    <t>1128조 1572억 135만</t>
   </si>
   <si>
     <t>냐은</t>
@@ -1476,7 +1458,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%B0%EB%B4%89</t>
   </si>
   <si>
-    <t>952조 4188억 521만</t>
+    <t>952조 4457억 9458만</t>
   </si>
   <si>
     <t>고숨도칭</t>
@@ -1485,7 +1467,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
   </si>
   <si>
-    <t>864조 3912억 902만</t>
+    <t>879조 345억 6976만</t>
   </si>
   <si>
     <t>태코찡</t>
@@ -1494,7 +1476,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
   </si>
   <si>
-    <t>845조 9463억 6641만</t>
+    <t>848조 4037억 9866만</t>
   </si>
   <si>
     <t>Doham</t>
@@ -1503,7 +1485,7 @@
     <t>https://mgf.gg/contents/character.php?n=Doham</t>
   </si>
   <si>
-    <t>803조 7038억 6082만</t>
+    <t>806조 785억 6034만</t>
   </si>
   <si>
     <t>유플러스</t>
@@ -1524,6 +1506,273 @@
     <t>355조 5297억 5157만</t>
   </si>
   <si>
+    <t>꺄꽁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BA%84%EA%BD%81</t>
+  </si>
+  <si>
+    <t>9119조 4659억 904만</t>
+  </si>
+  <si>
+    <t>별쌥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A5</t>
+  </si>
+  <si>
+    <t>7850조 6568억 5740만</t>
+  </si>
+  <si>
+    <t>진욱이에요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9A%B1%EC%9D%B4%EC%97%90%EC%9A%94</t>
+  </si>
+  <si>
+    <t>4749조 892억 3024만</t>
+  </si>
+  <si>
+    <t>낭만황금망치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%ED%99%A9%EA%B8%88%EB%A7%9D%EC%B9%98</t>
+  </si>
+  <si>
+    <t>4088조 6937억 8303만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A5%B4%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>3997조 3647억 9275만</t>
+  </si>
+  <si>
+    <t>김슴줌1</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%8A%B4%EC%A4%8C1</t>
+  </si>
+  <si>
+    <t>3490조 3012억 4881만</t>
+  </si>
+  <si>
+    <t>천달</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EB%8B%AC</t>
+  </si>
+  <si>
+    <t>3241조 6352억 3954만</t>
+  </si>
+  <si>
+    <t>호두와감자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%91%90%EC%99%80%EA%B0%90%EC%9E%90</t>
+  </si>
+  <si>
+    <t>2661조 4151억 6001만</t>
+  </si>
+  <si>
+    <t>활용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%9C%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>2636조 7277억 398만</t>
+  </si>
+  <si>
+    <t>쿠댜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EB%8C%9C</t>
+  </si>
+  <si>
+    <t>2251조 5837억 3846만</t>
+  </si>
+  <si>
+    <t>뚜징</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EC%A7%95</t>
+  </si>
+  <si>
+    <t>1975조 6421억 1426만</t>
+  </si>
+  <si>
+    <t>게렬곰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%EB%A0%AC%EA%B3%B0</t>
+  </si>
+  <si>
+    <t>1092조 4657억 282만</t>
+  </si>
+  <si>
+    <t>별곡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EA%B3%A1</t>
+  </si>
+  <si>
+    <t>1054조 8889억 3800만</t>
+  </si>
+  <si>
+    <t>턍ol</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%84%8Dol</t>
+  </si>
+  <si>
+    <t>977조 5376억 1470만</t>
+  </si>
+  <si>
+    <t>까쿠미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EC%BF%A0%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>968조 6592억 9407만</t>
+  </si>
+  <si>
+    <t>동래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%9E%98</t>
+  </si>
+  <si>
+    <t>938조 9632억 708만</t>
+  </si>
+  <si>
+    <t>초이레</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%B4%EB%A0%88</t>
+  </si>
+  <si>
+    <t>865조 3202억 7527만</t>
+  </si>
+  <si>
+    <t>별쌤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A4</t>
+  </si>
+  <si>
+    <t>845조 4777억 7201만</t>
+  </si>
+  <si>
+    <t>띠우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%A0%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>724조 6318억 7556만</t>
+  </si>
+  <si>
+    <t>쿠까미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EA%B9%8C%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>639조 2231억 5295만</t>
+  </si>
+  <si>
+    <t>민족고대감자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%A1%B1%EA%B3%A0%EB%8C%80%EA%B0%90%EC%9E%90</t>
+  </si>
+  <si>
+    <t>599조 9447억 4751만</t>
+  </si>
+  <si>
+    <t>끄챰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%81%84%EC%B1%B0</t>
+  </si>
+  <si>
+    <t>479조 7098억 5560만</t>
+  </si>
+  <si>
+    <t>08217</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=08217</t>
+  </si>
+  <si>
+    <t>464조 5454억 7899만</t>
+  </si>
+  <si>
+    <t>승아의하루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%EC%95%84%EC%9D%98%ED%95%98%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>451조 854억 6819만</t>
+  </si>
+  <si>
+    <t>왕단단이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EB%8B%A8%EB%8B%A8%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>439조 2480억 4063만</t>
+  </si>
+  <si>
+    <t>루이쥔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%9D%B4%EC%A5%94</t>
+  </si>
+  <si>
+    <t>369조 3190억 5898만</t>
+  </si>
+  <si>
+    <t>택Ol</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%9DOl</t>
+  </si>
+  <si>
+    <t>349조 6925억 3741만</t>
+  </si>
+  <si>
+    <t>툼스데이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%88%BC%EC%8A%A4%EB%8D%B0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>285조 1117억 8099만</t>
+  </si>
+  <si>
+    <t>달갸뤼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EA%B0%B8%EB%A4%BC</t>
+  </si>
+  <si>
+    <t>167조 1400억 2161만</t>
+  </si>
+  <si>
+    <t>꾸현</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%ED%98%84</t>
+  </si>
+  <si>
+    <t>89조 2810억 5186만</t>
+  </si>
+  <si>
     <t>전액할부</t>
   </si>
   <si>
@@ -1548,7 +1797,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%80%EC%A0%84</t>
   </si>
   <si>
-    <t>4537조 7475억 1863만</t>
+    <t>4551조 3955억 8705만</t>
   </si>
   <si>
     <t>숭타이준</t>
@@ -1557,7 +1806,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%ED%83%80%EC%9D%B4%EC%A4%80</t>
   </si>
   <si>
-    <t>3569조 1779억 1697만</t>
+    <t>3633조 7230억 9510만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%94%9C%ED%8F%BF</t>
@@ -1572,7 +1821,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%91%EA%B1%B8</t>
   </si>
   <si>
-    <t>2401조 9715억 7435만</t>
+    <t>2413조 2862억 6442만</t>
   </si>
   <si>
     <t>지존빵수</t>
@@ -1581,7 +1830,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%B5%EC%88%98</t>
   </si>
   <si>
-    <t>2308조 4760억 1242만</t>
+    <t>2321조 72억 7628만</t>
   </si>
   <si>
     <t>탱폿</t>
@@ -1593,13 +1842,22 @@
     <t>1888조 1422억 7967만</t>
   </si>
   <si>
+    <t>아이리쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EB%A6%AC%EC%89%AC</t>
+  </si>
+  <si>
+    <t>1837조 7763억 5221만</t>
+  </si>
+  <si>
     <t>뮬이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AE%AC%EC%9D%B4</t>
   </si>
   <si>
-    <t>1776조 1606억 9310만</t>
+    <t>1825조 3094억 670만</t>
   </si>
   <si>
     <t>야키산</t>
@@ -1608,7 +1866,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%82%A4%EC%82%B0</t>
   </si>
   <si>
-    <t>1773조 2884억 5347만</t>
+    <t>1773조 7138억 3038만</t>
   </si>
   <si>
     <t>문제적남자</t>
@@ -1620,15 +1878,6 @@
     <t>1758조 5739억 8468만</t>
   </si>
   <si>
-    <t>아이리쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EB%A6%AC%EC%89%AC</t>
-  </si>
-  <si>
-    <t>1720조 9654억 9587만</t>
-  </si>
-  <si>
     <t>화둥에불낸년</t>
   </si>
   <si>
@@ -1638,6 +1887,15 @@
     <t>1459조 5948억 5940만</t>
   </si>
   <si>
+    <t>독스케</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%8A%A4%EC%BC%80</t>
+  </si>
+  <si>
+    <t>1327조 8028억 7915만</t>
+  </si>
+  <si>
     <t>우즈2텐겐</t>
   </si>
   <si>
@@ -1647,22 +1905,13 @@
     <t>1317조 4439억 6807만</t>
   </si>
   <si>
-    <t>독스케</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%8A%A4%EC%BC%80</t>
-  </si>
-  <si>
-    <t>1307조 8641억 6141만</t>
-  </si>
-  <si>
     <t>이게용</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B2%8C%EC%9A%A9</t>
   </si>
   <si>
-    <t>1077조 2244억 2379만</t>
+    <t>1077조 4898억 5524만</t>
   </si>
   <si>
     <t>우월별하</t>
@@ -1680,7 +1929,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%ED%99%94%EB%A1%9C%EC%9D%B4</t>
   </si>
   <si>
-    <t>1009조 7400억 8966만</t>
+    <t>1010조 1348억 1749만</t>
   </si>
   <si>
     <t>구도류</t>
@@ -1689,7 +1938,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%8F%84%EB%A5%98</t>
   </si>
   <si>
-    <t>1004조 3247억 5882만</t>
+    <t>1006조 7901억 659만</t>
   </si>
   <si>
     <t>기똥찬벌레</t>
@@ -1698,7 +1947,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%98%A5%EC%B0%AC%EB%B2%8C%EB%A0%88</t>
   </si>
   <si>
-    <t>996조 5921억 5383만</t>
+    <t>998조 5197억 7663만</t>
   </si>
   <si>
     <t>JJuna</t>
@@ -1707,7 +1956,7 @@
     <t>https://mgf.gg/contents/character.php?n=JJuna</t>
   </si>
   <si>
-    <t>846조 2980억 4433만</t>
+    <t>860조 6445억 9230만</t>
   </si>
   <si>
     <t>난센</t>
@@ -1725,7 +1974,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%ED%94%84%EB%9E%8C</t>
   </si>
   <si>
-    <t>793조 9880억 7830만</t>
+    <t>794조 8159억 9149만</t>
   </si>
   <si>
     <t>콜리셰마드르</t>
@@ -1734,7 +1983,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%9C%EB%A6%AC%EC%85%B0%EB%A7%88%EB%93%9C%EB%A5%B4</t>
   </si>
   <si>
-    <t>775조 3471억 4564만</t>
+    <t>777조 7687억 9355만</t>
+  </si>
+  <si>
+    <t>조단23</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%8B%A823</t>
+  </si>
+  <si>
+    <t>667조 4856억 8254만</t>
   </si>
   <si>
     <t>유채아버지</t>
@@ -1746,15 +2004,6 @@
     <t>666조 1493억 2746만</t>
   </si>
   <si>
-    <t>조단23</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%8B%A823</t>
-  </si>
-  <si>
-    <t>664조 5237억 9537만</t>
-  </si>
-  <si>
     <t>아콩린</t>
   </si>
   <si>
@@ -1773,280 +2022,13 @@
     <t>512조 2710억 6899만</t>
   </si>
   <si>
-    <t>꺄꽁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BA%84%EA%BD%81</t>
-  </si>
-  <si>
-    <t>9113조 5821억 4815만</t>
-  </si>
-  <si>
-    <t>별쌥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A5</t>
-  </si>
-  <si>
-    <t>7374조 3275억 4141만</t>
-  </si>
-  <si>
-    <t>진욱이에요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9A%B1%EC%9D%B4%EC%97%90%EC%9A%94</t>
-  </si>
-  <si>
-    <t>4749조 892억 3024만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A5%B4%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>3978조 8791억 1664만</t>
-  </si>
-  <si>
-    <t>낭만황금망치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%ED%99%A9%EA%B8%88%EB%A7%9D%EC%B9%98</t>
-  </si>
-  <si>
-    <t>3964조 9837억 1147만</t>
-  </si>
-  <si>
-    <t>김슴줌1</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%8A%B4%EC%A4%8C1</t>
-  </si>
-  <si>
-    <t>3490조 3012억 4881만</t>
-  </si>
-  <si>
-    <t>천달</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EB%8B%AC</t>
-  </si>
-  <si>
-    <t>3179조 1126억 5293만</t>
-  </si>
-  <si>
-    <t>호두와감자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%91%90%EC%99%80%EA%B0%90%EC%9E%90</t>
-  </si>
-  <si>
-    <t>2661조 4151억 6001만</t>
-  </si>
-  <si>
-    <t>활용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%9C%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>2566조 503억 9435만</t>
-  </si>
-  <si>
-    <t>쿠댜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EB%8C%9C</t>
-  </si>
-  <si>
-    <t>2251조 5837억 3846만</t>
-  </si>
-  <si>
-    <t>뚜징</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EC%A7%95</t>
-  </si>
-  <si>
-    <t>1975조 6421억 1426만</t>
-  </si>
-  <si>
-    <t>게렬곰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%EB%A0%AC%EA%B3%B0</t>
-  </si>
-  <si>
-    <t>1092조 4657억 282만</t>
-  </si>
-  <si>
-    <t>별곡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EA%B3%A1</t>
-  </si>
-  <si>
-    <t>1052조 607억 2317만</t>
-  </si>
-  <si>
-    <t>턍ol</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%84%8Dol</t>
-  </si>
-  <si>
-    <t>945조 3772억 7776만</t>
-  </si>
-  <si>
-    <t>동래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%9E%98</t>
-  </si>
-  <si>
-    <t>903조 5825억 2349만</t>
-  </si>
-  <si>
-    <t>까쿠미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EC%BF%A0%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>891조 610억 5144만</t>
-  </si>
-  <si>
-    <t>초이레</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%B4%EB%A0%88</t>
-  </si>
-  <si>
-    <t>863조 1058억 6521만</t>
-  </si>
-  <si>
-    <t>별쌤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A4</t>
-  </si>
-  <si>
-    <t>839조 4891억 2876만</t>
-  </si>
-  <si>
-    <t>띠우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%A0%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>724조 6318억 7556만</t>
-  </si>
-  <si>
-    <t>쿠까미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EA%B9%8C%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>639조 2231억 5295만</t>
-  </si>
-  <si>
-    <t>민족고대감자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%A1%B1%EA%B3%A0%EB%8C%80%EA%B0%90%EC%9E%90</t>
-  </si>
-  <si>
-    <t>563조 9268억 1222만</t>
-  </si>
-  <si>
-    <t>끄챰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%81%84%EC%B1%B0</t>
-  </si>
-  <si>
-    <t>479조 7098억 5560만</t>
-  </si>
-  <si>
-    <t>승아의하루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%EC%95%84%EC%9D%98%ED%95%98%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>451조 854억 6819만</t>
-  </si>
-  <si>
-    <t>08217</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=08217</t>
-  </si>
-  <si>
-    <t>447조 4288억 7860만</t>
-  </si>
-  <si>
-    <t>왕단단이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EB%8B%A8%EB%8B%A8%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>438조 9996억 5330만</t>
-  </si>
-  <si>
-    <t>루이쥔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%9D%B4%EC%A5%94</t>
-  </si>
-  <si>
-    <t>368조 1850억 3501만</t>
-  </si>
-  <si>
-    <t>택Ol</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%9DOl</t>
-  </si>
-  <si>
-    <t>344조 1217억 6727만</t>
-  </si>
-  <si>
-    <t>툼스데이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%88%BC%EC%8A%A4%EB%8D%B0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>285조 1117억 8099만</t>
-  </si>
-  <si>
-    <t>달갸뤼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EA%B0%B8%EB%A4%BC</t>
-  </si>
-  <si>
-    <t>167조 517억 2138만</t>
-  </si>
-  <si>
-    <t>꾸현</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%ED%98%84</t>
-  </si>
-  <si>
-    <t>89조 2810억 5186만</t>
-  </si>
-  <si>
     <t>교주만두</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%90%EC%A3%BC%EB%A7%8C%EB%91%90</t>
   </si>
   <si>
-    <t>8경 2362조 3435억 4962만</t>
+    <t>8경 2914조 8737억 9357만</t>
   </si>
   <si>
     <t>할바이</t>
@@ -2079,7 +2061,19 @@
     <t>106</t>
   </si>
   <si>
-    <t>74조 4621억 8540만</t>
+    <t>76조 5457억 7624만</t>
+  </si>
+  <si>
+    <t>코잉코잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%9E%89%EC%BD%94%EC%9E%89</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>56조 8646억 8660만</t>
   </si>
   <si>
     <t>낭랑28세</t>
@@ -2094,25 +2088,13 @@
     <t>53조 5707억 3136만</t>
   </si>
   <si>
-    <t>코잉코잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%9E%89%EC%BD%94%EC%9E%89</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>52조 4162억 5487만</t>
-  </si>
-  <si>
     <t>오스띤</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%8A%A4%EB%9D%A4</t>
   </si>
   <si>
-    <t>46조 6669억 1509만</t>
+    <t>47조 5214억 8979만</t>
   </si>
   <si>
     <t>빵신궁</t>
@@ -2169,7 +2151,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%82%A4%EB%A7%9B%ED%82%A4%EB%A7%88</t>
   </si>
   <si>
-    <t>29조 5158억 9903만</t>
+    <t>29조 8851억 6176만</t>
   </si>
   <si>
     <t>킬혁</t>
@@ -2193,22 +2175,22 @@
     <t>26조 6167억 1779만</t>
   </si>
   <si>
+    <t>배렛나루왁서</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%EB%A0%9B%EB%82%98%EB%A3%A8%EC%99%81%EC%84%9C</t>
+  </si>
+  <si>
+    <t>24조 7085억 8938만</t>
+  </si>
+  <si>
     <t>땡요나퐁</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%95%A1%EC%9A%94%EB%82%98%ED%90%81</t>
   </si>
   <si>
-    <t>24조 2392억 8962만</t>
-  </si>
-  <si>
-    <t>배렛나루왁서</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%EB%A0%9B%EB%82%98%EB%A3%A8%EC%99%81%EC%84%9C</t>
-  </si>
-  <si>
-    <t>22조 7587억 8669만</t>
+    <t>24조 3652억 7650만</t>
   </si>
   <si>
     <t>썬콜법사ss</t>
@@ -2217,7 +2199,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%ACss</t>
   </si>
   <si>
-    <t>22조 1581억 577만</t>
+    <t>23조 4797억 4876만</t>
   </si>
   <si>
     <t>페프릭2</t>
@@ -2226,7 +2208,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8E%98%ED%94%84%EB%A6%AD2</t>
   </si>
   <si>
-    <t>21조 1071억 3891만</t>
+    <t>21조 2410억 9658만</t>
   </si>
   <si>
     <t>포디케이</t>
@@ -2235,13 +2217,25 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%94%94%EC%BC%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>11조 8245억 1379만</t>
+    <t>11조 9917억 1373만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%ED%82%A4%EB%B9%84%ED%82%A4</t>
   </si>
   <si>
-    <t>9조 2258억 9744만</t>
+    <t>9조 9543억 7897만</t>
+  </si>
+  <si>
+    <t>즈나니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A6%88%EB%82%98%EB%8B%88</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>4조 7298억 6480만</t>
   </si>
   <si>
     <t>갈음</t>
@@ -2250,19 +2244,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%88%EC%9D%8C</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
     <t>4조 2142억 3853만</t>
-  </si>
-  <si>
-    <t>즈나니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A6%88%EB%82%98%EB%8B%88</t>
-  </si>
-  <si>
-    <t>4조 1149억 2956만</t>
   </si>
   <si>
     <t>닝윤</t>
@@ -2893,7 +2875,7 @@
         <v>60</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2934,7 +2916,7 @@
         <v>68</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2995,7 +2977,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3004,7 +2986,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3508,13 +3490,13 @@
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>159</v>
+        <v>103</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3525,28 +3507,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3557,28 +3539,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3589,16 +3571,16 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
@@ -3610,7 +3592,7 @@
         <v>154</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3621,28 +3603,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3653,28 +3635,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>164</v>
+        <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3685,25 +3667,25 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="H22" s="2" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>185</v>
@@ -3735,10 +3717,10 @@
         <v>189</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3749,28 +3731,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>194</v>
+        <v>144</v>
       </c>
       <c r="H24" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3781,16 +3763,16 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
@@ -3799,10 +3781,10 @@
         <v>144</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3813,16 +3795,16 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
@@ -3834,7 +3816,7 @@
         <v>154</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3845,25 +3827,25 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="H27" s="2" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>208</v>
@@ -3892,13 +3874,13 @@
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3909,25 +3891,25 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>153</v>
+        <v>207</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>217</v>
@@ -3956,10 +3938,10 @@
         <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>221</v>
@@ -3968,40 +3950,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -4032,7 +3982,6 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4099,19 +4048,19 @@
         <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>108</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>159</v>
+        <v>207</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>98</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -4125,13 +4074,13 @@
         <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
@@ -4140,10 +4089,10 @@
         <v>91</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -4157,13 +4106,13 @@
         <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
@@ -4175,7 +4124,7 @@
         <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -4189,25 +4138,25 @@
         <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -4221,13 +4170,13 @@
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>90</v>
@@ -4239,7 +4188,7 @@
         <v>104</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -4253,13 +4202,13 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
@@ -4271,7 +4220,7 @@
         <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -4285,13 +4234,13 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
@@ -4303,7 +4252,7 @@
         <v>135</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -4317,13 +4266,13 @@
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
@@ -4335,7 +4284,7 @@
         <v>126</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -4349,25 +4298,25 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -4381,13 +4330,13 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -4399,7 +4348,7 @@
         <v>135</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -4413,13 +4362,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
@@ -4431,7 +4380,7 @@
         <v>126</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -4445,13 +4394,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
@@ -4463,7 +4412,7 @@
         <v>135</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -4477,25 +4426,25 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -4509,25 +4458,25 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>91</v>
+        <v>184</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -4541,13 +4490,13 @@
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
@@ -4559,7 +4508,7 @@
         <v>154</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -4570,28 +4519,28 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -4602,28 +4551,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>189</v>
+        <v>97</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -4634,28 +4583,28 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>280</v>
+        <v>184</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -4666,28 +4615,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>109</v>
+        <v>279</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -4698,28 +4647,28 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>280</v>
+        <v>109</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -4730,28 +4679,28 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>103</v>
+        <v>279</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -4765,13 +4714,13 @@
         <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
@@ -4780,10 +4729,10 @@
         <v>103</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>195</v>
+        <v>154</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -4794,28 +4743,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>189</v>
+        <v>103</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -4826,28 +4775,28 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -4858,16 +4807,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
@@ -4876,10 +4825,10 @@
         <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -4890,28 +4839,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>91</v>
+        <v>189</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -4925,25 +4874,25 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>194</v>
+        <v>91</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -4954,28 +4903,28 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -4989,13 +4938,13 @@
         <v>218</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
@@ -5007,7 +4956,7 @@
         <v>154</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -5018,16 +4967,16 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>222</v>
+        <v>311</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>90</v>
@@ -5036,10 +4985,10 @@
         <v>153</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>34</v>
@@ -5085,7 +5034,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5137,13 +5086,13 @@
         <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
@@ -5155,7 +5104,7 @@
         <v>98</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>43</v>
@@ -5169,13 +5118,13 @@
         <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
@@ -5187,7 +5136,7 @@
         <v>135</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>43</v>
@@ -5201,25 +5150,25 @@
         <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>43</v>
@@ -5233,25 +5182,25 @@
         <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>43</v>
@@ -5265,25 +5214,25 @@
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>97</v>
+        <v>207</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>43</v>
@@ -5297,25 +5246,25 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>91</v>
+        <v>207</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>43</v>
@@ -5329,25 +5278,25 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>43</v>
@@ -5367,7 +5316,7 @@
         <v>42</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>108</v>
@@ -5379,7 +5328,7 @@
         <v>154</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>43</v>
@@ -5393,25 +5342,25 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>159</v>
+        <v>207</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>43</v>
@@ -5425,25 +5374,25 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>43</v>
@@ -5457,25 +5406,25 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>43</v>
@@ -5489,13 +5438,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
@@ -5507,7 +5456,7 @@
         <v>154</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>43</v>
@@ -5521,13 +5470,13 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
@@ -5539,7 +5488,7 @@
         <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>43</v>
@@ -5553,25 +5502,25 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>159</v>
+        <v>207</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>43</v>
@@ -5585,13 +5534,13 @@
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
@@ -5600,10 +5549,10 @@
         <v>97</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>43</v>
@@ -5614,16 +5563,16 @@
         <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
@@ -5635,7 +5584,7 @@
         <v>126</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>43</v>
@@ -5646,28 +5595,28 @@
         <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>43</v>
@@ -5678,16 +5627,16 @@
         <v>35</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
@@ -5696,10 +5645,10 @@
         <v>91</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>43</v>
@@ -5710,16 +5659,16 @@
         <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
@@ -5731,7 +5680,7 @@
         <v>154</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>43</v>
@@ -5742,16 +5691,16 @@
         <v>35</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
@@ -5763,7 +5712,7 @@
         <v>154</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>43</v>
@@ -5774,16 +5723,16 @@
         <v>35</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
@@ -5792,10 +5741,10 @@
         <v>91</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>43</v>
@@ -5809,13 +5758,13 @@
         <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
@@ -5824,10 +5773,10 @@
         <v>109</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>43</v>
@@ -5838,16 +5787,16 @@
         <v>35</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
@@ -5856,10 +5805,10 @@
         <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>43</v>
@@ -5870,16 +5819,16 @@
         <v>35</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
@@ -5888,10 +5837,10 @@
         <v>91</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>43</v>
@@ -5902,16 +5851,16 @@
         <v>35</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
@@ -5920,10 +5869,10 @@
         <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>43</v>
@@ -5934,16 +5883,16 @@
         <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
@@ -5952,10 +5901,10 @@
         <v>109</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>43</v>
@@ -5969,25 +5918,25 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>194</v>
+        <v>97</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>195</v>
+        <v>314</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>43</v>
@@ -5998,28 +5947,28 @@
         <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>97</v>
+        <v>279</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>317</v>
+        <v>212</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>43</v>
@@ -6033,64 +5982,32 @@
         <v>218</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>280</v>
+        <v>91</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -6121,7 +6038,6 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6182,25 +6098,25 @@
         <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>159</v>
+        <v>207</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>43</v>
@@ -6214,25 +6130,25 @@
         <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>43</v>
@@ -6246,13 +6162,13 @@
         <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
@@ -6264,7 +6180,7 @@
         <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>43</v>
@@ -6278,25 +6194,25 @@
         <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>43</v>
@@ -6310,13 +6226,13 @@
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>90</v>
@@ -6328,7 +6244,7 @@
         <v>135</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>43</v>
@@ -6342,13 +6258,13 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
@@ -6360,7 +6276,7 @@
         <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>43</v>
@@ -6374,13 +6290,13 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
@@ -6392,7 +6308,7 @@
         <v>135</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>43</v>
@@ -6406,13 +6322,13 @@
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
@@ -6424,7 +6340,7 @@
         <v>126</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>43</v>
@@ -6438,25 +6354,25 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>43</v>
@@ -6470,25 +6386,25 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>43</v>
@@ -6502,25 +6418,25 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>43</v>
@@ -6534,25 +6450,25 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>43</v>
@@ -6566,13 +6482,13 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
@@ -6584,7 +6500,7 @@
         <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>43</v>
@@ -6598,25 +6514,25 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>43</v>
@@ -6630,13 +6546,13 @@
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
@@ -6648,7 +6564,7 @@
         <v>135</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>43</v>
@@ -6659,16 +6575,16 @@
         <v>44</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
@@ -6680,7 +6596,7 @@
         <v>126</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>43</v>
@@ -6691,28 +6607,28 @@
         <v>44</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>43</v>
@@ -6723,28 +6639,28 @@
         <v>44</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>52</v>
+        <v>453</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>52</v>
+        <v>453</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>43</v>
@@ -6755,28 +6671,28 @@
         <v>44</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>461</v>
+        <v>52</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>461</v>
+        <v>52</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>91</v>
+        <v>184</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>43</v>
@@ -6787,16 +6703,16 @@
         <v>44</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
@@ -6808,7 +6724,7 @@
         <v>126</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>43</v>
@@ -6819,16 +6735,16 @@
         <v>44</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
@@ -6837,10 +6753,10 @@
         <v>91</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>43</v>
@@ -6854,13 +6770,13 @@
         <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
@@ -6872,7 +6788,7 @@
         <v>154</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>43</v>
@@ -6883,16 +6799,16 @@
         <v>44</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
@@ -6904,7 +6820,7 @@
         <v>126</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>43</v>
@@ -6915,28 +6831,28 @@
         <v>44</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>43</v>
@@ -6947,16 +6863,16 @@
         <v>44</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
@@ -6965,10 +6881,10 @@
         <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>43</v>
@@ -6979,28 +6895,28 @@
         <v>44</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>43</v>
@@ -7014,13 +6930,13 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
@@ -7032,7 +6948,7 @@
         <v>154</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>43</v>
@@ -7043,16 +6959,16 @@
         <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
@@ -7061,10 +6977,10 @@
         <v>103</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>43</v>
@@ -7078,13 +6994,13 @@
         <v>218</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
@@ -7096,7 +7012,7 @@
         <v>154</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>43</v>
@@ -7107,28 +7023,28 @@
         <v>44</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>222</v>
+        <v>311</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>43</v>
@@ -7174,985 +7090,6 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J29"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8200,19 +7137,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>580</v>
+        <v>491</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>580</v>
+        <v>491</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>581</v>
+        <v>492</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
@@ -8221,10 +7158,10 @@
         <v>103</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>582</v>
+        <v>493</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>43</v>
@@ -8232,19 +7169,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>583</v>
+        <v>494</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>583</v>
+        <v>494</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>584</v>
+        <v>495</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
@@ -8253,10 +7190,10 @@
         <v>103</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>585</v>
+        <v>496</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>43</v>
@@ -8264,31 +7201,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>586</v>
+        <v>497</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>586</v>
+        <v>497</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>587</v>
+        <v>498</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>588</v>
+        <v>499</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>43</v>
@@ -8296,31 +7233,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>68</v>
+        <v>500</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>68</v>
+        <v>500</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>589</v>
+        <v>501</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>590</v>
+        <v>502</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>43</v>
@@ -8328,31 +7265,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>591</v>
+        <v>60</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>591</v>
+        <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>592</v>
+        <v>503</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>593</v>
+        <v>504</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>43</v>
@@ -8360,31 +7297,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>594</v>
+        <v>505</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>594</v>
+        <v>505</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>595</v>
+        <v>506</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>596</v>
+        <v>507</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>43</v>
@@ -8392,19 +7329,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>597</v>
+        <v>508</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>597</v>
+        <v>508</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>598</v>
+        <v>509</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
@@ -8416,7 +7353,7 @@
         <v>135</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>599</v>
+        <v>510</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>43</v>
@@ -8424,19 +7361,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>600</v>
+        <v>511</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>600</v>
+        <v>511</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>601</v>
+        <v>512</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
@@ -8448,7 +7385,7 @@
         <v>135</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>602</v>
+        <v>513</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>43</v>
@@ -8456,19 +7393,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>603</v>
+        <v>514</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>603</v>
+        <v>514</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>604</v>
+        <v>515</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
@@ -8480,7 +7417,7 @@
         <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>605</v>
+        <v>516</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>43</v>
@@ -8488,19 +7425,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>606</v>
+        <v>517</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>606</v>
+        <v>517</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>607</v>
+        <v>518</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -8512,7 +7449,7 @@
         <v>135</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>608</v>
+        <v>519</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>43</v>
@@ -8520,19 +7457,19 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>609</v>
+        <v>520</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>609</v>
+        <v>520</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>610</v>
+        <v>521</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
@@ -8544,7 +7481,7 @@
         <v>135</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>611</v>
+        <v>522</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>43</v>
@@ -8552,19 +7489,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>612</v>
+        <v>523</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>612</v>
+        <v>523</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>613</v>
+        <v>524</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
@@ -8576,7 +7513,7 @@
         <v>154</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>614</v>
+        <v>525</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>43</v>
@@ -8584,19 +7521,19 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>615</v>
+        <v>526</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>615</v>
+        <v>526</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>616</v>
+        <v>527</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
@@ -8608,7 +7545,7 @@
         <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>617</v>
+        <v>528</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>43</v>
@@ -8616,19 +7553,19 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>618</v>
+        <v>529</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>618</v>
+        <v>529</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>619</v>
+        <v>530</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
@@ -8640,7 +7577,7 @@
         <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>620</v>
+        <v>531</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>43</v>
@@ -8648,31 +7585,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>621</v>
+        <v>532</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>621</v>
+        <v>532</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>622</v>
+        <v>533</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>91</v>
+        <v>279</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>623</v>
+        <v>534</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>43</v>
@@ -8680,31 +7617,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>624</v>
+        <v>535</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>624</v>
+        <v>535</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>625</v>
+        <v>536</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>280</v>
+        <v>91</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>195</v>
+        <v>154</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>626</v>
+        <v>537</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>43</v>
@@ -8712,19 +7649,19 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>627</v>
+        <v>538</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>627</v>
+        <v>538</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>628</v>
+        <v>539</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
@@ -8736,7 +7673,7 @@
         <v>154</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>629</v>
+        <v>540</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>43</v>
@@ -8744,19 +7681,19 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>630</v>
+        <v>541</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>630</v>
+        <v>541</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>631</v>
+        <v>542</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
@@ -8768,7 +7705,7 @@
         <v>154</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>632</v>
+        <v>543</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>43</v>
@@ -8776,19 +7713,19 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>633</v>
+        <v>544</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>633</v>
+        <v>544</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>634</v>
+        <v>545</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
@@ -8797,10 +7734,10 @@
         <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>635</v>
+        <v>546</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>43</v>
@@ -8808,19 +7745,19 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>636</v>
+        <v>547</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>636</v>
+        <v>547</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>637</v>
+        <v>548</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
@@ -8829,10 +7766,10 @@
         <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>638</v>
+        <v>549</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>43</v>
@@ -8840,19 +7777,19 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>639</v>
+        <v>550</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>639</v>
+        <v>550</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>640</v>
+        <v>551</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
@@ -8861,10 +7798,10 @@
         <v>153</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>641</v>
+        <v>552</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>43</v>
@@ -8872,19 +7809,19 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>642</v>
+        <v>553</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>642</v>
+        <v>553</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>643</v>
+        <v>554</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
@@ -8893,10 +7830,10 @@
         <v>109</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>644</v>
+        <v>555</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>43</v>
@@ -8904,19 +7841,19 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>645</v>
+        <v>556</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>645</v>
+        <v>556</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>646</v>
+        <v>557</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
@@ -8925,10 +7862,10 @@
         <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>647</v>
+        <v>558</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>43</v>
@@ -8936,19 +7873,19 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>648</v>
+        <v>559</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>648</v>
+        <v>559</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>649</v>
+        <v>560</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
@@ -8957,10 +7894,10 @@
         <v>91</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>650</v>
+        <v>561</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>43</v>
@@ -8968,31 +7905,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>651</v>
+        <v>562</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>651</v>
+        <v>562</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>652</v>
+        <v>563</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>653</v>
+        <v>564</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>43</v>
@@ -9000,19 +7937,19 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>654</v>
+        <v>565</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>654</v>
+        <v>565</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>655</v>
+        <v>566</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
@@ -9021,10 +7958,10 @@
         <v>91</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>656</v>
+        <v>567</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>43</v>
@@ -9032,19 +7969,19 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>657</v>
+        <v>568</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>657</v>
+        <v>568</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>658</v>
+        <v>569</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
@@ -9053,10 +7990,10 @@
         <v>97</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>659</v>
+        <v>570</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>43</v>
@@ -9064,19 +8001,19 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>660</v>
+        <v>571</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>660</v>
+        <v>571</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>661</v>
+        <v>572</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
@@ -9085,10 +8022,10 @@
         <v>91</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>662</v>
+        <v>573</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>43</v>
@@ -9096,19 +8033,19 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>218</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>663</v>
+        <v>574</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>663</v>
+        <v>574</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>664</v>
+        <v>575</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
@@ -9117,10 +8054,10 @@
         <v>103</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>665</v>
+        <v>576</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>43</v>
@@ -9128,19 +8065,19 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>222</v>
+        <v>311</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>666</v>
+        <v>577</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>666</v>
+        <v>577</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>667</v>
+        <v>578</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>90</v>
@@ -9149,10 +8086,10 @@
         <v>91</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>668</v>
+        <v>579</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>43</v>
@@ -9196,6 +8133,985 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J29"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J25"/>
@@ -9251,13 +9167,13 @@
         <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
@@ -9269,7 +9185,7 @@
         <v>92</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -9283,13 +9199,13 @@
         <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
@@ -9298,10 +9214,10 @@
         <v>91</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -9315,13 +9231,13 @@
         <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
@@ -9330,10 +9246,10 @@
         <v>103</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -9347,13 +9263,13 @@
         <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
@@ -9362,10 +9278,10 @@
         <v>91</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -9379,13 +9295,13 @@
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>90</v>
@@ -9394,10 +9310,10 @@
         <v>153</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -9411,13 +9327,13 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
@@ -9426,10 +9342,10 @@
         <v>153</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -9443,13 +9359,13 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
@@ -9458,10 +9374,10 @@
         <v>103</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -9475,13 +9391,13 @@
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
@@ -9490,10 +9406,10 @@
         <v>153</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -9507,25 +9423,25 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -9539,25 +9455,25 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -9571,13 +9487,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
@@ -9586,10 +9502,10 @@
         <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -9603,13 +9519,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
@@ -9618,10 +9534,10 @@
         <v>91</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -9635,25 +9551,25 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -9667,13 +9583,13 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
@@ -9682,10 +9598,10 @@
         <v>103</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -9699,25 +9615,25 @@
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -9728,28 +9644,28 @@
         <v>69</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>109</v>
+        <v>207</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -9760,28 +9676,28 @@
         <v>69</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -9792,28 +9708,28 @@
         <v>69</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -9824,16 +9740,16 @@
         <v>69</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
@@ -9842,10 +9758,10 @@
         <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -9856,28 +9772,28 @@
         <v>69</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -9888,7 +9804,7 @@
         <v>69</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>78</v>
@@ -9897,19 +9813,19 @@
         <v>78</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>108</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -9923,25 +9839,25 @@
         <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>91</v>
+        <v>184</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -9952,28 +9868,28 @@
         <v>69</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -9984,28 +9900,28 @@
         <v>69</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">따숨!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">만영!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">바텀!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">빅딜!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">빅딜!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">지존길드!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2174" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2164" uniqueCount="738">
   <si>
     <t>guild_name</t>
   </si>
@@ -312,7 +312,7 @@
     <t>117</t>
   </si>
   <si>
-    <t>8경 1141조 4236억 9441만</t>
+    <t>8경 8132조 7374억 560만</t>
   </si>
   <si>
     <t>2</t>
@@ -363,7 +363,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>7477조 5337억 4346만</t>
+    <t>7478조 5755억 856만</t>
   </si>
   <si>
     <t>5</t>
@@ -375,7 +375,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%90%EC%B1%A0</t>
   </si>
   <si>
-    <t>6566조 8993억 2840만</t>
+    <t>6597조 9904억 9169만</t>
   </si>
   <si>
     <t>6</t>
@@ -399,7 +399,7 @@
     <t>https://mgf.gg/contents/character.php?n=GOD%EB%82%A0%EB%91%90</t>
   </si>
   <si>
-    <t>5267조 3069억 6491만</t>
+    <t>5484조 2958억 3188만</t>
   </si>
   <si>
     <t>8</t>
@@ -414,7 +414,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>4448조 4463억 2650만</t>
+    <t>4453조 691억 2403만</t>
   </si>
   <si>
     <t>9</t>
@@ -441,7 +441,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>3245조 2928억 8407만</t>
+    <t>3359조 9731억 5679만</t>
   </si>
   <si>
     <t>11</t>
@@ -453,7 +453,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B0%8C%EB%B0%94%EB%A6%AC%EC%9D%B4</t>
   </si>
   <si>
-    <t>3236조 4179억 3396만</t>
+    <t>3352조 3307억 2632만</t>
   </si>
   <si>
     <t>12</t>
@@ -561,7 +561,7 @@
     <t>https://mgf.gg/contents/character.php?n=v%EB%B0%95%ED%9A%A8%EC%8B%A0v</t>
   </si>
   <si>
-    <t>1335조 2774억 3624만</t>
+    <t>1339조 4695억 4612만</t>
   </si>
   <si>
     <t>20</t>
@@ -573,12 +573,30 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%A6%BF</t>
   </si>
   <si>
-    <t>1256조 4669억 2721만</t>
+    <t>1278조 5550억 2130만</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
+    <t>초읍사나이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%8D%EC%82%AC%EB%82%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1236조 4493억 2491만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>시간이돈</t>
   </si>
   <si>
@@ -591,24 +609,6 @@
     <t>1234조 123억 1646만</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>초읍사나이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%8D%EC%82%AC%EB%82%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>1153조 479억 7983만</t>
-  </si>
-  <si>
     <t>23</t>
   </si>
   <si>
@@ -618,7 +618,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
   </si>
   <si>
-    <t>1056조 8727억 2763만</t>
+    <t>1062조 6693억 5639만</t>
   </si>
   <si>
     <t>24</t>
@@ -684,7 +684,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A6%AC%EB%AF%B8%EC%BF%B5</t>
   </si>
   <si>
-    <t>540조 9494억 6800만</t>
+    <t>569조 3151억 7266만</t>
   </si>
   <si>
     <t>29</t>
@@ -696,13 +696,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%8A%94%EB%B0%B0%EB%B6%88%EB%9F%AC%EC%9A%94</t>
   </si>
   <si>
-    <t>502조 1051억 5367만</t>
+    <t>502조 1728억 9075만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EA%B8%B0%EC%9C%A0%EB%AC%B4</t>
   </si>
   <si>
-    <t>1경 3183조 5333억 2516만</t>
+    <t>1경 3234조 1846억 692만</t>
   </si>
   <si>
     <t>무곽</t>
@@ -723,7 +723,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%95%ED%8C%A1%ED%8C%A1%EC%9D%B4</t>
   </si>
   <si>
-    <t>5210조 3974억 4208만</t>
+    <t>5214조 4616억 1127만</t>
   </si>
   <si>
     <t>붉은모자</t>
@@ -741,7 +741,7 @@
     <t>https://mgf.gg/contents/character.php?n=2%EB%B2%88%EC%A7%B8%EC%BA%90%EB%A6%AD</t>
   </si>
   <si>
-    <t>3706조 3989억 6467만</t>
+    <t>3715조 6465억 812만</t>
   </si>
   <si>
     <t>장뱁새</t>
@@ -750,7 +750,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B1%81%EC%83%88</t>
   </si>
   <si>
-    <t>3484조 3912억 6973만</t>
+    <t>3493조 726억 9027만</t>
   </si>
   <si>
     <t>히테라</t>
@@ -759,7 +759,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%85%8C%EB%9D%BC</t>
   </si>
   <si>
-    <t>3388조 1795억 6만</t>
+    <t>3458조 4117억 9738만</t>
   </si>
   <si>
     <t>꽁꽁냉법</t>
@@ -768,7 +768,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EA%BD%81%EB%83%89%EB%B2%95</t>
   </si>
   <si>
-    <t>2571조 2622억 8515만</t>
+    <t>2621조 4316억 1142만</t>
   </si>
   <si>
     <t>테토일남</t>
@@ -780,7 +780,7 @@
     <t>다크나이트</t>
   </si>
   <si>
-    <t>2485조 8540억 6298만</t>
+    <t>2514조 7331억 505만</t>
   </si>
   <si>
     <t>뚜기파파</t>
@@ -807,7 +807,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%A5%AC%EB%A5%B4</t>
   </si>
   <si>
-    <t>1631조 7745억 9292만</t>
+    <t>1634조 4438억 7950만</t>
   </si>
   <si>
     <t>초앤</t>
@@ -816,7 +816,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%95%A4</t>
   </si>
   <si>
-    <t>1575조 5348억 5955만</t>
+    <t>1624조 6840억 4543만</t>
   </si>
   <si>
     <t>재미있게놀래</t>
@@ -825,7 +825,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EB%AF%B8%EC%9E%88%EA%B2%8C%EB%86%80%EB%9E%98</t>
   </si>
   <si>
-    <t>1384조 7511억 4574만</t>
+    <t>1387조 5077억 7016만</t>
+  </si>
+  <si>
+    <t>가덴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%8D%B4</t>
+  </si>
+  <si>
+    <t>1342조 5953억 2254만</t>
   </si>
   <si>
     <t>빙율</t>
@@ -843,7 +852,7 @@
     <t>https://mgf.gg/contents/character.php?n=33%EC%84%B8%EB%B0%B0%EC%9E%A5%ED%98%B8</t>
   </si>
   <si>
-    <t>1247조 6774억 6373만</t>
+    <t>1261조 3167억 8788만</t>
   </si>
   <si>
     <t>적젹적</t>
@@ -852,16 +861,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%81%EC%A0%B9%EC%A0%81</t>
   </si>
   <si>
-    <t>1155조 2525억 2408만</t>
-  </si>
-  <si>
-    <t>가덴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%8D%B4</t>
-  </si>
-  <si>
-    <t>1042조 615억 229만</t>
+    <t>1243조 5020억 7126만</t>
   </si>
   <si>
     <t>최빵쭈</t>
@@ -876,22 +876,22 @@
     <t>980조 2953억 7066만</t>
   </si>
   <si>
+    <t>타뤽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%A4%BD</t>
+  </si>
+  <si>
+    <t>909조 5942억 1194만</t>
+  </si>
+  <si>
     <t>정기휴므</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EA%B8%B0%ED%9C%B4%EB%AF%80</t>
   </si>
   <si>
-    <t>891조 2847억 9662만</t>
-  </si>
-  <si>
-    <t>타뤽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%A4%BD</t>
-  </si>
-  <si>
-    <t>804조 8666억 5004만</t>
+    <t>891조 8517억 7136만</t>
   </si>
   <si>
     <t>무르스</t>
@@ -900,7 +900,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%A5%B4%EC%8A%A4</t>
   </si>
   <si>
-    <t>782조 4234억 7902만</t>
+    <t>783조 2410억 1299만</t>
   </si>
   <si>
     <t>채황새</t>
@@ -921,6 +921,15 @@
     <t>699조 6704억 9749만</t>
   </si>
   <si>
+    <t>넬샷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%AC%EC%83%B7</t>
+  </si>
+  <si>
+    <t>635조 5234억 8915만</t>
+  </si>
+  <si>
     <t>박도란</t>
   </si>
   <si>
@@ -930,22 +939,13 @@
     <t>631조 424억 363만</t>
   </si>
   <si>
-    <t>넬샷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%AC%EC%83%B7</t>
-  </si>
-  <si>
-    <t>540조 8323억 210만</t>
-  </si>
-  <si>
     <t>장기휴무</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
   </si>
   <si>
-    <t>539조 87억 1816만</t>
+    <t>546조 4316억 58만</t>
   </si>
   <si>
     <t>뿌앵뿌앵</t>
@@ -963,7 +963,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%ED%99%8D%EC%9D%B4</t>
   </si>
   <si>
-    <t>325조 8254억 8546만</t>
+    <t>366조 5656억 4392만</t>
   </si>
   <si>
     <t>30</t>
@@ -987,7 +987,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
   </si>
   <si>
-    <t>2경 255조 6179억 2423만</t>
+    <t>2경 321조 1980억 8092만</t>
   </si>
   <si>
     <t>굴러가는일상</t>
@@ -996,7 +996,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
   </si>
   <si>
-    <t>7944조 993억 9474만</t>
+    <t>8237조 7144억 4543만</t>
   </si>
   <si>
     <t>엘라임</t>
@@ -1005,7 +1005,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
   </si>
   <si>
-    <t>4704조 7804억 542만</t>
+    <t>5059조 4008억 4197만</t>
   </si>
   <si>
     <t>흑두부</t>
@@ -1032,16 +1032,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>2958조 4121억 9385만</t>
-  </si>
-  <si>
-    <t>퍼퓸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
-  </si>
-  <si>
-    <t>2845조 5542억 8706만</t>
+    <t>2971조 3297억 316만</t>
+  </si>
+  <si>
+    <t>야가다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>2586조 1679억 2303만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
@@ -1056,7 +1056,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>2155조 4511억 6887만</t>
+    <t>2224조 2393억 3922만</t>
   </si>
   <si>
     <t>뻥뻥</t>
@@ -1068,22 +1068,13 @@
     <t>2043조 9656억 4336만</t>
   </si>
   <si>
-    <t>야가다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>1697조 755억 7134만</t>
-  </si>
-  <si>
     <t>불보독지</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
   </si>
   <si>
-    <t>1324조 9226억 3624만</t>
+    <t>1330조 9299억 4958만</t>
   </si>
   <si>
     <t>단풍카우</t>
@@ -1092,7 +1083,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>1134조 9932억 8765만</t>
+    <t>1139조 3354억 3997만</t>
   </si>
   <si>
     <t>호우기</t>
@@ -1119,7 +1110,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
   </si>
   <si>
-    <t>1077조 4158억 5356만</t>
+    <t>1081조 8986억 458만</t>
   </si>
   <si>
     <t>뽀송히</t>
@@ -1128,7 +1119,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
   </si>
   <si>
-    <t>1042조 2381억 369만</t>
+    <t>1050조 6657억 3307만</t>
   </si>
   <si>
     <t>좀치는형님</t>
@@ -1146,7 +1137,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
   </si>
   <si>
-    <t>970조 2899억 6670만</t>
+    <t>972조 152억 3118만</t>
   </si>
   <si>
     <t>라탱호</t>
@@ -1155,7 +1146,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%ED%83%B1%ED%98%B8</t>
   </si>
   <si>
-    <t>878조 9823억 5133만</t>
+    <t>881조 7556억 9106만</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -1173,7 +1164,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%A4%EB%98%98</t>
   </si>
   <si>
-    <t>671조 5173억 6638만</t>
+    <t>671조 9525억 1752만</t>
   </si>
   <si>
     <t>팡대지</t>
@@ -1185,22 +1176,22 @@
     <t>575조 1653억 9478만</t>
   </si>
   <si>
+    <t>박준우2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
+  </si>
+  <si>
+    <t>568조 4360억 6361만</t>
+  </si>
+  <si>
     <t>민들레꽃</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>558조 368억 4937만</t>
-  </si>
-  <si>
-    <t>박준우2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
-  </si>
-  <si>
-    <t>538조 1761억 3296만</t>
+    <t>559조 1192억 5788만</t>
   </si>
   <si>
     <t>솔인</t>
@@ -1218,7 +1209,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>337조 7925억 8502만</t>
+    <t>338조 1338억 8268만</t>
   </si>
   <si>
     <t>여눈</t>
@@ -1227,7 +1218,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
   </si>
   <si>
-    <t>292조 9201억 6015만</t>
+    <t>328조 9422억 4240만</t>
   </si>
   <si>
     <t>꼬북빵야</t>
@@ -1245,7 +1236,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
   </si>
   <si>
-    <t>9743조 813억 3813만</t>
+    <t>9888조 9654억 14만</t>
   </si>
   <si>
     <t>수텍</t>
@@ -1263,7 +1254,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
   </si>
   <si>
-    <t>4492조 1878억 3268만</t>
+    <t>4544조 7861억 2132만</t>
   </si>
   <si>
     <t>협의</t>
@@ -1281,7 +1272,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
   </si>
   <si>
-    <t>3689조 8892억 3174만</t>
+    <t>3694조 4730억 5673만</t>
   </si>
   <si>
     <t>기뽐</t>
@@ -1299,7 +1290,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>2840조 4958억 3412만</t>
+    <t>2884조 3838억 7409만</t>
   </si>
   <si>
     <t>포항가자미</t>
@@ -1308,7 +1299,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
   </si>
   <si>
-    <t>2582조 4683억 1990만</t>
+    <t>2585조 8424억 4496만</t>
   </si>
   <si>
     <t>뿡쓰</t>
@@ -1317,7 +1308,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
   </si>
   <si>
-    <t>2530조 3491억 7461만</t>
+    <t>2533조 6647억 4576만</t>
   </si>
   <si>
     <t>지존빼앙</t>
@@ -1338,6 +1329,15 @@
     <t>2465조 3877억 3257만</t>
   </si>
   <si>
+    <t>온백</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
+  </si>
+  <si>
+    <t>2338조 5666억 805만</t>
+  </si>
+  <si>
     <t>엘르가든</t>
   </si>
   <si>
@@ -1347,15 +1347,6 @@
     <t>2313조 7071억 7362만</t>
   </si>
   <si>
-    <t>온백</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
-  </si>
-  <si>
-    <t>2292조 9975억 215만</t>
-  </si>
-  <si>
     <t>파울</t>
   </si>
   <si>
@@ -1374,6 +1365,15 @@
     <t>1889조 8524억 3410만</t>
   </si>
   <si>
+    <t>대좀이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1488조 1251억 1121만</t>
+  </si>
+  <si>
     <t>오옹나이스</t>
   </si>
   <si>
@@ -1383,28 +1383,28 @@
     <t>1379조 1810억 4031만</t>
   </si>
   <si>
-    <t>대좀이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1338조 9567억 2031만</t>
-  </si>
-  <si>
     <t>모짜리코베르</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
   </si>
   <si>
-    <t>1337조 9988억 6043만</t>
+    <t>1378조 9632억 3810만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
   </si>
   <si>
-    <t>1316조 5131억 3303만</t>
+    <t>1319조 631억 7399만</t>
+  </si>
+  <si>
+    <t>김허덕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
+  </si>
+  <si>
+    <t>1206조 1272억 7177만</t>
   </si>
   <si>
     <t>마갤</t>
@@ -1416,15 +1416,6 @@
     <t>1200조 1472억 1769만</t>
   </si>
   <si>
-    <t>김허덕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
-  </si>
-  <si>
-    <t>1173조 7299억 1919만</t>
-  </si>
-  <si>
     <t>짱잘자쿨냥</t>
   </si>
   <si>
@@ -1458,7 +1449,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%B0%EB%B4%89</t>
   </si>
   <si>
-    <t>952조 4457억 9458만</t>
+    <t>1019조 5372억 3078만</t>
   </si>
   <si>
     <t>고숨도칭</t>
@@ -1476,7 +1467,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
   </si>
   <si>
-    <t>848조 4037억 9866만</t>
+    <t>850조 4940억 4514만</t>
   </si>
   <si>
     <t>Doham</t>
@@ -1485,7 +1476,7 @@
     <t>https://mgf.gg/contents/character.php?n=Doham</t>
   </si>
   <si>
-    <t>806조 785억 6034만</t>
+    <t>822조 168억 4984만</t>
   </si>
   <si>
     <t>유플러스</t>
@@ -1512,7 +1503,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BA%84%EA%BD%81</t>
   </si>
   <si>
-    <t>9119조 4659억 904만</t>
+    <t>1경 402조 885억 6882만</t>
   </si>
   <si>
     <t>별쌥</t>
@@ -1530,7 +1521,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9A%B1%EC%9D%B4%EC%97%90%EC%9A%94</t>
   </si>
   <si>
-    <t>4749조 892억 3024만</t>
+    <t>4939조 5954억 5774만</t>
   </si>
   <si>
     <t>낭만황금망치</t>
@@ -1539,13 +1530,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%ED%99%A9%EA%B8%88%EB%A7%9D%EC%B9%98</t>
   </si>
   <si>
-    <t>4088조 6937억 8303만</t>
+    <t>4225조 3118억 1638만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A5%B4%EB%AA%AC</t>
   </si>
   <si>
-    <t>3997조 3647억 9275만</t>
+    <t>4208조 8898억 7771만</t>
   </si>
   <si>
     <t>김슴줌1</t>
@@ -1554,7 +1545,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%8A%B4%EC%A4%8C1</t>
   </si>
   <si>
-    <t>3490조 3012억 4881만</t>
+    <t>3765조 1886억 2045만</t>
   </si>
   <si>
     <t>천달</t>
@@ -1563,7 +1554,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EB%8B%AC</t>
   </si>
   <si>
-    <t>3241조 6352억 3954만</t>
+    <t>3358조 869억 3060만</t>
+  </si>
+  <si>
+    <t>활용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%9C%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>2743조 9212억 5191만</t>
   </si>
   <si>
     <t>호두와감자</t>
@@ -1575,22 +1575,13 @@
     <t>2661조 4151억 6001만</t>
   </si>
   <si>
-    <t>활용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%9C%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>2636조 7277억 398만</t>
-  </si>
-  <si>
     <t>쿠댜</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EB%8C%9C</t>
   </si>
   <si>
-    <t>2251조 5837억 3846만</t>
+    <t>2284조 7558억 6909만</t>
   </si>
   <si>
     <t>뚜징</t>
@@ -1608,7 +1599,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%EB%A0%AC%EA%B3%B0</t>
   </si>
   <si>
-    <t>1092조 4657억 282만</t>
+    <t>1106조 9910억 8653만</t>
   </si>
   <si>
     <t>별곡</t>
@@ -1626,7 +1617,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%84%8Dol</t>
   </si>
   <si>
-    <t>977조 5376억 1470만</t>
+    <t>989조 1144억 7869만</t>
+  </si>
+  <si>
+    <t>동래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%9E%98</t>
+  </si>
+  <si>
+    <t>968조 7399억 9311만</t>
   </si>
   <si>
     <t>까쿠미</t>
@@ -1638,22 +1638,13 @@
     <t>968조 6592억 9407만</t>
   </si>
   <si>
-    <t>동래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%9E%98</t>
-  </si>
-  <si>
-    <t>938조 9632억 708만</t>
-  </si>
-  <si>
     <t>초이레</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%B4%EB%A0%88</t>
   </si>
   <si>
-    <t>865조 3202억 7527만</t>
+    <t>869조 9507억 6002만</t>
   </si>
   <si>
     <t>별쌤</t>
@@ -1671,7 +1662,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%A0%EC%9A%B0</t>
   </si>
   <si>
-    <t>724조 6318억 7556만</t>
+    <t>725조 2731억 3447만</t>
   </si>
   <si>
     <t>쿠까미</t>
@@ -1707,7 +1698,7 @@
     <t>https://mgf.gg/contents/character.php?n=08217</t>
   </si>
   <si>
-    <t>464조 5454억 7899만</t>
+    <t>464조 8617억 3924만</t>
   </si>
   <si>
     <t>승아의하루</t>
@@ -1725,7 +1716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EB%8B%A8%EB%8B%A8%EC%9D%B4</t>
   </si>
   <si>
-    <t>439조 2480억 4063만</t>
+    <t>439조 6821억 4352만</t>
   </si>
   <si>
     <t>루이쥔</t>
@@ -1734,7 +1725,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%9D%B4%EC%A5%94</t>
   </si>
   <si>
-    <t>369조 3190억 5898만</t>
+    <t>403조 7730억 6533만</t>
   </si>
   <si>
     <t>택Ol</t>
@@ -1761,7 +1752,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EA%B0%B8%EB%A4%BC</t>
   </si>
   <si>
-    <t>167조 1400억 2161만</t>
+    <t>167조 3030억 3553만</t>
   </si>
   <si>
     <t>꾸현</t>
@@ -1788,7 +1779,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%96%A5</t>
   </si>
   <si>
-    <t>9352조 8862억 9035만</t>
+    <t>9873조 1430억 5286만</t>
   </si>
   <si>
     <t>례전</t>
@@ -1797,7 +1788,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%80%EC%A0%84</t>
   </si>
   <si>
-    <t>4551조 3955억 8705만</t>
+    <t>4565조 3068억 6482만</t>
   </si>
   <si>
     <t>숭타이준</t>
@@ -1806,7 +1797,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%ED%83%80%EC%9D%B4%EC%A4%80</t>
   </si>
   <si>
-    <t>3633조 7230억 9510만</t>
+    <t>3714조 5791억 7385만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%94%9C%ED%8F%BF</t>
@@ -1830,7 +1821,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%B5%EC%88%98</t>
   </si>
   <si>
-    <t>2321조 72억 7628만</t>
+    <t>2321조 2333억 3182만</t>
+  </si>
+  <si>
+    <t>문제적남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EC%A0%9C%EC%A0%81%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>1997조 2870억 868만</t>
   </si>
   <si>
     <t>탱폿</t>
@@ -1842,22 +1842,31 @@
     <t>1888조 1422억 7967만</t>
   </si>
   <si>
+    <t>뮬이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AE%AC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1849조 6243억 90만</t>
+  </si>
+  <si>
     <t>아이리쉬</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EB%A6%AC%EC%89%AC</t>
   </si>
   <si>
-    <t>1837조 7763억 5221만</t>
-  </si>
-  <si>
-    <t>뮬이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AE%AC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1825조 3094억 670만</t>
+    <t>1839조 8251억 1365만</t>
+  </si>
+  <si>
+    <t>화둥에불낸년</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EB%91%A5%EC%97%90%EB%B6%88%EB%82%B8%EB%85%84</t>
+  </si>
+  <si>
+    <t>1819조 1559억 3691만</t>
   </si>
   <si>
     <t>야키산</t>
@@ -1866,25 +1875,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%82%A4%EC%82%B0</t>
   </si>
   <si>
-    <t>1773조 7138억 3038만</t>
-  </si>
-  <si>
-    <t>문제적남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EC%A0%9C%EC%A0%81%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>1758조 5739억 8468만</t>
-  </si>
-  <si>
-    <t>화둥에불낸년</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EB%91%A5%EC%97%90%EB%B6%88%EB%82%B8%EB%85%84</t>
-  </si>
-  <si>
-    <t>1459조 5948억 5940만</t>
+    <t>1774조 331억 3651만</t>
   </si>
   <si>
     <t>독스케</t>
@@ -1893,7 +1884,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%8A%A4%EC%BC%80</t>
   </si>
   <si>
-    <t>1327조 8028억 7915만</t>
+    <t>1352조 6582억 9239만</t>
   </si>
   <si>
     <t>우즈2텐겐</t>
@@ -1923,22 +1914,22 @@
     <t>1032조 7712억 9061만</t>
   </si>
   <si>
+    <t>구도류</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%8F%84%EB%A5%98</t>
+  </si>
+  <si>
+    <t>1020조 6439억 2084만</t>
+  </si>
+  <si>
     <t>매화로이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%ED%99%94%EB%A1%9C%EC%9D%B4</t>
   </si>
   <si>
-    <t>1010조 1348억 1749만</t>
-  </si>
-  <si>
-    <t>구도류</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%8F%84%EB%A5%98</t>
-  </si>
-  <si>
-    <t>1006조 7901억 659만</t>
+    <t>1010조 4076억 8841만</t>
   </si>
   <si>
     <t>기똥찬벌레</t>
@@ -1956,7 +1947,7 @@
     <t>https://mgf.gg/contents/character.php?n=JJuna</t>
   </si>
   <si>
-    <t>860조 6445억 9230만</t>
+    <t>936조 4240억 6417만</t>
   </si>
   <si>
     <t>난센</t>
@@ -1965,7 +1956,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EC%84%BC</t>
   </si>
   <si>
-    <t>796조 7724억 80만</t>
+    <t>797조 8464억 6504만</t>
   </si>
   <si>
     <t>에프람</t>
@@ -1974,7 +1965,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%ED%94%84%EB%9E%8C</t>
   </si>
   <si>
-    <t>794조 8159억 9149만</t>
+    <t>795조 2999억 6288만</t>
   </si>
   <si>
     <t>콜리셰마드르</t>
@@ -1983,7 +1974,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%9C%EB%A6%AC%EC%85%B0%EB%A7%88%EB%93%9C%EB%A5%B4</t>
   </si>
   <si>
-    <t>777조 7687억 9355만</t>
+    <t>778조 3878억 4322만</t>
+  </si>
+  <si>
+    <t>유채아버지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%B1%84%EC%95%84%EB%B2%84%EC%A7%80</t>
+  </si>
+  <si>
+    <t>670조 9011억 2995만</t>
   </si>
   <si>
     <t>조단23</t>
@@ -1992,16 +1992,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%8B%A823</t>
   </si>
   <si>
-    <t>667조 4856억 8254만</t>
-  </si>
-  <si>
-    <t>유채아버지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%B1%84%EC%95%84%EB%B2%84%EC%A7%80</t>
-  </si>
-  <si>
-    <t>666조 1493억 2746만</t>
+    <t>667조 7732억 1410만</t>
   </si>
   <si>
     <t>아콩린</t>
@@ -2019,7 +2010,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A3%A8%EB%A3%A8</t>
   </si>
   <si>
-    <t>512조 2710억 6899만</t>
+    <t>513조 4329억 1903만</t>
   </si>
   <si>
     <t>교주만두</t>
@@ -2028,7 +2019,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%90%EC%A3%BC%EB%A7%8C%EB%91%90</t>
   </si>
   <si>
-    <t>8경 2914조 8737억 9357만</t>
+    <t>9경 1385조 9371억 1706만</t>
   </si>
   <si>
     <t>할바이</t>
@@ -2061,7 +2052,7 @@
     <t>106</t>
   </si>
   <si>
-    <t>76조 5457억 7624만</t>
+    <t>80조 5817억 7403만</t>
   </si>
   <si>
     <t>코잉코잉</t>
@@ -2073,7 +2064,16 @@
     <t>105</t>
   </si>
   <si>
-    <t>56조 8646억 8660만</t>
+    <t>56조 9863억 3123만</t>
+  </si>
+  <si>
+    <t>토벤숍이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%B2%A4%EC%88%8D%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>53조 7183억 6678만</t>
   </si>
   <si>
     <t>낭랑28세</t>
@@ -2094,7 +2094,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%8A%A4%EB%9D%A4</t>
   </si>
   <si>
-    <t>47조 5214억 8979만</t>
+    <t>47조 5727억 92만</t>
   </si>
   <si>
     <t>빵신궁</t>
@@ -2103,16 +2103,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EC%8B%A0%EA%B6%81</t>
   </si>
   <si>
-    <t>40조 1172억 2624만</t>
-  </si>
-  <si>
-    <t>토벤숍이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%B2%A4%EC%88%8D%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>37조 9497억 6922만</t>
+    <t>42조 3794억 7995만</t>
   </si>
   <si>
     <t>썬콜우체국</t>
@@ -2124,7 +2115,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>33조 9631억 9118만</t>
+    <t>35조 905억 9156만</t>
   </si>
   <si>
     <t>밀초크코</t>
@@ -2142,7 +2133,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%ED%86%B5%EB%B0%9B%EB%8A%94%EA%B0%88%EB%B9%84</t>
   </si>
   <si>
-    <t>30조 3417억 9621만</t>
+    <t>31조 7895억 5650만</t>
   </si>
   <si>
     <t>마키맛키마</t>
@@ -2151,7 +2142,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%82%A4%EB%A7%9B%ED%82%A4%EB%A7%88</t>
   </si>
   <si>
-    <t>29조 8851억 6176만</t>
+    <t>30조 4248억 9041만</t>
   </si>
   <si>
     <t>킬혁</t>
@@ -2184,22 +2175,22 @@
     <t>24조 7085억 8938만</t>
   </si>
   <si>
+    <t>썬콜법사ss</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%ACss</t>
+  </si>
+  <si>
+    <t>24조 5393억 7309만</t>
+  </si>
+  <si>
     <t>땡요나퐁</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%95%A1%EC%9A%94%EB%82%98%ED%90%81</t>
   </si>
   <si>
-    <t>24조 3652억 7650만</t>
-  </si>
-  <si>
-    <t>썬콜법사ss</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%ACss</t>
-  </si>
-  <si>
-    <t>23조 4797억 4876만</t>
+    <t>24조 4450억 3191만</t>
   </si>
   <si>
     <t>페프릭2</t>
@@ -2217,7 +2208,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%94%94%EC%BC%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>11조 9917억 1373만</t>
+    <t>12조 9292억 7540만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%ED%82%A4%EB%B9%84%ED%82%A4</t>
@@ -2244,7 +2235,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%88%EC%9D%8C</t>
   </si>
   <si>
-    <t>4조 2142억 3853만</t>
+    <t>4조 3884억 1717만</t>
   </si>
   <si>
     <t>닝윤</t>
@@ -2986,7 +2977,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3685,10 +3676,10 @@
         <v>184</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3699,25 +3690,25 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>190</v>
+        <v>154</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>191</v>
@@ -3845,7 +3836,7 @@
         <v>207</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>208</v>
@@ -3909,7 +3900,7 @@
         <v>207</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>217</v>
@@ -3938,10 +3929,10 @@
         <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>221</v>
@@ -4150,7 +4141,7 @@
         <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>126</v>
@@ -4470,7 +4461,7 @@
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>154</v>
@@ -4502,10 +4493,10 @@
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>91</v>
+        <v>190</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>267</v>
@@ -4566,7 +4557,7 @@
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>154</v>
@@ -4598,10 +4589,10 @@
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>184</v>
+        <v>97</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>276</v>
@@ -4662,7 +4653,7 @@
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>109</v>
+        <v>279</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>154</v>
@@ -4694,7 +4685,7 @@
         <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>279</v>
+        <v>109</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>154</v>
@@ -4711,7 +4702,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>287</v>
@@ -4761,7 +4752,7 @@
         <v>103</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>292</v>
@@ -4790,7 +4781,7 @@
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>212</v>
@@ -4822,10 +4813,10 @@
         <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>91</v>
+        <v>184</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>298</v>
@@ -4854,10 +4845,10 @@
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>301</v>
@@ -4889,7 +4880,7 @@
         <v>91</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>304</v>
@@ -5034,7 +5025,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5290,7 +5281,7 @@
         <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>91</v>
+        <v>184</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>135</v>
@@ -5386,7 +5377,7 @@
         <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>154</v>
@@ -5418,10 +5409,10 @@
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>189</v>
+        <v>144</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>347</v>
@@ -5450,10 +5441,10 @@
         <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>350</v>
@@ -5482,10 +5473,10 @@
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>97</v>
+        <v>207</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>353</v>
@@ -5514,10 +5505,10 @@
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>207</v>
+        <v>97</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>356</v>
@@ -5546,10 +5537,10 @@
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>190</v>
+        <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>359</v>
@@ -5578,10 +5569,10 @@
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>362</v>
@@ -5610,10 +5601,10 @@
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>163</v>
+        <v>91</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>365</v>
@@ -5645,7 +5636,7 @@
         <v>91</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>190</v>
+        <v>154</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>368</v>
@@ -5674,7 +5665,7 @@
         <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>154</v>
@@ -5706,10 +5697,10 @@
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>374</v>
@@ -5738,10 +5729,10 @@
         <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>377</v>
@@ -5755,7 +5746,7 @@
         <v>35</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>378</v>
@@ -5770,10 +5761,10 @@
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>380</v>
@@ -5805,7 +5796,7 @@
         <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>383</v>
@@ -5837,7 +5828,7 @@
         <v>91</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>386</v>
@@ -5866,10 +5857,10 @@
         <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>389</v>
@@ -5898,10 +5889,10 @@
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>212</v>
+        <v>314</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>392</v>
@@ -5930,10 +5921,10 @@
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>97</v>
+        <v>279</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>314</v>
+        <v>212</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>395</v>
@@ -5962,7 +5953,7 @@
         <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>279</v>
+        <v>91</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>212</v>
@@ -5974,40 +5965,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J29"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -6037,7 +5996,6 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6098,13 +6056,13 @@
         <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
@@ -6116,7 +6074,7 @@
         <v>226</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>43</v>
@@ -6130,13 +6088,13 @@
         <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
@@ -6148,7 +6106,7 @@
         <v>226</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>43</v>
@@ -6162,13 +6120,13 @@
         <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
@@ -6180,7 +6138,7 @@
         <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>43</v>
@@ -6194,13 +6152,13 @@
         <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
@@ -6212,7 +6170,7 @@
         <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>43</v>
@@ -6226,13 +6184,13 @@
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>90</v>
@@ -6244,7 +6202,7 @@
         <v>135</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>43</v>
@@ -6258,13 +6216,13 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
@@ -6276,7 +6234,7 @@
         <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>43</v>
@@ -6290,13 +6248,13 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
@@ -6308,7 +6266,7 @@
         <v>135</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>43</v>
@@ -6322,13 +6280,13 @@
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
@@ -6340,7 +6298,7 @@
         <v>126</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>43</v>
@@ -6354,13 +6312,13 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
@@ -6372,7 +6330,7 @@
         <v>154</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>43</v>
@@ -6386,25 +6344,25 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>43</v>
@@ -6418,25 +6376,25 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>43</v>
@@ -6450,25 +6408,25 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>43</v>
@@ -6482,25 +6440,25 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>43</v>
@@ -6514,13 +6472,13 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
@@ -6532,7 +6490,7 @@
         <v>135</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>43</v>
@@ -6546,13 +6504,13 @@
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
@@ -6564,7 +6522,7 @@
         <v>135</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>43</v>
@@ -6578,25 +6536,25 @@
         <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>97</v>
+        <v>190</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>43</v>
@@ -6610,25 +6568,25 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>184</v>
+        <v>97</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>43</v>
@@ -6642,13 +6600,13 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
@@ -6660,7 +6618,7 @@
         <v>126</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>43</v>
@@ -6680,19 +6638,19 @@
         <v>52</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>108</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>43</v>
@@ -6706,13 +6664,13 @@
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
@@ -6724,7 +6682,7 @@
         <v>126</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>43</v>
@@ -6738,13 +6696,13 @@
         <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
@@ -6756,7 +6714,7 @@
         <v>126</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>43</v>
@@ -6767,16 +6725,16 @@
         <v>44</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
@@ -6788,7 +6746,7 @@
         <v>154</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>43</v>
@@ -6802,13 +6760,13 @@
         <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
@@ -6820,7 +6778,7 @@
         <v>126</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>43</v>
@@ -6834,13 +6792,13 @@
         <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
@@ -6852,7 +6810,7 @@
         <v>154</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>43</v>
@@ -6866,13 +6824,13 @@
         <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
@@ -6881,10 +6839,10 @@
         <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>43</v>
@@ -6898,13 +6856,13 @@
         <v>204</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
@@ -6913,10 +6871,10 @@
         <v>248</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>43</v>
@@ -6930,13 +6888,13 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
@@ -6948,7 +6906,7 @@
         <v>154</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>43</v>
@@ -6962,13 +6920,13 @@
         <v>214</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
@@ -6977,10 +6935,10 @@
         <v>103</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>43</v>
@@ -6994,13 +6952,13 @@
         <v>218</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
@@ -7012,7 +6970,7 @@
         <v>154</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>43</v>
@@ -7026,13 +6984,13 @@
         <v>311</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>90</v>
@@ -7044,7 +7002,7 @@
         <v>212</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>43</v>
@@ -7099,7 +7057,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7143,13 +7101,13 @@
         <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
@@ -7161,7 +7119,7 @@
         <v>226</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>43</v>
@@ -7175,13 +7133,13 @@
         <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
@@ -7193,7 +7151,7 @@
         <v>226</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>43</v>
@@ -7207,13 +7165,13 @@
         <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
@@ -7225,7 +7183,7 @@
         <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>43</v>
@@ -7239,13 +7197,13 @@
         <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
@@ -7257,7 +7215,7 @@
         <v>135</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>43</v>
@@ -7277,7 +7235,7 @@
         <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>108</v>
@@ -7289,7 +7247,7 @@
         <v>104</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>43</v>
@@ -7303,13 +7261,13 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
@@ -7318,10 +7276,10 @@
         <v>248</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>43</v>
@@ -7335,13 +7293,13 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
@@ -7353,7 +7311,7 @@
         <v>135</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>43</v>
@@ -7367,25 +7325,25 @@
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>43</v>
@@ -7399,25 +7357,25 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>43</v>
@@ -7431,13 +7389,13 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -7449,7 +7407,7 @@
         <v>135</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>43</v>
@@ -7463,13 +7421,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
@@ -7481,7 +7439,7 @@
         <v>135</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>43</v>
@@ -7495,13 +7453,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
@@ -7510,10 +7468,10 @@
         <v>91</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>43</v>
@@ -7527,13 +7485,13 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
@@ -7545,7 +7503,7 @@
         <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>43</v>
@@ -7559,13 +7517,13 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
@@ -7577,7 +7535,7 @@
         <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>43</v>
@@ -7591,25 +7549,25 @@
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>279</v>
+        <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>190</v>
+        <v>154</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>43</v>
@@ -7623,25 +7581,25 @@
         <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>91</v>
+        <v>279</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>43</v>
@@ -7655,13 +7613,13 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
@@ -7673,7 +7631,7 @@
         <v>154</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>43</v>
@@ -7687,13 +7645,13 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
@@ -7705,7 +7663,7 @@
         <v>154</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>43</v>
@@ -7719,13 +7677,13 @@
         <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
@@ -7734,10 +7692,10 @@
         <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>43</v>
@@ -7751,13 +7709,13 @@
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
@@ -7769,7 +7727,7 @@
         <v>212</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>43</v>
@@ -7783,13 +7741,13 @@
         <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
@@ -7798,10 +7756,10 @@
         <v>153</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>43</v>
@@ -7812,16 +7770,16 @@
         <v>53</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
@@ -7830,10 +7788,10 @@
         <v>109</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>43</v>
@@ -7847,13 +7805,13 @@
         <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
@@ -7862,10 +7820,10 @@
         <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>43</v>
@@ -7879,13 +7837,13 @@
         <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
@@ -7894,10 +7852,10 @@
         <v>91</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>43</v>
@@ -7911,13 +7869,13 @@
         <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
@@ -7926,10 +7884,10 @@
         <v>248</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>43</v>
@@ -7943,13 +7901,13 @@
         <v>204</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
@@ -7958,10 +7916,10 @@
         <v>91</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>43</v>
@@ -7975,13 +7933,13 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
@@ -7993,7 +7951,7 @@
         <v>212</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>43</v>
@@ -8007,13 +7965,13 @@
         <v>214</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
@@ -8022,10 +7980,10 @@
         <v>91</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>43</v>
@@ -8039,13 +7997,13 @@
         <v>218</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
@@ -8054,10 +8012,10 @@
         <v>103</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>314</v>
+        <v>212</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>43</v>
@@ -8071,13 +8029,13 @@
         <v>311</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>90</v>
@@ -8089,7 +8047,7 @@
         <v>314</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>43</v>
@@ -8188,13 +8146,13 @@
         <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
@@ -8206,7 +8164,7 @@
         <v>104</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -8220,25 +8178,25 @@
         <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -8252,13 +8210,13 @@
         <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
@@ -8270,7 +8228,7 @@
         <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -8284,13 +8242,13 @@
         <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
@@ -8299,10 +8257,10 @@
         <v>91</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -8322,7 +8280,7 @@
         <v>68</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>108</v>
@@ -8334,7 +8292,7 @@
         <v>135</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -8348,25 +8306,25 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -8380,13 +8338,13 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
@@ -8398,7 +8356,7 @@
         <v>126</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -8412,25 +8370,25 @@
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>279</v>
+        <v>91</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -8444,25 +8402,25 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>91</v>
+        <v>279</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -8476,13 +8434,13 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -8494,7 +8452,7 @@
         <v>135</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -8508,13 +8466,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
@@ -8523,10 +8481,10 @@
         <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -8540,13 +8498,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
@@ -8555,10 +8513,10 @@
         <v>91</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -8572,13 +8530,13 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
@@ -8587,10 +8545,10 @@
         <v>91</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -8604,13 +8562,13 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
@@ -8622,7 +8580,7 @@
         <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -8636,13 +8594,13 @@
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
@@ -8654,7 +8612,7 @@
         <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -8668,25 +8626,25 @@
         <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -8700,13 +8658,13 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
@@ -8718,7 +8676,7 @@
         <v>154</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -8732,13 +8690,13 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
@@ -8750,7 +8708,7 @@
         <v>154</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -8764,13 +8722,13 @@
         <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
@@ -8782,7 +8740,7 @@
         <v>154</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -8796,13 +8754,13 @@
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
@@ -8814,7 +8772,7 @@
         <v>154</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -8828,25 +8786,25 @@
         <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -8857,16 +8815,16 @@
         <v>61</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
@@ -8878,7 +8836,7 @@
         <v>154</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -8892,13 +8850,13 @@
         <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
@@ -8910,7 +8868,7 @@
         <v>126</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -8924,13 +8882,13 @@
         <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
@@ -8942,7 +8900,7 @@
         <v>154</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -8956,25 +8914,25 @@
         <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>248</v>
+        <v>103</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -8988,25 +8946,25 @@
         <v>204</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>103</v>
+        <v>248</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>190</v>
+        <v>154</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -9020,13 +8978,13 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
@@ -9038,7 +8996,7 @@
         <v>154</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -9052,13 +9010,13 @@
         <v>214</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
@@ -9070,7 +9028,7 @@
         <v>212</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -9167,13 +9125,13 @@
         <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
@@ -9185,7 +9143,7 @@
         <v>92</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -9199,13 +9157,13 @@
         <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
@@ -9214,10 +9172,10 @@
         <v>91</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -9231,13 +9189,13 @@
         <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
@@ -9249,7 +9207,7 @@
         <v>212</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -9263,13 +9221,13 @@
         <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
@@ -9278,10 +9236,10 @@
         <v>91</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -9295,13 +9253,13 @@
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>90</v>
@@ -9310,10 +9268,10 @@
         <v>153</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -9327,25 +9285,25 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -9359,25 +9317,25 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>683</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -9391,25 +9349,25 @@
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>153</v>
+        <v>103</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>683</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -9423,25 +9381,25 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>683</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -9455,13 +9413,13 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -9470,10 +9428,10 @@
         <v>163</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -9487,13 +9445,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
@@ -9505,7 +9463,7 @@
         <v>683</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -9519,13 +9477,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
@@ -9537,7 +9495,7 @@
         <v>683</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -9551,13 +9509,13 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
@@ -9566,10 +9524,10 @@
         <v>163</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -9583,13 +9541,13 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
@@ -9601,7 +9559,7 @@
         <v>683</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -9615,13 +9573,13 @@
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
@@ -9630,10 +9588,10 @@
         <v>279</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -9647,13 +9605,13 @@
         <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
@@ -9665,7 +9623,7 @@
         <v>683</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -9679,25 +9637,25 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>109</v>
+        <v>163</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>683</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -9711,25 +9669,25 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>683</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -9743,13 +9701,13 @@
         <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
@@ -9758,10 +9716,10 @@
         <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -9775,13 +9733,13 @@
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
@@ -9790,10 +9748,10 @@
         <v>279</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -9813,7 +9771,7 @@
         <v>78</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>108</v>
@@ -9822,10 +9780,10 @@
         <v>248</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -9836,28 +9794,28 @@
         <v>69</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>731</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>734</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -9871,13 +9829,13 @@
         <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
@@ -9886,10 +9844,10 @@
         <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -9903,25 +9861,25 @@
         <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -10,28 +10,28 @@
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="든솔" sheetId="2" r:id="rId2"/>
     <sheet name="만영" sheetId="3" r:id="rId3"/>
-    <sheet name="빅딜" sheetId="4" r:id="rId4"/>
-    <sheet name="지존길드" sheetId="5" r:id="rId5"/>
-    <sheet name="따숨" sheetId="6" r:id="rId6"/>
-    <sheet name="바텀" sheetId="7" r:id="rId7"/>
+    <sheet name="지존길드" sheetId="4" r:id="rId4"/>
+    <sheet name="바텀" sheetId="5" r:id="rId5"/>
+    <sheet name="빅딜" sheetId="6" r:id="rId6"/>
+    <sheet name="따숨" sheetId="7" r:id="rId7"/>
     <sheet name="더위사냥" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">더위사냥!$A$1:$J$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">든솔!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">따숨!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">만영!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">바텀!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">빅딜!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">지존길드!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">따숨!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">만영!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">바텀!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">빅딜!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">지존길드!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2164" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2164" uniqueCount="737">
   <si>
     <t>guild_name</t>
   </si>
@@ -84,10 +84,10 @@
     <t>Scania 13</t>
   </si>
   <si>
-    <t>873</t>
-  </si>
-  <si>
-    <t>36위</t>
+    <t>883</t>
+  </si>
+  <si>
+    <t>35위</t>
   </si>
   <si>
     <t>Lv.9</t>
@@ -117,10 +117,10 @@
     <t>Scania 23</t>
   </si>
   <si>
-    <t>941</t>
-  </si>
-  <si>
-    <t>12위</t>
+    <t>951</t>
+  </si>
+  <si>
+    <t>14위</t>
   </si>
   <si>
     <t>29명</t>
@@ -138,6 +138,60 @@
     <t>2026.09.20</t>
   </si>
   <si>
+    <t>지존길드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A7%80%EC%A1%B4%EA%B8%B8%EB%93%9C</t>
+  </si>
+  <si>
+    <t>Scania 4</t>
+  </si>
+  <si>
+    <t>894</t>
+  </si>
+  <si>
+    <t>33위</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>4경 9428조 9087억 197만</t>
+  </si>
+  <si>
+    <t>지존길드 공지용 오픈채팅 필수참여입니다.</t>
+  </si>
+  <si>
+    <t>지존순찌</t>
+  </si>
+  <si>
+    <t>2026.09.21</t>
+  </si>
+  <si>
+    <t>바텀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%94%ED%85%80</t>
+  </si>
+  <si>
+    <t>Scania 29</t>
+  </si>
+  <si>
+    <t>910</t>
+  </si>
+  <si>
+    <t>16위</t>
+  </si>
+  <si>
+    <t>4경 7638조 4057억 173만</t>
+  </si>
+  <si>
+    <t>바텀에서 캐리하실분! (톡방필수)</t>
+  </si>
+  <si>
+    <t>딜폿</t>
+  </si>
+  <si>
     <t>빅딜</t>
   </si>
   <si>
@@ -147,10 +201,10 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>866</t>
-  </si>
-  <si>
-    <t>39위</t>
+    <t>876</t>
+  </si>
+  <si>
+    <t>40위</t>
   </si>
   <si>
     <t>5경 985조 128억 1537만</t>
@@ -162,36 +216,6 @@
     <t>자유이용껀</t>
   </si>
   <si>
-    <t>2026.09.21</t>
-  </si>
-  <si>
-    <t>지존길드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A7%80%EC%A1%B4%EA%B8%B8%EB%93%9C</t>
-  </si>
-  <si>
-    <t>Scania 4</t>
-  </si>
-  <si>
-    <t>883</t>
-  </si>
-  <si>
-    <t>30위</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>4경 9428조 9087억 197만</t>
-  </si>
-  <si>
-    <t>지존길드 공지용 오픈채팅 필수참여입니다.</t>
-  </si>
-  <si>
-    <t>지존순찌</t>
-  </si>
-  <si>
     <t>따숨</t>
   </si>
   <si>
@@ -201,10 +225,10 @@
     <t>Scania 3</t>
   </si>
   <si>
-    <t>936</t>
-  </si>
-  <si>
-    <t>40위</t>
+    <t>946</t>
+  </si>
+  <si>
+    <t>42위</t>
   </si>
   <si>
     <t>4경 3027조 2732억 9013만</t>
@@ -216,30 +240,6 @@
     <t>호르몬</t>
   </si>
   <si>
-    <t>바텀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%94%ED%85%80</t>
-  </si>
-  <si>
-    <t>Scania 29</t>
-  </si>
-  <si>
-    <t>892</t>
-  </si>
-  <si>
-    <t>16위</t>
-  </si>
-  <si>
-    <t>4경 7638조 4057억 173만</t>
-  </si>
-  <si>
-    <t>바텀에서 캐리하실분! (톡방필수)</t>
-  </si>
-  <si>
-    <t>딜폿</t>
-  </si>
-  <si>
     <t>더위사냥</t>
   </si>
   <si>
@@ -249,7 +249,7 @@
     <t>Scania 50</t>
   </si>
   <si>
-    <t>891</t>
+    <t>909</t>
   </si>
   <si>
     <t>4위</t>
@@ -363,7 +363,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>7478조 5755억 856만</t>
+    <t>7537조 836억 5059만</t>
   </si>
   <si>
     <t>5</t>
@@ -387,7 +387,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%84%EA%B5%AC</t>
   </si>
   <si>
-    <t>5795조 243억 391만</t>
+    <t>5813조 6035억 4073만</t>
   </si>
   <si>
     <t>7</t>
@@ -399,7 +399,7 @@
     <t>https://mgf.gg/contents/character.php?n=GOD%EB%82%A0%EB%91%90</t>
   </si>
   <si>
-    <t>5484조 2958억 3188만</t>
+    <t>5618조 2831억 6335만</t>
   </si>
   <si>
     <t>8</t>
@@ -414,12 +414,39 @@
     <t>112</t>
   </si>
   <si>
-    <t>4453조 691억 2403만</t>
+    <t>4764조 9443억 42만</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
+    <t>하찌바리이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B0%8C%EB%B0%94%EB%A6%AC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>3469조 7402억 7786만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>러브포티</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%B8%8C%ED%8F%AC%ED%8B%B0</t>
+  </si>
+  <si>
+    <t>3374조 9102억 7995만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>주요엘농산</t>
   </si>
   <si>
@@ -429,33 +456,6 @@
     <t>3372조 7251억 8925만</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>러브포티</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%B8%8C%ED%8F%AC%ED%8B%B0</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>3359조 9731억 5679만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>하찌바리이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B0%8C%EB%B0%94%EB%A6%AC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>3352조 3307억 2632만</t>
-  </si>
-  <si>
     <t>12</t>
   </si>
   <si>
@@ -525,7 +525,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>2134조 7264억 6794만</t>
+    <t>2140조 472억 1466만</t>
   </si>
   <si>
     <t>17</t>
@@ -561,7 +561,7 @@
     <t>https://mgf.gg/contents/character.php?n=v%EB%B0%95%ED%9A%A8%EC%8B%A0v</t>
   </si>
   <si>
-    <t>1339조 4695억 4612만</t>
+    <t>1383조 4073억 6000만</t>
   </si>
   <si>
     <t>20</t>
@@ -618,7 +618,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
   </si>
   <si>
-    <t>1062조 6693억 5639만</t>
+    <t>1104조 386억 5983만</t>
   </si>
   <si>
     <t>24</t>
@@ -630,7 +630,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%9C%BC%EB%86%8D</t>
   </si>
   <si>
-    <t>992조 4375억 6722만</t>
+    <t>1065조 6768억 9164만</t>
   </si>
   <si>
     <t>25</t>
@@ -672,7 +672,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>613조 4694억 3249만</t>
+    <t>654조 3071억 5615만</t>
   </si>
   <si>
     <t>28</t>
@@ -696,13 +696,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%8A%94%EB%B0%B0%EB%B6%88%EB%9F%AC%EC%9A%94</t>
   </si>
   <si>
-    <t>502조 1728억 9075만</t>
+    <t>509조 8552억 8334만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EA%B8%B0%EC%9C%A0%EB%AC%B4</t>
   </si>
   <si>
-    <t>1경 3234조 1846억 692만</t>
+    <t>1경 3469조 465억 1587만</t>
   </si>
   <si>
     <t>무곽</t>
@@ -723,7 +723,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%95%ED%8C%A1%ED%8C%A1%EC%9D%B4</t>
   </si>
   <si>
-    <t>5214조 4616억 1127만</t>
+    <t>5421조 8420억 8만</t>
+  </si>
+  <si>
+    <t>2번째캐릭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=2%EB%B2%88%EC%A7%B8%EC%BA%90%EB%A6%AD</t>
+  </si>
+  <si>
+    <t>3757조 3831억 1657만</t>
   </si>
   <si>
     <t>붉은모자</t>
@@ -732,16 +741,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%89%EC%9D%80%EB%AA%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>3716조 2349억 9071만</t>
-  </si>
-  <si>
-    <t>2번째캐릭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=2%EB%B2%88%EC%A7%B8%EC%BA%90%EB%A6%AD</t>
-  </si>
-  <si>
-    <t>3715조 6465억 812만</t>
+    <t>3716조 7347억 5296만</t>
   </si>
   <si>
     <t>장뱁새</t>
@@ -750,16 +750,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B1%81%EC%83%88</t>
   </si>
   <si>
-    <t>3493조 726억 9027만</t>
-  </si>
-  <si>
-    <t>히테라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%85%8C%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>3458조 4117억 9738만</t>
+    <t>3515조 9941억 5767만</t>
   </si>
   <si>
     <t>꽁꽁냉법</t>
@@ -768,7 +759,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EA%BD%81%EB%83%89%EB%B2%95</t>
   </si>
   <si>
-    <t>2621조 4316억 1142만</t>
+    <t>2626조 5073억 8510만</t>
   </si>
   <si>
     <t>테토일남</t>
@@ -780,7 +771,7 @@
     <t>다크나이트</t>
   </si>
   <si>
-    <t>2514조 7331억 505만</t>
+    <t>2556조 134억 3692만</t>
   </si>
   <si>
     <t>뚜기파파</t>
@@ -807,7 +798,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%A5%AC%EB%A5%B4</t>
   </si>
   <si>
-    <t>1634조 4438억 7950만</t>
+    <t>1661조 5880억 9788만</t>
   </si>
   <si>
     <t>초앤</t>
@@ -816,7 +807,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%95%A4</t>
   </si>
   <si>
-    <t>1624조 6840억 4543만</t>
+    <t>1630조 3439억 1814만</t>
   </si>
   <si>
     <t>재미있게놀래</t>
@@ -825,7 +816,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EB%AF%B8%EC%9E%88%EA%B2%8C%EB%86%80%EB%9E%98</t>
   </si>
   <si>
-    <t>1387조 5077억 7016만</t>
+    <t>1392조 5593억 9126만</t>
   </si>
   <si>
     <t>가덴</t>
@@ -834,7 +825,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%8D%B4</t>
   </si>
   <si>
-    <t>1342조 5953억 2254만</t>
+    <t>1381조 775억 6791만</t>
+  </si>
+  <si>
+    <t>33세배장호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=33%EC%84%B8%EB%B0%B0%EC%9E%A5%ED%98%B8</t>
+  </si>
+  <si>
+    <t>1370조 349억 8666만</t>
   </si>
   <si>
     <t>빙율</t>
@@ -846,22 +846,13 @@
     <t>1314조 7187억 8022만</t>
   </si>
   <si>
-    <t>33세배장호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=33%EC%84%B8%EB%B0%B0%EC%9E%A5%ED%98%B8</t>
-  </si>
-  <si>
-    <t>1261조 3167억 8788만</t>
-  </si>
-  <si>
     <t>적젹적</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%81%EC%A0%B9%EC%A0%81</t>
   </si>
   <si>
-    <t>1243조 5020억 7126만</t>
+    <t>1246조 3736억 6450만</t>
   </si>
   <si>
     <t>최빵쭈</t>
@@ -882,7 +873,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%A4%BD</t>
   </si>
   <si>
-    <t>909조 5942억 1194만</t>
+    <t>938조 3323억 3393만</t>
   </si>
   <si>
     <t>정기휴므</t>
@@ -909,7 +900,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%ED%99%A9%EC%83%88</t>
   </si>
   <si>
-    <t>759조 9478억 7922만</t>
+    <t>760조 4377억 7091만</t>
   </si>
   <si>
     <t>저기휴무</t>
@@ -927,7 +918,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%AC%EC%83%B7</t>
   </si>
   <si>
-    <t>635조 5234억 8915만</t>
+    <t>639조 5314억 3480만</t>
   </si>
   <si>
     <t>박도란</t>
@@ -945,7 +936,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
   </si>
   <si>
-    <t>546조 4316억 58만</t>
+    <t>547조 7047억 3326만</t>
   </si>
   <si>
     <t>뿌앵뿌앵</t>
@@ -963,22 +954,538 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%ED%99%8D%EC%9D%B4</t>
   </si>
   <si>
-    <t>366조 5656억 4392만</t>
+    <t>367조 2308억 5887만</t>
+  </si>
+  <si>
+    <t>윤빵쭈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EB%B9%B5%EC%AD%88</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>309조 4737억 1028만</t>
+  </si>
+  <si>
+    <t>지존쫀파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>9961조 4670억 6144만</t>
+  </si>
+  <si>
+    <t>수텍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%ED%85%8D</t>
+  </si>
+  <si>
+    <t>7731조 8382억 7567만</t>
+  </si>
+  <si>
+    <t>포항엄석대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
+  </si>
+  <si>
+    <t>4565조 7703억 9896만</t>
+  </si>
+  <si>
+    <t>협의</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%91%EC%9D%98</t>
+  </si>
+  <si>
+    <t>4402조 1032억 4015만</t>
+  </si>
+  <si>
+    <t>타개</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
+  </si>
+  <si>
+    <t>3724조 5498억 5962만</t>
+  </si>
+  <si>
+    <t>기뽐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%BD%90</t>
+  </si>
+  <si>
+    <t>3303조 6174억 3840만</t>
+  </si>
+  <si>
+    <t>댜니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>2886조 9873억 5134만</t>
+  </si>
+  <si>
+    <t>포항가자미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>2601조 9210억 8658만</t>
+  </si>
+  <si>
+    <t>뿡쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
+  </si>
+  <si>
+    <t>2537조 271억 3333만</t>
+  </si>
+  <si>
+    <t>지존빼앙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
+  </si>
+  <si>
+    <t>2515조 2382억 6614만</t>
+  </si>
+  <si>
+    <t>변신술사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
+  </si>
+  <si>
+    <t>2465조 3877억 3257만</t>
+  </si>
+  <si>
+    <t>온백</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
+  </si>
+  <si>
+    <t>2349조 265억 3189만</t>
+  </si>
+  <si>
+    <t>엘르가든</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
+  </si>
+  <si>
+    <t>2313조 7071억 7362만</t>
+  </si>
+  <si>
+    <t>파울</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
+  </si>
+  <si>
+    <t>1901조 6768억 6078만</t>
+  </si>
+  <si>
+    <t>마카롱롱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
+  </si>
+  <si>
+    <t>1889조 8524억 3410만</t>
+  </si>
+  <si>
+    <t>대좀이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1495조 1977억 19만</t>
+  </si>
+  <si>
+    <t>모짜리코베르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>1383조 7789억 8243만</t>
+  </si>
+  <si>
+    <t>오옹나이스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%B9%EB%82%98%EC%9D%B4%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>1379조 1810억 4031만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
+  </si>
+  <si>
+    <t>1319조 631억 7399만</t>
+  </si>
+  <si>
+    <t>마갤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
+  </si>
+  <si>
+    <t>1227조 5969억 4490만</t>
+  </si>
+  <si>
+    <t>김허덕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
+  </si>
+  <si>
+    <t>1206조 1272억 7177만</t>
+  </si>
+  <si>
+    <t>짱잘자쿨냥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%9E%98%EC%9E%90%EC%BF%A8%EB%83%A5</t>
+  </si>
+  <si>
+    <t>1149조 8047억 287만</t>
+  </si>
+  <si>
+    <t>기본이리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1144조 139억 6724만</t>
+  </si>
+  <si>
+    <t>냐은</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EC%9D%80</t>
+  </si>
+  <si>
+    <t>1087조 8953억 2222만</t>
+  </si>
+  <si>
+    <t>전산봉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%B0%EB%B4%89</t>
+  </si>
+  <si>
+    <t>1062조 2713억 1289만</t>
+  </si>
+  <si>
+    <t>고숨도칭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
+  </si>
+  <si>
+    <t>892조 2063억 3717만</t>
+  </si>
+  <si>
+    <t>태코찡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
+  </si>
+  <si>
+    <t>852조 6312억 8197만</t>
+  </si>
+  <si>
+    <t>Doham</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Doham</t>
+  </si>
+  <si>
+    <t>824조 940억 8761만</t>
+  </si>
+  <si>
+    <t>유플러스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%94%8C%EB%9F%AC%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>649조 5527억 6316만</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>윤빵쭈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EB%B9%B5%EC%AD%88</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>283조 3014억 3900만</t>
+    <t>빵후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%ED%9B%84</t>
+  </si>
+  <si>
+    <t>355조 5297억 5157만</t>
+  </si>
+  <si>
+    <t>전액할부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%95%A1%ED%95%A0%EB%B6%80</t>
+  </si>
+  <si>
+    <t>1경 2872조 7013억 2041만</t>
+  </si>
+  <si>
+    <t>사랑향</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%96%A5</t>
+  </si>
+  <si>
+    <t>9930조 6490억 2812만</t>
+  </si>
+  <si>
+    <t>례전</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%80%EC%A0%84</t>
+  </si>
+  <si>
+    <t>4565조 3068억 6482만</t>
+  </si>
+  <si>
+    <t>숭타이준</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%ED%83%80%EC%9D%B4%EC%A4%80</t>
+  </si>
+  <si>
+    <t>3793조 2729억 2175만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%9C%ED%8F%BF</t>
+  </si>
+  <si>
+    <t>2598조 7115억 1793만</t>
+  </si>
+  <si>
+    <t>뻑걸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%91%EA%B1%B8</t>
+  </si>
+  <si>
+    <t>2430조 2751억 4025만</t>
+  </si>
+  <si>
+    <t>지존빵수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%B5%EC%88%98</t>
+  </si>
+  <si>
+    <t>2349조 4168억 2105만</t>
+  </si>
+  <si>
+    <t>야키산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%82%A4%EC%82%B0</t>
+  </si>
+  <si>
+    <t>2340조 2137억 7570만</t>
+  </si>
+  <si>
+    <t>탱폿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%8F%BF</t>
+  </si>
+  <si>
+    <t>2109조 1360억 8174만</t>
+  </si>
+  <si>
+    <t>문제적남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EC%A0%9C%EC%A0%81%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>1997조 2870억 868만</t>
+  </si>
+  <si>
+    <t>뮬이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AE%AC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1849조 6243억 90만</t>
+  </si>
+  <si>
+    <t>아이리쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EB%A6%AC%EC%89%AC</t>
+  </si>
+  <si>
+    <t>1839조 8251억 1365만</t>
+  </si>
+  <si>
+    <t>화둥에불낸년</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EB%91%A5%EC%97%90%EB%B6%88%EB%82%B8%EB%85%84</t>
+  </si>
+  <si>
+    <t>1819조 1559억 3691만</t>
+  </si>
+  <si>
+    <t>독스케</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%8A%A4%EC%BC%80</t>
+  </si>
+  <si>
+    <t>1356조 2214억 186만</t>
+  </si>
+  <si>
+    <t>우즈2텐겐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%A6%882%ED%85%90%EA%B2%90</t>
+  </si>
+  <si>
+    <t>1317조 4439억 6807만</t>
+  </si>
+  <si>
+    <t>이게용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B2%8C%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>1077조 4898억 5524만</t>
+  </si>
+  <si>
+    <t>우월별하</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9B%94%EB%B3%84%ED%95%98</t>
+  </si>
+  <si>
+    <t>1032조 7712억 9061만</t>
+  </si>
+  <si>
+    <t>기똥찬벌레</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%98%A5%EC%B0%AC%EB%B2%8C%EB%A0%88</t>
+  </si>
+  <si>
+    <t>1031조 4047억 5773만</t>
+  </si>
+  <si>
+    <t>구도류</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%8F%84%EB%A5%98</t>
+  </si>
+  <si>
+    <t>1020조 6439억 2084만</t>
+  </si>
+  <si>
+    <t>매화로이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%ED%99%94%EB%A1%9C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1010조 4076억 8841만</t>
+  </si>
+  <si>
+    <t>JJuna</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=JJuna</t>
+  </si>
+  <si>
+    <t>939조 2803억 6578만</t>
+  </si>
+  <si>
+    <t>난센</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EC%84%BC</t>
+  </si>
+  <si>
+    <t>798조 3691억 7640만</t>
+  </si>
+  <si>
+    <t>에프람</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%ED%94%84%EB%9E%8C</t>
+  </si>
+  <si>
+    <t>796조 3154억 1093만</t>
+  </si>
+  <si>
+    <t>콜리셰마드르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%9C%EB%A6%AC%EC%85%B0%EB%A7%88%EB%93%9C%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>779조 4483억 3378만</t>
+  </si>
+  <si>
+    <t>유채아버지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%B1%84%EC%95%84%EB%B2%84%EC%A7%80</t>
+  </si>
+  <si>
+    <t>670조 9011억 2995만</t>
+  </si>
+  <si>
+    <t>조단23</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%8B%A823</t>
+  </si>
+  <si>
+    <t>667조 7732억 1410만</t>
+  </si>
+  <si>
+    <t>아콩린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BD%A9%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>567조 831억 836만</t>
+  </si>
+  <si>
+    <t>별루루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A3%A8%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>520조 3064억 1208만</t>
   </si>
   <si>
     <t>아이스꾸임</t>
@@ -987,7 +1494,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
   </si>
   <si>
-    <t>2경 321조 1980억 8092만</t>
+    <t>2경 374조 8201억 5764만</t>
   </si>
   <si>
     <t>굴러가는일상</t>
@@ -1005,7 +1512,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
   </si>
   <si>
-    <t>5059조 4008억 4197만</t>
+    <t>5067조 550억 6840만</t>
   </si>
   <si>
     <t>흑두부</t>
@@ -1014,7 +1521,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>4261조 8121억 2145만</t>
+    <t>4269조 1039억 8746만</t>
   </si>
   <si>
     <t>대방어조아</t>
@@ -1023,7 +1530,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>3924조 2536억 9340만</t>
+    <t>4145조 5731억 3307만</t>
   </si>
   <si>
     <t>서포터즈</t>
@@ -1032,7 +1539,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>2971조 3297억 316만</t>
+    <t>3109조 5410억 3413만</t>
   </si>
   <si>
     <t>야가다</t>
@@ -1044,10 +1551,19 @@
     <t>2586조 1679억 2303만</t>
   </si>
   <si>
+    <t>뻥뻥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
+  </si>
+  <si>
+    <t>2486조 1038억 1649만</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
   </si>
   <si>
-    <t>2301조 7318억 5637만</t>
+    <t>2422조 114억 1172만</t>
   </si>
   <si>
     <t>KR#TAKIN9CP37</t>
@@ -1056,16 +1572,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>2224조 2393억 3922만</t>
-  </si>
-  <si>
-    <t>뻥뻥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
-  </si>
-  <si>
-    <t>2043조 9656억 4336만</t>
+    <t>2247조 5088억 7013만</t>
   </si>
   <si>
     <t>불보독지</t>
@@ -1074,7 +1581,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
   </si>
   <si>
-    <t>1330조 9299억 4958만</t>
+    <t>1339조 3325억 1781만</t>
+  </si>
+  <si>
+    <t>우후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
+  </si>
+  <si>
+    <t>1214조 8117억 7531만</t>
+  </si>
+  <si>
+    <t>호우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>1154조 5842억 8701만</t>
   </si>
   <si>
     <t>단풍카우</t>
@@ -1086,31 +1611,13 @@
     <t>1139조 3354억 3997만</t>
   </si>
   <si>
-    <t>호우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>1124조 2763억 6571만</t>
-  </si>
-  <si>
-    <t>우후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
-  </si>
-  <si>
-    <t>1109조 9165억 9489만</t>
-  </si>
-  <si>
     <t>채무조정</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
   </si>
   <si>
-    <t>1081조 8986억 458만</t>
+    <t>1082조 2012억 4397만</t>
   </si>
   <si>
     <t>뽀송히</t>
@@ -1119,7 +1626,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
   </si>
   <si>
-    <t>1050조 6657억 3307만</t>
+    <t>1065조 4129억 9767만</t>
   </si>
   <si>
     <t>좀치는형님</t>
@@ -1128,7 +1635,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
   </si>
   <si>
-    <t>1035조 3847억 2058만</t>
+    <t>1044조 7501억 1470만</t>
   </si>
   <si>
     <t>정태준</t>
@@ -1137,7 +1644,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
   </si>
   <si>
-    <t>972조 152억 3118만</t>
+    <t>974조 8229억 1308만</t>
   </si>
   <si>
     <t>라탱호</t>
@@ -1146,7 +1653,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%ED%83%B1%ED%98%B8</t>
   </si>
   <si>
-    <t>881조 7556억 9106만</t>
+    <t>924조 4741억 2884만</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -1155,7 +1662,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>789조 2546억 9378만</t>
+    <t>792조 9853억 5939만</t>
   </si>
   <si>
     <t>짤똘</t>
@@ -1164,7 +1671,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%A4%EB%98%98</t>
   </si>
   <si>
-    <t>671조 9525억 1752만</t>
+    <t>789조 1148억 491만</t>
   </si>
   <si>
     <t>팡대지</t>
@@ -1173,7 +1680,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
   </si>
   <si>
-    <t>575조 1653억 9478만</t>
+    <t>633조 4865억 8284만</t>
   </si>
   <si>
     <t>박준우2</t>
@@ -1191,7 +1698,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>559조 1192억 5788만</t>
+    <t>560조 2034억 59만</t>
+  </si>
+  <si>
+    <t>컨덱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A8%EB%8D%B1</t>
+  </si>
+  <si>
+    <t>541조 1466억 9068만</t>
   </si>
   <si>
     <t>솔인</t>
@@ -1200,7 +1716,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
   </si>
   <si>
-    <t>468조 4891억 849만</t>
+    <t>491조 909억 6019만</t>
+  </si>
+  <si>
+    <t>3030</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=3030</t>
+  </si>
+  <si>
+    <t>412조 6404억 5230만</t>
   </si>
   <si>
     <t>아르미느</t>
@@ -1209,7 +1734,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>338조 1338억 8268만</t>
+    <t>342조 6836억 897만</t>
   </si>
   <si>
     <t>여눈</t>
@@ -1230,273 +1755,6 @@
     <t>275조 6869억 3523만</t>
   </si>
   <si>
-    <t>지존쫀파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>9888조 9654억 14만</t>
-  </si>
-  <si>
-    <t>수텍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%ED%85%8D</t>
-  </si>
-  <si>
-    <t>7731조 8382억 7567만</t>
-  </si>
-  <si>
-    <t>포항엄석대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
-  </si>
-  <si>
-    <t>4544조 7861억 2132만</t>
-  </si>
-  <si>
-    <t>협의</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%91%EC%9D%98</t>
-  </si>
-  <si>
-    <t>4402조 1032억 4015만</t>
-  </si>
-  <si>
-    <t>타개</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
-  </si>
-  <si>
-    <t>3694조 4730억 5673만</t>
-  </si>
-  <si>
-    <t>기뽐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%BD%90</t>
-  </si>
-  <si>
-    <t>3303조 6174억 3840만</t>
-  </si>
-  <si>
-    <t>댜니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>2884조 3838억 7409만</t>
-  </si>
-  <si>
-    <t>포항가자미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>2585조 8424억 4496만</t>
-  </si>
-  <si>
-    <t>뿡쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
-  </si>
-  <si>
-    <t>2533조 6647억 4576만</t>
-  </si>
-  <si>
-    <t>지존빼앙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
-  </si>
-  <si>
-    <t>2515조 2382억 6614만</t>
-  </si>
-  <si>
-    <t>변신술사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
-  </si>
-  <si>
-    <t>2465조 3877억 3257만</t>
-  </si>
-  <si>
-    <t>온백</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
-  </si>
-  <si>
-    <t>2338조 5666억 805만</t>
-  </si>
-  <si>
-    <t>엘르가든</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
-  </si>
-  <si>
-    <t>2313조 7071억 7362만</t>
-  </si>
-  <si>
-    <t>파울</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
-  </si>
-  <si>
-    <t>1901조 6768억 6078만</t>
-  </si>
-  <si>
-    <t>마카롱롱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
-  </si>
-  <si>
-    <t>1889조 8524억 3410만</t>
-  </si>
-  <si>
-    <t>대좀이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1488조 1251억 1121만</t>
-  </si>
-  <si>
-    <t>오옹나이스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%B9%EB%82%98%EC%9D%B4%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>1379조 1810억 4031만</t>
-  </si>
-  <si>
-    <t>모짜리코베르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>1378조 9632억 3810만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
-  </si>
-  <si>
-    <t>1319조 631억 7399만</t>
-  </si>
-  <si>
-    <t>김허덕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
-  </si>
-  <si>
-    <t>1206조 1272억 7177만</t>
-  </si>
-  <si>
-    <t>마갤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
-  </si>
-  <si>
-    <t>1200조 1472억 1769만</t>
-  </si>
-  <si>
-    <t>짱잘자쿨냥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%9E%98%EC%9E%90%EC%BF%A8%EB%83%A5</t>
-  </si>
-  <si>
-    <t>1149조 8047억 287만</t>
-  </si>
-  <si>
-    <t>기본이리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1128조 1572억 135만</t>
-  </si>
-  <si>
-    <t>냐은</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EC%9D%80</t>
-  </si>
-  <si>
-    <t>1068조 2571억 1131만</t>
-  </si>
-  <si>
-    <t>전산봉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%B0%EB%B4%89</t>
-  </si>
-  <si>
-    <t>1019조 5372억 3078만</t>
-  </si>
-  <si>
-    <t>고숨도칭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
-  </si>
-  <si>
-    <t>879조 345억 6976만</t>
-  </si>
-  <si>
-    <t>태코찡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
-  </si>
-  <si>
-    <t>850조 4940억 4514만</t>
-  </si>
-  <si>
-    <t>Doham</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Doham</t>
-  </si>
-  <si>
-    <t>822조 168억 4984만</t>
-  </si>
-  <si>
-    <t>유플러스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%94%8C%EB%9F%AC%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>649조 5527억 6316만</t>
-  </si>
-  <si>
-    <t>빵후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%ED%9B%84</t>
-  </si>
-  <si>
-    <t>355조 5297억 5157만</t>
-  </si>
-  <si>
     <t>꺄꽁</t>
   </si>
   <si>
@@ -1524,6 +1782,12 @@
     <t>4939조 5954억 5774만</t>
   </si>
   <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A5%B4%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>4495조 3986억 4568만</t>
+  </si>
+  <si>
     <t>낭만황금망치</t>
   </si>
   <si>
@@ -1533,19 +1797,13 @@
     <t>4225조 3118억 1638만</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A5%B4%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>4208조 8898억 7771만</t>
-  </si>
-  <si>
     <t>김슴줌1</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%8A%B4%EC%A4%8C1</t>
   </si>
   <si>
-    <t>3765조 1886억 2045만</t>
+    <t>3803조 9933억 2656만</t>
   </si>
   <si>
     <t>천달</t>
@@ -1563,7 +1821,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%9C%EC%9A%A9</t>
   </si>
   <si>
-    <t>2743조 9212억 5191만</t>
+    <t>3037조 886억 2134만</t>
   </si>
   <si>
     <t>호두와감자</t>
@@ -1599,7 +1857,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%EB%A0%AC%EA%B3%B0</t>
   </si>
   <si>
-    <t>1106조 9910억 8653만</t>
+    <t>1153조 760억 2019만</t>
   </si>
   <si>
     <t>별곡</t>
@@ -1617,7 +1875,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%84%8Dol</t>
   </si>
   <si>
-    <t>989조 1144억 7869만</t>
+    <t>990조 7766억 5895만</t>
   </si>
   <si>
     <t>동래</t>
@@ -1626,7 +1884,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%9E%98</t>
   </si>
   <si>
-    <t>968조 7399억 9311만</t>
+    <t>973조 5531억 361만</t>
   </si>
   <si>
     <t>까쿠미</t>
@@ -1653,7 +1911,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A4</t>
   </si>
   <si>
-    <t>845조 4777억 7201만</t>
+    <t>855조 3774억 7726만</t>
   </si>
   <si>
     <t>띠우</t>
@@ -1662,7 +1920,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%A0%EC%9A%B0</t>
   </si>
   <si>
-    <t>725조 2731억 3447만</t>
+    <t>735조 7344억 4695만</t>
   </si>
   <si>
     <t>쿠까미</t>
@@ -1689,7 +1947,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%81%84%EC%B1%B0</t>
   </si>
   <si>
-    <t>479조 7098억 5560만</t>
+    <t>528조 8805억 3793만</t>
+  </si>
+  <si>
+    <t>왕단단이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EB%8B%A8%EB%8B%A8%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>484조 9630억 1552만</t>
   </si>
   <si>
     <t>08217</t>
@@ -1710,22 +1977,13 @@
     <t>451조 854억 6819만</t>
   </si>
   <si>
-    <t>왕단단이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EB%8B%A8%EB%8B%A8%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>439조 6821억 4352만</t>
-  </si>
-  <si>
     <t>루이쥔</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%9D%B4%EC%A5%94</t>
   </si>
   <si>
-    <t>403조 7730억 6533만</t>
+    <t>414조 8166억 3897만</t>
   </si>
   <si>
     <t>택Ol</t>
@@ -1734,7 +1992,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9DOl</t>
   </si>
   <si>
-    <t>349조 6925억 3741만</t>
+    <t>350조 223억 2730만</t>
   </si>
   <si>
     <t>툼스데이</t>
@@ -1752,265 +2010,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EA%B0%B8%EB%A4%BC</t>
   </si>
   <si>
-    <t>167조 3030억 3553만</t>
-  </si>
-  <si>
-    <t>꾸현</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%ED%98%84</t>
-  </si>
-  <si>
-    <t>89조 2810억 5186만</t>
-  </si>
-  <si>
-    <t>전액할부</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%95%A1%ED%95%A0%EB%B6%80</t>
-  </si>
-  <si>
-    <t>1경 2872조 7013억 2041만</t>
-  </si>
-  <si>
-    <t>사랑향</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%96%A5</t>
-  </si>
-  <si>
-    <t>9873조 1430억 5286만</t>
-  </si>
-  <si>
-    <t>례전</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%80%EC%A0%84</t>
-  </si>
-  <si>
-    <t>4565조 3068억 6482만</t>
-  </si>
-  <si>
-    <t>숭타이준</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%ED%83%80%EC%9D%B4%EC%A4%80</t>
-  </si>
-  <si>
-    <t>3714조 5791억 7385만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%9C%ED%8F%BF</t>
-  </si>
-  <si>
-    <t>2598조 7115억 1793만</t>
-  </si>
-  <si>
-    <t>뻑걸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%91%EA%B1%B8</t>
-  </si>
-  <si>
-    <t>2413조 2862억 6442만</t>
-  </si>
-  <si>
-    <t>지존빵수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%B5%EC%88%98</t>
-  </si>
-  <si>
-    <t>2321조 2333억 3182만</t>
-  </si>
-  <si>
-    <t>문제적남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EC%A0%9C%EC%A0%81%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>1997조 2870억 868만</t>
-  </si>
-  <si>
-    <t>탱폿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%8F%BF</t>
-  </si>
-  <si>
-    <t>1888조 1422억 7967만</t>
-  </si>
-  <si>
-    <t>뮬이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AE%AC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1849조 6243억 90만</t>
-  </si>
-  <si>
-    <t>아이리쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EB%A6%AC%EC%89%AC</t>
-  </si>
-  <si>
-    <t>1839조 8251억 1365만</t>
-  </si>
-  <si>
-    <t>화둥에불낸년</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EB%91%A5%EC%97%90%EB%B6%88%EB%82%B8%EB%85%84</t>
-  </si>
-  <si>
-    <t>1819조 1559억 3691만</t>
-  </si>
-  <si>
-    <t>야키산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%82%A4%EC%82%B0</t>
-  </si>
-  <si>
-    <t>1774조 331억 3651만</t>
-  </si>
-  <si>
-    <t>독스케</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%8A%A4%EC%BC%80</t>
-  </si>
-  <si>
-    <t>1352조 6582억 9239만</t>
-  </si>
-  <si>
-    <t>우즈2텐겐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%A6%882%ED%85%90%EA%B2%90</t>
-  </si>
-  <si>
-    <t>1317조 4439억 6807만</t>
-  </si>
-  <si>
-    <t>이게용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B2%8C%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>1077조 4898억 5524만</t>
-  </si>
-  <si>
-    <t>우월별하</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9B%94%EB%B3%84%ED%95%98</t>
-  </si>
-  <si>
-    <t>1032조 7712억 9061만</t>
-  </si>
-  <si>
-    <t>구도류</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%8F%84%EB%A5%98</t>
-  </si>
-  <si>
-    <t>1020조 6439억 2084만</t>
-  </si>
-  <si>
-    <t>매화로이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%ED%99%94%EB%A1%9C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1010조 4076억 8841만</t>
-  </si>
-  <si>
-    <t>기똥찬벌레</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%98%A5%EC%B0%AC%EB%B2%8C%EB%A0%88</t>
-  </si>
-  <si>
-    <t>998조 5197억 7663만</t>
-  </si>
-  <si>
-    <t>JJuna</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=JJuna</t>
-  </si>
-  <si>
-    <t>936조 4240억 6417만</t>
-  </si>
-  <si>
-    <t>난센</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EC%84%BC</t>
-  </si>
-  <si>
-    <t>797조 8464억 6504만</t>
-  </si>
-  <si>
-    <t>에프람</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%ED%94%84%EB%9E%8C</t>
-  </si>
-  <si>
-    <t>795조 2999억 6288만</t>
-  </si>
-  <si>
-    <t>콜리셰마드르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%9C%EB%A6%AC%EC%85%B0%EB%A7%88%EB%93%9C%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>778조 3878억 4322만</t>
-  </si>
-  <si>
-    <t>유채아버지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%B1%84%EC%95%84%EB%B2%84%EC%A7%80</t>
-  </si>
-  <si>
-    <t>670조 9011억 2995만</t>
-  </si>
-  <si>
-    <t>조단23</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%8B%A823</t>
-  </si>
-  <si>
-    <t>667조 7732억 1410만</t>
-  </si>
-  <si>
-    <t>아콩린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BD%A9%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>567조 831억 836만</t>
-  </si>
-  <si>
-    <t>별루루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A3%A8%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>513조 4329억 1903만</t>
+    <t>168조 5059억 2996만</t>
   </si>
   <si>
     <t>교주만두</t>
@@ -2049,10 +2049,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EA%B5%AC%EB%82%A8%EC%84%B1</t>
   </si>
   <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>80조 5817억 7403만</t>
+    <t>82조 2455억 9709만</t>
   </si>
   <si>
     <t>코잉코잉</t>
@@ -2064,7 +2061,16 @@
     <t>105</t>
   </si>
   <si>
-    <t>56조 9863억 3123만</t>
+    <t>63조 2334억 7566만</t>
+  </si>
+  <si>
+    <t>오스띤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%8A%A4%EB%9D%A4</t>
+  </si>
+  <si>
+    <t>60조 1221억 2441만</t>
   </si>
   <si>
     <t>토벤숍이</t>
@@ -2073,7 +2079,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%B2%A4%EC%88%8D%EC%9D%B4</t>
   </si>
   <si>
-    <t>53조 7183억 6678만</t>
+    <t>54조 1795억 9515만</t>
   </si>
   <si>
     <t>낭랑28세</t>
@@ -2088,22 +2094,13 @@
     <t>53조 5707억 3136만</t>
   </si>
   <si>
-    <t>오스띤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%8A%A4%EB%9D%A4</t>
-  </si>
-  <si>
-    <t>47조 5727억 92만</t>
-  </si>
-  <si>
     <t>빵신궁</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EC%8B%A0%EA%B6%81</t>
   </si>
   <si>
-    <t>42조 3794억 7995만</t>
+    <t>42조 5176억 8210만</t>
   </si>
   <si>
     <t>썬콜우체국</t>
@@ -2115,7 +2112,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>35조 905억 9156만</t>
+    <t>35조 1910억 811만</t>
   </si>
   <si>
     <t>밀초크코</t>
@@ -2124,7 +2121,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%EC%B4%88%ED%81%AC%EC%BD%94</t>
   </si>
   <si>
-    <t>32조 1651억 7516만</t>
+    <t>34조 2125억 4874만</t>
+  </si>
+  <si>
+    <t>킬혁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%AC%ED%98%81</t>
+  </si>
+  <si>
+    <t>31조 8417억 1019만</t>
   </si>
   <si>
     <t>고통받는갈비</t>
@@ -2142,16 +2148,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%82%A4%EB%A7%9B%ED%82%A4%EB%A7%88</t>
   </si>
   <si>
-    <t>30조 4248억 9041만</t>
-  </si>
-  <si>
-    <t>킬혁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%AC%ED%98%81</t>
-  </si>
-  <si>
-    <t>28조 916억 22만</t>
+    <t>30조 4349억 5953만</t>
   </si>
   <si>
     <t>문보겨엉</t>
@@ -2166,6 +2163,15 @@
     <t>26조 6167억 1779만</t>
   </si>
   <si>
+    <t>땡요나퐁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%95%A1%EC%9A%94%EB%82%98%ED%90%81</t>
+  </si>
+  <si>
+    <t>25조 7434억 2413만</t>
+  </si>
+  <si>
     <t>배렛나루왁서</t>
   </si>
   <si>
@@ -2184,15 +2190,6 @@
     <t>24조 5393억 7309만</t>
   </si>
   <si>
-    <t>땡요나퐁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%95%A1%EC%9A%94%EB%82%98%ED%90%81</t>
-  </si>
-  <si>
-    <t>24조 4450억 3191만</t>
-  </si>
-  <si>
     <t>페프릭2</t>
   </si>
   <si>
@@ -2208,7 +2205,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%94%94%EC%BC%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>12조 9292억 7540만</t>
+    <t>17조 2732억 7149만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%ED%82%A4%EB%B9%84%ED%82%A4</t>
@@ -2235,7 +2232,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%88%EC%9D%8C</t>
   </si>
   <si>
-    <t>4조 3884억 1717만</t>
+    <t>4조 4122억 7297만</t>
   </si>
   <si>
     <t>닝윤</t>
@@ -2772,48 +2769,48 @@
         <v>19</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>50</v>
@@ -2825,7 +2822,7 @@
         <v>52</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2854,7 +2851,7 @@
         <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>58</v>
@@ -2866,7 +2863,7 @@
         <v>60</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2895,7 +2892,7 @@
         <v>19</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>66</v>
@@ -2907,7 +2904,7 @@
         <v>68</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -3292,10 +3289,10 @@
         <v>103</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3306,16 +3303,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -3324,7 +3321,7 @@
         <v>91</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>136</v>
@@ -3356,7 +3353,7 @@
         <v>103</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>140</v>
@@ -3388,7 +3385,7 @@
         <v>144</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>145</v>
@@ -3420,7 +3417,7 @@
         <v>103</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>149</v>
@@ -3484,7 +3481,7 @@
         <v>103</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>159</v>
@@ -3980,7 +3977,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4141,10 +4138,10 @@
         <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>190</v>
+        <v>109</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>233</v>
@@ -4173,10 +4170,10 @@
         <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>109</v>
+        <v>190</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>236</v>
@@ -4208,7 +4205,7 @@
         <v>91</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>239</v>
@@ -4237,10 +4234,10 @@
         <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>242</v>
@@ -4269,13 +4266,13 @@
         <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -4289,22 +4286,22 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>248</v>
+        <v>91</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>249</v>
@@ -4318,7 +4315,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>250</v>
@@ -4333,10 +4330,10 @@
         <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>252</v>
@@ -4365,10 +4362,10 @@
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>255</v>
@@ -4397,10 +4394,10 @@
         <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>258</v>
@@ -4429,10 +4426,10 @@
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>91</v>
+        <v>190</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>261</v>
@@ -4464,7 +4461,7 @@
         <v>190</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>264</v>
@@ -4493,10 +4490,10 @@
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>190</v>
+        <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>267</v>
@@ -4557,7 +4554,7 @@
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>154</v>
@@ -4589,13 +4586,13 @@
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>97</v>
+        <v>276</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -4609,19 +4606,19 @@
         <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>154</v>
@@ -4653,7 +4650,7 @@
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>279</v>
+        <v>109</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>154</v>
@@ -4685,7 +4682,7 @@
         <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>154</v>
@@ -4720,7 +4717,7 @@
         <v>103</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>289</v>
@@ -4749,10 +4746,10 @@
         <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>103</v>
+        <v>184</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>292</v>
@@ -4813,10 +4810,10 @@
         <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>184</v>
+        <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>298</v>
@@ -4877,10 +4874,10 @@
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>304</v>
@@ -4909,7 +4906,7 @@
         <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>163</v>
+        <v>91</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>154</v>
@@ -4941,48 +4938,1060 @@
         <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J30"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>91</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>153</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>310</v>
+        <v>397</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>311</v>
+        <v>398</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>312</v>
+        <v>399</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>312</v>
+        <v>399</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>313</v>
+        <v>400</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>153</v>
+        <v>276</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>314</v>
+        <v>212</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>315</v>
+        <v>401</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -5023,17 +6032,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5071,115 +6081,115 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>316</v>
+        <v>402</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>316</v>
+        <v>402</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>317</v>
+        <v>403</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>318</v>
+        <v>404</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>319</v>
+        <v>405</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>319</v>
+        <v>405</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>320</v>
+        <v>406</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>91</v>
+        <v>190</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>321</v>
+        <v>407</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>322</v>
+        <v>408</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>322</v>
+        <v>408</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>323</v>
+        <v>409</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>97</v>
+        <v>245</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>324</v>
+        <v>410</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>325</v>
+        <v>411</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>325</v>
+        <v>411</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>326</v>
+        <v>412</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
@@ -5188,414 +6198,414 @@
         <v>91</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>327</v>
+        <v>413</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>328</v>
+        <v>52</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>328</v>
+        <v>52</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>329</v>
+        <v>414</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>207</v>
+        <v>91</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>330</v>
+        <v>415</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>331</v>
+        <v>416</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>331</v>
+        <v>416</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>332</v>
+        <v>417</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>333</v>
+        <v>418</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>334</v>
+        <v>419</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>334</v>
+        <v>419</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>335</v>
+        <v>420</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>184</v>
+        <v>103</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>336</v>
+        <v>421</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>42</v>
+        <v>422</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>42</v>
+        <v>422</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>337</v>
+        <v>423</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>338</v>
+        <v>424</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>339</v>
+        <v>425</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>339</v>
+        <v>425</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>340</v>
+        <v>426</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>207</v>
+        <v>276</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>341</v>
+        <v>427</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>342</v>
+        <v>428</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>342</v>
+        <v>428</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>343</v>
+        <v>429</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>184</v>
+        <v>91</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>344</v>
+        <v>430</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>345</v>
+        <v>431</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>345</v>
+        <v>431</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>346</v>
+        <v>432</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>347</v>
+        <v>433</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>348</v>
+        <v>434</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>348</v>
+        <v>434</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>349</v>
+        <v>435</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>350</v>
+        <v>436</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>351</v>
+        <v>437</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>351</v>
+        <v>437</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>352</v>
+        <v>438</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>207</v>
+        <v>91</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>353</v>
+        <v>439</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>354</v>
+        <v>440</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>354</v>
+        <v>440</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>355</v>
+        <v>441</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>185</v>
+        <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>356</v>
+        <v>442</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>357</v>
+        <v>443</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>357</v>
+        <v>443</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>358</v>
+        <v>444</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>359</v>
+        <v>445</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>360</v>
+        <v>446</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>360</v>
+        <v>446</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>361</v>
+        <v>447</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>362</v>
+        <v>448</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>363</v>
+        <v>449</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>363</v>
+        <v>449</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>364</v>
+        <v>450</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
@@ -5604,190 +6614,190 @@
         <v>91</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>365</v>
+        <v>451</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>366</v>
+        <v>452</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>366</v>
+        <v>452</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>367</v>
+        <v>453</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>368</v>
+        <v>454</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>369</v>
+        <v>455</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>369</v>
+        <v>455</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>370</v>
+        <v>456</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>97</v>
+        <v>276</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>371</v>
+        <v>457</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>372</v>
+        <v>458</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>372</v>
+        <v>458</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>373</v>
+        <v>459</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>91</v>
+        <v>276</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>374</v>
+        <v>460</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>375</v>
+        <v>461</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>375</v>
+        <v>461</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>376</v>
+        <v>462</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>109</v>
+        <v>184</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>377</v>
+        <v>463</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>378</v>
+        <v>464</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>378</v>
+        <v>464</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>379</v>
+        <v>465</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>91</v>
+        <v>276</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>380</v>
+        <v>466</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>381</v>
+        <v>467</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>381</v>
+        <v>467</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>382</v>
+        <v>468</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
@@ -5796,158 +6806,158 @@
         <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>185</v>
+        <v>126</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>383</v>
+        <v>469</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>384</v>
+        <v>470</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>384</v>
+        <v>470</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>385</v>
+        <v>471</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>386</v>
+        <v>472</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>387</v>
+        <v>473</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>387</v>
+        <v>473</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>388</v>
+        <v>474</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>389</v>
+        <v>475</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>204</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>390</v>
+        <v>476</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>390</v>
+        <v>476</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>391</v>
+        <v>477</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>97</v>
+        <v>245</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>314</v>
+        <v>154</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>392</v>
+        <v>478</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>393</v>
+        <v>479</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>393</v>
+        <v>479</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>394</v>
+        <v>480</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>279</v>
+        <v>91</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>395</v>
+        <v>481</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>214</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>396</v>
+        <v>482</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>396</v>
+        <v>482</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>397</v>
+        <v>483</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
@@ -5959,10 +6969,10 @@
         <v>212</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>398</v>
+        <v>484</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -6001,1051 +7011,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J31"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
@@ -7053,11 +7018,10 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7101,28 +7065,28 @@
         <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>226</v>
+        <v>98</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -7133,28 +7097,28 @@
         <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>226</v>
+        <v>104</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -7165,28 +7129,28 @@
         <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>279</v>
+        <v>97</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -7197,28 +7161,28 @@
         <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -7229,28 +7193,28 @@
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>60</v>
+        <v>497</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>60</v>
+        <v>497</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>91</v>
+        <v>207</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -7261,28 +7225,28 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>504</v>
-      </c>
       <c r="J7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -7293,28 +7257,28 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>507</v>
-      </c>
       <c r="J8" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -7325,28 +7289,28 @@
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>510</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -7357,28 +7321,28 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>511</v>
+        <v>60</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>511</v>
+        <v>60</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -7386,31 +7350,31 @@
         <v>53</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>91</v>
+        <v>207</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -7421,28 +7385,28 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -7453,28 +7417,28 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -7485,28 +7449,28 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>103</v>
+        <v>207</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -7517,28 +7481,28 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -7549,13 +7513,13 @@
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
@@ -7564,13 +7528,13 @@
         <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -7581,28 +7545,28 @@
         <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>279</v>
+        <v>163</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>185</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -7613,13 +7577,13 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
@@ -7628,13 +7592,13 @@
         <v>91</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -7645,13 +7609,13 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
@@ -7663,10 +7627,10 @@
         <v>154</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -7677,28 +7641,28 @@
         <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -7709,13 +7673,13 @@
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
@@ -7724,13 +7688,13 @@
         <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -7741,28 +7705,28 @@
         <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>153</v>
+        <v>109</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>185</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -7773,28 +7737,28 @@
         <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -7805,13 +7769,13 @@
         <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
@@ -7823,10 +7787,10 @@
         <v>185</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -7837,13 +7801,13 @@
         <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
@@ -7855,10 +7819,10 @@
         <v>185</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -7869,28 +7833,28 @@
         <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>248</v>
+        <v>97</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>185</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -7901,28 +7865,28 @@
         <v>204</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -7933,28 +7897,28 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>212</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -7965,28 +7929,28 @@
         <v>214</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>185</v>
+        <v>310</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -7997,28 +7961,28 @@
         <v>218</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>103</v>
+        <v>276</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>212</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -8026,16 +7990,16 @@
         <v>53</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>311</v>
+        <v>398</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>90</v>
@@ -8044,13 +8008,13 @@
         <v>91</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>314</v>
+        <v>212</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -8093,7 +8057,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -8102,7 +8066,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8146,28 +8110,28 @@
         <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>104</v>
+        <v>226</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -8178,28 +8142,28 @@
         <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>190</v>
+        <v>103</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>104</v>
+        <v>226</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -8210,28 +8174,28 @@
         <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -8242,16 +8206,16 @@
         <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>586</v>
+        <v>68</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>586</v>
+        <v>68</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>91</v>
@@ -8260,10 +8224,10 @@
         <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -8274,28 +8238,28 @@
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>68</v>
+        <v>585</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>68</v>
+        <v>585</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -8306,28 +8270,28 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>190</v>
+        <v>245</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -8338,28 +8302,28 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -8370,28 +8334,28 @@
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -8402,28 +8366,28 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>279</v>
+        <v>91</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -8431,16 +8395,16 @@
         <v>61</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -8449,13 +8413,13 @@
         <v>91</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -8466,13 +8430,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
@@ -8481,13 +8445,13 @@
         <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -8498,13 +8462,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
@@ -8513,13 +8477,13 @@
         <v>91</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -8530,28 +8494,28 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -8562,13 +8526,13 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
@@ -8580,10 +8544,10 @@
         <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -8594,28 +8558,28 @@
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -8626,28 +8590,28 @@
         <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>184</v>
+        <v>276</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -8658,13 +8622,13 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
@@ -8676,10 +8640,10 @@
         <v>154</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -8690,28 +8654,28 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>279</v>
+        <v>91</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -8722,28 +8686,28 @@
         <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>279</v>
+        <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -8754,28 +8718,28 @@
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>154</v>
+        <v>212</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -8786,28 +8750,28 @@
         <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -8818,28 +8782,28 @@
         <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>279</v>
+        <v>109</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -8850,28 +8814,28 @@
         <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -8882,28 +8846,28 @@
         <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -8914,28 +8878,28 @@
         <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>185</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -8946,28 +8910,28 @@
         <v>204</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>248</v>
+        <v>91</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -8978,28 +8942,28 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>154</v>
+        <v>212</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -9010,13 +8974,13 @@
         <v>214</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
@@ -9025,17 +8989,49 @@
         <v>91</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="J29" s="2" t="s">
-        <v>34</v>
+      <c r="J30" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -9065,6 +9061,7 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9236,10 +9233,10 @@
         <v>91</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>673</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -9253,13 +9250,13 @@
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>674</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>675</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>90</v>
@@ -9268,10 +9265,10 @@
         <v>153</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>677</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -9285,25 +9282,25 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>680</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -9317,25 +9314,25 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>682</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>684</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -9349,25 +9346,25 @@
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>686</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>687</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -9381,13 +9378,13 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>688</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>689</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
@@ -9396,10 +9393,10 @@
         <v>153</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -9410,16 +9407,16 @@
         <v>69</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>691</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>692</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -9428,10 +9425,10 @@
         <v>163</v>
       </c>
       <c r="H11" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>693</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>694</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -9445,13 +9442,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>695</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>696</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
@@ -9460,10 +9457,10 @@
         <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -9477,25 +9474,25 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>699</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>700</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -9509,25 +9506,25 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>702</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>703</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -9541,25 +9538,25 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>705</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>706</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -9573,25 +9570,25 @@
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="H16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>709</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>710</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -9605,25 +9602,25 @@
         <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>712</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>713</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -9637,25 +9634,25 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>715</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>716</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -9669,25 +9666,25 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>718</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>719</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -9701,13 +9698,13 @@
         <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>720</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>721</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
@@ -9716,10 +9713,10 @@
         <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -9733,25 +9730,25 @@
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>724</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>725</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -9771,19 +9768,19 @@
         <v>78</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>108</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -9797,13 +9794,13 @@
         <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>728</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>729</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
@@ -9812,10 +9809,10 @@
         <v>190</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>730</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>731</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -9829,13 +9826,13 @@
         <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>732</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>733</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
@@ -9844,10 +9841,10 @@
         <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -9861,13 +9858,13 @@
         <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>735</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>736</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
@@ -9876,10 +9873,10 @@
         <v>190</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -84,7 +84,7 @@
     <t>Scania 13</t>
   </si>
   <si>
-    <t>883</t>
+    <t>888</t>
   </si>
   <si>
     <t>35위</t>
@@ -147,7 +147,7 @@
     <t>Scania 4</t>
   </si>
   <si>
-    <t>894</t>
+    <t>896</t>
   </si>
   <si>
     <t>33위</t>
@@ -177,7 +177,7 @@
     <t>Scania 29</t>
   </si>
   <si>
-    <t>910</t>
+    <t>906</t>
   </si>
   <si>
     <t>16위</t>
@@ -201,7 +201,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>876</t>
+    <t>879</t>
   </si>
   <si>
     <t>40위</t>
@@ -225,7 +225,7 @@
     <t>Scania 3</t>
   </si>
   <si>
-    <t>946</t>
+    <t>947</t>
   </si>
   <si>
     <t>42위</t>
@@ -249,7 +249,7 @@
     <t>Scania 50</t>
   </si>
   <si>
-    <t>909</t>
+    <t>905</t>
   </si>
   <si>
     <t>4위</t>
@@ -363,7 +363,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>7537조 836억 5059만</t>
+    <t>7580조 4757억 655만</t>
   </si>
   <si>
     <t>5</t>
@@ -375,7 +375,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%90%EC%B1%A0</t>
   </si>
   <si>
-    <t>6597조 9904억 9169만</t>
+    <t>6982조 9487억 2261만</t>
   </si>
   <si>
     <t>6</t>
@@ -387,7 +387,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%84%EA%B5%AC</t>
   </si>
   <si>
-    <t>5813조 6035억 4073만</t>
+    <t>5900조 1804억 1254만</t>
   </si>
   <si>
     <t>7</t>
@@ -399,7 +399,7 @@
     <t>https://mgf.gg/contents/character.php?n=GOD%EB%82%A0%EB%91%90</t>
   </si>
   <si>
-    <t>5618조 2831억 6335만</t>
+    <t>5630조 1490억 7657만</t>
   </si>
   <si>
     <t>8</t>
@@ -411,48 +411,48 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%8C%EB%B0%B0%EA%B8%B0</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>4963조 5845억 4685만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>하찌바리이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B0%8C%EB%B0%94%EB%A6%AC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>3513조 4639억 5612만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>러브포티</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%B8%8C%ED%8F%AC%ED%8B%B0</t>
+  </si>
+  <si>
+    <t>3376조 9569억 1183만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>주요엘농산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%9A%94%EC%97%98%EB%86%8D%EC%82%B0</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>4764조 9443억 42만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>하찌바리이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B0%8C%EB%B0%94%EB%A6%AC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>3469조 7402억 7786만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>러브포티</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%B8%8C%ED%8F%AC%ED%8B%B0</t>
-  </si>
-  <si>
-    <t>3374조 9102억 7995만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>주요엘농산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%9A%94%EC%97%98%EB%86%8D%EC%82%B0</t>
-  </si>
-  <si>
     <t>3372조 7251억 8925만</t>
   </si>
   <si>
@@ -495,36 +495,36 @@
     <t>신궁</t>
   </si>
   <si>
+    <t>2429조 2480억 9194만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>서늘한그늘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%8A%98%ED%95%9C%EA%B7%B8%EB%8A%98</t>
+  </si>
+  <si>
+    <t>2349조 6211억 5045만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>88치킨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=88%EC%B9%98%ED%82%A8</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>2356조 71억 4926만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>서늘한그늘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%8A%98%ED%95%9C%EA%B7%B8%EB%8A%98</t>
-  </si>
-  <si>
-    <t>2349조 6211억 5045만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>88치킨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=88%EC%B9%98%ED%82%A8</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
     <t>2140조 472억 1466만</t>
   </si>
   <si>
@@ -555,6 +555,18 @@
     <t>19</t>
   </si>
   <si>
+    <t>도레오</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%88%EC%98%A4</t>
+  </si>
+  <si>
+    <t>1384조 3289억 6509만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
     <t>v박효신v</t>
   </si>
   <si>
@@ -564,7 +576,7 @@
     <t>1383조 4073억 6000만</t>
   </si>
   <si>
-    <t>20</t>
+    <t>21</t>
   </si>
   <si>
     <t>여릿</t>
@@ -576,7 +588,19 @@
     <t>1278조 5550억 2130만</t>
   </si>
   <si>
-    <t>21</t>
+    <t>22</t>
+  </si>
+  <si>
+    <t>다둉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1264조 4180억 6567만</t>
+  </si>
+  <si>
+    <t>23</t>
   </si>
   <si>
     <t>초읍사나이</t>
@@ -591,10 +615,10 @@
     <t>110</t>
   </si>
   <si>
-    <t>1236조 4493억 2491만</t>
-  </si>
-  <si>
-    <t>22</t>
+    <t>1251조 9810억 5510만</t>
+  </si>
+  <si>
+    <t>24</t>
   </si>
   <si>
     <t>시간이돈</t>
@@ -606,22 +630,10 @@
     <t>캡틴</t>
   </si>
   <si>
-    <t>1234조 123억 1646만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>다둉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1104조 386억 5983만</t>
-  </si>
-  <si>
-    <t>24</t>
+    <t>1239조 8487억 6409만</t>
+  </si>
+  <si>
+    <t>25</t>
   </si>
   <si>
     <t>고으농</t>
@@ -633,18 +645,6 @@
     <t>1065조 6768억 9164만</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>도레오</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%88%EC%98%A4</t>
-  </si>
-  <si>
-    <t>985조 3833억 8106만</t>
-  </si>
-  <si>
     <t>26</t>
   </si>
   <si>
@@ -684,7 +684,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A6%AC%EB%AF%B8%EC%BF%B5</t>
   </si>
   <si>
-    <t>569조 3151억 7266만</t>
+    <t>577조 741억 7164만</t>
   </si>
   <si>
     <t>29</t>
@@ -711,271 +711,271 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EA%B3%BD</t>
   </si>
   <si>
+    <t>1경 2526조 6847억 9408만</t>
+  </si>
+  <si>
+    <t>형팡팡이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%95%ED%8C%A1%ED%8C%A1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>5445조 3408억 1191만</t>
+  </si>
+  <si>
+    <t>붉은모자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%89%EC%9D%80%EB%AA%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>3914조 7883억 9112만</t>
+  </si>
+  <si>
+    <t>2번째캐릭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=2%EB%B2%88%EC%A7%B8%EC%BA%90%EB%A6%AD</t>
+  </si>
+  <si>
+    <t>3763조 8427억 4548만</t>
+  </si>
+  <si>
+    <t>장뱁새</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B1%81%EC%83%88</t>
+  </si>
+  <si>
+    <t>3529조 2576억 465만</t>
+  </si>
+  <si>
+    <t>꽁꽁냉법</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EA%BD%81%EB%83%89%EB%B2%95</t>
+  </si>
+  <si>
+    <t>2784조 9520억 6600만</t>
+  </si>
+  <si>
+    <t>테토일남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%85%8C%ED%86%A0%EC%9D%BC%EB%82%A8</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>2605조 9827억 5496만</t>
+  </si>
+  <si>
+    <t>뚜기파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EA%B8%B0%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>2130조 4991억 7426만</t>
+  </si>
+  <si>
+    <t>브네</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%84%A4</t>
+  </si>
+  <si>
+    <t>1928조 5981억 7061만</t>
+  </si>
+  <si>
+    <t>라쥬르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%A5%AC%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>1664조 1742억 9004만</t>
+  </si>
+  <si>
+    <t>초앤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%95%A4</t>
+  </si>
+  <si>
+    <t>1643조 2907억 5359만</t>
+  </si>
+  <si>
+    <t>재미있게놀래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EB%AF%B8%EC%9E%88%EA%B2%8C%EB%86%80%EB%9E%98</t>
+  </si>
+  <si>
+    <t>1459조 9219억 3077만</t>
+  </si>
+  <si>
+    <t>가덴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%8D%B4</t>
+  </si>
+  <si>
+    <t>1383조 229억 4504만</t>
+  </si>
+  <si>
+    <t>33세배장호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=33%EC%84%B8%EB%B0%B0%EC%9E%A5%ED%98%B8</t>
+  </si>
+  <si>
+    <t>1370조 349억 8666만</t>
+  </si>
+  <si>
+    <t>빙율</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%99%EC%9C%A8</t>
+  </si>
+  <si>
+    <t>1314조 7187억 8022만</t>
+  </si>
+  <si>
+    <t>적젹적</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%81%EC%A0%B9%EC%A0%81</t>
+  </si>
+  <si>
+    <t>1248조 9061억 9176만</t>
+  </si>
+  <si>
+    <t>최빵쭈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EB%B9%B5%EC%AD%88</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>980조 2953억 7066만</t>
+  </si>
+  <si>
+    <t>타뤽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%A4%BD</t>
+  </si>
+  <si>
+    <t>961조 5316억 9637만</t>
+  </si>
+  <si>
+    <t>정기휴므</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EA%B8%B0%ED%9C%B4%EB%AF%80</t>
+  </si>
+  <si>
+    <t>916조 586억 5018만</t>
+  </si>
+  <si>
+    <t>무르스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%A5%B4%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>785조 1486억 9137만</t>
+  </si>
+  <si>
+    <t>채황새</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%ED%99%A9%EC%83%88</t>
+  </si>
+  <si>
+    <t>775조 3453억 3804만</t>
+  </si>
+  <si>
+    <t>저기휴무</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%80%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>699조 6704억 9749만</t>
+  </si>
+  <si>
+    <t>넬샷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%AC%EC%83%B7</t>
+  </si>
+  <si>
+    <t>639조 5314억 3480만</t>
+  </si>
+  <si>
+    <t>박도란</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%8F%84%EB%9E%80</t>
+  </si>
+  <si>
+    <t>631조 424억 363만</t>
+  </si>
+  <si>
+    <t>장기휴무</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>547조 7047억 3326만</t>
+  </si>
+  <si>
+    <t>뿌앵뿌앵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EC%95%B5%EB%BF%8C%EC%95%B5</t>
+  </si>
+  <si>
+    <t>418조 4422억 2130만</t>
+  </si>
+  <si>
+    <t>냥홍이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%ED%99%8D%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>378조 3540억 524만</t>
+  </si>
+  <si>
+    <t>윤빵쭈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EB%B9%B5%EC%AD%88</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>309조 4737억 1028만</t>
+  </si>
+  <si>
+    <t>지존쫀파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
+  </si>
+  <si>
     <t>115</t>
   </si>
   <si>
-    <t>1경 2526조 6847억 9408만</t>
-  </si>
-  <si>
-    <t>형팡팡이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%95%ED%8C%A1%ED%8C%A1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>5421조 8420억 8만</t>
-  </si>
-  <si>
-    <t>2번째캐릭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=2%EB%B2%88%EC%A7%B8%EC%BA%90%EB%A6%AD</t>
-  </si>
-  <si>
-    <t>3757조 3831억 1657만</t>
-  </si>
-  <si>
-    <t>붉은모자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%89%EC%9D%80%EB%AA%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>3716조 7347억 5296만</t>
-  </si>
-  <si>
-    <t>장뱁새</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B1%81%EC%83%88</t>
-  </si>
-  <si>
-    <t>3515조 9941억 5767만</t>
-  </si>
-  <si>
-    <t>꽁꽁냉법</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EA%BD%81%EB%83%89%EB%B2%95</t>
-  </si>
-  <si>
-    <t>2626조 5073억 8510만</t>
-  </si>
-  <si>
-    <t>테토일남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%85%8C%ED%86%A0%EC%9D%BC%EB%82%A8</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>2556조 134억 3692만</t>
-  </si>
-  <si>
-    <t>뚜기파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EA%B8%B0%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>2025조 6243억 9048만</t>
-  </si>
-  <si>
-    <t>브네</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%84%A4</t>
-  </si>
-  <si>
-    <t>1928조 5981억 7061만</t>
-  </si>
-  <si>
-    <t>라쥬르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%A5%AC%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>1661조 5880억 9788만</t>
-  </si>
-  <si>
-    <t>초앤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%95%A4</t>
-  </si>
-  <si>
-    <t>1630조 3439억 1814만</t>
-  </si>
-  <si>
-    <t>재미있게놀래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EB%AF%B8%EC%9E%88%EA%B2%8C%EB%86%80%EB%9E%98</t>
-  </si>
-  <si>
-    <t>1392조 5593억 9126만</t>
-  </si>
-  <si>
-    <t>가덴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%8D%B4</t>
-  </si>
-  <si>
-    <t>1381조 775억 6791만</t>
-  </si>
-  <si>
-    <t>33세배장호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=33%EC%84%B8%EB%B0%B0%EC%9E%A5%ED%98%B8</t>
-  </si>
-  <si>
-    <t>1370조 349억 8666만</t>
-  </si>
-  <si>
-    <t>빙율</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%99%EC%9C%A8</t>
-  </si>
-  <si>
-    <t>1314조 7187억 8022만</t>
-  </si>
-  <si>
-    <t>적젹적</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%81%EC%A0%B9%EC%A0%81</t>
-  </si>
-  <si>
-    <t>1246조 3736억 6450만</t>
-  </si>
-  <si>
-    <t>최빵쭈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EB%B9%B5%EC%AD%88</t>
-  </si>
-  <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>980조 2953억 7066만</t>
-  </si>
-  <si>
-    <t>타뤽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%A4%BD</t>
-  </si>
-  <si>
-    <t>938조 3323억 3393만</t>
-  </si>
-  <si>
-    <t>정기휴므</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EA%B8%B0%ED%9C%B4%EB%AF%80</t>
-  </si>
-  <si>
-    <t>891조 8517억 7136만</t>
-  </si>
-  <si>
-    <t>무르스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%A5%B4%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>783조 2410억 1299만</t>
-  </si>
-  <si>
-    <t>채황새</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%ED%99%A9%EC%83%88</t>
-  </si>
-  <si>
-    <t>760조 4377억 7091만</t>
-  </si>
-  <si>
-    <t>저기휴무</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%80%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
-  </si>
-  <si>
-    <t>699조 6704억 9749만</t>
-  </si>
-  <si>
-    <t>넬샷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%AC%EC%83%B7</t>
-  </si>
-  <si>
-    <t>639조 5314억 3480만</t>
-  </si>
-  <si>
-    <t>박도란</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%8F%84%EB%9E%80</t>
-  </si>
-  <si>
-    <t>631조 424억 363만</t>
-  </si>
-  <si>
-    <t>장기휴무</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
-  </si>
-  <si>
-    <t>547조 7047억 3326만</t>
-  </si>
-  <si>
-    <t>뿌앵뿌앵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EC%95%B5%EB%BF%8C%EC%95%B5</t>
-  </si>
-  <si>
-    <t>418조 4422억 2130만</t>
-  </si>
-  <si>
-    <t>냥홍이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%ED%99%8D%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>367조 2308억 5887만</t>
-  </si>
-  <si>
-    <t>윤빵쭈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EB%B9%B5%EC%AD%88</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>309조 4737억 1028만</t>
-  </si>
-  <si>
-    <t>지존쫀파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>9961조 4670억 6144만</t>
+    <t>9978조 808억 2146만</t>
   </si>
   <si>
     <t>수텍</t>
@@ -984,7 +984,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%ED%85%8D</t>
   </si>
   <si>
-    <t>7731조 8382억 7567만</t>
+    <t>7780조 8362억 2093만</t>
   </si>
   <si>
     <t>포항엄석대</t>
@@ -993,7 +993,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
   </si>
   <si>
-    <t>4565조 7703억 9896만</t>
+    <t>4590조 9887억 9442만</t>
   </si>
   <si>
     <t>협의</t>
@@ -1005,22 +1005,22 @@
     <t>4402조 1032억 4015만</t>
   </si>
   <si>
+    <t>기뽐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%BD%90</t>
+  </si>
+  <si>
+    <t>3807조 6451억 3805만</t>
+  </si>
+  <si>
     <t>타개</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
   </si>
   <si>
-    <t>3724조 5498억 5962만</t>
-  </si>
-  <si>
-    <t>기뽐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%BD%90</t>
-  </si>
-  <si>
-    <t>3303조 6174억 3840만</t>
+    <t>3748조 4878억 3605만</t>
   </si>
   <si>
     <t>댜니</t>
@@ -1047,7 +1047,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
   </si>
   <si>
-    <t>2537조 271억 3333만</t>
+    <t>2601조 5344억 7218만</t>
+  </si>
+  <si>
+    <t>엘르가든</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
+  </si>
+  <si>
+    <t>2524조 5509억 437만</t>
   </si>
   <si>
     <t>지존빼앙</t>
@@ -1074,16 +1083,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
   </si>
   <si>
-    <t>2349조 265억 3189만</t>
-  </si>
-  <si>
-    <t>엘르가든</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
-  </si>
-  <si>
-    <t>2313조 7071억 7362만</t>
+    <t>2417조 8596억 1972만</t>
   </si>
   <si>
     <t>파울</t>
@@ -1092,7 +1092,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
   </si>
   <si>
-    <t>1901조 6768억 6078만</t>
+    <t>2101조 5950억 688만</t>
   </si>
   <si>
     <t>마카롱롱</t>
@@ -1119,7 +1119,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
   </si>
   <si>
-    <t>1383조 7789억 8243만</t>
+    <t>1412조 3496억 5023만</t>
   </si>
   <si>
     <t>오옹나이스</t>
@@ -1143,7 +1143,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
   </si>
   <si>
-    <t>1227조 5969억 4490만</t>
+    <t>1239조 6065억 5601만</t>
   </si>
   <si>
     <t>김허덕</t>
@@ -1155,6 +1155,15 @@
     <t>1206조 1272억 7177만</t>
   </si>
   <si>
+    <t>기본이리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1163조 6084억 6277만</t>
+  </si>
+  <si>
     <t>짱잘자쿨냥</t>
   </si>
   <si>
@@ -1164,22 +1173,13 @@
     <t>1149조 8047억 287만</t>
   </si>
   <si>
-    <t>기본이리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1144조 139억 6724만</t>
-  </si>
-  <si>
     <t>냐은</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EC%9D%80</t>
   </si>
   <si>
-    <t>1087조 8953억 2222만</t>
+    <t>1091조 572억 7018만</t>
   </si>
   <si>
     <t>전산봉</t>
@@ -1197,7 +1197,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
   </si>
   <si>
-    <t>892조 2063억 3717만</t>
+    <t>892조 4230억 8515만</t>
   </si>
   <si>
     <t>태코찡</t>
@@ -1206,7 +1206,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
   </si>
   <si>
-    <t>852조 6312억 8197만</t>
+    <t>863조 8050억 2721만</t>
   </si>
   <si>
     <t>Doham</t>
@@ -1215,7 +1215,7 @@
     <t>https://mgf.gg/contents/character.php?n=Doham</t>
   </si>
   <si>
-    <t>824조 940억 8761만</t>
+    <t>825조 9666억 8220만</t>
   </si>
   <si>
     <t>유플러스</t>
@@ -1254,7 +1254,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%96%A5</t>
   </si>
   <si>
-    <t>9930조 6490억 2812만</t>
+    <t>1경 247조 8680억 9380만</t>
   </si>
   <si>
     <t>례전</t>
@@ -1263,7 +1263,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%80%EC%A0%84</t>
   </si>
   <si>
-    <t>4565조 3068억 6482만</t>
+    <t>4585조 3930억 967만</t>
   </si>
   <si>
     <t>숭타이준</t>
@@ -1272,13 +1272,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%ED%83%80%EC%9D%B4%EC%A4%80</t>
   </si>
   <si>
-    <t>3793조 2729억 2175만</t>
+    <t>3854조 5686억 5069만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%94%9C%ED%8F%BF</t>
   </si>
   <si>
-    <t>2598조 7115억 1793만</t>
+    <t>2987조 5147억 8598만</t>
   </si>
   <si>
     <t>뻑걸</t>
@@ -1287,7 +1287,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%91%EA%B1%B8</t>
   </si>
   <si>
-    <t>2430조 2751억 4025만</t>
+    <t>2431조 2307억 9064만</t>
   </si>
   <si>
     <t>지존빵수</t>
@@ -1296,7 +1296,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%B5%EC%88%98</t>
   </si>
   <si>
-    <t>2349조 4168억 2105만</t>
+    <t>2382조 2085억 8241만</t>
   </si>
   <si>
     <t>야키산</t>
@@ -1314,7 +1314,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%8F%BF</t>
   </si>
   <si>
-    <t>2109조 1360억 8174만</t>
+    <t>2110조 5743억 8233만</t>
   </si>
   <si>
     <t>문제적남자</t>
@@ -1326,22 +1326,22 @@
     <t>1997조 2870억 868만</t>
   </si>
   <si>
+    <t>아이리쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EB%A6%AC%EC%89%AC</t>
+  </si>
+  <si>
+    <t>1925조 8327억 6550만</t>
+  </si>
+  <si>
     <t>뮬이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AE%AC%EC%9D%B4</t>
   </si>
   <si>
-    <t>1849조 6243억 90만</t>
-  </si>
-  <si>
-    <t>아이리쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EB%A6%AC%EC%89%AC</t>
-  </si>
-  <si>
-    <t>1839조 8251억 1365만</t>
+    <t>1853조 5868억 1940만</t>
   </si>
   <si>
     <t>화둥에불낸년</t>
@@ -1359,7 +1359,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%8A%A4%EC%BC%80</t>
   </si>
   <si>
-    <t>1356조 2214억 186만</t>
+    <t>1360조 4786억 2292만</t>
   </si>
   <si>
     <t>우즈2텐겐</t>
@@ -1377,7 +1377,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B2%8C%EC%9A%A9</t>
   </si>
   <si>
-    <t>1077조 4898억 5524만</t>
+    <t>1104조 4725억 1959만</t>
+  </si>
+  <si>
+    <t>기똥찬벌레</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%98%A5%EC%B0%AC%EB%B2%8C%EB%A0%88</t>
+  </si>
+  <si>
+    <t>1064조 4710억 2623만</t>
+  </si>
+  <si>
+    <t>구도류</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%8F%84%EB%A5%98</t>
+  </si>
+  <si>
+    <t>1034조 7715억 4058만</t>
   </si>
   <si>
     <t>우월별하</t>
@@ -1389,24 +1407,6 @@
     <t>1032조 7712억 9061만</t>
   </si>
   <si>
-    <t>기똥찬벌레</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%98%A5%EC%B0%AC%EB%B2%8C%EB%A0%88</t>
-  </si>
-  <si>
-    <t>1031조 4047억 5773만</t>
-  </si>
-  <si>
-    <t>구도류</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%8F%84%EB%A5%98</t>
-  </si>
-  <si>
-    <t>1020조 6439억 2084만</t>
-  </si>
-  <si>
     <t>매화로이</t>
   </si>
   <si>
@@ -1422,7 +1422,16 @@
     <t>https://mgf.gg/contents/character.php?n=JJuna</t>
   </si>
   <si>
-    <t>939조 2803억 6578만</t>
+    <t>939조 5662억 4094만</t>
+  </si>
+  <si>
+    <t>콜리셰마드르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%9C%EB%A6%AC%EC%85%B0%EB%A7%88%EB%93%9C%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>856조 9999억 6656만</t>
   </si>
   <si>
     <t>난센</t>
@@ -1431,7 +1440,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EC%84%BC</t>
   </si>
   <si>
-    <t>798조 3691억 7640만</t>
+    <t>838조 4774억 5664만</t>
   </si>
   <si>
     <t>에프람</t>
@@ -1440,16 +1449,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%ED%94%84%EB%9E%8C</t>
   </si>
   <si>
-    <t>796조 3154억 1093만</t>
-  </si>
-  <si>
-    <t>콜리셰마드르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%9C%EB%A6%AC%EC%85%B0%EB%A7%88%EB%93%9C%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>779조 4483억 3378만</t>
+    <t>796조 7994억 2727만</t>
   </si>
   <si>
     <t>유채아버지</t>
@@ -1458,7 +1458,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%B1%84%EC%95%84%EB%B2%84%EC%A7%80</t>
   </si>
   <si>
-    <t>670조 9011억 2995만</t>
+    <t>690조 1540억 2234만</t>
   </si>
   <si>
     <t>조단23</t>
@@ -1467,7 +1467,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%8B%A823</t>
   </si>
   <si>
-    <t>667조 7732억 1410만</t>
+    <t>669조 6960억 2046만</t>
   </si>
   <si>
     <t>아콩린</t>
@@ -1494,7 +1494,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
   </si>
   <si>
-    <t>2경 374조 8201억 5764만</t>
+    <t>2경 1286조 1305억 8124만</t>
   </si>
   <si>
     <t>굴러가는일상</t>
@@ -1512,7 +1512,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
   </si>
   <si>
-    <t>5067조 550억 6840만</t>
+    <t>5071조 9596억 5566만</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>4270조 7688억 5784만</t>
   </si>
   <si>
     <t>흑두부</t>
@@ -1524,22 +1533,13 @@
     <t>4269조 1039억 8746만</t>
   </si>
   <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>4145조 5731억 3307만</t>
-  </si>
-  <si>
     <t>서포터즈</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>3109조 5410억 3413만</t>
+    <t>3121조 7410억 5159만</t>
   </si>
   <si>
     <t>야가다</t>
@@ -1572,7 +1572,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>2247조 5088억 7013만</t>
+    <t>2398조 1780억 1990만</t>
   </si>
   <si>
     <t>불보독지</t>
@@ -1581,7 +1581,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
   </si>
   <si>
-    <t>1339조 3325억 1781만</t>
+    <t>1369조 9106억 6331만</t>
   </si>
   <si>
     <t>우후</t>
@@ -1590,7 +1590,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>1214조 8117억 7531만</t>
+    <t>1220조 2777억 7534만</t>
+  </si>
+  <si>
+    <t>단풍카우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>1160조 9002억 9166만</t>
   </si>
   <si>
     <t>호우기</t>
@@ -1599,16 +1608,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>1154조 5842억 8701만</t>
-  </si>
-  <si>
-    <t>단풍카우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>1139조 3354억 3997만</t>
+    <t>1157조 1910억 165만</t>
   </si>
   <si>
     <t>채무조정</t>
@@ -1617,7 +1617,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
   </si>
   <si>
-    <t>1082조 2012억 4397만</t>
+    <t>1109조 6605억 1793만</t>
   </si>
   <si>
     <t>뽀송히</t>
@@ -1626,7 +1626,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
   </si>
   <si>
-    <t>1065조 4129억 9767만</t>
+    <t>1075조 4922억 3766만</t>
   </si>
   <si>
     <t>좀치는형님</t>
@@ -1644,7 +1644,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
   </si>
   <si>
-    <t>974조 8229억 1308만</t>
+    <t>978조 1277억 921만</t>
   </si>
   <si>
     <t>라탱호</t>
@@ -1653,7 +1653,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%ED%83%B1%ED%98%B8</t>
   </si>
   <si>
-    <t>924조 4741억 2884만</t>
+    <t>949조 844억 137만</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -1662,7 +1662,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>792조 9853억 5939만</t>
+    <t>795조 8961억 4737만</t>
   </si>
   <si>
     <t>짤똘</t>
@@ -1689,7 +1689,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
   </si>
   <si>
-    <t>568조 4360억 6361만</t>
+    <t>588조 4551억 8369만</t>
   </si>
   <si>
     <t>민들레꽃</t>
@@ -1698,7 +1698,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>560조 2034억 59만</t>
+    <t>560조 8091억 6899만</t>
   </si>
   <si>
     <t>컨덱</t>
@@ -1725,7 +1725,7 @@
     <t>https://mgf.gg/contents/character.php?n=3030</t>
   </si>
   <si>
-    <t>412조 6404억 5230만</t>
+    <t>414조 4027억 9667만</t>
   </si>
   <si>
     <t>아르미느</t>
@@ -1779,13 +1779,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9A%B1%EC%9D%B4%EC%97%90%EC%9A%94</t>
   </si>
   <si>
-    <t>4939조 5954억 5774만</t>
+    <t>4981조 9035억 244만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A5%B4%EB%AA%AC</t>
   </si>
   <si>
-    <t>4495조 3986억 4568만</t>
+    <t>4829조 6442억 8620만</t>
+  </si>
+  <si>
+    <t>극강딘딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B9%EA%B0%95%EB%94%98%EB%94%98</t>
+  </si>
+  <si>
+    <t>4673조 2270억 6338만</t>
   </si>
   <si>
     <t>낭만황금망치</t>
@@ -1803,7 +1812,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%8A%B4%EC%A4%8C1</t>
   </si>
   <si>
-    <t>3803조 9933억 2656만</t>
+    <t>3828조 8506억 7503만</t>
   </si>
   <si>
     <t>천달</t>
@@ -1812,7 +1821,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EB%8B%AC</t>
   </si>
   <si>
-    <t>3358조 869억 3060만</t>
+    <t>3401조 2076억 5645만</t>
   </si>
   <si>
     <t>활용</t>
@@ -1821,7 +1830,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%9C%EC%9A%A9</t>
   </si>
   <si>
-    <t>3037조 886억 2134만</t>
+    <t>3044조 648억 9902만</t>
   </si>
   <si>
     <t>호두와감자</t>
@@ -1869,22 +1878,22 @@
     <t>1054조 8889억 3800만</t>
   </si>
   <si>
+    <t>동래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%9E%98</t>
+  </si>
+  <si>
+    <t>1019조 1472억 4526만</t>
+  </si>
+  <si>
     <t>턍ol</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%84%8Dol</t>
   </si>
   <si>
-    <t>990조 7766억 5895만</t>
-  </si>
-  <si>
-    <t>동래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%9E%98</t>
-  </si>
-  <si>
-    <t>973조 5531억 361만</t>
+    <t>1018조 423억 1232만</t>
   </si>
   <si>
     <t>까쿠미</t>
@@ -1893,7 +1902,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EC%BF%A0%EB%AF%B8</t>
   </si>
   <si>
-    <t>968조 6592억 9407만</t>
+    <t>982조 6170억 9165만</t>
   </si>
   <si>
     <t>초이레</t>
@@ -1911,7 +1920,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A4</t>
   </si>
   <si>
-    <t>855조 3774억 7726만</t>
+    <t>857조 1724억 1289만</t>
   </si>
   <si>
     <t>띠우</t>
@@ -1920,7 +1929,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%A0%EC%9A%B0</t>
   </si>
   <si>
-    <t>735조 7344억 4695만</t>
+    <t>738조 8473억 6027만</t>
   </si>
   <si>
     <t>쿠까미</t>
@@ -1956,7 +1965,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EB%8B%A8%EB%8B%A8%EC%9D%B4</t>
   </si>
   <si>
-    <t>484조 9630억 1552만</t>
+    <t>491조 5157억 1429만</t>
   </si>
   <si>
     <t>08217</t>
@@ -1983,7 +1992,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%9D%B4%EC%A5%94</t>
   </si>
   <si>
-    <t>414조 8166억 3897만</t>
+    <t>414조 9409억 2274만</t>
   </si>
   <si>
     <t>택Ol</t>
@@ -1992,16 +2001,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9DOl</t>
   </si>
   <si>
-    <t>350조 223억 2730만</t>
-  </si>
-  <si>
-    <t>툼스데이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%88%BC%EC%8A%A4%EB%8D%B0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>285조 1117억 8099만</t>
+    <t>353조 685억 3200만</t>
   </si>
   <si>
     <t>달갸뤼</t>
@@ -2010,7 +2010,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EA%B0%B8%EB%A4%BC</t>
   </si>
   <si>
-    <t>168조 5059억 2996만</t>
+    <t>168조 5947억 734만</t>
   </si>
   <si>
     <t>교주만두</t>
@@ -2019,7 +2019,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%90%EC%A3%BC%EB%A7%8C%EB%91%90</t>
   </si>
   <si>
-    <t>9경 1385조 9371억 1706만</t>
+    <t>9경 2199조 6025억 4870만</t>
   </si>
   <si>
     <t>할바이</t>
@@ -2040,7 +2040,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B9%EB%B0%8D</t>
   </si>
   <si>
-    <t>242조 6051억 9884만</t>
+    <t>249조 6678억 2263만</t>
   </si>
   <si>
     <t>대구남성</t>
@@ -2049,7 +2049,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EA%B5%AC%EB%82%A8%EC%84%B1</t>
   </si>
   <si>
-    <t>82조 2455억 9709만</t>
+    <t>82조 3950억 4249만</t>
   </si>
   <si>
     <t>코잉코잉</t>
@@ -2061,7 +2061,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>63조 2334억 7566만</t>
+    <t>73조 3330억 5992만</t>
   </si>
   <si>
     <t>오스띤</t>
@@ -2070,7 +2070,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%8A%A4%EB%9D%A4</t>
   </si>
   <si>
-    <t>60조 1221억 2441만</t>
+    <t>73조 2175억 2395만</t>
+  </si>
+  <si>
+    <t>낭랑28세</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%9E%9128%EC%84%B8</t>
+  </si>
+  <si>
+    <t>72조 3944억 920만</t>
   </si>
   <si>
     <t>토벤숍이</t>
@@ -2079,28 +2088,19 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%B2%A4%EC%88%8D%EC%9D%B4</t>
   </si>
   <si>
-    <t>54조 1795억 9515만</t>
-  </si>
-  <si>
-    <t>낭랑28세</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%9E%9128%EC%84%B8</t>
+    <t>55조 717억 8007만</t>
+  </si>
+  <si>
+    <t>빵신궁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EC%8B%A0%EA%B6%81</t>
   </si>
   <si>
     <t>104</t>
   </si>
   <si>
-    <t>53조 5707억 3136만</t>
-  </si>
-  <si>
-    <t>빵신궁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EC%8B%A0%EA%B6%81</t>
-  </si>
-  <si>
-    <t>42조 5176억 8210만</t>
+    <t>42조 5391억 2100만</t>
   </si>
   <si>
     <t>썬콜우체국</t>
@@ -2112,7 +2112,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>35조 1910억 811만</t>
+    <t>35조 6541억 2160만</t>
   </si>
   <si>
     <t>밀초크코</t>
@@ -2130,7 +2130,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%AC%ED%98%81</t>
   </si>
   <si>
-    <t>31조 8417억 1019만</t>
+    <t>31조 8779억 9321만</t>
   </si>
   <si>
     <t>고통받는갈비</t>
@@ -2148,7 +2148,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%82%A4%EB%A7%9B%ED%82%A4%EB%A7%88</t>
   </si>
   <si>
-    <t>30조 4349억 5953만</t>
+    <t>30조 6567억 26만</t>
+  </si>
+  <si>
+    <t>배렛나루왁서</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%EB%A0%9B%EB%82%98%EB%A3%A8%EC%99%81%EC%84%9C</t>
+  </si>
+  <si>
+    <t>27조 8183억 2622만</t>
   </si>
   <si>
     <t>문보겨엉</t>
@@ -2172,15 +2181,6 @@
     <t>25조 7434억 2413만</t>
   </si>
   <si>
-    <t>배렛나루왁서</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%EB%A0%9B%EB%82%98%EB%A3%A8%EC%99%81%EC%84%9C</t>
-  </si>
-  <si>
-    <t>24조 7085억 8938만</t>
-  </si>
-  <si>
     <t>썬콜법사ss</t>
   </si>
   <si>
@@ -2196,7 +2196,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8E%98%ED%94%84%EB%A6%AD2</t>
   </si>
   <si>
-    <t>21조 2410억 9658만</t>
+    <t>21조 8848억 7036만</t>
   </si>
   <si>
     <t>포디케이</t>
@@ -2211,7 +2211,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%ED%82%A4%EB%B9%84%ED%82%A4</t>
   </si>
   <si>
-    <t>9조 9543억 7897만</t>
+    <t>13조 1191억 1937만</t>
   </si>
   <si>
     <t>즈나니</t>
@@ -2223,7 +2223,7 @@
     <t>100</t>
   </si>
   <si>
-    <t>4조 7298억 6480만</t>
+    <t>5조 4511억 5185만</t>
   </si>
   <si>
     <t>갈음</t>
@@ -2232,7 +2232,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%88%EC%9D%8C</t>
   </si>
   <si>
-    <t>4조 4122억 7297만</t>
+    <t>4조 4423억 9198만</t>
   </si>
   <si>
     <t>닝윤</t>
@@ -2241,7 +2241,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%9D%EC%9C%A4</t>
   </si>
   <si>
-    <t>4조 360억 3466만</t>
+    <t>4조 365억 7156만</t>
   </si>
 </sst>
 </file>
@@ -3289,10 +3289,10 @@
         <v>103</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3303,16 +3303,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -3321,10 +3321,10 @@
         <v>91</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3335,16 +3335,16 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
@@ -3353,7 +3353,7 @@
         <v>103</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>140</v>
@@ -3385,7 +3385,7 @@
         <v>144</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>145</v>
@@ -3417,7 +3417,7 @@
         <v>103</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>149</v>
@@ -3449,10 +3449,10 @@
         <v>153</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3463,16 +3463,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
@@ -3481,10 +3481,10 @@
         <v>103</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3495,25 +3495,25 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>164</v>
@@ -3545,7 +3545,7 @@
         <v>91</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>168</v>
@@ -3577,7 +3577,7 @@
         <v>91</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>172</v>
@@ -3606,10 +3606,10 @@
         <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>176</v>
@@ -3638,10 +3638,10 @@
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>91</v>
+        <v>162</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>180</v>
@@ -3670,13 +3670,13 @@
         <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3687,28 +3687,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>191</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3719,28 +3719,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="I24" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3751,25 +3751,25 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="H25" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>199</v>
@@ -3798,10 +3798,10 @@
         <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>203</v>
@@ -3833,7 +3833,7 @@
         <v>207</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>208</v>
@@ -3897,7 +3897,7 @@
         <v>207</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>217</v>
@@ -3926,10 +3926,10 @@
         <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>221</v>
@@ -4077,10 +4077,10 @@
         <v>91</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>227</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -4094,13 +4094,13 @@
         <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>229</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
@@ -4112,7 +4112,7 @@
         <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -4126,25 +4126,25 @@
         <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>233</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -4158,25 +4158,25 @@
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>236</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -4190,13 +4190,13 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
@@ -4205,10 +4205,10 @@
         <v>91</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -4222,13 +4222,13 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>241</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
@@ -4240,7 +4240,7 @@
         <v>126</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -4254,25 +4254,25 @@
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>246</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -4286,13 +4286,13 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>248</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
@@ -4301,10 +4301,10 @@
         <v>91</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -4315,16 +4315,16 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>251</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -4333,10 +4333,10 @@
         <v>109</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -4347,16 +4347,16 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
@@ -4365,10 +4365,10 @@
         <v>144</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -4382,13 +4382,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
@@ -4397,10 +4397,10 @@
         <v>91</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -4414,25 +4414,25 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>261</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -4446,25 +4446,25 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -4475,16 +4475,16 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
@@ -4493,10 +4493,10 @@
         <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -4507,16 +4507,16 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>269</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
@@ -4525,10 +4525,10 @@
         <v>91</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -4542,13 +4542,13 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
@@ -4557,10 +4557,10 @@
         <v>97</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -4574,25 +4574,25 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G19" s="2" t="s">
+      <c r="H19" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>277</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -4606,25 +4606,25 @@
         <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -4638,13 +4638,13 @@
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
@@ -4653,10 +4653,10 @@
         <v>109</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -4670,13 +4670,13 @@
         <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
@@ -4685,10 +4685,10 @@
         <v>103</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -4699,16 +4699,16 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>288</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
@@ -4717,10 +4717,10 @@
         <v>103</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -4731,28 +4731,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="H24" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>292</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -4763,28 +4763,28 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>294</v>
-      </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>212</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -4798,13 +4798,13 @@
         <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
@@ -4813,10 +4813,10 @@
         <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -4830,13 +4830,13 @@
         <v>204</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
@@ -4845,10 +4845,10 @@
         <v>91</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -4862,25 +4862,25 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -4894,13 +4894,13 @@
         <v>214</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
@@ -4909,10 +4909,10 @@
         <v>91</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -4926,13 +4926,13 @@
         <v>218</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
@@ -4941,10 +4941,10 @@
         <v>153</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>311</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -5042,13 +5042,13 @@
         <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>313</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
@@ -5057,7 +5057,7 @@
         <v>207</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>226</v>
+        <v>313</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>314</v>
@@ -5086,10 +5086,10 @@
         <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>226</v>
+        <v>313</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>317</v>
@@ -5150,7 +5150,7 @@
         <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>104</v>
@@ -5182,10 +5182,10 @@
         <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>326</v>
@@ -5214,10 +5214,10 @@
         <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>329</v>
@@ -5249,7 +5249,7 @@
         <v>91</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>332</v>
@@ -5281,7 +5281,7 @@
         <v>109</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>335</v>
@@ -5310,10 +5310,10 @@
         <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>338</v>
@@ -5327,7 +5327,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>339</v>
@@ -5342,10 +5342,10 @@
         <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>341</v>
@@ -5359,7 +5359,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>342</v>
@@ -5374,10 +5374,10 @@
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>344</v>
@@ -5406,10 +5406,10 @@
         <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>97</v>
+        <v>198</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>347</v>
@@ -5438,10 +5438,10 @@
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>350</v>
@@ -5470,10 +5470,10 @@
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>353</v>
@@ -5487,7 +5487,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>354</v>
@@ -5519,7 +5519,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>357</v>
@@ -5534,10 +5534,10 @@
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>359</v>
@@ -5569,7 +5569,7 @@
         <v>91</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>362</v>
@@ -5601,7 +5601,7 @@
         <v>97</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>365</v>
@@ -5630,10 +5630,10 @@
         <v>108</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>367</v>
@@ -5665,7 +5665,7 @@
         <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>370</v>
@@ -5697,7 +5697,7 @@
         <v>91</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>373</v>
@@ -5711,7 +5711,7 @@
         <v>35</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>374</v>
@@ -5729,7 +5729,7 @@
         <v>91</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>376</v>
@@ -5743,7 +5743,7 @@
         <v>35</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>377</v>
@@ -5761,7 +5761,7 @@
         <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>379</v>
@@ -5775,7 +5775,7 @@
         <v>35</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>380</v>
@@ -5790,10 +5790,10 @@
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>382</v>
@@ -5825,7 +5825,7 @@
         <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>385</v>
@@ -5854,10 +5854,10 @@
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>388</v>
@@ -5889,7 +5889,7 @@
         <v>91</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>391</v>
@@ -5921,7 +5921,7 @@
         <v>103</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>394</v>
@@ -5953,7 +5953,7 @@
         <v>153</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>397</v>
@@ -5982,7 +5982,7 @@
         <v>90</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>212</v>
@@ -6131,7 +6131,7 @@
         <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>104</v>
@@ -6163,7 +6163,7 @@
         <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>104</v>
@@ -6230,7 +6230,7 @@
         <v>91</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>415</v>
@@ -6259,10 +6259,10 @@
         <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>418</v>
@@ -6294,7 +6294,7 @@
         <v>103</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>421</v>
@@ -6326,7 +6326,7 @@
         <v>91</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>424</v>
@@ -6355,10 +6355,10 @@
         <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>427</v>
@@ -6372,7 +6372,7 @@
         <v>45</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>428</v>
@@ -6390,7 +6390,7 @@
         <v>91</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>430</v>
@@ -6404,7 +6404,7 @@
         <v>45</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>431</v>
@@ -6422,7 +6422,7 @@
         <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>433</v>
@@ -6454,7 +6454,7 @@
         <v>91</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>436</v>
@@ -6486,7 +6486,7 @@
         <v>91</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>439</v>
@@ -6518,7 +6518,7 @@
         <v>103</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>442</v>
@@ -6532,7 +6532,7 @@
         <v>45</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>443</v>
@@ -6550,7 +6550,7 @@
         <v>103</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>445</v>
@@ -6564,7 +6564,7 @@
         <v>45</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>446</v>
@@ -6579,10 +6579,10 @@
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>448</v>
@@ -6611,10 +6611,10 @@
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>451</v>
@@ -6643,10 +6643,10 @@
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>109</v>
+        <v>275</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>454</v>
@@ -6675,10 +6675,10 @@
         <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>276</v>
+        <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>457</v>
@@ -6707,10 +6707,10 @@
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>460</v>
@@ -6739,10 +6739,10 @@
         <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>463</v>
@@ -6756,7 +6756,7 @@
         <v>45</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>464</v>
@@ -6771,10 +6771,10 @@
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>276</v>
+        <v>103</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>466</v>
@@ -6788,7 +6788,7 @@
         <v>45</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>467</v>
@@ -6803,10 +6803,10 @@
         <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>91</v>
+        <v>275</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>469</v>
@@ -6820,7 +6820,7 @@
         <v>45</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>470</v>
@@ -6835,10 +6835,10 @@
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>472</v>
@@ -6870,7 +6870,7 @@
         <v>103</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>475</v>
@@ -6899,10 +6899,10 @@
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>478</v>
@@ -6934,7 +6934,7 @@
         <v>91</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>481</v>
@@ -7021,7 +7021,7 @@
     <col min="3" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7144,7 +7144,7 @@
         <v>97</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>493</v>
@@ -7173,10 +7173,10 @@
         <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>91</v>
+        <v>207</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>496</v>
@@ -7205,10 +7205,10 @@
         <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>207</v>
+        <v>91</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>499</v>
@@ -7240,7 +7240,7 @@
         <v>207</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>502</v>
@@ -7269,10 +7269,10 @@
         <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>505</v>
@@ -7301,10 +7301,10 @@
         <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>508</v>
@@ -7336,7 +7336,7 @@
         <v>103</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>510</v>
@@ -7350,7 +7350,7 @@
         <v>53</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>511</v>
@@ -7368,7 +7368,7 @@
         <v>207</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>513</v>
@@ -7382,7 +7382,7 @@
         <v>53</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>514</v>
@@ -7400,7 +7400,7 @@
         <v>144</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>516</v>
@@ -7432,7 +7432,7 @@
         <v>97</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>519</v>
@@ -7461,10 +7461,10 @@
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>207</v>
+        <v>97</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>522</v>
@@ -7493,7 +7493,7 @@
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>97</v>
+        <v>207</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>126</v>
@@ -7510,7 +7510,7 @@
         <v>53</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>526</v>
@@ -7528,7 +7528,7 @@
         <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>528</v>
@@ -7542,7 +7542,7 @@
         <v>53</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>529</v>
@@ -7557,10 +7557,10 @@
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>531</v>
@@ -7592,7 +7592,7 @@
         <v>91</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>534</v>
@@ -7624,7 +7624,7 @@
         <v>91</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>537</v>
@@ -7656,7 +7656,7 @@
         <v>97</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>540</v>
@@ -7688,7 +7688,7 @@
         <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>543</v>
@@ -7720,7 +7720,7 @@
         <v>109</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>546</v>
@@ -7734,7 +7734,7 @@
         <v>53</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>547</v>
@@ -7752,7 +7752,7 @@
         <v>91</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>549</v>
@@ -7766,7 +7766,7 @@
         <v>53</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>550</v>
@@ -7784,7 +7784,7 @@
         <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>552</v>
@@ -7798,7 +7798,7 @@
         <v>53</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>553</v>
@@ -7816,7 +7816,7 @@
         <v>91</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>555</v>
@@ -7848,7 +7848,7 @@
         <v>97</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>558</v>
@@ -7944,7 +7944,7 @@
         <v>97</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>567</v>
@@ -7973,7 +7973,7 @@
         <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>212</v>
@@ -8125,7 +8125,7 @@
         <v>103</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>226</v>
+        <v>313</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>576</v>
@@ -8157,7 +8157,7 @@
         <v>103</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>226</v>
+        <v>313</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>579</v>
@@ -8186,7 +8186,7 @@
         <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>104</v>
@@ -8250,7 +8250,7 @@
         <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>104</v>
@@ -8282,7 +8282,7 @@
         <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>245</v>
+        <v>109</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>104</v>
@@ -8314,10 +8314,10 @@
         <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>593</v>
@@ -8346,7 +8346,7 @@
         <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>126</v>
@@ -8378,10 +8378,10 @@
         <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>599</v>
@@ -8395,7 +8395,7 @@
         <v>61</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>600</v>
@@ -8413,7 +8413,7 @@
         <v>91</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>602</v>
@@ -8427,7 +8427,7 @@
         <v>61</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>603</v>
@@ -8445,7 +8445,7 @@
         <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>605</v>
@@ -8506,10 +8506,10 @@
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>611</v>
@@ -8541,7 +8541,7 @@
         <v>103</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>614</v>
@@ -8555,7 +8555,7 @@
         <v>61</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>615</v>
@@ -8573,7 +8573,7 @@
         <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>617</v>
@@ -8587,7 +8587,7 @@
         <v>61</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>618</v>
@@ -8602,10 +8602,10 @@
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>276</v>
+        <v>103</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>620</v>
@@ -8634,10 +8634,10 @@
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>91</v>
+        <v>275</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>154</v>
+        <v>193</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>623</v>
@@ -8669,7 +8669,7 @@
         <v>91</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>626</v>
@@ -8701,7 +8701,7 @@
         <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>629</v>
@@ -8733,7 +8733,7 @@
         <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>632</v>
@@ -8762,10 +8762,10 @@
         <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>153</v>
+        <v>91</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>635</v>
@@ -8779,7 +8779,7 @@
         <v>61</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>636</v>
@@ -8794,10 +8794,10 @@
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>109</v>
+        <v>153</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>638</v>
@@ -8811,7 +8811,7 @@
         <v>61</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>639</v>
@@ -8826,10 +8826,10 @@
         <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>245</v>
+        <v>109</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>641</v>
@@ -8843,7 +8843,7 @@
         <v>61</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>642</v>
@@ -8858,10 +8858,10 @@
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>644</v>
@@ -8893,7 +8893,7 @@
         <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>647</v>
@@ -8925,7 +8925,7 @@
         <v>91</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>650</v>
@@ -8954,10 +8954,10 @@
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>653</v>
@@ -8986,10 +8986,10 @@
         <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>656</v>
@@ -9326,7 +9326,7 @@
         <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>675</v>
@@ -9358,13 +9358,13 @@
         <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>153</v>
+        <v>198</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>685</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>686</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -9378,13 +9378,13 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>687</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>688</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
@@ -9393,7 +9393,7 @@
         <v>153</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>689</v>
@@ -9407,7 +9407,7 @@
         <v>69</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>690</v>
@@ -9422,7 +9422,7 @@
         <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>692</v>
@@ -9439,7 +9439,7 @@
         <v>69</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>694</v>
@@ -9457,7 +9457,7 @@
         <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>696</v>
@@ -9489,7 +9489,7 @@
         <v>103</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>699</v>
@@ -9521,7 +9521,7 @@
         <v>91</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>702</v>
@@ -9550,7 +9550,7 @@
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>675</v>
@@ -9567,7 +9567,7 @@
         <v>69</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>706</v>
@@ -9582,13 +9582,13 @@
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>276</v>
+        <v>207</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>708</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>709</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -9599,25 +9599,25 @@
         <v>69</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>711</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>685</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>712</v>
@@ -9646,10 +9646,10 @@
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>207</v>
+        <v>109</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>715</v>
@@ -9678,10 +9678,10 @@
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>718</v>
@@ -9713,7 +9713,7 @@
         <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>721</v>
@@ -9742,10 +9742,10 @@
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>724</v>
@@ -9774,7 +9774,7 @@
         <v>108</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>692</v>
@@ -9791,7 +9791,7 @@
         <v>69</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>727</v>
@@ -9806,7 +9806,7 @@
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>729</v>
@@ -9823,7 +9823,7 @@
         <v>69</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>731</v>
@@ -9855,7 +9855,7 @@
         <v>69</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>734</v>
@@ -9870,7 +9870,7 @@
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>729</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -11,19 +11,19 @@
     <sheet name="든솔" sheetId="2" r:id="rId2"/>
     <sheet name="만영" sheetId="3" r:id="rId3"/>
     <sheet name="지존길드" sheetId="4" r:id="rId4"/>
-    <sheet name="바텀" sheetId="5" r:id="rId5"/>
-    <sheet name="빅딜" sheetId="6" r:id="rId6"/>
+    <sheet name="빅딜" sheetId="5" r:id="rId5"/>
+    <sheet name="바텀" sheetId="6" r:id="rId6"/>
     <sheet name="따숨" sheetId="7" r:id="rId7"/>
     <sheet name="더위사냥" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">더위사냥!$A$1:$J$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">더위사냥!$A$1:$J$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">든솔!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">따숨!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">만영!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">바텀!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">빅딜!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">만영!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">바텀!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">빅딜!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">지존길드!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -84,7 +84,7 @@
     <t>Scania 13</t>
   </si>
   <si>
-    <t>888</t>
+    <t>890</t>
   </si>
   <si>
     <t>35위</t>
@@ -117,7 +117,7 @@
     <t>Scania 23</t>
   </si>
   <si>
-    <t>951</t>
+    <t>954</t>
   </si>
   <si>
     <t>14위</t>
@@ -168,6 +168,30 @@
     <t>2026.09.21</t>
   </si>
   <si>
+    <t>빅딜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%85%EB%94%9C</t>
+  </si>
+  <si>
+    <t>Scania 2</t>
+  </si>
+  <si>
+    <t>882</t>
+  </si>
+  <si>
+    <t>40위</t>
+  </si>
+  <si>
+    <t>5경 985조 128억 1537만</t>
+  </si>
+  <si>
+    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
+  </si>
+  <si>
+    <t>자유이용껀</t>
+  </si>
+  <si>
     <t>바텀</t>
   </si>
   <si>
@@ -177,7 +201,7 @@
     <t>Scania 29</t>
   </si>
   <si>
-    <t>906</t>
+    <t>909</t>
   </si>
   <si>
     <t>16위</t>
@@ -192,30 +216,6 @@
     <t>딜폿</t>
   </si>
   <si>
-    <t>빅딜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%85%EB%94%9C</t>
-  </si>
-  <si>
-    <t>Scania 2</t>
-  </si>
-  <si>
-    <t>879</t>
-  </si>
-  <si>
-    <t>40위</t>
-  </si>
-  <si>
-    <t>5경 985조 128억 1537만</t>
-  </si>
-  <si>
-    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
-  </si>
-  <si>
-    <t>자유이용껀</t>
-  </si>
-  <si>
     <t>따숨</t>
   </si>
   <si>
@@ -225,7 +225,7 @@
     <t>Scania 3</t>
   </si>
   <si>
-    <t>947</t>
+    <t>949</t>
   </si>
   <si>
     <t>42위</t>
@@ -249,7 +249,7 @@
     <t>Scania 50</t>
   </si>
   <si>
-    <t>905</t>
+    <t>908</t>
   </si>
   <si>
     <t>4위</t>
@@ -312,7 +312,7 @@
     <t>117</t>
   </si>
   <si>
-    <t>8경 8132조 7374억 560만</t>
+    <t>8경 9205조 5700억 6269만</t>
   </si>
   <si>
     <t>2</t>
@@ -363,7 +363,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>7580조 4757억 655만</t>
+    <t>7824조 6823억 4302만</t>
   </si>
   <si>
     <t>5</t>
@@ -375,7 +375,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%90%EC%B1%A0</t>
   </si>
   <si>
-    <t>6982조 9487억 2261만</t>
+    <t>6998조 1081억 3954만</t>
   </si>
   <si>
     <t>6</t>
@@ -387,7 +387,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%84%EA%B5%AC</t>
   </si>
   <si>
-    <t>5900조 1804억 1254만</t>
+    <t>6115조 7277억 9367만</t>
   </si>
   <si>
     <t>7</t>
@@ -399,7 +399,7 @@
     <t>https://mgf.gg/contents/character.php?n=GOD%EB%82%A0%EB%91%90</t>
   </si>
   <si>
-    <t>5630조 1490억 7657만</t>
+    <t>5633조 1947억 2114만</t>
   </si>
   <si>
     <t>8</t>
@@ -426,7 +426,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B0%8C%EB%B0%94%EB%A6%AC%EC%9D%B4</t>
   </si>
   <si>
-    <t>3513조 4639억 5612만</t>
+    <t>3528조 3231억 9159만</t>
   </si>
   <si>
     <t>10</t>
@@ -438,7 +438,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%B8%8C%ED%8F%AC%ED%8B%B0</t>
   </si>
   <si>
-    <t>3376조 9569억 1183만</t>
+    <t>3490조 5566억 1483만</t>
   </si>
   <si>
     <t>11</t>
@@ -474,6 +474,18 @@
     <t>13</t>
   </si>
   <si>
+    <t>서늘한그늘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%8A%98%ED%95%9C%EA%B7%B8%EB%8A%98</t>
+  </si>
+  <si>
+    <t>2609조 7534억 1122만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>황금어금니</t>
   </si>
   <si>
@@ -483,7 +495,7 @@
     <t>2498조 4801억 4342만</t>
   </si>
   <si>
-    <t>14</t>
+    <t>15</t>
   </si>
   <si>
     <t>탕비실도우미</t>
@@ -495,19 +507,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>2429조 2480억 9194만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>서늘한그늘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%8A%98%ED%95%9C%EA%B7%B8%EB%8A%98</t>
-  </si>
-  <si>
-    <t>2349조 6211억 5045만</t>
+    <t>2452조 2872억 9425만</t>
   </si>
   <si>
     <t>16</t>
@@ -537,7 +537,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9D%B4%ED%95%98%EB%A1%9C%ED%95%98%EB%9D%BC</t>
   </si>
   <si>
-    <t>1698조 5982억 3367만</t>
+    <t>1811조 9907억 8986만</t>
   </si>
   <si>
     <t>18</t>
@@ -597,7 +597,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
   </si>
   <si>
-    <t>1264조 4180억 6567만</t>
+    <t>1275조 6700억 9290만</t>
   </si>
   <si>
     <t>23</t>
@@ -615,7 +615,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>1251조 9810억 5510만</t>
+    <t>1256조 2669억 6167만</t>
   </si>
   <si>
     <t>24</t>
@@ -642,7 +642,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%9C%BC%EB%86%8D</t>
   </si>
   <si>
-    <t>1065조 6768억 9164만</t>
+    <t>1114조 4365억 3877만</t>
   </si>
   <si>
     <t>26</t>
@@ -684,7 +684,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A6%AC%EB%AF%B8%EC%BF%B5</t>
   </si>
   <si>
-    <t>577조 741억 7164만</t>
+    <t>578조 7351억 3168만</t>
   </si>
   <si>
     <t>29</t>
@@ -711,7 +711,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EA%B3%BD</t>
   </si>
   <si>
-    <t>1경 2526조 6847억 9408만</t>
+    <t>1경 3453조 1884억 923만</t>
   </si>
   <si>
     <t>형팡팡이</t>
@@ -738,7 +738,7 @@
     <t>https://mgf.gg/contents/character.php?n=2%EB%B2%88%EC%A7%B8%EC%BA%90%EB%A6%AD</t>
   </si>
   <si>
-    <t>3763조 8427억 4548만</t>
+    <t>3871조 8690억 6725만</t>
   </si>
   <si>
     <t>장뱁새</t>
@@ -747,7 +747,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B1%81%EC%83%88</t>
   </si>
   <si>
-    <t>3529조 2576억 465만</t>
+    <t>3529조 4313억 8306만</t>
   </si>
   <si>
     <t>꽁꽁냉법</t>
@@ -777,7 +777,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EA%B8%B0%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>2130조 4991억 7426만</t>
+    <t>2186조 8015억 8258만</t>
   </si>
   <si>
     <t>브네</t>
@@ -789,22 +789,31 @@
     <t>1928조 5981억 7061만</t>
   </si>
   <si>
+    <t>초앤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%95%A4</t>
+  </si>
+  <si>
+    <t>1836조 5603억 229만</t>
+  </si>
+  <si>
     <t>라쥬르</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%A5%AC%EB%A5%B4</t>
   </si>
   <si>
-    <t>1664조 1742억 9004만</t>
-  </si>
-  <si>
-    <t>초앤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%95%A4</t>
-  </si>
-  <si>
-    <t>1643조 2907억 5359만</t>
+    <t>1666조 7604억 8903만</t>
+  </si>
+  <si>
+    <t>33세배장호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=33%EC%84%B8%EB%B0%B0%EC%9E%A5%ED%98%B8</t>
+  </si>
+  <si>
+    <t>1476조 4908억 6363만</t>
   </si>
   <si>
     <t>재미있게놀래</t>
@@ -825,13 +834,13 @@
     <t>1383조 229억 4504만</t>
   </si>
   <si>
-    <t>33세배장호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=33%EC%84%B8%EB%B0%B0%EC%9E%A5%ED%98%B8</t>
-  </si>
-  <si>
-    <t>1370조 349억 8666만</t>
+    <t>적젹적</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%81%EC%A0%B9%EC%A0%81</t>
+  </si>
+  <si>
+    <t>1351조 4089억 5127만</t>
   </si>
   <si>
     <t>빙율</t>
@@ -843,34 +852,16 @@
     <t>1314조 7187억 8022만</t>
   </si>
   <si>
-    <t>적젹적</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%81%EC%A0%B9%EC%A0%81</t>
-  </si>
-  <si>
-    <t>1248조 9061억 9176만</t>
-  </si>
-  <si>
-    <t>최빵쭈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EB%B9%B5%EC%AD%88</t>
+    <t>타뤽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%A4%BD</t>
   </si>
   <si>
     <t>바이퍼</t>
   </si>
   <si>
-    <t>980조 2953억 7066만</t>
-  </si>
-  <si>
-    <t>타뤽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%A4%BD</t>
-  </si>
-  <si>
-    <t>961조 5316억 9637만</t>
+    <t>963조 2666억 6563만</t>
   </si>
   <si>
     <t>정기휴므</t>
@@ -879,7 +870,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EA%B8%B0%ED%9C%B4%EB%AF%80</t>
   </si>
   <si>
-    <t>916조 586억 5018만</t>
+    <t>951조 4170억 2333만</t>
   </si>
   <si>
     <t>무르스</t>
@@ -888,7 +879,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%A5%B4%EC%8A%A4</t>
   </si>
   <si>
-    <t>785조 1486억 9137만</t>
+    <t>794조 7429억 9895만</t>
   </si>
   <si>
     <t>채황새</t>
@@ -915,7 +906,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%AC%EC%83%B7</t>
   </si>
   <si>
-    <t>639조 5314억 3480만</t>
+    <t>640조 1353억 8502만</t>
   </si>
   <si>
     <t>박도란</t>
@@ -942,7 +933,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EC%95%B5%EB%BF%8C%EC%95%B5</t>
   </si>
   <si>
-    <t>418조 4422억 2130만</t>
+    <t>428조 4505억 9744만</t>
   </si>
   <si>
     <t>냥홍이</t>
@@ -951,7 +942,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%ED%99%8D%EC%9D%B4</t>
   </si>
   <si>
-    <t>378조 3540억 524만</t>
+    <t>395조 9488억 9628만</t>
   </si>
   <si>
     <t>윤빵쭈</t>
@@ -975,7 +966,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>9978조 808억 2146만</t>
+    <t>1경 2조 9357억 3558만</t>
   </si>
   <si>
     <t>수텍</t>
@@ -1020,7 +1011,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
   </si>
   <si>
-    <t>3748조 4878억 3605만</t>
+    <t>3780조 4364억 4613만</t>
   </si>
   <si>
     <t>댜니</t>
@@ -1032,22 +1023,22 @@
     <t>2886조 9873억 5134만</t>
   </si>
   <si>
+    <t>뿡쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
+  </si>
+  <si>
+    <t>2633조 4371억 8860만</t>
+  </si>
+  <si>
     <t>포항가자미</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
   </si>
   <si>
-    <t>2601조 9210억 8658만</t>
-  </si>
-  <si>
-    <t>뿡쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
-  </si>
-  <si>
-    <t>2601조 5344억 7218만</t>
+    <t>2608조 4541억 5961만</t>
   </si>
   <si>
     <t>엘르가든</t>
@@ -1083,7 +1074,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
   </si>
   <si>
-    <t>2417조 8596억 1972만</t>
+    <t>2435조 2954억 8900만</t>
   </si>
   <si>
     <t>파울</t>
@@ -1101,7 +1092,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
   </si>
   <si>
-    <t>1889조 8524억 3410만</t>
+    <t>2053조 6196억 299만</t>
   </si>
   <si>
     <t>대좀이</t>
@@ -1110,7 +1101,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>1495조 1977억 19만</t>
+    <t>1497조 9515억 7380만</t>
   </si>
   <si>
     <t>모짜리코베르</t>
@@ -1119,7 +1110,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
   </si>
   <si>
-    <t>1412조 3496억 5023만</t>
+    <t>1415조 2191억 2464만</t>
   </si>
   <si>
     <t>오옹나이스</t>
@@ -1152,7 +1143,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
   </si>
   <si>
-    <t>1206조 1272억 7177만</t>
+    <t>1235조 7285억 909만</t>
   </si>
   <si>
     <t>기본이리</t>
@@ -1161,7 +1152,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
   </si>
   <si>
-    <t>1163조 6084억 6277만</t>
+    <t>1176조 3129억 5474만</t>
   </si>
   <si>
     <t>짱잘자쿨냥</t>
@@ -1179,7 +1170,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EC%9D%80</t>
   </si>
   <si>
-    <t>1091조 572억 7018만</t>
+    <t>1109조 1781억 7811만</t>
   </si>
   <si>
     <t>전산봉</t>
@@ -1206,7 +1197,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
   </si>
   <si>
-    <t>863조 8050억 2721만</t>
+    <t>865조 8935억 5088만</t>
   </si>
   <si>
     <t>Doham</t>
@@ -1215,7 +1206,7 @@
     <t>https://mgf.gg/contents/character.php?n=Doham</t>
   </si>
   <si>
-    <t>825조 9666억 8220만</t>
+    <t>840조 147억 74만</t>
   </si>
   <si>
     <t>유플러스</t>
@@ -1224,7 +1215,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%94%8C%EB%9F%AC%EC%8A%A4</t>
   </si>
   <si>
-    <t>649조 5527억 6316만</t>
+    <t>651조 6536억 3056만</t>
   </si>
   <si>
     <t>30</t>
@@ -1239,6 +1230,273 @@
     <t>355조 5297억 5157만</t>
   </si>
   <si>
+    <t>아이스꾸임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
+  </si>
+  <si>
+    <t>2경 1503조 25억 9857만</t>
+  </si>
+  <si>
+    <t>굴러가는일상</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
+  </si>
+  <si>
+    <t>8237조 7144억 4543만</t>
+  </si>
+  <si>
+    <t>엘라임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
+  </si>
+  <si>
+    <t>5314조 9961억 763만</t>
+  </si>
+  <si>
+    <t>흑두부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
+  </si>
+  <si>
+    <t>4279조 3156억 7061만</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>4270조 7688억 5784만</t>
+  </si>
+  <si>
+    <t>서포터즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
+  </si>
+  <si>
+    <t>3121조 7410억 5159만</t>
+  </si>
+  <si>
+    <t>야가다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>2586조 1679억 2303만</t>
+  </si>
+  <si>
+    <t>뻥뻥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
+  </si>
+  <si>
+    <t>2486조 1038억 1649만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
+    <t>2422조 114억 1172만</t>
+  </si>
+  <si>
+    <t>KR#TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>2398조 1780억 1990만</t>
+  </si>
+  <si>
+    <t>불보독지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
+  </si>
+  <si>
+    <t>1385조 8857억 654만</t>
+  </si>
+  <si>
+    <t>우후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
+  </si>
+  <si>
+    <t>1289조 3983억 8443만</t>
+  </si>
+  <si>
+    <t>단풍카우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>1165조 9797억 9783만</t>
+  </si>
+  <si>
+    <t>호우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>1162조 8444억 6844만</t>
+  </si>
+  <si>
+    <t>채무조정</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
+  </si>
+  <si>
+    <t>1109조 8902억 2955만</t>
+  </si>
+  <si>
+    <t>뽀송히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
+  </si>
+  <si>
+    <t>1083조 1337억 843만</t>
+  </si>
+  <si>
+    <t>좀치는형님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
+  </si>
+  <si>
+    <t>1079조 4522억 1643만</t>
+  </si>
+  <si>
+    <t>정태준</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
+  </si>
+  <si>
+    <t>980조 8900억 6780만</t>
+  </si>
+  <si>
+    <t>라탱호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%ED%83%B1%ED%98%B8</t>
+  </si>
+  <si>
+    <t>962조 9548억 692만</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>800조 2195억 6508만</t>
+  </si>
+  <si>
+    <t>짤똘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%A4%EB%98%98</t>
+  </si>
+  <si>
+    <t>789조 1148억 491만</t>
+  </si>
+  <si>
+    <t>팡대지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
+  </si>
+  <si>
+    <t>660조 4847억 7151만</t>
+  </si>
+  <si>
+    <t>민들레꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
+  </si>
+  <si>
+    <t>636조 6762억 2968만</t>
+  </si>
+  <si>
+    <t>박준우2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
+  </si>
+  <si>
+    <t>588조 4551억 8369만</t>
+  </si>
+  <si>
+    <t>컨덱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A8%EB%8D%B1</t>
+  </si>
+  <si>
+    <t>541조 1466억 9068만</t>
+  </si>
+  <si>
+    <t>솔인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>491조 909억 6019만</t>
+  </si>
+  <si>
+    <t>3030</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=3030</t>
+  </si>
+  <si>
+    <t>414조 4027억 9667만</t>
+  </si>
+  <si>
+    <t>아르미느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
+  </si>
+  <si>
+    <t>343조 4896억 82만</t>
+  </si>
+  <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>332조 666억 5468만</t>
+  </si>
+  <si>
+    <t>꼬북빵야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
+  </si>
+  <si>
+    <t>275조 6869억 3523만</t>
+  </si>
+  <si>
     <t>전액할부</t>
   </si>
   <si>
@@ -1254,7 +1512,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%96%A5</t>
   </si>
   <si>
-    <t>1경 247조 8680억 9380만</t>
+    <t>1경 264조 2244억 9740만</t>
   </si>
   <si>
     <t>례전</t>
@@ -1263,7 +1521,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%80%EC%A0%84</t>
   </si>
   <si>
-    <t>4585조 3930억 967만</t>
+    <t>4593조 9364억 5767만</t>
   </si>
   <si>
     <t>숭타이준</t>
@@ -1272,13 +1530,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%ED%83%80%EC%9D%B4%EC%A4%80</t>
   </si>
   <si>
-    <t>3854조 5686억 5069만</t>
+    <t>3869조 4442억 8322만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%94%9C%ED%8F%BF</t>
   </si>
   <si>
-    <t>2987조 5147억 8598만</t>
+    <t>3234조 771억 9586만</t>
   </si>
   <si>
     <t>뻑걸</t>
@@ -1287,7 +1545,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%91%EA%B1%B8</t>
   </si>
   <si>
-    <t>2431조 2307억 9064만</t>
+    <t>2511조 2446억 4802만</t>
   </si>
   <si>
     <t>지존빵수</t>
@@ -1296,7 +1554,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%B5%EC%88%98</t>
   </si>
   <si>
-    <t>2382조 2085억 8241만</t>
+    <t>2383조 6169억 7980만</t>
   </si>
   <si>
     <t>야키산</t>
@@ -1314,7 +1572,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%8F%BF</t>
   </si>
   <si>
-    <t>2110조 5743억 8233만</t>
+    <t>2237조 7036억 8468만</t>
   </si>
   <si>
     <t>문제적남자</t>
@@ -1323,7 +1581,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EC%A0%9C%EC%A0%81%EB%82%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>1997조 2870억 868만</t>
+    <t>2058조 8049억 2498만</t>
   </si>
   <si>
     <t>아이리쉬</t>
@@ -1341,7 +1599,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AE%AC%EC%9D%B4</t>
   </si>
   <si>
-    <t>1853조 5868억 1940만</t>
+    <t>1870조 5997억 7289만</t>
   </si>
   <si>
     <t>화둥에불낸년</t>
@@ -1359,7 +1617,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%8A%A4%EC%BC%80</t>
   </si>
   <si>
-    <t>1360조 4786억 2292만</t>
+    <t>1362조 6987억 8889만</t>
   </si>
   <si>
     <t>우즈2텐겐</t>
@@ -1377,7 +1635,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B2%8C%EC%9A%A9</t>
   </si>
   <si>
-    <t>1104조 4725억 1959만</t>
+    <t>1106조 6561억 6466만</t>
   </si>
   <si>
     <t>기똥찬벌레</t>
@@ -1386,7 +1644,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%98%A5%EC%B0%AC%EB%B2%8C%EB%A0%88</t>
   </si>
   <si>
-    <t>1064조 4710억 2623만</t>
+    <t>1066조 4037억 2386만</t>
   </si>
   <si>
     <t>구도류</t>
@@ -1422,7 +1680,7 @@
     <t>https://mgf.gg/contents/character.php?n=JJuna</t>
   </si>
   <si>
-    <t>939조 5662억 4094만</t>
+    <t>962조 959억 5775만</t>
   </si>
   <si>
     <t>콜리셰마드르</t>
@@ -1431,7 +1689,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%9C%EB%A6%AC%EC%85%B0%EB%A7%88%EB%93%9C%EB%A5%B4</t>
   </si>
   <si>
-    <t>856조 9999억 6656만</t>
+    <t>858조 8456억 8798만</t>
   </si>
   <si>
     <t>난센</t>
@@ -1440,7 +1698,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EC%84%BC</t>
   </si>
   <si>
-    <t>838조 4774억 5664만</t>
+    <t>839조 5564억 6737만</t>
   </si>
   <si>
     <t>에프람</t>
@@ -1458,7 +1716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%B1%84%EC%95%84%EB%B2%84%EC%A7%80</t>
   </si>
   <si>
-    <t>690조 1540억 2234만</t>
+    <t>707조 3486억 5299만</t>
   </si>
   <si>
     <t>조단23</t>
@@ -1467,7 +1725,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%8B%A823</t>
   </si>
   <si>
-    <t>669조 6960억 2046만</t>
+    <t>673조 6230억 6232만</t>
   </si>
   <si>
     <t>아콩린</t>
@@ -1476,7 +1734,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BD%A9%EB%A6%B0</t>
   </si>
   <si>
-    <t>567조 831억 836만</t>
+    <t>633조 5157억 4903만</t>
   </si>
   <si>
     <t>별루루</t>
@@ -1488,273 +1746,6 @@
     <t>520조 3064억 1208만</t>
   </si>
   <si>
-    <t>아이스꾸임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
-  </si>
-  <si>
-    <t>2경 1286조 1305억 8124만</t>
-  </si>
-  <si>
-    <t>굴러가는일상</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
-  </si>
-  <si>
-    <t>8237조 7144억 4543만</t>
-  </si>
-  <si>
-    <t>엘라임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
-  </si>
-  <si>
-    <t>5071조 9596억 5566만</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>4270조 7688억 5784만</t>
-  </si>
-  <si>
-    <t>흑두부</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
-  </si>
-  <si>
-    <t>4269조 1039억 8746만</t>
-  </si>
-  <si>
-    <t>서포터즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
-  </si>
-  <si>
-    <t>3121조 7410억 5159만</t>
-  </si>
-  <si>
-    <t>야가다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>2586조 1679억 2303만</t>
-  </si>
-  <si>
-    <t>뻥뻥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
-  </si>
-  <si>
-    <t>2486조 1038억 1649만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
-  </si>
-  <si>
-    <t>2422조 114억 1172만</t>
-  </si>
-  <si>
-    <t>KR#TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>2398조 1780억 1990만</t>
-  </si>
-  <si>
-    <t>불보독지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
-  </si>
-  <si>
-    <t>1369조 9106억 6331만</t>
-  </si>
-  <si>
-    <t>우후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
-  </si>
-  <si>
-    <t>1220조 2777억 7534만</t>
-  </si>
-  <si>
-    <t>단풍카우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>1160조 9002억 9166만</t>
-  </si>
-  <si>
-    <t>호우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>1157조 1910억 165만</t>
-  </si>
-  <si>
-    <t>채무조정</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
-  </si>
-  <si>
-    <t>1109조 6605억 1793만</t>
-  </si>
-  <si>
-    <t>뽀송히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
-  </si>
-  <si>
-    <t>1075조 4922억 3766만</t>
-  </si>
-  <si>
-    <t>좀치는형님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
-  </si>
-  <si>
-    <t>1044조 7501억 1470만</t>
-  </si>
-  <si>
-    <t>정태준</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
-  </si>
-  <si>
-    <t>978조 1277억 921만</t>
-  </si>
-  <si>
-    <t>라탱호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%ED%83%B1%ED%98%B8</t>
-  </si>
-  <si>
-    <t>949조 844억 137만</t>
-  </si>
-  <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>795조 8961억 4737만</t>
-  </si>
-  <si>
-    <t>짤똘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%A4%EB%98%98</t>
-  </si>
-  <si>
-    <t>789조 1148억 491만</t>
-  </si>
-  <si>
-    <t>팡대지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
-  </si>
-  <si>
-    <t>633조 4865억 8284만</t>
-  </si>
-  <si>
-    <t>박준우2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
-  </si>
-  <si>
-    <t>588조 4551억 8369만</t>
-  </si>
-  <si>
-    <t>민들레꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
-  </si>
-  <si>
-    <t>560조 8091억 6899만</t>
-  </si>
-  <si>
-    <t>컨덱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A8%EB%8D%B1</t>
-  </si>
-  <si>
-    <t>541조 1466억 9068만</t>
-  </si>
-  <si>
-    <t>솔인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>491조 909억 6019만</t>
-  </si>
-  <si>
-    <t>3030</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=3030</t>
-  </si>
-  <si>
-    <t>414조 4027억 9667만</t>
-  </si>
-  <si>
-    <t>아르미느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
-  </si>
-  <si>
-    <t>342조 6836억 897만</t>
-  </si>
-  <si>
-    <t>여눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
-  </si>
-  <si>
-    <t>328조 9422억 4240만</t>
-  </si>
-  <si>
-    <t>꼬북빵야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
-  </si>
-  <si>
-    <t>275조 6869억 3523만</t>
-  </si>
-  <si>
     <t>꺄꽁</t>
   </si>
   <si>
@@ -1788,10 +1779,10 @@
     <t>4829조 6442억 8620만</t>
   </si>
   <si>
-    <t>극강딘딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B9%EA%B0%95%EB%94%98%EB%94%98</t>
+    <t>루미딘딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%AF%B8%EB%94%98%EB%94%98</t>
   </si>
   <si>
     <t>4673조 2270억 6338만</t>
@@ -1803,7 +1794,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%ED%99%A9%EA%B8%88%EB%A7%9D%EC%B9%98</t>
   </si>
   <si>
-    <t>4225조 3118억 1638만</t>
+    <t>4337조 2344억 5028만</t>
   </si>
   <si>
     <t>김슴줌1</t>
@@ -1812,7 +1803,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%8A%B4%EC%A4%8C1</t>
   </si>
   <si>
-    <t>3828조 8506억 7503만</t>
+    <t>4035조 8043억 3887만</t>
   </si>
   <si>
     <t>천달</t>
@@ -1821,7 +1812,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EB%8B%AC</t>
   </si>
   <si>
-    <t>3401조 2076억 5645만</t>
+    <t>3451조 2225억 9996만</t>
   </si>
   <si>
     <t>활용</t>
@@ -1848,7 +1839,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EB%8C%9C</t>
   </si>
   <si>
-    <t>2284조 7558억 6909만</t>
+    <t>2330조 8222억 622만</t>
   </si>
   <si>
     <t>뚜징</t>
@@ -1857,7 +1848,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EC%A7%95</t>
   </si>
   <si>
-    <t>1975조 6421억 1426만</t>
+    <t>1992조 8747억 4996만</t>
   </si>
   <si>
     <t>게렬곰</t>
@@ -1866,7 +1857,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%EB%A0%AC%EA%B3%B0</t>
   </si>
   <si>
-    <t>1153조 760억 2019만</t>
+    <t>1254조 8103억 1015만</t>
   </si>
   <si>
     <t>별곡</t>
@@ -1875,7 +1866,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EA%B3%A1</t>
   </si>
   <si>
-    <t>1054조 8889억 3800만</t>
+    <t>1083조 4642억 8142만</t>
+  </si>
+  <si>
+    <t>턍ol</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%84%8Dol</t>
+  </si>
+  <si>
+    <t>1037조 7222억 2898만</t>
   </si>
   <si>
     <t>동래</t>
@@ -1887,15 +1887,6 @@
     <t>1019조 1472억 4526만</t>
   </si>
   <si>
-    <t>턍ol</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%84%8Dol</t>
-  </si>
-  <si>
-    <t>1018조 423억 1232만</t>
-  </si>
-  <si>
     <t>까쿠미</t>
   </si>
   <si>
@@ -1920,7 +1911,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A4</t>
   </si>
   <si>
-    <t>857조 1724억 1289만</t>
+    <t>868조 9917억 7790만</t>
   </si>
   <si>
     <t>띠우</t>
@@ -1929,7 +1920,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%A0%EC%9A%B0</t>
   </si>
   <si>
-    <t>738조 8473억 6027만</t>
+    <t>772조 7389억 4886만</t>
   </si>
   <si>
     <t>쿠까미</t>
@@ -1956,7 +1947,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%81%84%EC%B1%B0</t>
   </si>
   <si>
-    <t>528조 8805억 3793만</t>
+    <t>552조 4981억 6746만</t>
   </si>
   <si>
     <t>왕단단이</t>
@@ -1974,7 +1965,7 @@
     <t>https://mgf.gg/contents/character.php?n=08217</t>
   </si>
   <si>
-    <t>464조 8617억 3924만</t>
+    <t>467조 4072억 9599만</t>
   </si>
   <si>
     <t>승아의하루</t>
@@ -1992,7 +1983,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%9D%B4%EC%A5%94</t>
   </si>
   <si>
-    <t>414조 9409억 2274만</t>
+    <t>417조 1392억 4322만</t>
   </si>
   <si>
     <t>택Ol</t>
@@ -2001,7 +1992,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9DOl</t>
   </si>
   <si>
-    <t>353조 685억 3200만</t>
+    <t>359조 477억 8424만</t>
   </si>
   <si>
     <t>달갸뤼</t>
@@ -2010,7 +2001,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EA%B0%B8%EB%A4%BC</t>
   </si>
   <si>
-    <t>168조 5947억 734만</t>
+    <t>168조 6781억 8660만</t>
   </si>
   <si>
     <t>교주만두</t>
@@ -2019,7 +2010,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%90%EC%A3%BC%EB%A7%8C%EB%91%90</t>
   </si>
   <si>
-    <t>9경 2199조 6025억 4870만</t>
+    <t>9경 2881조 1976억 6044만</t>
+  </si>
+  <si>
+    <t>섹밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B9%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>253조 1410억 7134만</t>
   </si>
   <si>
     <t>할바이</t>
@@ -2034,22 +2034,13 @@
     <t>249조 9358억 1984만</t>
   </si>
   <si>
-    <t>섹밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B9%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>249조 6678억 2263만</t>
-  </si>
-  <si>
     <t>대구남성</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EA%B5%AC%EB%82%A8%EC%84%B1</t>
   </si>
   <si>
-    <t>82조 3950억 4249만</t>
+    <t>95조 2278억 1384만</t>
   </si>
   <si>
     <t>코잉코잉</t>
@@ -2061,7 +2052,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>73조 3330억 5992만</t>
+    <t>76조 2120억 9520만</t>
   </si>
   <si>
     <t>오스띤</t>
@@ -2088,7 +2079,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%B2%A4%EC%88%8D%EC%9D%B4</t>
   </si>
   <si>
-    <t>55조 717억 8007만</t>
+    <t>55조 7824억 2223만</t>
   </si>
   <si>
     <t>빵신궁</t>
@@ -2100,7 +2091,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>42조 5391억 2100만</t>
+    <t>42조 9188억 4648만</t>
   </si>
   <si>
     <t>썬콜우체국</t>
@@ -2112,7 +2103,25 @@
     <t>103</t>
   </si>
   <si>
-    <t>35조 6541억 2160만</t>
+    <t>35조 8175억 3821만</t>
+  </si>
+  <si>
+    <t>배렛나루왁서</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%EB%A0%9B%EB%82%98%EB%A3%A8%EC%99%81%EC%84%9C</t>
+  </si>
+  <si>
+    <t>35조 7009억 9309만</t>
+  </si>
+  <si>
+    <t>킬혁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%AC%ED%98%81</t>
+  </si>
+  <si>
+    <t>34조 8764억 1955만</t>
   </si>
   <si>
     <t>밀초크코</t>
@@ -2124,13 +2133,13 @@
     <t>34조 2125억 4874만</t>
   </si>
   <si>
-    <t>킬혁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%AC%ED%98%81</t>
-  </si>
-  <si>
-    <t>31조 8779억 9321만</t>
+    <t>마키맛키마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%82%A4%EB%A7%9B%ED%82%A4%EB%A7%88</t>
+  </si>
+  <si>
+    <t>32조 3628억 58만</t>
   </si>
   <si>
     <t>고통받는갈비</t>
@@ -2142,24 +2151,6 @@
     <t>31조 7895억 5650만</t>
   </si>
   <si>
-    <t>마키맛키마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%82%A4%EB%A7%9B%ED%82%A4%EB%A7%88</t>
-  </si>
-  <si>
-    <t>30조 6567억 26만</t>
-  </si>
-  <si>
-    <t>배렛나루왁서</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%EB%A0%9B%EB%82%98%EB%A3%A8%EC%99%81%EC%84%9C</t>
-  </si>
-  <si>
-    <t>27조 8183억 2622만</t>
-  </si>
-  <si>
     <t>문보겨엉</t>
   </si>
   <si>
@@ -2178,7 +2169,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%95%A1%EC%9A%94%EB%82%98%ED%90%81</t>
   </si>
   <si>
-    <t>25조 7434억 2413만</t>
+    <t>26조 1277억 5625만</t>
   </si>
   <si>
     <t>썬콜법사ss</t>
@@ -2187,7 +2178,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%ACss</t>
   </si>
   <si>
-    <t>24조 5393억 7309만</t>
+    <t>25조 2013억 7487만</t>
+  </si>
+  <si>
+    <t>맹탐정코난</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%B9%ED%83%90%EC%A0%95%EC%BD%94%EB%82%9C</t>
+  </si>
+  <si>
+    <t>22조 6919억 8673만</t>
   </si>
   <si>
     <t>페프릭2</t>
@@ -2196,7 +2196,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8E%98%ED%94%84%EB%A6%AD2</t>
   </si>
   <si>
-    <t>21조 8848억 7036만</t>
+    <t>22조 4519억 9962만</t>
   </si>
   <si>
     <t>포디케이</t>
@@ -2205,7 +2205,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%94%94%EC%BC%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>17조 2732억 7149만</t>
+    <t>17조 4010억 8790만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%ED%82%A4%EB%B9%84%ED%82%A4</t>
@@ -2241,7 +2241,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%9D%EC%9C%A4</t>
   </si>
   <si>
-    <t>4조 365억 7156만</t>
+    <t>4조 381억 8679만</t>
   </si>
 </sst>
 </file>
@@ -2810,7 +2810,7 @@
         <v>19</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>50</v>
@@ -2822,7 +2822,7 @@
         <v>52</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2851,7 +2851,7 @@
         <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>58</v>
@@ -2863,7 +2863,7 @@
         <v>60</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2974,7 +2974,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3446,13 +3446,13 @@
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3463,25 +3463,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="H16" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>158</v>
@@ -3862,7 +3862,7 @@
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>212</v>
@@ -3977,7 +3977,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3986,7 +3986,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4333,7 +4333,7 @@
         <v>109</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>251</v>
@@ -4362,10 +4362,10 @@
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>254</v>
@@ -4394,10 +4394,10 @@
         <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>257</v>
@@ -4426,7 +4426,7 @@
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>198</v>
+        <v>91</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>163</v>
@@ -4461,7 +4461,7 @@
         <v>198</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>263</v>
@@ -4475,7 +4475,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>264</v>
@@ -4490,10 +4490,10 @@
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>91</v>
+        <v>198</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>163</v>
+        <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>266</v>
@@ -4522,7 +4522,7 @@
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>163</v>
@@ -4554,7 +4554,7 @@
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>163</v>
@@ -4618,7 +4618,7 @@
         <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>275</v>
+        <v>109</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>163</v>
@@ -4650,7 +4650,7 @@
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>163</v>
@@ -4685,7 +4685,7 @@
         <v>103</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>285</v>
@@ -4714,7 +4714,7 @@
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>103</v>
+        <v>192</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>193</v>
@@ -4749,7 +4749,7 @@
         <v>192</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>291</v>
@@ -4778,10 +4778,10 @@
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>192</v>
+        <v>91</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>294</v>
@@ -4842,10 +4842,10 @@
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>91</v>
+        <v>162</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>300</v>
@@ -4874,7 +4874,7 @@
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>163</v>
@@ -4906,52 +4906,20 @@
         <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>91</v>
+        <v>157</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>163</v>
+        <v>306</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J29"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -4981,7 +4949,6 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5042,13 +5009,13 @@
         <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
@@ -5057,10 +5024,10 @@
         <v>207</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>44</v>
@@ -5074,13 +5041,13 @@
         <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
@@ -5089,10 +5056,10 @@
         <v>244</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>44</v>
@@ -5106,13 +5073,13 @@
         <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
@@ -5124,7 +5091,7 @@
         <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>44</v>
@@ -5138,13 +5105,13 @@
         <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
@@ -5156,7 +5123,7 @@
         <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>44</v>
@@ -5170,13 +5137,13 @@
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>90</v>
@@ -5188,7 +5155,7 @@
         <v>126</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>44</v>
@@ -5202,13 +5169,13 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
@@ -5220,7 +5187,7 @@
         <v>104</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>44</v>
@@ -5234,13 +5201,13 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
@@ -5252,7 +5219,7 @@
         <v>126</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>44</v>
@@ -5266,25 +5233,25 @@
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>139</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>44</v>
@@ -5298,25 +5265,25 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>162</v>
+        <v>109</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>139</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>44</v>
@@ -5330,13 +5297,13 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -5348,7 +5315,7 @@
         <v>104</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>44</v>
@@ -5362,13 +5329,13 @@
         <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
@@ -5380,7 +5347,7 @@
         <v>139</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>44</v>
@@ -5394,13 +5361,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
@@ -5412,7 +5379,7 @@
         <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>44</v>
@@ -5426,13 +5393,13 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
@@ -5444,7 +5411,7 @@
         <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>44</v>
@@ -5458,13 +5425,13 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
@@ -5476,7 +5443,7 @@
         <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>44</v>
@@ -5487,16 +5454,16 @@
         <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
@@ -5508,7 +5475,7 @@
         <v>104</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>44</v>
@@ -5522,13 +5489,13 @@
         <v>159</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
@@ -5540,7 +5507,7 @@
         <v>139</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>44</v>
@@ -5554,13 +5521,13 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
@@ -5572,7 +5539,7 @@
         <v>139</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>44</v>
@@ -5586,13 +5553,13 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
@@ -5604,7 +5571,7 @@
         <v>139</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>44</v>
@@ -5624,7 +5591,7 @@
         <v>43</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>108</v>
@@ -5636,7 +5603,7 @@
         <v>139</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>44</v>
@@ -5650,13 +5617,13 @@
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
@@ -5668,7 +5635,7 @@
         <v>139</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>44</v>
@@ -5682,13 +5649,13 @@
         <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
@@ -5700,7 +5667,7 @@
         <v>139</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>44</v>
@@ -5714,13 +5681,13 @@
         <v>185</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
@@ -5732,7 +5699,7 @@
         <v>139</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>44</v>
@@ -5746,13 +5713,13 @@
         <v>189</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
@@ -5764,7 +5731,7 @@
         <v>163</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>44</v>
@@ -5778,13 +5745,13 @@
         <v>195</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
@@ -5796,7 +5763,7 @@
         <v>163</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>44</v>
@@ -5810,13 +5777,13 @@
         <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
@@ -5828,7 +5795,7 @@
         <v>193</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>44</v>
@@ -5842,13 +5809,13 @@
         <v>204</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
@@ -5860,7 +5827,7 @@
         <v>193</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>44</v>
@@ -5874,13 +5841,13 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
@@ -5892,7 +5859,7 @@
         <v>163</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>44</v>
@@ -5906,13 +5873,13 @@
         <v>214</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
@@ -5924,7 +5891,7 @@
         <v>193</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>44</v>
@@ -5938,25 +5905,25 @@
         <v>218</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>163</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>44</v>
@@ -5967,16 +5934,16 @@
         <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>90</v>
@@ -5988,7 +5955,7 @@
         <v>212</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>44</v>
@@ -6034,985 +6001,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J29"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7021,7 +6009,7 @@
     <col min="3" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7059,19 +6047,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>485</v>
+        <v>399</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>485</v>
+        <v>399</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>486</v>
+        <v>400</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
@@ -7083,7 +6071,7 @@
         <v>98</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>487</v>
+        <v>401</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>44</v>
@@ -7091,19 +6079,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>488</v>
+        <v>402</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>488</v>
+        <v>402</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>489</v>
+        <v>403</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
@@ -7115,7 +6103,7 @@
         <v>104</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>490</v>
+        <v>404</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>44</v>
@@ -7123,19 +6111,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>491</v>
+        <v>405</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>491</v>
+        <v>405</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>492</v>
+        <v>406</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
@@ -7147,7 +6135,7 @@
         <v>126</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>493</v>
+        <v>407</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>44</v>
@@ -7155,31 +6143,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>494</v>
+        <v>408</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>494</v>
+        <v>408</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>495</v>
+        <v>409</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>207</v>
+        <v>91</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>496</v>
+        <v>410</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>44</v>
@@ -7187,31 +6175,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>497</v>
+        <v>411</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>497</v>
+        <v>411</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>498</v>
+        <v>412</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>91</v>
+        <v>207</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>499</v>
+        <v>413</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>44</v>
@@ -7219,19 +6207,19 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>500</v>
+        <v>414</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>500</v>
+        <v>414</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>501</v>
+        <v>415</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
@@ -7243,7 +6231,7 @@
         <v>126</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>502</v>
+        <v>416</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>44</v>
@@ -7251,19 +6239,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>503</v>
+        <v>417</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>503</v>
+        <v>417</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>504</v>
+        <v>418</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
@@ -7275,7 +6263,7 @@
         <v>126</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>505</v>
+        <v>419</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>44</v>
@@ -7283,19 +6271,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>506</v>
+        <v>420</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>506</v>
+        <v>420</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>507</v>
+        <v>421</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
@@ -7307,7 +6295,7 @@
         <v>163</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>508</v>
+        <v>422</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>44</v>
@@ -7315,19 +6303,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>509</v>
+        <v>423</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>108</v>
@@ -7339,7 +6327,7 @@
         <v>163</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>510</v>
+        <v>424</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>44</v>
@@ -7347,19 +6335,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>511</v>
+        <v>425</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>511</v>
+        <v>425</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>512</v>
+        <v>426</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -7371,7 +6359,7 @@
         <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>513</v>
+        <v>427</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>44</v>
@@ -7379,19 +6367,19 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>514</v>
+        <v>428</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>514</v>
+        <v>428</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>515</v>
+        <v>429</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
@@ -7403,7 +6391,7 @@
         <v>163</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>516</v>
+        <v>430</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>44</v>
@@ -7411,19 +6399,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>517</v>
+        <v>431</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>517</v>
+        <v>431</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>518</v>
+        <v>432</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
@@ -7435,7 +6423,7 @@
         <v>163</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>519</v>
+        <v>433</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>44</v>
@@ -7443,19 +6431,19 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>520</v>
+        <v>434</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>520</v>
+        <v>434</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>521</v>
+        <v>435</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
@@ -7467,7 +6455,7 @@
         <v>139</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>522</v>
+        <v>436</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>44</v>
@@ -7475,19 +6463,19 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>523</v>
+        <v>437</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>523</v>
+        <v>437</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>524</v>
+        <v>438</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
@@ -7499,7 +6487,7 @@
         <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>525</v>
+        <v>439</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>44</v>
@@ -7507,19 +6495,19 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>526</v>
+        <v>440</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>526</v>
+        <v>440</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>527</v>
+        <v>441</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
@@ -7531,7 +6519,7 @@
         <v>139</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>528</v>
+        <v>442</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>44</v>
@@ -7539,19 +6527,19 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>529</v>
+        <v>443</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>529</v>
+        <v>443</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>530</v>
+        <v>444</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
@@ -7563,7 +6551,7 @@
         <v>193</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>531</v>
+        <v>445</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>44</v>
@@ -7571,19 +6559,19 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>532</v>
+        <v>446</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>532</v>
+        <v>446</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>533</v>
+        <v>447</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
@@ -7595,7 +6583,7 @@
         <v>163</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>534</v>
+        <v>448</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>44</v>
@@ -7603,19 +6591,19 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>535</v>
+        <v>449</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>535</v>
+        <v>449</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>536</v>
+        <v>450</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
@@ -7627,7 +6615,7 @@
         <v>163</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>537</v>
+        <v>451</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>44</v>
@@ -7635,19 +6623,19 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>538</v>
+        <v>452</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>538</v>
+        <v>452</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>539</v>
+        <v>453</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
@@ -7659,7 +6647,7 @@
         <v>163</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>540</v>
+        <v>454</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>44</v>
@@ -7667,19 +6655,19 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>541</v>
+        <v>455</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>541</v>
+        <v>455</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>542</v>
+        <v>456</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
@@ -7691,7 +6679,7 @@
         <v>193</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>543</v>
+        <v>457</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>44</v>
@@ -7699,19 +6687,19 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>544</v>
+        <v>458</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>544</v>
+        <v>458</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>545</v>
+        <v>459</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
@@ -7723,7 +6711,7 @@
         <v>193</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>546</v>
+        <v>460</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>44</v>
@@ -7731,19 +6719,19 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>547</v>
+        <v>461</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>547</v>
+        <v>461</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>548</v>
+        <v>462</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
@@ -7755,7 +6743,7 @@
         <v>163</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>549</v>
+        <v>463</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>44</v>
@@ -7763,19 +6751,19 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>189</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>550</v>
+        <v>464</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>550</v>
+        <v>464</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>551</v>
+        <v>465</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
@@ -7787,7 +6775,7 @@
         <v>193</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>552</v>
+        <v>466</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>44</v>
@@ -7795,19 +6783,19 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>195</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>553</v>
+        <v>467</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>553</v>
+        <v>467</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>554</v>
+        <v>468</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
@@ -7819,7 +6807,7 @@
         <v>193</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>555</v>
+        <v>469</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>44</v>
@@ -7827,19 +6815,19 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>556</v>
+        <v>470</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>556</v>
+        <v>470</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>557</v>
+        <v>471</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
@@ -7851,7 +6839,7 @@
         <v>193</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>558</v>
+        <v>472</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>44</v>
@@ -7859,19 +6847,19 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>204</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>559</v>
+        <v>473</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>559</v>
+        <v>473</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>560</v>
+        <v>474</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
@@ -7883,7 +6871,7 @@
         <v>212</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>561</v>
+        <v>475</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>44</v>
@@ -7891,19 +6879,19 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>562</v>
+        <v>476</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>562</v>
+        <v>476</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>563</v>
+        <v>477</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
@@ -7915,7 +6903,7 @@
         <v>212</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>564</v>
+        <v>478</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>44</v>
@@ -7923,19 +6911,19 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>214</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>565</v>
+        <v>479</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>565</v>
+        <v>479</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>566</v>
+        <v>480</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
@@ -7944,10 +6932,10 @@
         <v>97</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>567</v>
+        <v>481</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>44</v>
@@ -7955,19 +6943,19 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>218</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>568</v>
+        <v>482</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>568</v>
+        <v>482</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>569</v>
+        <v>483</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
@@ -7979,7 +6967,7 @@
         <v>212</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>570</v>
+        <v>484</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>44</v>
@@ -7987,19 +6975,19 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>571</v>
+        <v>485</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>571</v>
+        <v>485</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>572</v>
+        <v>486</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>90</v>
@@ -8011,7 +6999,7 @@
         <v>212</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>573</v>
+        <v>487</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>44</v>
@@ -8055,6 +7043,985 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J29"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J30"/>
@@ -8110,13 +8077,13 @@
         <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
@@ -8125,10 +8092,10 @@
         <v>103</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>44</v>
@@ -8142,13 +8109,13 @@
         <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
@@ -8157,10 +8124,10 @@
         <v>103</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>44</v>
@@ -8174,13 +8141,13 @@
         <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
@@ -8192,7 +8159,7 @@
         <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>44</v>
@@ -8212,7 +8179,7 @@
         <v>68</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>108</v>
@@ -8224,7 +8191,7 @@
         <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>44</v>
@@ -8238,13 +8205,13 @@
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>90</v>
@@ -8256,7 +8223,7 @@
         <v>104</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>44</v>
@@ -8270,13 +8237,13 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
@@ -8288,7 +8255,7 @@
         <v>104</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>44</v>
@@ -8302,13 +8269,13 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
@@ -8320,7 +8287,7 @@
         <v>104</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>44</v>
@@ -8334,13 +8301,13 @@
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
@@ -8352,7 +8319,7 @@
         <v>126</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>44</v>
@@ -8366,13 +8333,13 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
@@ -8384,7 +8351,7 @@
         <v>139</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>44</v>
@@ -8398,13 +8365,13 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -8416,7 +8383,7 @@
         <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>44</v>
@@ -8430,13 +8397,13 @@
         <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
@@ -8448,7 +8415,7 @@
         <v>126</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>44</v>
@@ -8462,13 +8429,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
@@ -8480,7 +8447,7 @@
         <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>44</v>
@@ -8494,13 +8461,13 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
@@ -8512,7 +8479,7 @@
         <v>139</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>44</v>
@@ -8526,13 +8493,13 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
@@ -8544,7 +8511,7 @@
         <v>139</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>44</v>
@@ -8555,28 +8522,28 @@
         <v>61</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>44</v>
@@ -8590,25 +8557,25 @@
         <v>159</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>44</v>
@@ -8622,13 +8589,13 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
@@ -8640,7 +8607,7 @@
         <v>193</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>44</v>
@@ -8654,13 +8621,13 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
@@ -8672,7 +8639,7 @@
         <v>163</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>44</v>
@@ -8686,13 +8653,13 @@
         <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
@@ -8701,10 +8668,10 @@
         <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>44</v>
@@ -8718,13 +8685,13 @@
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
@@ -8736,7 +8703,7 @@
         <v>193</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>44</v>
@@ -8750,13 +8717,13 @@
         <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
@@ -8768,7 +8735,7 @@
         <v>212</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>44</v>
@@ -8782,25 +8749,25 @@
         <v>185</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>193</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>44</v>
@@ -8814,13 +8781,13 @@
         <v>189</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
@@ -8832,7 +8799,7 @@
         <v>193</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>44</v>
@@ -8846,13 +8813,13 @@
         <v>195</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
@@ -8864,7 +8831,7 @@
         <v>193</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>44</v>
@@ -8878,13 +8845,13 @@
         <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
@@ -8896,7 +8863,7 @@
         <v>193</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>44</v>
@@ -8910,13 +8877,13 @@
         <v>204</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
@@ -8928,7 +8895,7 @@
         <v>193</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>44</v>
@@ -8942,13 +8909,13 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
@@ -8960,7 +8927,7 @@
         <v>193</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>44</v>
@@ -8974,13 +8941,13 @@
         <v>214</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
@@ -8992,7 +8959,7 @@
         <v>212</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>44</v>
@@ -9006,13 +8973,13 @@
         <v>218</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
@@ -9024,7 +8991,7 @@
         <v>212</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>44</v>
@@ -9069,7 +9036,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -9122,13 +9089,13 @@
         <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
@@ -9140,7 +9107,7 @@
         <v>92</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -9154,25 +9121,25 @@
         <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>665</v>
+        <v>212</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -9186,25 +9153,25 @@
         <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>212</v>
+        <v>665</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -9218,13 +9185,13 @@
         <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
@@ -9236,7 +9203,7 @@
         <v>665</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -9250,25 +9217,25 @@
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>673</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>676</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -9282,13 +9249,13 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
@@ -9297,10 +9264,10 @@
         <v>103</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -9314,25 +9281,25 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -9346,13 +9313,13 @@
         <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
@@ -9361,10 +9328,10 @@
         <v>198</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -9378,25 +9345,25 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>686</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>689</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -9410,13 +9377,13 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -9425,10 +9392,10 @@
         <v>162</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -9442,25 +9409,25 @@
         <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>91</v>
+        <v>207</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>688</v>
+        <v>672</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -9474,13 +9441,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
@@ -9489,10 +9456,10 @@
         <v>103</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -9506,13 +9473,13 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
@@ -9521,10 +9488,10 @@
         <v>91</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -9538,13 +9505,13 @@
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
@@ -9553,10 +9520,10 @@
         <v>162</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -9567,28 +9534,28 @@
         <v>69</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>207</v>
+        <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -9602,13 +9569,13 @@
         <v>159</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
@@ -9617,10 +9584,10 @@
         <v>275</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -9634,13 +9601,13 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
@@ -9649,10 +9616,10 @@
         <v>109</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -9666,13 +9633,13 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
@@ -9681,10 +9648,10 @@
         <v>162</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -9698,25 +9665,25 @@
         <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>711</v>
+        <v>685</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -9730,25 +9697,25 @@
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>275</v>
+        <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -9762,25 +9729,25 @@
         <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>78</v>
+        <v>722</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>78</v>
+        <v>722</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>244</v>
+        <v>275</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>692</v>
+        <v>708</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -9794,25 +9761,25 @@
         <v>185</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>727</v>
+        <v>78</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>727</v>
+        <v>78</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>198</v>
+        <v>244</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>729</v>
+        <v>689</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -9826,25 +9793,25 @@
         <v>189</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>91</v>
+        <v>198</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>729</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -9858,32 +9825,64 @@
         <v>195</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>198</v>
+        <v>91</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>729</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
       </c>
     </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J25"/>
+  <autoFilter ref="A1:J26"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -9909,6 +9908,7 @@
     <hyperlink ref="E23" r:id="rId22"/>
     <hyperlink ref="E24" r:id="rId23"/>
     <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -11,19 +11,19 @@
     <sheet name="든솔" sheetId="2" r:id="rId2"/>
     <sheet name="만영" sheetId="3" r:id="rId3"/>
     <sheet name="지존길드" sheetId="4" r:id="rId4"/>
-    <sheet name="빅딜" sheetId="5" r:id="rId5"/>
-    <sheet name="바텀" sheetId="6" r:id="rId6"/>
+    <sheet name="바텀" sheetId="5" r:id="rId5"/>
+    <sheet name="빅딜" sheetId="6" r:id="rId6"/>
     <sheet name="따숨" sheetId="7" r:id="rId7"/>
     <sheet name="더위사냥" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">더위사냥!$A$1:$J$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">더위사냥!$A$1:$J$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">든솔!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">따숨!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">만영!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">바텀!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">빅딜!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">바텀!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">빅딜!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">지존길드!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2164" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2184" uniqueCount="744">
   <si>
     <t>guild_name</t>
   </si>
@@ -84,7 +84,7 @@
     <t>Scania 13</t>
   </si>
   <si>
-    <t>890</t>
+    <t>900</t>
   </si>
   <si>
     <t>35위</t>
@@ -117,7 +117,7 @@
     <t>Scania 23</t>
   </si>
   <si>
-    <t>954</t>
+    <t>975</t>
   </si>
   <si>
     <t>14위</t>
@@ -147,10 +147,10 @@
     <t>Scania 4</t>
   </si>
   <si>
-    <t>896</t>
-  </si>
-  <si>
-    <t>33위</t>
+    <t>908</t>
+  </si>
+  <si>
+    <t>34위</t>
   </si>
   <si>
     <t>30명</t>
@@ -168,6 +168,30 @@
     <t>2026.09.21</t>
   </si>
   <si>
+    <t>바텀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%94%ED%85%80</t>
+  </si>
+  <si>
+    <t>Scania 29</t>
+  </si>
+  <si>
+    <t>922</t>
+  </si>
+  <si>
+    <t>17위</t>
+  </si>
+  <si>
+    <t>4경 7638조 4057억 173만</t>
+  </si>
+  <si>
+    <t>바텀에서 캐리하실분! (톡방필수)</t>
+  </si>
+  <si>
+    <t>딜폿</t>
+  </si>
+  <si>
     <t>빅딜</t>
   </si>
   <si>
@@ -177,7 +201,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>882</t>
+    <t>892</t>
   </si>
   <si>
     <t>40위</t>
@@ -192,30 +216,6 @@
     <t>자유이용껀</t>
   </si>
   <si>
-    <t>바텀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%94%ED%85%80</t>
-  </si>
-  <si>
-    <t>Scania 29</t>
-  </si>
-  <si>
-    <t>909</t>
-  </si>
-  <si>
-    <t>16위</t>
-  </si>
-  <si>
-    <t>4경 7638조 4057억 173만</t>
-  </si>
-  <si>
-    <t>바텀에서 캐리하실분! (톡방필수)</t>
-  </si>
-  <si>
-    <t>딜폿</t>
-  </si>
-  <si>
     <t>따숨</t>
   </si>
   <si>
@@ -225,10 +225,10 @@
     <t>Scania 3</t>
   </si>
   <si>
-    <t>949</t>
-  </si>
-  <si>
-    <t>42위</t>
+    <t>971</t>
+  </si>
+  <si>
+    <t>45위</t>
   </si>
   <si>
     <t>4경 3027조 2732억 9013만</t>
@@ -249,7 +249,7 @@
     <t>Scania 50</t>
   </si>
   <si>
-    <t>908</t>
+    <t>919</t>
   </si>
   <si>
     <t>4위</t>
@@ -312,7 +312,7 @@
     <t>117</t>
   </si>
   <si>
-    <t>8경 9205조 5700억 6269만</t>
+    <t>9경 1891조 4546억 7144만</t>
   </si>
   <si>
     <t>2</t>
@@ -363,7 +363,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>7824조 6823억 4302만</t>
+    <t>7952조 1707억 8254만</t>
   </si>
   <si>
     <t>5</t>
@@ -375,7 +375,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%90%EC%B1%A0</t>
   </si>
   <si>
-    <t>6998조 1081억 3954만</t>
+    <t>7119조 3554억 8851만</t>
   </si>
   <si>
     <t>6</t>
@@ -387,7 +387,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%84%EA%B5%AC</t>
   </si>
   <si>
-    <t>6115조 7277억 9367만</t>
+    <t>6768조 5337억 7518만</t>
   </si>
   <si>
     <t>7</t>
@@ -399,7 +399,10 @@
     <t>https://mgf.gg/contents/character.php?n=GOD%EB%82%A0%EB%91%90</t>
   </si>
   <si>
-    <t>5633조 1947억 2114만</t>
+    <t>115</t>
+  </si>
+  <si>
+    <t>5693조 8001억 5478만</t>
   </si>
   <si>
     <t>8</t>
@@ -414,22 +417,52 @@
     <t>113</t>
   </si>
   <si>
-    <t>4963조 5845억 4685만</t>
+    <t>5233조 6124억 7121만</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
+    <t>주요엘농산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%9A%94%EC%97%98%EB%86%8D%EC%82%B0</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>3856조 7505억 127만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>하찌바리이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B0%8C%EB%B0%94%EB%A6%AC%EC%9D%B4</t>
   </si>
   <si>
-    <t>3528조 3231억 9159만</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>3708조 3110억 8709만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>테이킷슬로우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%85%8C%EC%9D%B4%ED%82%B7%EC%8A%AC%EB%A1%9C%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>3649조 8657억 275만</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>러브포티</t>
@@ -438,52 +471,37 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%B8%8C%ED%8F%AC%ED%8B%B0</t>
   </si>
   <si>
-    <t>3490조 5566억 1483만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>주요엘농산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%9A%94%EC%97%98%EB%86%8D%EC%82%B0</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>3372조 7251억 8925만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>테이킷슬로우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%85%8C%EC%9D%B4%ED%82%B7%EC%8A%AC%EB%A1%9C%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>3050조 3867억 6933만</t>
+    <t>3575조 4316억 1154만</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
+    <t>탕비실도우미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%95%EB%B9%84%EC%8B%A4%EB%8F%84%EC%9A%B0%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>3309조 7030억 7956만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>서늘한그늘</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%8A%98%ED%95%9C%EA%B7%B8%EB%8A%98</t>
   </si>
   <si>
-    <t>2609조 7534억 1122만</t>
-  </si>
-  <si>
-    <t>14</t>
+    <t>2892조 153억 4667만</t>
+  </si>
+  <si>
+    <t>15</t>
   </si>
   <si>
     <t>황금어금니</t>
@@ -492,22 +510,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EA%B8%88%EC%96%B4%EA%B8%88%EB%8B%88</t>
   </si>
   <si>
-    <t>2498조 4801억 4342만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>탕비실도우미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%95%EB%B9%84%EC%8B%A4%EB%8F%84%EC%9A%B0%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>2452조 2872억 9425만</t>
+    <t>2533조 7204억 4731만</t>
   </si>
   <si>
     <t>16</t>
@@ -537,12 +540,36 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9D%B4%ED%95%98%EB%A1%9C%ED%95%98%EB%9D%BC</t>
   </si>
   <si>
-    <t>1811조 9907억 8986만</t>
+    <t>1914조 9984억 8034만</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
+    <t>v박효신v</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=v%EB%B0%95%ED%9A%A8%EC%8B%A0v</t>
+  </si>
+  <si>
+    <t>1586조 1009억 3234만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>다둉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1575조 684억 3841만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
     <t>차보이</t>
   </si>
   <si>
@@ -552,7 +579,40 @@
     <t>1479조 8061억 8067만</t>
   </si>
   <si>
-    <t>19</t>
+    <t>21</t>
+  </si>
+  <si>
+    <t>초읍사나이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%8D%EC%82%AC%EB%82%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1455조 5942억 9898만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>시간이돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B0%84%EC%9D%B4%EB%8F%88</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>1453조 5880억 353만</t>
+  </si>
+  <si>
+    <t>23</t>
   </si>
   <si>
     <t>도레오</t>
@@ -564,19 +624,7 @@
     <t>1384조 3289억 6509만</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>v박효신v</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=v%EB%B0%95%ED%9A%A8%EC%8B%A0v</t>
-  </si>
-  <si>
-    <t>1383조 4073억 6000만</t>
-  </si>
-  <si>
-    <t>21</t>
+    <t>24</t>
   </si>
   <si>
     <t>여릿</t>
@@ -585,52 +633,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%A6%BF</t>
   </si>
   <si>
-    <t>1278조 5550억 2130만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>다둉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1275조 6700억 9290만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>초읍사나이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%8D%EC%82%AC%EB%82%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>1256조 2669억 6167만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>시간이돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B0%84%EC%9D%B4%EB%8F%88</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>1239조 8487억 6409만</t>
+    <t>1291조 9574억 2430만</t>
   </si>
   <si>
     <t>25</t>
@@ -642,7 +645,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%9C%BC%EB%86%8D</t>
   </si>
   <si>
-    <t>1114조 4365억 3877만</t>
+    <t>1114조 9646억 246만</t>
   </si>
   <si>
     <t>26</t>
@@ -657,12 +660,24 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>713조 1621억 2270만</t>
+    <t>723조 3246억 3458만</t>
   </si>
   <si>
     <t>27</t>
   </si>
   <si>
+    <t>아리미쿵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A6%AC%EB%AF%B8%EC%BF%B5</t>
+  </si>
+  <si>
+    <t>701조 1996억 3799만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
     <t>하엘이</t>
   </si>
   <si>
@@ -672,19 +687,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>654조 3071억 5615만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>아리미쿵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A6%AC%EB%AF%B8%EC%BF%B5</t>
-  </si>
-  <si>
-    <t>578조 7351억 3168만</t>
+    <t>697조 1473억 4229만</t>
   </si>
   <si>
     <t>29</t>
@@ -696,13 +699,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%8A%94%EB%B0%B0%EB%B6%88%EB%9F%AC%EC%9A%94</t>
   </si>
   <si>
-    <t>509조 8552억 8334만</t>
+    <t>510조 761억 1148만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EA%B8%B0%EC%9C%A0%EB%AC%B4</t>
   </si>
   <si>
-    <t>1경 3469조 465억 1587만</t>
+    <t>1경 3765조 6550억 7154만</t>
   </si>
   <si>
     <t>무곽</t>
@@ -711,7 +714,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EA%B3%BD</t>
   </si>
   <si>
-    <t>1경 3453조 1884억 923만</t>
+    <t>1경 3728조 1246억 9139만</t>
   </si>
   <si>
     <t>형팡팡이</t>
@@ -720,7 +723,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%95%ED%8C%A1%ED%8C%A1%EC%9D%B4</t>
   </si>
   <si>
-    <t>5445조 3408억 1191만</t>
+    <t>5554조 4045억 8503만</t>
   </si>
   <si>
     <t>붉은모자</t>
@@ -729,7 +732,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%89%EC%9D%80%EB%AA%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>3914조 7883억 9112만</t>
+    <t>3941조 3004억 9798만</t>
   </si>
   <si>
     <t>2번째캐릭</t>
@@ -738,7 +741,7 @@
     <t>https://mgf.gg/contents/character.php?n=2%EB%B2%88%EC%A7%B8%EC%BA%90%EB%A6%AD</t>
   </si>
   <si>
-    <t>3871조 8690억 6725만</t>
+    <t>3877조 1207억 653만</t>
   </si>
   <si>
     <t>장뱁새</t>
@@ -747,7 +750,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B1%81%EC%83%88</t>
   </si>
   <si>
-    <t>3529조 4313억 8306만</t>
+    <t>3678조 546억 5982만</t>
   </si>
   <si>
     <t>꽁꽁냉법</t>
@@ -756,7 +759,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EA%BD%81%EB%83%89%EB%B2%95</t>
   </si>
   <si>
-    <t>2784조 9520억 6600만</t>
+    <t>2876조 2396억 7252만</t>
   </si>
   <si>
     <t>테토일남</t>
@@ -768,7 +771,7 @@
     <t>다크나이트</t>
   </si>
   <si>
-    <t>2605조 9827억 5496만</t>
+    <t>2642조 4985억 2130만</t>
   </si>
   <si>
     <t>뚜기파파</t>
@@ -777,7 +780,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EA%B8%B0%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>2186조 8015억 8258만</t>
+    <t>2414조 5788억 534만</t>
+  </si>
+  <si>
+    <t>초앤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%95%A4</t>
+  </si>
+  <si>
+    <t>2186조 9379억 4603만</t>
   </si>
   <si>
     <t>브네</t>
@@ -786,16 +798,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%84%A4</t>
   </si>
   <si>
-    <t>1928조 5981억 7061만</t>
-  </si>
-  <si>
-    <t>초앤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%95%A4</t>
-  </si>
-  <si>
-    <t>1836조 5603억 229만</t>
+    <t>2048조 7252억 8730만</t>
   </si>
   <si>
     <t>라쥬르</t>
@@ -804,7 +807,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%A5%AC%EB%A5%B4</t>
   </si>
   <si>
-    <t>1666조 7604억 8903만</t>
+    <t>1695조 3370억 1322만</t>
+  </si>
+  <si>
+    <t>재미있게놀래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EB%AF%B8%EC%9E%88%EA%B2%8C%EB%86%80%EB%9E%98</t>
+  </si>
+  <si>
+    <t>1569조 3601억 2584만</t>
+  </si>
+  <si>
+    <t>가덴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%8D%B4</t>
+  </si>
+  <si>
+    <t>1528조 5814억 937만</t>
   </si>
   <si>
     <t>33세배장호</t>
@@ -813,25 +834,16 @@
     <t>https://mgf.gg/contents/character.php?n=33%EC%84%B8%EB%B0%B0%EC%9E%A5%ED%98%B8</t>
   </si>
   <si>
-    <t>1476조 4908억 6363만</t>
-  </si>
-  <si>
-    <t>재미있게놀래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EB%AF%B8%EC%9E%88%EA%B2%8C%EB%86%80%EB%9E%98</t>
-  </si>
-  <si>
-    <t>1459조 9219억 3077만</t>
-  </si>
-  <si>
-    <t>가덴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%8D%B4</t>
-  </si>
-  <si>
-    <t>1383조 229억 4504만</t>
+    <t>1525조 4907억 7875만</t>
+  </si>
+  <si>
+    <t>빙율</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%99%EC%9C%A8</t>
+  </si>
+  <si>
+    <t>1437조 8262억 4311만</t>
   </si>
   <si>
     <t>적젹적</t>
@@ -840,16 +852,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%81%EC%A0%B9%EC%A0%81</t>
   </si>
   <si>
-    <t>1351조 4089억 5127만</t>
-  </si>
-  <si>
-    <t>빙율</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%99%EC%9C%A8</t>
-  </si>
-  <si>
-    <t>1314조 7187억 8022만</t>
+    <t>1395조 667억 8252만</t>
   </si>
   <si>
     <t>타뤽</t>
@@ -861,7 +864,7 @@
     <t>바이퍼</t>
   </si>
   <si>
-    <t>963조 2666억 6563만</t>
+    <t>987조 5641억 8689만</t>
   </si>
   <si>
     <t>정기휴므</t>
@@ -879,7 +882,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%A5%B4%EC%8A%A4</t>
   </si>
   <si>
-    <t>794조 7429억 9895만</t>
+    <t>849조 2924억 4559만</t>
   </si>
   <si>
     <t>채황새</t>
@@ -906,7 +909,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%AC%EC%83%B7</t>
   </si>
   <si>
-    <t>640조 1353억 8502만</t>
+    <t>644조 8542억 7096만</t>
   </si>
   <si>
     <t>박도란</t>
@@ -924,7 +927,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
   </si>
   <si>
-    <t>547조 7047억 3326만</t>
+    <t>590조 1720억 3150만</t>
   </si>
   <si>
     <t>뿌앵뿌앵</t>
@@ -942,7 +945,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%ED%99%8D%EC%9D%B4</t>
   </si>
   <si>
-    <t>395조 9488억 9628만</t>
+    <t>413조 8619억 2015만</t>
   </si>
   <si>
     <t>윤빵쭈</t>
@@ -954,7 +957,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>309조 4737억 1028만</t>
+    <t>328조 2553억 9563만</t>
   </si>
   <si>
     <t>지존쫀파</t>
@@ -963,10 +966,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
   </si>
   <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>1경 2조 9357억 3558만</t>
+    <t>1경 19조 5741억 8934만</t>
   </si>
   <si>
     <t>수텍</t>
@@ -975,7 +975,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%ED%85%8D</t>
   </si>
   <si>
-    <t>7780조 8362억 2093만</t>
+    <t>8359조 1134억 9009만</t>
   </si>
   <si>
     <t>포항엄석대</t>
@@ -984,7 +984,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
   </si>
   <si>
-    <t>4590조 9887억 9442만</t>
+    <t>4805조 3834억 2878만</t>
   </si>
   <si>
     <t>협의</t>
@@ -1002,7 +1002,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%BD%90</t>
   </si>
   <si>
-    <t>3807조 6451억 3805만</t>
+    <t>4080조 9809억 5335만</t>
   </si>
   <si>
     <t>타개</t>
@@ -1011,7 +1011,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
   </si>
   <si>
-    <t>3780조 4364억 4613만</t>
+    <t>3782조 6408억 7406만</t>
+  </si>
+  <si>
+    <t>엘르가든</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
+  </si>
+  <si>
+    <t>3123조 4735억 6276만</t>
   </si>
   <si>
     <t>댜니</t>
@@ -1023,40 +1032,40 @@
     <t>2886조 9873억 5134만</t>
   </si>
   <si>
+    <t>포항가자미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>2663조 699억 5090만</t>
+  </si>
+  <si>
+    <t>지존빼앙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
+  </si>
+  <si>
+    <t>2653조 9585억 17만</t>
+  </si>
+  <si>
     <t>뿡쓰</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
   </si>
   <si>
-    <t>2633조 4371억 8860만</t>
-  </si>
-  <si>
-    <t>포항가자미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>2608조 4541억 5961만</t>
-  </si>
-  <si>
-    <t>엘르가든</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
-  </si>
-  <si>
-    <t>2524조 5509억 437만</t>
-  </si>
-  <si>
-    <t>지존빼앙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
-  </si>
-  <si>
-    <t>2515조 2382억 6614만</t>
+    <t>2636조 1861억 8167만</t>
+  </si>
+  <si>
+    <t>온백</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
+  </si>
+  <si>
+    <t>2524조 740억 8103만</t>
   </si>
   <si>
     <t>변신술사</t>
@@ -1065,16 +1074,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
   </si>
   <si>
-    <t>2465조 3877억 3257만</t>
-  </si>
-  <si>
-    <t>온백</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
-  </si>
-  <si>
-    <t>2435조 2954억 8900만</t>
+    <t>2467조 3128억 8047만</t>
   </si>
   <si>
     <t>파울</t>
@@ -1083,7 +1083,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
   </si>
   <si>
-    <t>2101조 5950억 688만</t>
+    <t>2279조 9475억 9043만</t>
   </si>
   <si>
     <t>마카롱롱</t>
@@ -1092,7 +1092,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
   </si>
   <si>
-    <t>2053조 6196억 299만</t>
+    <t>2081조 696억 8626만</t>
   </si>
   <si>
     <t>대좀이</t>
@@ -1101,7 +1101,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>1497조 9515억 7380만</t>
+    <t>2017조 9844억 3571만</t>
+  </si>
+  <si>
+    <t>기본이리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1729조 25억 6838만</t>
   </si>
   <si>
     <t>모짜리코베르</t>
@@ -1110,7 +1119,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
   </si>
   <si>
-    <t>1415조 2191억 2464만</t>
+    <t>1439조 5681억 1783만</t>
   </si>
   <si>
     <t>오옹나이스</t>
@@ -1122,6 +1131,15 @@
     <t>1379조 1810억 4031만</t>
   </si>
   <si>
+    <t>짱잘자쿨냥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%9E%98%EC%9E%90%EC%BF%A8%EB%83%A5</t>
+  </si>
+  <si>
+    <t>1375조 2703억 161만</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
   </si>
   <si>
@@ -1134,7 +1152,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
   </si>
   <si>
-    <t>1239조 6065억 5601만</t>
+    <t>1262조 5083억 6310만</t>
   </si>
   <si>
     <t>김허덕</t>
@@ -1146,31 +1164,13 @@
     <t>1235조 7285억 909만</t>
   </si>
   <si>
-    <t>기본이리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1176조 3129억 5474만</t>
-  </si>
-  <si>
-    <t>짱잘자쿨냥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%9E%98%EC%9E%90%EC%BF%A8%EB%83%A5</t>
-  </si>
-  <si>
-    <t>1149조 8047억 287만</t>
-  </si>
-  <si>
     <t>냐은</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EC%9D%80</t>
   </si>
   <si>
-    <t>1109조 1781억 7811만</t>
+    <t>1217조 4797억 6146만</t>
   </si>
   <si>
     <t>전산봉</t>
@@ -1179,7 +1179,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%B0%EB%B4%89</t>
   </si>
   <si>
-    <t>1062조 2713억 1289만</t>
+    <t>1062조 8365억 4696만</t>
   </si>
   <si>
     <t>고숨도칭</t>
@@ -1188,7 +1188,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
   </si>
   <si>
-    <t>892조 4230억 8515만</t>
+    <t>984조 1408억 2996만</t>
   </si>
   <si>
     <t>태코찡</t>
@@ -1197,7 +1197,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
   </si>
   <si>
-    <t>865조 8935억 5088만</t>
+    <t>872조 8476억 3790만</t>
   </si>
   <si>
     <t>Doham</t>
@@ -1206,7 +1206,7 @@
     <t>https://mgf.gg/contents/character.php?n=Doham</t>
   </si>
   <si>
-    <t>840조 147억 74만</t>
+    <t>857조 1587억 7359만</t>
   </si>
   <si>
     <t>유플러스</t>
@@ -1215,7 +1215,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%94%8C%EB%9F%AC%EC%8A%A4</t>
   </si>
   <si>
-    <t>651조 6536억 3056만</t>
+    <t>669조 2133억 2214만</t>
   </si>
   <si>
     <t>30</t>
@@ -1230,13 +1230,271 @@
     <t>355조 5297억 5157만</t>
   </si>
   <si>
+    <t>전액할부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%95%A1%ED%95%A0%EB%B6%80</t>
+  </si>
+  <si>
+    <t>1경 2872조 7013억 2041만</t>
+  </si>
+  <si>
+    <t>사랑향</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%96%A5</t>
+  </si>
+  <si>
+    <t>1경 851조 745억 4971만</t>
+  </si>
+  <si>
+    <t>례전</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%80%EC%A0%84</t>
+  </si>
+  <si>
+    <t>4593조 9364억 5767만</t>
+  </si>
+  <si>
+    <t>숭타이준</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%ED%83%80%EC%9D%B4%EC%A4%80</t>
+  </si>
+  <si>
+    <t>3869조 4442억 8322만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%9C%ED%8F%BF</t>
+  </si>
+  <si>
+    <t>3636조 5993억 4835만</t>
+  </si>
+  <si>
+    <t>지존빵수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%B5%EC%88%98</t>
+  </si>
+  <si>
+    <t>2686조 4905억 8219만</t>
+  </si>
+  <si>
+    <t>뻑걸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%91%EA%B1%B8</t>
+  </si>
+  <si>
+    <t>2649조 9001억 1441만</t>
+  </si>
+  <si>
+    <t>탱폿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%8F%BF</t>
+  </si>
+  <si>
+    <t>2344조 6384억 832만</t>
+  </si>
+  <si>
+    <t>야키산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%82%A4%EC%82%B0</t>
+  </si>
+  <si>
+    <t>2340조 2137억 7570만</t>
+  </si>
+  <si>
+    <t>문제적남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EC%A0%9C%EC%A0%81%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>2058조 8049억 2498만</t>
+  </si>
+  <si>
+    <t>아이리쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EB%A6%AC%EC%89%AC</t>
+  </si>
+  <si>
+    <t>1948조 7529억 6256만</t>
+  </si>
+  <si>
+    <t>뮬이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AE%AC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1904조 9831억 9881만</t>
+  </si>
+  <si>
+    <t>화둥에불낸년</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EB%91%A5%EC%97%90%EB%B6%88%EB%82%B8%EB%85%84</t>
+  </si>
+  <si>
+    <t>1819조 1559억 3691만</t>
+  </si>
+  <si>
+    <t>기똥찬벌레</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%98%A5%EC%B0%AC%EB%B2%8C%EB%A0%88</t>
+  </si>
+  <si>
+    <t>1678조 1189억 7776만</t>
+  </si>
+  <si>
+    <t>독스케</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%8A%A4%EC%BC%80</t>
+  </si>
+  <si>
+    <t>1411조 5379억 545만</t>
+  </si>
+  <si>
+    <t>우즈2텐겐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%A6%882%ED%85%90%EA%B2%90</t>
+  </si>
+  <si>
+    <t>1317조 4439억 6807만</t>
+  </si>
+  <si>
+    <t>이게용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B2%8C%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>1232조 3436억 1021만</t>
+  </si>
+  <si>
+    <t>구도류</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%8F%84%EB%A5%98</t>
+  </si>
+  <si>
+    <t>1150조 5525억 1141만</t>
+  </si>
+  <si>
+    <t>매화로이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%ED%99%94%EB%A1%9C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1096조 205억 5033만</t>
+  </si>
+  <si>
+    <t>우월별하</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9B%94%EB%B3%84%ED%95%98</t>
+  </si>
+  <si>
+    <t>1046조 8917억 6990만</t>
+  </si>
+  <si>
+    <t>JJuna</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=JJuna</t>
+  </si>
+  <si>
+    <t>1046조 1084억 7886만</t>
+  </si>
+  <si>
+    <t>통닭아저씨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%B5%EB%8B%AD%EC%95%84%EC%A0%80%EC%94%A8</t>
+  </si>
+  <si>
+    <t>955조 6925억 3334만</t>
+  </si>
+  <si>
+    <t>콜리셰마드르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%9C%EB%A6%AC%EC%85%B0%EB%A7%88%EB%93%9C%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>898조 1930억 311만</t>
+  </si>
+  <si>
+    <t>에프람</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%ED%94%84%EB%9E%8C</t>
+  </si>
+  <si>
+    <t>878조 6824억 7297만</t>
+  </si>
+  <si>
+    <t>난센</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EC%84%BC</t>
+  </si>
+  <si>
+    <t>872조 6305억 5392만</t>
+  </si>
+  <si>
+    <t>유채아버지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%B1%84%EC%95%84%EB%B2%84%EC%A7%80</t>
+  </si>
+  <si>
+    <t>752조 3802억 2219만</t>
+  </si>
+  <si>
+    <t>조단23</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%8B%A823</t>
+  </si>
+  <si>
+    <t>675조 8613억 9777만</t>
+  </si>
+  <si>
+    <t>아콩린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BD%A9%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>639조 1166억 8153만</t>
+  </si>
+  <si>
+    <t>별루루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A3%A8%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>527조 7482억 7197만</t>
+  </si>
+  <si>
     <t>아이스꾸임</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
   </si>
   <si>
-    <t>2경 1503조 25억 9857만</t>
+    <t>2경 2364조 4361억 7762만</t>
   </si>
   <si>
     <t>굴러가는일상</t>
@@ -1245,7 +1503,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
   </si>
   <si>
-    <t>8237조 7144억 4543만</t>
+    <t>8489조 1115억 3293만</t>
   </si>
   <si>
     <t>엘라임</t>
@@ -1254,7 +1512,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
   </si>
   <si>
-    <t>5314조 9961억 763만</t>
+    <t>5951조 9782억 4923만</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>4756조 5792억 5235만</t>
   </si>
   <si>
     <t>흑두부</t>
@@ -1263,16 +1530,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>4279조 3156억 7061만</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>4270조 7688억 5784만</t>
+    <t>4628조 662억 4303만</t>
   </si>
   <si>
     <t>서포터즈</t>
@@ -1281,7 +1539,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>3121조 7410억 5159만</t>
+    <t>3234조 5737억 6679만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
+    <t>2651조 5906억 3120만</t>
   </si>
   <si>
     <t>야가다</t>
@@ -1302,19 +1566,13 @@
     <t>2486조 1038억 1649만</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
-  </si>
-  <si>
-    <t>2422조 114억 1172만</t>
-  </si>
-  <si>
     <t>KR#TAKIN9CP37</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>2398조 1780억 1990만</t>
+    <t>2457조 2707억 1660만</t>
   </si>
   <si>
     <t>불보독지</t>
@@ -1323,7 +1581,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
   </si>
   <si>
-    <t>1385조 8857억 654만</t>
+    <t>1422조 4939억 8525만</t>
   </si>
   <si>
     <t>우후</t>
@@ -1332,7 +1590,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>1289조 3983억 8443만</t>
+    <t>1355조 4951억 7854만</t>
   </si>
   <si>
     <t>단풍카우</t>
@@ -1341,7 +1599,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>1165조 9797억 9783만</t>
+    <t>1201조 1944억 9793만</t>
   </si>
   <si>
     <t>호우기</t>
@@ -1350,7 +1608,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>1162조 8444억 6844만</t>
+    <t>1194조 4121억 3596만</t>
   </si>
   <si>
     <t>채무조정</t>
@@ -1359,7 +1617,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
   </si>
   <si>
-    <t>1109조 8902억 2955만</t>
+    <t>1189조 7991억 4389만</t>
+  </si>
+  <si>
+    <t>좀치는형님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
+  </si>
+  <si>
+    <t>1165조 2458억 8174만</t>
   </si>
   <si>
     <t>뽀송히</t>
@@ -1368,16 +1635,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
   </si>
   <si>
-    <t>1083조 1337억 843만</t>
-  </si>
-  <si>
-    <t>좀치는형님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
-  </si>
-  <si>
-    <t>1079조 4522억 1643만</t>
+    <t>1108조 602억 8804만</t>
   </si>
   <si>
     <t>정태준</t>
@@ -1386,7 +1644,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
   </si>
   <si>
-    <t>980조 8900억 6780만</t>
+    <t>993조 7776억 2843만</t>
   </si>
   <si>
     <t>라탱호</t>
@@ -1395,7 +1653,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%ED%83%B1%ED%98%B8</t>
   </si>
   <si>
-    <t>962조 9548억 692만</t>
+    <t>990조 3580억 4657만</t>
+  </si>
+  <si>
+    <t>짤똘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%A4%EB%98%98</t>
+  </si>
+  <si>
+    <t>944조 6476억 5876만</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -1404,16 +1671,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>800조 2195억 6508만</t>
-  </si>
-  <si>
-    <t>짤똘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%A4%EB%98%98</t>
-  </si>
-  <si>
-    <t>789조 1148억 491만</t>
+    <t>831조 6415억 6371만</t>
   </si>
   <si>
     <t>팡대지</t>
@@ -1422,7 +1680,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
   </si>
   <si>
-    <t>660조 4847억 7151만</t>
+    <t>660조 5832억 2854만</t>
   </si>
   <si>
     <t>민들레꽃</t>
@@ -1431,7 +1689,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>636조 6762억 2968만</t>
+    <t>654조 6101억 1525만</t>
   </si>
   <si>
     <t>박준우2</t>
@@ -1440,7 +1698,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
   </si>
   <si>
-    <t>588조 4551억 8369만</t>
+    <t>623조 361억 6485만</t>
   </si>
   <si>
     <t>컨덱</t>
@@ -1449,7 +1707,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BB%A8%EB%8D%B1</t>
   </si>
   <si>
-    <t>541조 1466억 9068만</t>
+    <t>549조 8778억 1673만</t>
   </si>
   <si>
     <t>솔인</t>
@@ -1458,7 +1716,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
   </si>
   <si>
-    <t>491조 909억 6019만</t>
+    <t>547조 8134억 5636만</t>
+  </si>
+  <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>432조 6270억 8444만</t>
   </si>
   <si>
     <t>3030</t>
@@ -1476,16 +1743,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>343조 4896억 82만</t>
-  </si>
-  <si>
-    <t>여눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
-  </si>
-  <si>
-    <t>332조 666억 5468만</t>
+    <t>345조 7556억 8839만</t>
   </si>
   <si>
     <t>꼬북빵야</t>
@@ -1497,255 +1755,6 @@
     <t>275조 6869억 3523만</t>
   </si>
   <si>
-    <t>전액할부</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%95%A1%ED%95%A0%EB%B6%80</t>
-  </si>
-  <si>
-    <t>1경 2872조 7013억 2041만</t>
-  </si>
-  <si>
-    <t>사랑향</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%96%A5</t>
-  </si>
-  <si>
-    <t>1경 264조 2244억 9740만</t>
-  </si>
-  <si>
-    <t>례전</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%80%EC%A0%84</t>
-  </si>
-  <si>
-    <t>4593조 9364억 5767만</t>
-  </si>
-  <si>
-    <t>숭타이준</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%ED%83%80%EC%9D%B4%EC%A4%80</t>
-  </si>
-  <si>
-    <t>3869조 4442억 8322만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%9C%ED%8F%BF</t>
-  </si>
-  <si>
-    <t>3234조 771억 9586만</t>
-  </si>
-  <si>
-    <t>뻑걸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%91%EA%B1%B8</t>
-  </si>
-  <si>
-    <t>2511조 2446억 4802만</t>
-  </si>
-  <si>
-    <t>지존빵수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%B5%EC%88%98</t>
-  </si>
-  <si>
-    <t>2383조 6169억 7980만</t>
-  </si>
-  <si>
-    <t>야키산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%82%A4%EC%82%B0</t>
-  </si>
-  <si>
-    <t>2340조 2137억 7570만</t>
-  </si>
-  <si>
-    <t>탱폿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%8F%BF</t>
-  </si>
-  <si>
-    <t>2237조 7036억 8468만</t>
-  </si>
-  <si>
-    <t>문제적남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EC%A0%9C%EC%A0%81%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>2058조 8049억 2498만</t>
-  </si>
-  <si>
-    <t>아이리쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EB%A6%AC%EC%89%AC</t>
-  </si>
-  <si>
-    <t>1925조 8327억 6550만</t>
-  </si>
-  <si>
-    <t>뮬이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AE%AC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1870조 5997억 7289만</t>
-  </si>
-  <si>
-    <t>화둥에불낸년</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EB%91%A5%EC%97%90%EB%B6%88%EB%82%B8%EB%85%84</t>
-  </si>
-  <si>
-    <t>1819조 1559억 3691만</t>
-  </si>
-  <si>
-    <t>독스케</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%8A%A4%EC%BC%80</t>
-  </si>
-  <si>
-    <t>1362조 6987억 8889만</t>
-  </si>
-  <si>
-    <t>우즈2텐겐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%A6%882%ED%85%90%EA%B2%90</t>
-  </si>
-  <si>
-    <t>1317조 4439억 6807만</t>
-  </si>
-  <si>
-    <t>이게용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B2%8C%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>1106조 6561억 6466만</t>
-  </si>
-  <si>
-    <t>기똥찬벌레</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%98%A5%EC%B0%AC%EB%B2%8C%EB%A0%88</t>
-  </si>
-  <si>
-    <t>1066조 4037억 2386만</t>
-  </si>
-  <si>
-    <t>구도류</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%8F%84%EB%A5%98</t>
-  </si>
-  <si>
-    <t>1034조 7715억 4058만</t>
-  </si>
-  <si>
-    <t>우월별하</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9B%94%EB%B3%84%ED%95%98</t>
-  </si>
-  <si>
-    <t>1032조 7712억 9061만</t>
-  </si>
-  <si>
-    <t>매화로이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%ED%99%94%EB%A1%9C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1010조 4076억 8841만</t>
-  </si>
-  <si>
-    <t>JJuna</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=JJuna</t>
-  </si>
-  <si>
-    <t>962조 959억 5775만</t>
-  </si>
-  <si>
-    <t>콜리셰마드르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%9C%EB%A6%AC%EC%85%B0%EB%A7%88%EB%93%9C%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>858조 8456억 8798만</t>
-  </si>
-  <si>
-    <t>난센</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EC%84%BC</t>
-  </si>
-  <si>
-    <t>839조 5564억 6737만</t>
-  </si>
-  <si>
-    <t>에프람</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%ED%94%84%EB%9E%8C</t>
-  </si>
-  <si>
-    <t>796조 7994억 2727만</t>
-  </si>
-  <si>
-    <t>유채아버지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%B1%84%EC%95%84%EB%B2%84%EC%A7%80</t>
-  </si>
-  <si>
-    <t>707조 3486억 5299만</t>
-  </si>
-  <si>
-    <t>조단23</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%8B%A823</t>
-  </si>
-  <si>
-    <t>673조 6230억 6232만</t>
-  </si>
-  <si>
-    <t>아콩린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BD%A9%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>633조 5157억 4903만</t>
-  </si>
-  <si>
-    <t>별루루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A3%A8%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>520조 3064억 1208만</t>
-  </si>
-  <si>
     <t>꺄꽁</t>
   </si>
   <si>
@@ -1761,7 +1770,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A5</t>
   </si>
   <si>
-    <t>7850조 6568억 5740만</t>
+    <t>8684조 3008억 1764만</t>
   </si>
   <si>
     <t>진욱이에요</t>
@@ -1770,13 +1779,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9A%B1%EC%9D%B4%EC%97%90%EC%9A%94</t>
   </si>
   <si>
-    <t>4981조 9035억 244만</t>
+    <t>5420조 7228억 2713만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A5%B4%EB%AA%AC</t>
   </si>
   <si>
-    <t>4829조 6442억 8620만</t>
+    <t>4957조 9841억 1038만</t>
   </si>
   <si>
     <t>루미딘딘</t>
@@ -1794,7 +1803,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%ED%99%A9%EA%B8%88%EB%A7%9D%EC%B9%98</t>
   </si>
   <si>
-    <t>4337조 2344억 5028만</t>
+    <t>4518조 2646억 7428만</t>
   </si>
   <si>
     <t>김슴줌1</t>
@@ -1803,7 +1812,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%8A%B4%EC%A4%8C1</t>
   </si>
   <si>
-    <t>4035조 8043억 3887만</t>
+    <t>4328조 4594억 6869만</t>
   </si>
   <si>
     <t>천달</t>
@@ -1812,7 +1821,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EB%8B%AC</t>
   </si>
   <si>
-    <t>3451조 2225억 9996만</t>
+    <t>3498조 3814억 9322만</t>
   </si>
   <si>
     <t>활용</t>
@@ -1821,7 +1830,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%9C%EC%9A%A9</t>
   </si>
   <si>
-    <t>3044조 648억 9902만</t>
+    <t>3491조 6713억 8330만</t>
   </si>
   <si>
     <t>호두와감자</t>
@@ -1839,7 +1848,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EB%8C%9C</t>
   </si>
   <si>
-    <t>2330조 8222억 622만</t>
+    <t>2386조 7994억 1638만</t>
   </si>
   <si>
     <t>뚜징</t>
@@ -1848,7 +1857,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EC%A7%95</t>
   </si>
   <si>
-    <t>1992조 8747억 4996만</t>
+    <t>2088조 9578억 5945만</t>
   </si>
   <si>
     <t>게렬곰</t>
@@ -1857,7 +1866,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%EB%A0%AC%EA%B3%B0</t>
   </si>
   <si>
-    <t>1254조 8103억 1015만</t>
+    <t>1333조 6986억 2260만</t>
   </si>
   <si>
     <t>별곡</t>
@@ -1866,7 +1875,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EA%B3%A1</t>
   </si>
   <si>
-    <t>1083조 4642억 8142만</t>
+    <t>1122조 7731억 7433만</t>
   </si>
   <si>
     <t>턍ol</t>
@@ -1875,7 +1884,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%84%8Dol</t>
   </si>
   <si>
-    <t>1037조 7222억 2898만</t>
+    <t>1079조 5702억 1117만</t>
   </si>
   <si>
     <t>동래</t>
@@ -1884,7 +1893,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%9E%98</t>
   </si>
   <si>
-    <t>1019조 1472억 4526만</t>
+    <t>1020조 9140억 5382만</t>
   </si>
   <si>
     <t>까쿠미</t>
@@ -1896,6 +1905,15 @@
     <t>982조 6170억 9165만</t>
   </si>
   <si>
+    <t>별쌤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A4</t>
+  </si>
+  <si>
+    <t>877조 9539억 128만</t>
+  </si>
+  <si>
     <t>초이레</t>
   </si>
   <si>
@@ -1905,22 +1923,13 @@
     <t>869조 9507억 6002만</t>
   </si>
   <si>
-    <t>별쌤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A4</t>
-  </si>
-  <si>
-    <t>868조 9917억 7790만</t>
-  </si>
-  <si>
     <t>띠우</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%A0%EC%9A%B0</t>
   </si>
   <si>
-    <t>772조 7389억 4886만</t>
+    <t>774조 5793억 5818만</t>
   </si>
   <si>
     <t>쿠까미</t>
@@ -1929,7 +1938,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EA%B9%8C%EB%AF%B8</t>
   </si>
   <si>
-    <t>639조 2231억 5295만</t>
+    <t>731조 414억 1816만</t>
   </si>
   <si>
     <t>민족고대감자</t>
@@ -1950,22 +1959,22 @@
     <t>552조 4981억 6746만</t>
   </si>
   <si>
+    <t>08217</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=08217</t>
+  </si>
+  <si>
+    <t>540조 2716억 858만</t>
+  </si>
+  <si>
     <t>왕단단이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EB%8B%A8%EB%8B%A8%EC%9D%B4</t>
   </si>
   <si>
-    <t>491조 5157억 1429만</t>
-  </si>
-  <si>
-    <t>08217</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=08217</t>
-  </si>
-  <si>
-    <t>467조 4072억 9599만</t>
+    <t>528조 9261억 2463만</t>
   </si>
   <si>
     <t>승아의하루</t>
@@ -1974,7 +1983,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%EC%95%84%EC%9D%98%ED%95%98%EB%A3%A8</t>
   </si>
   <si>
-    <t>451조 854억 6819만</t>
+    <t>488조 930억 5617만</t>
   </si>
   <si>
     <t>루이쥔</t>
@@ -1983,7 +1992,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%9D%B4%EC%A5%94</t>
   </si>
   <si>
-    <t>417조 1392억 4322만</t>
+    <t>433조 6314억 574만</t>
   </si>
   <si>
     <t>택Ol</t>
@@ -1992,7 +2001,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9DOl</t>
   </si>
   <si>
-    <t>359조 477억 8424만</t>
+    <t>386조 1563억 1233만</t>
   </si>
   <si>
     <t>달갸뤼</t>
@@ -2001,7 +2010,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EA%B0%B8%EB%A4%BC</t>
   </si>
   <si>
-    <t>168조 6781억 8660만</t>
+    <t>176조 1629억 7009만</t>
   </si>
   <si>
     <t>교주만두</t>
@@ -2010,7 +2019,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%90%EC%A3%BC%EB%A7%8C%EB%91%90</t>
   </si>
   <si>
-    <t>9경 2881조 1976억 6044만</t>
+    <t>9경 7538조 9143억 8733만</t>
   </si>
   <si>
     <t>섹밍</t>
@@ -2019,7 +2028,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B9%EB%B0%8D</t>
   </si>
   <si>
-    <t>253조 1410억 7134만</t>
+    <t>264조 5660억 620만</t>
   </si>
   <si>
     <t>할바이</t>
@@ -2040,7 +2049,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EA%B5%AC%EB%82%A8%EC%84%B1</t>
   </si>
   <si>
-    <t>95조 2278억 1384만</t>
+    <t>96조 7278억 5748만</t>
   </si>
   <si>
     <t>코잉코잉</t>
@@ -2052,7 +2061,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>76조 2120억 9520만</t>
+    <t>81조 1696억 411만</t>
   </si>
   <si>
     <t>오스띤</t>
@@ -2061,7 +2070,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%8A%A4%EB%9D%A4</t>
   </si>
   <si>
-    <t>73조 2175억 2395만</t>
+    <t>79조 7972억 6817만</t>
   </si>
   <si>
     <t>낭랑28세</t>
@@ -2070,7 +2079,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%9E%9128%EC%84%B8</t>
   </si>
   <si>
-    <t>72조 3944억 920만</t>
+    <t>73조 4803억 92만</t>
   </si>
   <si>
     <t>토벤숍이</t>
@@ -2079,7 +2088,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%B2%A4%EC%88%8D%EC%9D%B4</t>
   </si>
   <si>
-    <t>55조 7824억 2223만</t>
+    <t>65조 4600억 8571만</t>
+  </si>
+  <si>
+    <t>배렛나루왁서</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%EB%A0%9B%EB%82%98%EB%A3%A8%EC%99%81%EC%84%9C</t>
+  </si>
+  <si>
+    <t>47조 9447억 5769만</t>
   </si>
   <si>
     <t>빵신궁</t>
@@ -2091,7 +2109,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>42조 9188억 4648만</t>
+    <t>44조 1894억 4988만</t>
   </si>
   <si>
     <t>썬콜우체국</t>
@@ -2100,118 +2118,121 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9A%B0%EC%B2%B4%EA%B5%AD</t>
   </si>
   <si>
+    <t>39조 2198억 3836만</t>
+  </si>
+  <si>
+    <t>밀초크코</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%EC%B4%88%ED%81%AC%EC%BD%94</t>
+  </si>
+  <si>
+    <t>39조 1378억 2459만</t>
+  </si>
+  <si>
+    <t>킬혁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%AC%ED%98%81</t>
+  </si>
+  <si>
+    <t>37조 1739억 4618만</t>
+  </si>
+  <si>
+    <t>마키맛키마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%82%A4%EB%A7%9B%ED%82%A4%EB%A7%88</t>
+  </si>
+  <si>
+    <t>33조 6607억 6336만</t>
+  </si>
+  <si>
+    <t>고통받는갈비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%ED%86%B5%EB%B0%9B%EB%8A%94%EA%B0%88%EB%B9%84</t>
+  </si>
+  <si>
+    <t>31조 7895억 5650만</t>
+  </si>
+  <si>
+    <t>문보겨엉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B3%B4%EA%B2%A8%EC%97%89</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>26조 6167억 1779만</t>
+  </si>
+  <si>
+    <t>땡요나퐁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%95%A1%EC%9A%94%EB%82%98%ED%90%81</t>
+  </si>
+  <si>
+    <t>26조 3083억 9376만</t>
+  </si>
+  <si>
+    <t>썬콜법사ss</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%ACss</t>
+  </si>
+  <si>
+    <t>25조 4334억 9588만</t>
+  </si>
+  <si>
+    <t>페프릭2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8E%98%ED%94%84%EB%A6%AD2</t>
+  </si>
+  <si>
+    <t>22조 7152억 4028만</t>
+  </si>
+  <si>
+    <t>맹탐정코난</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%B9%ED%83%90%EC%A0%95%EC%BD%94%EB%82%9C</t>
+  </si>
+  <si>
+    <t>22조 6919억 8673만</t>
+  </si>
+  <si>
+    <t>포디케이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%94%94%EC%BC%80%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>18조 4182억 6920만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%ED%82%A4%EB%B9%84%ED%82%A4</t>
+  </si>
+  <si>
     <t>103</t>
   </si>
   <si>
-    <t>35조 8175억 3821만</t>
-  </si>
-  <si>
-    <t>배렛나루왁서</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%EB%A0%9B%EB%82%98%EB%A3%A8%EC%99%81%EC%84%9C</t>
-  </si>
-  <si>
-    <t>35조 7009억 9309만</t>
-  </si>
-  <si>
-    <t>킬혁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%AC%ED%98%81</t>
-  </si>
-  <si>
-    <t>34조 8764억 1955만</t>
-  </si>
-  <si>
-    <t>밀초크코</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%EC%B4%88%ED%81%AC%EC%BD%94</t>
-  </si>
-  <si>
-    <t>34조 2125억 4874만</t>
-  </si>
-  <si>
-    <t>마키맛키마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%82%A4%EB%A7%9B%ED%82%A4%EB%A7%88</t>
-  </si>
-  <si>
-    <t>32조 3628억 58만</t>
-  </si>
-  <si>
-    <t>고통받는갈비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%ED%86%B5%EB%B0%9B%EB%8A%94%EA%B0%88%EB%B9%84</t>
-  </si>
-  <si>
-    <t>31조 7895억 5650만</t>
-  </si>
-  <si>
-    <t>문보겨엉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B3%B4%EA%B2%A8%EC%97%89</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>26조 6167억 1779만</t>
-  </si>
-  <si>
-    <t>땡요나퐁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%95%A1%EC%9A%94%EB%82%98%ED%90%81</t>
-  </si>
-  <si>
-    <t>26조 1277억 5625만</t>
-  </si>
-  <si>
-    <t>썬콜법사ss</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%ACss</t>
-  </si>
-  <si>
-    <t>25조 2013억 7487만</t>
-  </si>
-  <si>
-    <t>맹탐정코난</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%B9%ED%83%90%EC%A0%95%EC%BD%94%EB%82%9C</t>
-  </si>
-  <si>
-    <t>22조 6919억 8673만</t>
-  </si>
-  <si>
-    <t>페프릭2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8E%98%ED%94%84%EB%A6%AD2</t>
-  </si>
-  <si>
-    <t>22조 4519억 9962만</t>
-  </si>
-  <si>
-    <t>포디케이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%94%94%EC%BC%80%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>17조 4010억 8790만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%ED%82%A4%EB%B9%84%ED%82%A4</t>
-  </si>
-  <si>
-    <t>13조 1191억 1937만</t>
+    <t>15조 7946억 3481만</t>
+  </si>
+  <si>
+    <t>카라멜읏차</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B9%B4%EB%9D%BC%EB%A9%9C%EC%9D%8F%EC%B0%A8</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>5조 5672억 8573만</t>
   </si>
   <si>
     <t>즈나니</t>
@@ -2810,7 +2831,7 @@
         <v>19</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>50</v>
@@ -2822,7 +2843,7 @@
         <v>52</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2851,7 +2872,7 @@
         <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>58</v>
@@ -2863,7 +2884,7 @@
         <v>60</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3225,10 +3246,10 @@
         <v>103</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3239,16 +3260,16 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
@@ -3257,10 +3278,10 @@
         <v>91</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3271,16 +3292,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
@@ -3289,10 +3310,10 @@
         <v>103</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3303,28 +3324,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3335,28 +3356,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3367,28 +3388,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3399,28 +3420,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>103</v>
+        <v>150</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3431,16 +3452,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
@@ -3449,10 +3470,10 @@
         <v>103</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3463,28 +3484,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>157</v>
+        <v>103</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3495,28 +3516,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3527,16 +3548,16 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
@@ -3545,10 +3566,10 @@
         <v>91</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3559,28 +3580,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3591,28 +3612,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3623,28 +3644,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3655,28 +3676,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>91</v>
+        <v>185</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3687,28 +3708,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3719,28 +3740,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>192</v>
+        <v>103</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3751,28 +3772,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>198</v>
+        <v>91</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3783,28 +3804,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3815,28 +3836,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3847,25 +3868,25 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>157</v>
+        <v>208</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>212</v>
+        <v>164</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>213</v>
@@ -3894,13 +3915,13 @@
         <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>207</v>
+        <v>150</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3911,28 +3932,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3986,7 +4007,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4036,19 +4057,19 @@
         <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>108</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>98</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -4062,13 +4083,13 @@
         <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
@@ -4080,7 +4101,7 @@
         <v>98</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -4094,13 +4115,13 @@
         <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
@@ -4112,7 +4133,7 @@
         <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -4126,25 +4147,25 @@
         <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -4158,13 +4179,13 @@
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>90</v>
@@ -4176,7 +4197,7 @@
         <v>104</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -4190,13 +4211,13 @@
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
@@ -4205,10 +4226,10 @@
         <v>91</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -4222,13 +4243,13 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
@@ -4237,10 +4258,10 @@
         <v>91</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -4251,28 +4272,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -4283,16 +4304,16 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
@@ -4301,10 +4322,10 @@
         <v>91</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -4315,28 +4336,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="I11" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -4347,28 +4368,28 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -4379,28 +4400,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -4411,28 +4432,28 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>91</v>
+        <v>191</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -4443,28 +4464,28 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -4475,28 +4496,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>198</v>
+        <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -4507,28 +4528,28 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -4539,28 +4560,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -4571,28 +4592,28 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -4603,16 +4624,16 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
@@ -4621,10 +4642,10 @@
         <v>109</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -4635,16 +4656,16 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
@@ -4653,10 +4674,10 @@
         <v>103</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -4667,16 +4688,16 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
@@ -4685,10 +4706,10 @@
         <v>103</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -4699,28 +4720,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="H23" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -4731,28 +4752,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -4763,16 +4784,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
@@ -4781,10 +4802,10 @@
         <v>91</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -4795,16 +4816,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
@@ -4813,10 +4834,10 @@
         <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -4827,28 +4848,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -4859,16 +4880,16 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
@@ -4877,10 +4898,10 @@
         <v>91</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -4894,25 +4915,25 @@
         <v>214</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -4965,7 +4986,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5009,22 +5030,22 @@
         <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>310</v>
+        <v>122</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>311</v>
@@ -5053,10 +5074,10 @@
         <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>310</v>
+        <v>98</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>314</v>
@@ -5117,7 +5138,7 @@
         <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>104</v>
@@ -5152,7 +5173,7 @@
         <v>109</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>323</v>
@@ -5213,10 +5234,10 @@
         <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>329</v>
@@ -5230,7 +5251,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>330</v>
@@ -5245,10 +5266,10 @@
         <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>332</v>
@@ -5262,7 +5283,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>333</v>
@@ -5280,7 +5301,7 @@
         <v>109</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>335</v>
@@ -5294,7 +5315,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>336</v>
@@ -5309,10 +5330,10 @@
         <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>338</v>
@@ -5326,7 +5347,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>339</v>
@@ -5341,10 +5362,10 @@
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>198</v>
+        <v>163</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>341</v>
@@ -5358,7 +5379,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>342</v>
@@ -5373,10 +5394,10 @@
         <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>198</v>
+        <v>97</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>344</v>
@@ -5390,7 +5411,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>345</v>
@@ -5405,10 +5426,10 @@
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>97</v>
+        <v>191</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>347</v>
@@ -5422,7 +5443,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>348</v>
@@ -5437,10 +5458,10 @@
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>350</v>
@@ -5454,7 +5475,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>351</v>
@@ -5486,7 +5507,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>354</v>
@@ -5501,10 +5522,10 @@
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>356</v>
@@ -5518,7 +5539,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>357</v>
@@ -5536,7 +5557,7 @@
         <v>91</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>359</v>
@@ -5550,7 +5571,7 @@
         <v>35</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>360</v>
@@ -5565,10 +5586,10 @@
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>362</v>
@@ -5582,28 +5603,28 @@
         <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>43</v>
+        <v>363</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>43</v>
+        <v>363</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>198</v>
+        <v>97</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>44</v>
@@ -5614,16 +5635,16 @@
         <v>35</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
@@ -5632,10 +5653,10 @@
         <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>44</v>
@@ -5646,25 +5667,25 @@
         <v>35</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>368</v>
+        <v>43</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>368</v>
+        <v>43</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>369</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>91</v>
+        <v>191</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>370</v>
@@ -5678,7 +5699,7 @@
         <v>35</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>371</v>
@@ -5696,7 +5717,7 @@
         <v>91</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>373</v>
@@ -5710,7 +5731,7 @@
         <v>35</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>374</v>
@@ -5728,7 +5749,7 @@
         <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>376</v>
@@ -5742,7 +5763,7 @@
         <v>35</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>377</v>
@@ -5757,10 +5778,10 @@
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>379</v>
@@ -5774,7 +5795,7 @@
         <v>35</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>380</v>
@@ -5792,7 +5813,7 @@
         <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>382</v>
@@ -5806,7 +5827,7 @@
         <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>383</v>
@@ -5821,10 +5842,10 @@
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>385</v>
@@ -5838,7 +5859,7 @@
         <v>35</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>386</v>
@@ -5856,7 +5877,7 @@
         <v>91</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>388</v>
@@ -5888,7 +5909,7 @@
         <v>103</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>391</v>
@@ -5902,7 +5923,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>392</v>
@@ -5917,10 +5938,10 @@
         <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>394</v>
@@ -5949,10 +5970,10 @@
         <v>90</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>398</v>
@@ -6001,6 +6022,1018 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J30"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6009,7 +7042,7 @@
     <col min="3" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6047,19 +7080,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>399</v>
+        <v>485</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>399</v>
+        <v>485</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>400</v>
+        <v>486</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
@@ -6071,7 +7104,7 @@
         <v>98</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>401</v>
+        <v>487</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>44</v>
@@ -6079,19 +7112,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>402</v>
+        <v>488</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>402</v>
+        <v>488</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>403</v>
+        <v>489</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
@@ -6103,7 +7136,7 @@
         <v>104</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>404</v>
+        <v>490</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>44</v>
@@ -6111,19 +7144,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>405</v>
+        <v>491</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>405</v>
+        <v>491</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>406</v>
+        <v>492</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
@@ -6132,10 +7165,10 @@
         <v>97</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>407</v>
+        <v>493</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>44</v>
@@ -6143,31 +7176,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>408</v>
+        <v>494</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>408</v>
+        <v>494</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>409</v>
+        <v>495</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>91</v>
+        <v>208</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>410</v>
+        <v>496</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>44</v>
@@ -6175,31 +7208,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>411</v>
+        <v>497</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>411</v>
+        <v>497</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>412</v>
+        <v>498</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>207</v>
+        <v>91</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>413</v>
+        <v>499</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>44</v>
@@ -6207,31 +7240,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>414</v>
+        <v>500</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>414</v>
+        <v>500</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>415</v>
+        <v>501</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>416</v>
+        <v>502</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>44</v>
@@ -6239,31 +7272,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>417</v>
+        <v>60</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>417</v>
+        <v>60</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>418</v>
+        <v>503</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>192</v>
+        <v>103</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>419</v>
+        <v>504</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>44</v>
@@ -6271,31 +7304,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>420</v>
+        <v>505</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>420</v>
+        <v>505</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>421</v>
+        <v>506</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>422</v>
+        <v>507</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>44</v>
@@ -6303,31 +7336,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>52</v>
+        <v>508</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>508</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>423</v>
+        <v>509</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>103</v>
+        <v>185</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>424</v>
+        <v>510</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>44</v>
@@ -6335,31 +7368,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>425</v>
+        <v>511</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>425</v>
+        <v>511</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>426</v>
+        <v>512</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>427</v>
+        <v>513</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>44</v>
@@ -6367,31 +7400,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>428</v>
+        <v>514</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>428</v>
+        <v>514</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>429</v>
+        <v>515</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>430</v>
+        <v>516</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>44</v>
@@ -6399,19 +7432,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>431</v>
+        <v>517</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>431</v>
+        <v>517</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>432</v>
+        <v>518</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
@@ -6420,10 +7453,10 @@
         <v>97</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>433</v>
+        <v>519</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>44</v>
@@ -6431,19 +7464,19 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>434</v>
+        <v>520</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>434</v>
+        <v>520</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>435</v>
+        <v>521</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
@@ -6452,10 +7485,10 @@
         <v>97</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>436</v>
+        <v>522</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>44</v>
@@ -6463,31 +7496,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>437</v>
+        <v>523</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>437</v>
+        <v>523</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>438</v>
+        <v>524</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>439</v>
+        <v>525</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>44</v>
@@ -6495,19 +7528,19 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>440</v>
+        <v>526</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>440</v>
+        <v>526</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>441</v>
+        <v>527</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
@@ -6516,10 +7549,10 @@
         <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>442</v>
+        <v>528</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>44</v>
@@ -6527,31 +7560,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>443</v>
+        <v>529</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>443</v>
+        <v>529</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>444</v>
+        <v>530</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>445</v>
+        <v>531</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>44</v>
@@ -6559,31 +7592,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>446</v>
+        <v>532</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>446</v>
+        <v>532</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>447</v>
+        <v>533</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>448</v>
+        <v>534</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>44</v>
@@ -6591,19 +7624,19 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>449</v>
+        <v>535</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>449</v>
+        <v>535</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>450</v>
+        <v>536</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
@@ -6612,10 +7645,10 @@
         <v>91</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>451</v>
+        <v>537</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>44</v>
@@ -6623,19 +7656,19 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>452</v>
+        <v>538</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>452</v>
+        <v>538</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>453</v>
+        <v>539</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
@@ -6644,10 +7677,10 @@
         <v>97</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>454</v>
+        <v>540</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>44</v>
@@ -6655,31 +7688,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>455</v>
+        <v>541</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>455</v>
+        <v>541</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>456</v>
+        <v>542</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>457</v>
+        <v>543</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>44</v>
@@ -6687,31 +7720,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>458</v>
+        <v>544</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>458</v>
+        <v>544</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>459</v>
+        <v>545</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>460</v>
+        <v>546</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>44</v>
@@ -6719,19 +7752,19 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>461</v>
+        <v>547</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>461</v>
+        <v>547</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>462</v>
+        <v>548</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
@@ -6740,10 +7773,10 @@
         <v>91</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>463</v>
+        <v>549</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>44</v>
@@ -6751,19 +7784,19 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>464</v>
+        <v>550</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>464</v>
+        <v>550</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>465</v>
+        <v>551</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
@@ -6772,10 +7805,10 @@
         <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>466</v>
+        <v>552</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>44</v>
@@ -6783,19 +7816,19 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>467</v>
+        <v>553</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>467</v>
+        <v>553</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>468</v>
+        <v>554</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
@@ -6804,10 +7837,10 @@
         <v>91</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>469</v>
+        <v>555</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>44</v>
@@ -6815,19 +7848,19 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>470</v>
+        <v>556</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>470</v>
+        <v>556</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>471</v>
+        <v>557</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
@@ -6836,10 +7869,10 @@
         <v>97</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>472</v>
+        <v>558</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>44</v>
@@ -6847,19 +7880,19 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>473</v>
+        <v>559</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>473</v>
+        <v>559</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>474</v>
+        <v>560</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
@@ -6868,10 +7901,10 @@
         <v>109</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>475</v>
+        <v>561</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>44</v>
@@ -6879,31 +7912,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>476</v>
+        <v>562</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>476</v>
+        <v>562</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>477</v>
+        <v>563</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>91</v>
+        <v>276</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>478</v>
+        <v>564</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>44</v>
@@ -6911,31 +7944,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>214</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>479</v>
+        <v>565</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>479</v>
+        <v>565</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>480</v>
+        <v>566</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>306</v>
+        <v>217</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>481</v>
+        <v>567</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>44</v>
@@ -6943,31 +7976,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>482</v>
+        <v>568</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>482</v>
+        <v>568</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>483</v>
+        <v>569</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>275</v>
+        <v>97</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>484</v>
+        <v>570</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>44</v>
@@ -6975,19 +8008,19 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>395</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>485</v>
+        <v>571</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>485</v>
+        <v>571</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>486</v>
+        <v>572</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>90</v>
@@ -6996,10 +8029,10 @@
         <v>91</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>487</v>
+        <v>573</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>44</v>
@@ -7043,985 +8076,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J29"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J30"/>
@@ -8077,13 +8131,13 @@
         <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
@@ -8092,10 +8146,10 @@
         <v>103</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>310</v>
+        <v>122</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>44</v>
@@ -8109,13 +8163,13 @@
         <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
@@ -8124,10 +8178,10 @@
         <v>103</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>310</v>
+        <v>122</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>44</v>
@@ -8141,25 +8195,25 @@
         <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>44</v>
@@ -8179,7 +8233,7 @@
         <v>68</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>108</v>
@@ -8191,7 +8245,7 @@
         <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>44</v>
@@ -8205,13 +8259,13 @@
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>583</v>
+        <v>5